--- a/vignettes/vignette-1/distribution_plot_data.xlsx
+++ b/vignettes/vignette-1/distribution_plot_data.xlsx
@@ -6826,7 +6826,7 @@
         <v>0</v>
       </c>
       <c r="C493" t="n">
-        <v>-0.771946</v>
+        <v>-0.534165</v>
       </c>
     </row>
     <row r="494">
@@ -6839,7 +6839,7 @@
         <v>1</v>
       </c>
       <c r="C494" t="n">
-        <v>-0.600761</v>
+        <v>-0.446897</v>
       </c>
     </row>
     <row r="495">
@@ -6852,7 +6852,7 @@
         <v>2</v>
       </c>
       <c r="C495" t="n">
-        <v>-0.319375</v>
+        <v>-0.326161</v>
       </c>
     </row>
     <row r="496">
@@ -6865,7 +6865,7 @@
         <v>3</v>
       </c>
       <c r="C496" t="n">
-        <v>-0.271172</v>
+        <v>-0.310604</v>
       </c>
     </row>
     <row r="497">
@@ -6878,7 +6878,7 @@
         <v>4</v>
       </c>
       <c r="C497" t="n">
-        <v>-0.241015</v>
+        <v>-0.306933</v>
       </c>
     </row>
     <row r="498">
@@ -6891,7 +6891,7 @@
         <v>5</v>
       </c>
       <c r="C498" t="n">
-        <v>-0.213281</v>
+        <v>-0.229764</v>
       </c>
     </row>
     <row r="499">
@@ -6904,7 +6904,7 @@
         <v>6</v>
       </c>
       <c r="C499" t="n">
-        <v>-0.201787</v>
+        <v>-0.213294</v>
       </c>
     </row>
     <row r="500">
@@ -6917,7 +6917,7 @@
         <v>7</v>
       </c>
       <c r="C500" t="n">
-        <v>-0.168004</v>
+        <v>-0.20509</v>
       </c>
     </row>
     <row r="501">
@@ -6930,7 +6930,7 @@
         <v>8</v>
       </c>
       <c r="C501" t="n">
-        <v>-0.132093</v>
+        <v>-0.156595</v>
       </c>
     </row>
     <row r="502">
@@ -6943,7 +6943,7 @@
         <v>9</v>
       </c>
       <c r="C502" t="n">
-        <v>-0.131858</v>
+        <v>-0.143285</v>
       </c>
     </row>
     <row r="503">
@@ -6956,7 +6956,7 @@
         <v>10</v>
       </c>
       <c r="C503" t="n">
-        <v>-0.119381</v>
+        <v>-0.142484</v>
       </c>
     </row>
     <row r="504">
@@ -6969,7 +6969,7 @@
         <v>11</v>
       </c>
       <c r="C504" t="n">
-        <v>-0.112048</v>
+        <v>-0.138366</v>
       </c>
     </row>
     <row r="505">
@@ -6982,7 +6982,7 @@
         <v>12</v>
       </c>
       <c r="C505" t="n">
-        <v>-0.108517</v>
+        <v>-0.126737</v>
       </c>
     </row>
     <row r="506">
@@ -6995,7 +6995,7 @@
         <v>13</v>
       </c>
       <c r="C506" t="n">
-        <v>-0.099177</v>
+        <v>-0.122493</v>
       </c>
     </row>
     <row r="507">
@@ -7008,7 +7008,7 @@
         <v>14</v>
       </c>
       <c r="C507" t="n">
-        <v>-0.098555</v>
+        <v>-0.120555</v>
       </c>
     </row>
     <row r="508">
@@ -7021,7 +7021,7 @@
         <v>15</v>
       </c>
       <c r="C508" t="n">
-        <v>-0.097384</v>
+        <v>-0.11929</v>
       </c>
     </row>
     <row r="509">
@@ -7034,7 +7034,7 @@
         <v>16</v>
       </c>
       <c r="C509" t="n">
-        <v>-0.097305</v>
+        <v>-0.111194</v>
       </c>
     </row>
     <row r="510">
@@ -7047,7 +7047,7 @@
         <v>17</v>
       </c>
       <c r="C510" t="n">
-        <v>-0.082326</v>
+        <v>-0.108562</v>
       </c>
     </row>
     <row r="511">
@@ -7060,7 +7060,7 @@
         <v>18</v>
       </c>
       <c r="C511" t="n">
-        <v>-0.082015</v>
+        <v>-0.107792</v>
       </c>
     </row>
     <row r="512">
@@ -7073,7 +7073,7 @@
         <v>19</v>
       </c>
       <c r="C512" t="n">
-        <v>-0.079433</v>
+        <v>-0.107176</v>
       </c>
     </row>
     <row r="513">
@@ -7086,7 +7086,7 @@
         <v>20</v>
       </c>
       <c r="C513" t="n">
-        <v>-0.078808</v>
+        <v>-0.106949</v>
       </c>
     </row>
     <row r="514">
@@ -7099,7 +7099,7 @@
         <v>21</v>
       </c>
       <c r="C514" t="n">
-        <v>-0.07510600000000001</v>
+        <v>-0.104958</v>
       </c>
     </row>
     <row r="515">
@@ -7112,7 +7112,7 @@
         <v>22</v>
       </c>
       <c r="C515" t="n">
-        <v>-0.07488499999999999</v>
+        <v>-0.098646</v>
       </c>
     </row>
     <row r="516">
@@ -7125,7 +7125,7 @@
         <v>23</v>
       </c>
       <c r="C516" t="n">
-        <v>-0.07427400000000001</v>
+        <v>-0.097469</v>
       </c>
     </row>
     <row r="517">
@@ -7138,7 +7138,7 @@
         <v>24</v>
       </c>
       <c r="C517" t="n">
-        <v>-0.072046</v>
+        <v>-0.097276</v>
       </c>
     </row>
     <row r="518">
@@ -7151,7 +7151,7 @@
         <v>25</v>
       </c>
       <c r="C518" t="n">
-        <v>-0.069452</v>
+        <v>-0.093706</v>
       </c>
     </row>
     <row r="519">
@@ -7164,7 +7164,7 @@
         <v>26</v>
       </c>
       <c r="C519" t="n">
-        <v>-0.06797300000000001</v>
+        <v>-0.092112</v>
       </c>
     </row>
     <row r="520">
@@ -7177,7 +7177,7 @@
         <v>27</v>
       </c>
       <c r="C520" t="n">
-        <v>-0.06744600000000001</v>
+        <v>-0.09056</v>
       </c>
     </row>
     <row r="521">
@@ -7190,7 +7190,7 @@
         <v>28</v>
       </c>
       <c r="C521" t="n">
-        <v>-0.06578000000000001</v>
+        <v>-0.089104</v>
       </c>
     </row>
     <row r="522">
@@ -7203,7 +7203,7 @@
         <v>29</v>
       </c>
       <c r="C522" t="n">
-        <v>-0.065638</v>
+        <v>-0.08684699999999999</v>
       </c>
     </row>
     <row r="523">
@@ -7216,7 +7216,7 @@
         <v>30</v>
       </c>
       <c r="C523" t="n">
-        <v>-0.062634</v>
+        <v>-0.086688</v>
       </c>
     </row>
     <row r="524">
@@ -7229,7 +7229,7 @@
         <v>31</v>
       </c>
       <c r="C524" t="n">
-        <v>-0.061105</v>
+        <v>-0.08667900000000001</v>
       </c>
     </row>
     <row r="525">
@@ -7242,7 +7242,7 @@
         <v>32</v>
       </c>
       <c r="C525" t="n">
-        <v>-0.059491</v>
+        <v>-0.08423700000000001</v>
       </c>
     </row>
     <row r="526">
@@ -7255,7 +7255,7 @@
         <v>33</v>
       </c>
       <c r="C526" t="n">
-        <v>-0.058445</v>
+        <v>-0.083871</v>
       </c>
     </row>
     <row r="527">
@@ -7268,7 +7268,7 @@
         <v>34</v>
       </c>
       <c r="C527" t="n">
-        <v>-0.05764</v>
+        <v>-0.083357</v>
       </c>
     </row>
     <row r="528">
@@ -7281,7 +7281,7 @@
         <v>35</v>
       </c>
       <c r="C528" t="n">
-        <v>-0.057234</v>
+        <v>-0.082457</v>
       </c>
     </row>
     <row r="529">
@@ -7294,7 +7294,7 @@
         <v>36</v>
       </c>
       <c r="C529" t="n">
-        <v>-0.056575</v>
+        <v>-0.08014499999999999</v>
       </c>
     </row>
     <row r="530">
@@ -7307,7 +7307,7 @@
         <v>37</v>
       </c>
       <c r="C530" t="n">
-        <v>-0.055637</v>
+        <v>-0.07894900000000001</v>
       </c>
     </row>
     <row r="531">
@@ -7320,7 +7320,7 @@
         <v>38</v>
       </c>
       <c r="C531" t="n">
-        <v>-0.054442</v>
+        <v>-0.07691000000000001</v>
       </c>
     </row>
     <row r="532">
@@ -7333,7 +7333,7 @@
         <v>39</v>
       </c>
       <c r="C532" t="n">
-        <v>-0.051116</v>
+        <v>-0.075859</v>
       </c>
     </row>
     <row r="533">
@@ -7346,7 +7346,7 @@
         <v>40</v>
       </c>
       <c r="C533" t="n">
-        <v>-0.050358</v>
+        <v>-0.073741</v>
       </c>
     </row>
     <row r="534">
@@ -7359,7 +7359,7 @@
         <v>41</v>
       </c>
       <c r="C534" t="n">
-        <v>-0.050088</v>
+        <v>-0.06974</v>
       </c>
     </row>
     <row r="535">
@@ -7372,7 +7372,7 @@
         <v>42</v>
       </c>
       <c r="C535" t="n">
-        <v>-0.049375</v>
+        <v>-0.069282</v>
       </c>
     </row>
     <row r="536">
@@ -7385,7 +7385,7 @@
         <v>43</v>
       </c>
       <c r="C536" t="n">
-        <v>-0.04913</v>
+        <v>-0.067916</v>
       </c>
     </row>
     <row r="537">
@@ -7398,7 +7398,7 @@
         <v>44</v>
       </c>
       <c r="C537" t="n">
-        <v>-0.049053</v>
+        <v>-0.06722</v>
       </c>
     </row>
     <row r="538">
@@ -7411,7 +7411,7 @@
         <v>45</v>
       </c>
       <c r="C538" t="n">
-        <v>-0.048756</v>
+        <v>-0.063911</v>
       </c>
     </row>
     <row r="539">
@@ -7424,7 +7424,7 @@
         <v>46</v>
       </c>
       <c r="C539" t="n">
-        <v>-0.048748</v>
+        <v>-0.06360499999999999</v>
       </c>
     </row>
     <row r="540">
@@ -7437,7 +7437,7 @@
         <v>47</v>
       </c>
       <c r="C540" t="n">
-        <v>-0.047252</v>
+        <v>-0.06335399999999999</v>
       </c>
     </row>
     <row r="541">
@@ -7450,7 +7450,7 @@
         <v>48</v>
       </c>
       <c r="C541" t="n">
-        <v>-0.047097</v>
+        <v>-0.063165</v>
       </c>
     </row>
     <row r="542">
@@ -7463,7 +7463,7 @@
         <v>49</v>
       </c>
       <c r="C542" t="n">
-        <v>-0.046883</v>
+        <v>-0.061894</v>
       </c>
     </row>
     <row r="543">
@@ -7476,7 +7476,7 @@
         <v>50</v>
       </c>
       <c r="C543" t="n">
-        <v>-0.046532</v>
+        <v>-0.061696</v>
       </c>
     </row>
     <row r="544">
@@ -7489,7 +7489,7 @@
         <v>51</v>
       </c>
       <c r="C544" t="n">
-        <v>-0.045631</v>
+        <v>-0.061654</v>
       </c>
     </row>
     <row r="545">
@@ -7502,7 +7502,7 @@
         <v>52</v>
       </c>
       <c r="C545" t="n">
-        <v>-0.045351</v>
+        <v>-0.061447</v>
       </c>
     </row>
     <row r="546">
@@ -7515,7 +7515,7 @@
         <v>53</v>
       </c>
       <c r="C546" t="n">
-        <v>-0.043432</v>
+        <v>-0.059194</v>
       </c>
     </row>
     <row r="547">
@@ -7528,7 +7528,7 @@
         <v>54</v>
       </c>
       <c r="C547" t="n">
-        <v>-0.043266</v>
+        <v>-0.058905</v>
       </c>
     </row>
     <row r="548">
@@ -7541,7 +7541,7 @@
         <v>55</v>
       </c>
       <c r="C548" t="n">
-        <v>-0.042284</v>
+        <v>-0.057409</v>
       </c>
     </row>
     <row r="549">
@@ -7554,7 +7554,7 @@
         <v>56</v>
       </c>
       <c r="C549" t="n">
-        <v>-0.042124</v>
+        <v>-0.056996</v>
       </c>
     </row>
     <row r="550">
@@ -7567,7 +7567,7 @@
         <v>57</v>
       </c>
       <c r="C550" t="n">
-        <v>-0.042098</v>
+        <v>-0.056136</v>
       </c>
     </row>
     <row r="551">
@@ -7580,7 +7580,7 @@
         <v>58</v>
       </c>
       <c r="C551" t="n">
-        <v>-0.040001</v>
+        <v>-0.056062</v>
       </c>
     </row>
     <row r="552">
@@ -7593,7 +7593,7 @@
         <v>59</v>
       </c>
       <c r="C552" t="n">
-        <v>-0.039282</v>
+        <v>-0.055624</v>
       </c>
     </row>
     <row r="553">
@@ -7606,7 +7606,7 @@
         <v>60</v>
       </c>
       <c r="C553" t="n">
-        <v>-0.038971</v>
+        <v>-0.054812</v>
       </c>
     </row>
     <row r="554">
@@ -7619,7 +7619,7 @@
         <v>61</v>
       </c>
       <c r="C554" t="n">
-        <v>-0.038658</v>
+        <v>-0.054327</v>
       </c>
     </row>
     <row r="555">
@@ -7632,7 +7632,7 @@
         <v>62</v>
       </c>
       <c r="C555" t="n">
-        <v>-0.03823</v>
+        <v>-0.05353</v>
       </c>
     </row>
     <row r="556">
@@ -7645,7 +7645,7 @@
         <v>63</v>
       </c>
       <c r="C556" t="n">
-        <v>-0.037679</v>
+        <v>-0.052796</v>
       </c>
     </row>
     <row r="557">
@@ -7658,7 +7658,7 @@
         <v>64</v>
       </c>
       <c r="C557" t="n">
-        <v>-0.036938</v>
+        <v>-0.051861</v>
       </c>
     </row>
     <row r="558">
@@ -7671,7 +7671,7 @@
         <v>65</v>
       </c>
       <c r="C558" t="n">
-        <v>-0.036458</v>
+        <v>-0.051328</v>
       </c>
     </row>
     <row r="559">
@@ -7684,7 +7684,7 @@
         <v>66</v>
       </c>
       <c r="C559" t="n">
-        <v>-0.036282</v>
+        <v>-0.050257</v>
       </c>
     </row>
     <row r="560">
@@ -7697,7 +7697,7 @@
         <v>67</v>
       </c>
       <c r="C560" t="n">
-        <v>-0.035989</v>
+        <v>-0.050132</v>
       </c>
     </row>
     <row r="561">
@@ -7710,7 +7710,7 @@
         <v>68</v>
       </c>
       <c r="C561" t="n">
-        <v>-0.035709</v>
+        <v>-0.049842</v>
       </c>
     </row>
     <row r="562">
@@ -7723,7 +7723,7 @@
         <v>69</v>
       </c>
       <c r="C562" t="n">
-        <v>-0.035505</v>
+        <v>-0.049004</v>
       </c>
     </row>
     <row r="563">
@@ -7736,7 +7736,7 @@
         <v>70</v>
       </c>
       <c r="C563" t="n">
-        <v>-0.035083</v>
+        <v>-0.048987</v>
       </c>
     </row>
     <row r="564">
@@ -7749,7 +7749,7 @@
         <v>71</v>
       </c>
       <c r="C564" t="n">
-        <v>-0.035032</v>
+        <v>-0.048846</v>
       </c>
     </row>
     <row r="565">
@@ -7762,7 +7762,7 @@
         <v>72</v>
       </c>
       <c r="C565" t="n">
-        <v>-0.034649</v>
+        <v>-0.048838</v>
       </c>
     </row>
     <row r="566">
@@ -7775,7 +7775,7 @@
         <v>73</v>
       </c>
       <c r="C566" t="n">
-        <v>-0.034091</v>
+        <v>-0.048174</v>
       </c>
     </row>
     <row r="567">
@@ -7788,7 +7788,7 @@
         <v>74</v>
       </c>
       <c r="C567" t="n">
-        <v>-0.033765</v>
+        <v>-0.047821</v>
       </c>
     </row>
     <row r="568">
@@ -7801,7 +7801,7 @@
         <v>75</v>
       </c>
       <c r="C568" t="n">
-        <v>-0.032518</v>
+        <v>-0.047365</v>
       </c>
     </row>
     <row r="569">
@@ -7814,7 +7814,7 @@
         <v>76</v>
       </c>
       <c r="C569" t="n">
-        <v>-0.032128</v>
+        <v>-0.047215</v>
       </c>
     </row>
     <row r="570">
@@ -7827,7 +7827,7 @@
         <v>77</v>
       </c>
       <c r="C570" t="n">
-        <v>-0.031617</v>
+        <v>-0.046157</v>
       </c>
     </row>
     <row r="571">
@@ -7840,7 +7840,7 @@
         <v>78</v>
       </c>
       <c r="C571" t="n">
-        <v>-0.030936</v>
+        <v>-0.045846</v>
       </c>
     </row>
     <row r="572">
@@ -7853,7 +7853,7 @@
         <v>79</v>
       </c>
       <c r="C572" t="n">
-        <v>-0.030761</v>
+        <v>-0.04581</v>
       </c>
     </row>
     <row r="573">
@@ -7866,7 +7866,7 @@
         <v>80</v>
       </c>
       <c r="C573" t="n">
-        <v>-0.030677</v>
+        <v>-0.045172</v>
       </c>
     </row>
     <row r="574">
@@ -7879,7 +7879,7 @@
         <v>81</v>
       </c>
       <c r="C574" t="n">
-        <v>-0.029086</v>
+        <v>-0.045117</v>
       </c>
     </row>
     <row r="575">
@@ -7892,7 +7892,7 @@
         <v>82</v>
       </c>
       <c r="C575" t="n">
-        <v>-0.028909</v>
+        <v>-0.044878</v>
       </c>
     </row>
     <row r="576">
@@ -7905,7 +7905,7 @@
         <v>83</v>
       </c>
       <c r="C576" t="n">
-        <v>-0.028561</v>
+        <v>-0.044291</v>
       </c>
     </row>
     <row r="577">
@@ -7918,7 +7918,7 @@
         <v>84</v>
       </c>
       <c r="C577" t="n">
-        <v>-0.028528</v>
+        <v>-0.044232</v>
       </c>
     </row>
     <row r="578">
@@ -7931,7 +7931,7 @@
         <v>85</v>
       </c>
       <c r="C578" t="n">
-        <v>-0.028461</v>
+        <v>-0.043954</v>
       </c>
     </row>
     <row r="579">
@@ -7944,7 +7944,7 @@
         <v>86</v>
       </c>
       <c r="C579" t="n">
-        <v>-0.028294</v>
+        <v>-0.043736</v>
       </c>
     </row>
     <row r="580">
@@ -7957,7 +7957,7 @@
         <v>87</v>
       </c>
       <c r="C580" t="n">
-        <v>-0.028291</v>
+        <v>-0.042317</v>
       </c>
     </row>
     <row r="581">
@@ -7970,7 +7970,7 @@
         <v>88</v>
       </c>
       <c r="C581" t="n">
-        <v>-0.028258</v>
+        <v>-0.041798</v>
       </c>
     </row>
     <row r="582">
@@ -7983,7 +7983,7 @@
         <v>89</v>
       </c>
       <c r="C582" t="n">
-        <v>-0.027685</v>
+        <v>-0.041377</v>
       </c>
     </row>
     <row r="583">
@@ -7996,7 +7996,7 @@
         <v>90</v>
       </c>
       <c r="C583" t="n">
-        <v>-0.027566</v>
+        <v>-0.041125</v>
       </c>
     </row>
     <row r="584">
@@ -8009,7 +8009,7 @@
         <v>91</v>
       </c>
       <c r="C584" t="n">
-        <v>-0.026975</v>
+        <v>-0.040427</v>
       </c>
     </row>
     <row r="585">
@@ -8022,7 +8022,7 @@
         <v>92</v>
       </c>
       <c r="C585" t="n">
-        <v>-0.026296</v>
+        <v>-0.04033</v>
       </c>
     </row>
     <row r="586">
@@ -8035,7 +8035,7 @@
         <v>93</v>
       </c>
       <c r="C586" t="n">
-        <v>-0.026102</v>
+        <v>-0.039994</v>
       </c>
     </row>
     <row r="587">
@@ -8048,7 +8048,7 @@
         <v>94</v>
       </c>
       <c r="C587" t="n">
-        <v>-0.025803</v>
+        <v>-0.039937</v>
       </c>
     </row>
     <row r="588">
@@ -8061,7 +8061,7 @@
         <v>95</v>
       </c>
       <c r="C588" t="n">
-        <v>-0.025551</v>
+        <v>-0.039555</v>
       </c>
     </row>
     <row r="589">
@@ -8074,7 +8074,7 @@
         <v>96</v>
       </c>
       <c r="C589" t="n">
-        <v>-0.025224</v>
+        <v>-0.03869</v>
       </c>
     </row>
     <row r="590">
@@ -8087,7 +8087,7 @@
         <v>97</v>
       </c>
       <c r="C590" t="n">
-        <v>-0.024828</v>
+        <v>-0.036622</v>
       </c>
     </row>
     <row r="591">
@@ -8100,7 +8100,7 @@
         <v>98</v>
       </c>
       <c r="C591" t="n">
-        <v>-0.024638</v>
+        <v>-0.036282</v>
       </c>
     </row>
     <row r="592">
@@ -8113,7 +8113,7 @@
         <v>99</v>
       </c>
       <c r="C592" t="n">
-        <v>-0.024458</v>
+        <v>-0.036035</v>
       </c>
     </row>
     <row r="593">
@@ -8126,7 +8126,7 @@
         <v>100</v>
       </c>
       <c r="C593" t="n">
-        <v>-0.024312</v>
+        <v>-0.0359</v>
       </c>
     </row>
     <row r="594">
@@ -8139,7 +8139,7 @@
         <v>101</v>
       </c>
       <c r="C594" t="n">
-        <v>-0.023992</v>
+        <v>-0.03455</v>
       </c>
     </row>
     <row r="595">
@@ -8152,7 +8152,7 @@
         <v>102</v>
       </c>
       <c r="C595" t="n">
-        <v>-0.023851</v>
+        <v>-0.033393</v>
       </c>
     </row>
     <row r="596">
@@ -8165,7 +8165,7 @@
         <v>103</v>
       </c>
       <c r="C596" t="n">
-        <v>-0.023337</v>
+        <v>-0.032628</v>
       </c>
     </row>
     <row r="597">
@@ -8178,7 +8178,7 @@
         <v>104</v>
       </c>
       <c r="C597" t="n">
-        <v>-0.023214</v>
+        <v>-0.031921</v>
       </c>
     </row>
     <row r="598">
@@ -8191,7 +8191,7 @@
         <v>105</v>
       </c>
       <c r="C598" t="n">
-        <v>-0.023157</v>
+        <v>-0.031772</v>
       </c>
     </row>
     <row r="599">
@@ -8204,7 +8204,7 @@
         <v>106</v>
       </c>
       <c r="C599" t="n">
-        <v>-0.02314</v>
+        <v>-0.031752</v>
       </c>
     </row>
     <row r="600">
@@ -8217,7 +8217,7 @@
         <v>107</v>
       </c>
       <c r="C600" t="n">
-        <v>-0.023107</v>
+        <v>-0.031582</v>
       </c>
     </row>
     <row r="601">
@@ -8230,7 +8230,7 @@
         <v>108</v>
       </c>
       <c r="C601" t="n">
-        <v>-0.023066</v>
+        <v>-0.031571</v>
       </c>
     </row>
     <row r="602">
@@ -8243,7 +8243,7 @@
         <v>109</v>
       </c>
       <c r="C602" t="n">
-        <v>-0.022995</v>
+        <v>-0.031398</v>
       </c>
     </row>
     <row r="603">
@@ -8256,7 +8256,7 @@
         <v>110</v>
       </c>
       <c r="C603" t="n">
-        <v>-0.022471</v>
+        <v>-0.030547</v>
       </c>
     </row>
     <row r="604">
@@ -8269,7 +8269,7 @@
         <v>111</v>
       </c>
       <c r="C604" t="n">
-        <v>-0.022254</v>
+        <v>-0.029823</v>
       </c>
     </row>
     <row r="605">
@@ -8282,7 +8282,7 @@
         <v>112</v>
       </c>
       <c r="C605" t="n">
-        <v>-0.02222</v>
+        <v>-0.029675</v>
       </c>
     </row>
     <row r="606">
@@ -8295,7 +8295,7 @@
         <v>113</v>
       </c>
       <c r="C606" t="n">
-        <v>-0.021984</v>
+        <v>-0.029151</v>
       </c>
     </row>
     <row r="607">
@@ -8308,7 +8308,7 @@
         <v>114</v>
       </c>
       <c r="C607" t="n">
-        <v>-0.021375</v>
+        <v>-0.028718</v>
       </c>
     </row>
     <row r="608">
@@ -8321,7 +8321,7 @@
         <v>115</v>
       </c>
       <c r="C608" t="n">
-        <v>-0.021067</v>
+        <v>-0.027984</v>
       </c>
     </row>
     <row r="609">
@@ -8334,7 +8334,7 @@
         <v>116</v>
       </c>
       <c r="C609" t="n">
-        <v>-0.020692</v>
+        <v>-0.027582</v>
       </c>
     </row>
     <row r="610">
@@ -8347,7 +8347,7 @@
         <v>117</v>
       </c>
       <c r="C610" t="n">
-        <v>-0.019596</v>
+        <v>-0.027536</v>
       </c>
     </row>
     <row r="611">
@@ -8360,7 +8360,7 @@
         <v>118</v>
       </c>
       <c r="C611" t="n">
-        <v>-0.019426</v>
+        <v>-0.027328</v>
       </c>
     </row>
     <row r="612">
@@ -8373,7 +8373,7 @@
         <v>119</v>
       </c>
       <c r="C612" t="n">
-        <v>-0.019128</v>
+        <v>-0.026797</v>
       </c>
     </row>
     <row r="613">
@@ -8386,7 +8386,7 @@
         <v>120</v>
       </c>
       <c r="C613" t="n">
-        <v>-0.018997</v>
+        <v>-0.026481</v>
       </c>
     </row>
     <row r="614">
@@ -8399,7 +8399,7 @@
         <v>121</v>
       </c>
       <c r="C614" t="n">
-        <v>-0.01886</v>
+        <v>-0.026272</v>
       </c>
     </row>
     <row r="615">
@@ -8412,7 +8412,7 @@
         <v>122</v>
       </c>
       <c r="C615" t="n">
-        <v>-0.018456</v>
+        <v>-0.026051</v>
       </c>
     </row>
     <row r="616">
@@ -8425,7 +8425,7 @@
         <v>123</v>
       </c>
       <c r="C616" t="n">
-        <v>-0.018322</v>
+        <v>-0.025523</v>
       </c>
     </row>
     <row r="617">
@@ -8438,7 +8438,7 @@
         <v>124</v>
       </c>
       <c r="C617" t="n">
-        <v>-0.018259</v>
+        <v>-0.025289</v>
       </c>
     </row>
     <row r="618">
@@ -8451,7 +8451,7 @@
         <v>125</v>
       </c>
       <c r="C618" t="n">
-        <v>-0.018173</v>
+        <v>-0.025125</v>
       </c>
     </row>
     <row r="619">
@@ -8464,7 +8464,7 @@
         <v>126</v>
       </c>
       <c r="C619" t="n">
-        <v>-0.017289</v>
+        <v>-0.024855</v>
       </c>
     </row>
     <row r="620">
@@ -8477,7 +8477,7 @@
         <v>127</v>
       </c>
       <c r="C620" t="n">
-        <v>-0.017221</v>
+        <v>-0.024609</v>
       </c>
     </row>
     <row r="621">
@@ -8490,7 +8490,7 @@
         <v>128</v>
       </c>
       <c r="C621" t="n">
-        <v>-0.01711</v>
+        <v>-0.024284</v>
       </c>
     </row>
     <row r="622">
@@ -8503,7 +8503,7 @@
         <v>129</v>
       </c>
       <c r="C622" t="n">
-        <v>-0.016919</v>
+        <v>-0.024125</v>
       </c>
     </row>
     <row r="623">
@@ -8516,7 +8516,7 @@
         <v>130</v>
       </c>
       <c r="C623" t="n">
-        <v>-0.016801</v>
+        <v>-0.023667</v>
       </c>
     </row>
     <row r="624">
@@ -8529,7 +8529,7 @@
         <v>131</v>
       </c>
       <c r="C624" t="n">
-        <v>-0.01669</v>
+        <v>-0.021869</v>
       </c>
     </row>
     <row r="625">
@@ -8542,7 +8542,7 @@
         <v>132</v>
       </c>
       <c r="C625" t="n">
-        <v>-0.016093</v>
+        <v>-0.021184</v>
       </c>
     </row>
     <row r="626">
@@ -8555,7 +8555,7 @@
         <v>133</v>
       </c>
       <c r="C626" t="n">
-        <v>-0.015902</v>
+        <v>-0.020783</v>
       </c>
     </row>
     <row r="627">
@@ -8568,7 +8568,7 @@
         <v>134</v>
       </c>
       <c r="C627" t="n">
-        <v>-0.015871</v>
+        <v>-0.019626</v>
       </c>
     </row>
     <row r="628">
@@ -8581,7 +8581,7 @@
         <v>135</v>
       </c>
       <c r="C628" t="n">
-        <v>-0.015612</v>
+        <v>-0.01955</v>
       </c>
     </row>
     <row r="629">
@@ -8594,7 +8594,7 @@
         <v>136</v>
       </c>
       <c r="C629" t="n">
-        <v>-0.015168</v>
+        <v>-0.018852</v>
       </c>
     </row>
     <row r="630">
@@ -8607,7 +8607,7 @@
         <v>137</v>
       </c>
       <c r="C630" t="n">
-        <v>-0.014841</v>
+        <v>-0.018837</v>
       </c>
     </row>
     <row r="631">
@@ -8620,7 +8620,7 @@
         <v>138</v>
       </c>
       <c r="C631" t="n">
-        <v>-0.014431</v>
+        <v>-0.018752</v>
       </c>
     </row>
     <row r="632">
@@ -8633,7 +8633,7 @@
         <v>139</v>
       </c>
       <c r="C632" t="n">
-        <v>-0.014381</v>
+        <v>-0.018617</v>
       </c>
     </row>
     <row r="633">
@@ -8646,7 +8646,7 @@
         <v>140</v>
       </c>
       <c r="C633" t="n">
-        <v>-0.014369</v>
+        <v>-0.018149</v>
       </c>
     </row>
     <row r="634">
@@ -8659,7 +8659,7 @@
         <v>141</v>
       </c>
       <c r="C634" t="n">
-        <v>-0.014342</v>
+        <v>-0.018045</v>
       </c>
     </row>
     <row r="635">
@@ -8672,7 +8672,7 @@
         <v>142</v>
       </c>
       <c r="C635" t="n">
-        <v>-0.014104</v>
+        <v>-0.017869</v>
       </c>
     </row>
     <row r="636">
@@ -8685,7 +8685,7 @@
         <v>143</v>
       </c>
       <c r="C636" t="n">
-        <v>-0.014058</v>
+        <v>-0.017819</v>
       </c>
     </row>
     <row r="637">
@@ -8698,7 +8698,7 @@
         <v>144</v>
       </c>
       <c r="C637" t="n">
-        <v>-0.0138</v>
+        <v>-0.017813</v>
       </c>
     </row>
     <row r="638">
@@ -8711,7 +8711,7 @@
         <v>145</v>
       </c>
       <c r="C638" t="n">
-        <v>-0.013454</v>
+        <v>-0.01752</v>
       </c>
     </row>
     <row r="639">
@@ -8724,7 +8724,7 @@
         <v>146</v>
       </c>
       <c r="C639" t="n">
-        <v>-0.013404</v>
+        <v>-0.017335</v>
       </c>
     </row>
     <row r="640">
@@ -8737,7 +8737,7 @@
         <v>147</v>
       </c>
       <c r="C640" t="n">
-        <v>-0.012204</v>
+        <v>-0.017258</v>
       </c>
     </row>
     <row r="641">
@@ -8750,7 +8750,7 @@
         <v>148</v>
       </c>
       <c r="C641" t="n">
-        <v>-0.011888</v>
+        <v>-0.0172</v>
       </c>
     </row>
     <row r="642">
@@ -8763,7 +8763,7 @@
         <v>149</v>
       </c>
       <c r="C642" t="n">
-        <v>-0.01169</v>
+        <v>-0.017153</v>
       </c>
     </row>
     <row r="643">
@@ -8776,7 +8776,7 @@
         <v>150</v>
       </c>
       <c r="C643" t="n">
-        <v>-0.011665</v>
+        <v>-0.017095</v>
       </c>
     </row>
     <row r="644">
@@ -8789,7 +8789,7 @@
         <v>151</v>
       </c>
       <c r="C644" t="n">
-        <v>-0.011236</v>
+        <v>-0.016985</v>
       </c>
     </row>
     <row r="645">
@@ -8802,7 +8802,7 @@
         <v>152</v>
       </c>
       <c r="C645" t="n">
-        <v>-0.01119</v>
+        <v>-0.0168</v>
       </c>
     </row>
     <row r="646">
@@ -8815,7 +8815,7 @@
         <v>153</v>
       </c>
       <c r="C646" t="n">
-        <v>-0.010937</v>
+        <v>-0.016462</v>
       </c>
     </row>
     <row r="647">
@@ -8828,7 +8828,7 @@
         <v>154</v>
       </c>
       <c r="C647" t="n">
-        <v>-0.010799</v>
+        <v>-0.015224</v>
       </c>
     </row>
     <row r="648">
@@ -8841,7 +8841,7 @@
         <v>155</v>
       </c>
       <c r="C648" t="n">
-        <v>-0.01045</v>
+        <v>-0.015033</v>
       </c>
     </row>
     <row r="649">
@@ -8854,7 +8854,7 @@
         <v>156</v>
       </c>
       <c r="C649" t="n">
-        <v>-0.010431</v>
+        <v>-0.014899</v>
       </c>
     </row>
     <row r="650">
@@ -8867,7 +8867,7 @@
         <v>157</v>
       </c>
       <c r="C650" t="n">
-        <v>-0.010387</v>
+        <v>-0.014776</v>
       </c>
     </row>
     <row r="651">
@@ -8880,7 +8880,7 @@
         <v>158</v>
       </c>
       <c r="C651" t="n">
-        <v>-0.01025</v>
+        <v>-0.014707</v>
       </c>
     </row>
     <row r="652">
@@ -8893,7 +8893,7 @@
         <v>159</v>
       </c>
       <c r="C652" t="n">
-        <v>-0.010087</v>
+        <v>-0.014293</v>
       </c>
     </row>
     <row r="653">
@@ -8906,7 +8906,7 @@
         <v>160</v>
       </c>
       <c r="C653" t="n">
-        <v>-0.009915999999999999</v>
+        <v>-0.013769</v>
       </c>
     </row>
     <row r="654">
@@ -8919,7 +8919,7 @@
         <v>161</v>
       </c>
       <c r="C654" t="n">
-        <v>-0.009749000000000001</v>
+        <v>-0.013248</v>
       </c>
     </row>
     <row r="655">
@@ -8932,7 +8932,7 @@
         <v>162</v>
       </c>
       <c r="C655" t="n">
-        <v>-0.009728000000000001</v>
+        <v>-0.01266</v>
       </c>
     </row>
     <row r="656">
@@ -8945,7 +8945,7 @@
         <v>163</v>
       </c>
       <c r="C656" t="n">
-        <v>-0.009286000000000001</v>
+        <v>-0.012644</v>
       </c>
     </row>
     <row r="657">
@@ -8958,7 +8958,7 @@
         <v>164</v>
       </c>
       <c r="C657" t="n">
-        <v>-0.00923</v>
+        <v>-0.012399</v>
       </c>
     </row>
     <row r="658">
@@ -8971,7 +8971,7 @@
         <v>165</v>
       </c>
       <c r="C658" t="n">
-        <v>-0.009209</v>
+        <v>-0.012349</v>
       </c>
     </row>
     <row r="659">
@@ -8984,7 +8984,7 @@
         <v>166</v>
       </c>
       <c r="C659" t="n">
-        <v>-0.008956</v>
+        <v>-0.012133</v>
       </c>
     </row>
     <row r="660">
@@ -8997,7 +8997,7 @@
         <v>167</v>
       </c>
       <c r="C660" t="n">
-        <v>-0.008626999999999999</v>
+        <v>-0.011245</v>
       </c>
     </row>
     <row r="661">
@@ -9010,7 +9010,7 @@
         <v>168</v>
       </c>
       <c r="C661" t="n">
-        <v>-0.008614999999999999</v>
+        <v>-0.010489</v>
       </c>
     </row>
     <row r="662">
@@ -9023,7 +9023,7 @@
         <v>169</v>
       </c>
       <c r="C662" t="n">
-        <v>-0.008518</v>
+        <v>-0.010218</v>
       </c>
     </row>
     <row r="663">
@@ -9036,7 +9036,7 @@
         <v>170</v>
       </c>
       <c r="C663" t="n">
-        <v>-0.008434000000000001</v>
+        <v>-0.009712999999999999</v>
       </c>
     </row>
     <row r="664">
@@ -9049,7 +9049,7 @@
         <v>171</v>
       </c>
       <c r="C664" t="n">
-        <v>-0.00801</v>
+        <v>-0.009584000000000001</v>
       </c>
     </row>
     <row r="665">
@@ -9062,7 +9062,7 @@
         <v>172</v>
       </c>
       <c r="C665" t="n">
-        <v>-0.007901</v>
+        <v>-0.00945</v>
       </c>
     </row>
     <row r="666">
@@ -9075,7 +9075,7 @@
         <v>173</v>
       </c>
       <c r="C666" t="n">
-        <v>-0.007593</v>
+        <v>-0.008638</v>
       </c>
     </row>
     <row r="667">
@@ -9088,7 +9088,7 @@
         <v>174</v>
       </c>
       <c r="C667" t="n">
-        <v>-0.00755</v>
+        <v>-0.008619</v>
       </c>
     </row>
     <row r="668">
@@ -9101,7 +9101,7 @@
         <v>175</v>
       </c>
       <c r="C668" t="n">
-        <v>-0.006976</v>
+        <v>-0.008172</v>
       </c>
     </row>
     <row r="669">
@@ -9114,7 +9114,7 @@
         <v>176</v>
       </c>
       <c r="C669" t="n">
-        <v>-0.006848</v>
+        <v>-0.008149999999999999</v>
       </c>
     </row>
     <row r="670">
@@ -9127,7 +9127,7 @@
         <v>177</v>
       </c>
       <c r="C670" t="n">
-        <v>-0.006755</v>
+        <v>-0.008128</v>
       </c>
     </row>
     <row r="671">
@@ -9140,7 +9140,7 @@
         <v>178</v>
       </c>
       <c r="C671" t="n">
-        <v>-0.006236</v>
+        <v>-0.007786</v>
       </c>
     </row>
     <row r="672">
@@ -9153,7 +9153,7 @@
         <v>179</v>
       </c>
       <c r="C672" t="n">
-        <v>-0.006213</v>
+        <v>-0.0074</v>
       </c>
     </row>
     <row r="673">
@@ -9166,7 +9166,7 @@
         <v>180</v>
       </c>
       <c r="C673" t="n">
-        <v>-0.006095</v>
+        <v>-0.007278</v>
       </c>
     </row>
     <row r="674">
@@ -9179,7 +9179,7 @@
         <v>181</v>
       </c>
       <c r="C674" t="n">
-        <v>-0.006056</v>
+        <v>-0.007169</v>
       </c>
     </row>
     <row r="675">
@@ -9192,7 +9192,7 @@
         <v>182</v>
       </c>
       <c r="C675" t="n">
-        <v>-0.006019</v>
+        <v>-0.006785</v>
       </c>
     </row>
     <row r="676">
@@ -9205,7 +9205,7 @@
         <v>183</v>
       </c>
       <c r="C676" t="n">
-        <v>-0.005999</v>
+        <v>-0.006597</v>
       </c>
     </row>
     <row r="677">
@@ -9218,7 +9218,7 @@
         <v>184</v>
       </c>
       <c r="C677" t="n">
-        <v>-0.005926</v>
+        <v>-0.006066</v>
       </c>
     </row>
     <row r="678">
@@ -9231,7 +9231,7 @@
         <v>185</v>
       </c>
       <c r="C678" t="n">
-        <v>-0.005662</v>
+        <v>-0.006058</v>
       </c>
     </row>
     <row r="679">
@@ -9244,7 +9244,7 @@
         <v>186</v>
       </c>
       <c r="C679" t="n">
-        <v>-0.005492</v>
+        <v>-0.00563</v>
       </c>
     </row>
     <row r="680">
@@ -9257,7 +9257,7 @@
         <v>187</v>
       </c>
       <c r="C680" t="n">
-        <v>-0.005204</v>
+        <v>-0.005026</v>
       </c>
     </row>
     <row r="681">
@@ -9270,7 +9270,7 @@
         <v>188</v>
       </c>
       <c r="C681" t="n">
-        <v>-0.005147</v>
+        <v>-0.004732</v>
       </c>
     </row>
     <row r="682">
@@ -9283,7 +9283,7 @@
         <v>189</v>
       </c>
       <c r="C682" t="n">
-        <v>-0.005046</v>
+        <v>-0.00454</v>
       </c>
     </row>
     <row r="683">
@@ -9296,7 +9296,7 @@
         <v>190</v>
       </c>
       <c r="C683" t="n">
-        <v>-0.00502</v>
+        <v>-0.004454</v>
       </c>
     </row>
     <row r="684">
@@ -9309,7 +9309,7 @@
         <v>191</v>
       </c>
       <c r="C684" t="n">
-        <v>-0.004753</v>
+        <v>-0.004092</v>
       </c>
     </row>
     <row r="685">
@@ -9322,7 +9322,7 @@
         <v>192</v>
       </c>
       <c r="C685" t="n">
-        <v>-0.004427</v>
+        <v>-0.00346</v>
       </c>
     </row>
     <row r="686">
@@ -9335,7 +9335,7 @@
         <v>193</v>
       </c>
       <c r="C686" t="n">
-        <v>-0.004411</v>
+        <v>-0.003105</v>
       </c>
     </row>
     <row r="687">
@@ -9348,7 +9348,7 @@
         <v>194</v>
       </c>
       <c r="C687" t="n">
-        <v>-0.003833</v>
+        <v>-0.003088</v>
       </c>
     </row>
     <row r="688">
@@ -9361,7 +9361,7 @@
         <v>195</v>
       </c>
       <c r="C688" t="n">
-        <v>-0.003831</v>
+        <v>-0.002812</v>
       </c>
     </row>
     <row r="689">
@@ -9374,7 +9374,7 @@
         <v>196</v>
       </c>
       <c r="C689" t="n">
-        <v>-0.003707</v>
+        <v>-0.002758</v>
       </c>
     </row>
     <row r="690">
@@ -9387,7 +9387,7 @@
         <v>197</v>
       </c>
       <c r="C690" t="n">
-        <v>-0.003524</v>
+        <v>-0.002194</v>
       </c>
     </row>
     <row r="691">
@@ -9400,7 +9400,7 @@
         <v>198</v>
       </c>
       <c r="C691" t="n">
-        <v>-0.003476</v>
+        <v>-0.001629</v>
       </c>
     </row>
     <row r="692">
@@ -9413,7 +9413,7 @@
         <v>199</v>
       </c>
       <c r="C692" t="n">
-        <v>-0.003144</v>
+        <v>-0.001496</v>
       </c>
     </row>
     <row r="693">
@@ -9426,7 +9426,7 @@
         <v>200</v>
       </c>
       <c r="C693" t="n">
-        <v>-0.003005</v>
+        <v>-0.001068</v>
       </c>
     </row>
     <row r="694">
@@ -9439,7 +9439,7 @@
         <v>201</v>
       </c>
       <c r="C694" t="n">
-        <v>-0.00297</v>
+        <v>-0.000967</v>
       </c>
     </row>
     <row r="695">
@@ -9452,7 +9452,7 @@
         <v>202</v>
       </c>
       <c r="C695" t="n">
-        <v>-0.002958</v>
+        <v>-0.000846</v>
       </c>
     </row>
     <row r="696">
@@ -9465,7 +9465,7 @@
         <v>203</v>
       </c>
       <c r="C696" t="n">
-        <v>-0.002929</v>
+        <v>-0.000619</v>
       </c>
     </row>
     <row r="697">
@@ -9478,7 +9478,7 @@
         <v>204</v>
       </c>
       <c r="C697" t="n">
-        <v>-0.002896</v>
+        <v>-0.000423</v>
       </c>
     </row>
     <row r="698">
@@ -9491,7 +9491,7 @@
         <v>205</v>
       </c>
       <c r="C698" t="n">
-        <v>-0.002794</v>
+        <v>-0.000379</v>
       </c>
     </row>
     <row r="699">
@@ -9504,7 +9504,7 @@
         <v>206</v>
       </c>
       <c r="C699" t="n">
-        <v>-0.002716</v>
+        <v>0.000497</v>
       </c>
     </row>
     <row r="700">
@@ -9517,7 +9517,7 @@
         <v>207</v>
       </c>
       <c r="C700" t="n">
-        <v>-0.002612</v>
+        <v>0.000508</v>
       </c>
     </row>
     <row r="701">
@@ -9530,7 +9530,7 @@
         <v>208</v>
       </c>
       <c r="C701" t="n">
-        <v>-0.002477</v>
+        <v>0.001733</v>
       </c>
     </row>
     <row r="702">
@@ -9543,7 +9543,7 @@
         <v>209</v>
       </c>
       <c r="C702" t="n">
-        <v>-0.002286</v>
+        <v>0.001931</v>
       </c>
     </row>
     <row r="703">
@@ -9556,7 +9556,7 @@
         <v>210</v>
       </c>
       <c r="C703" t="n">
-        <v>-0.002285</v>
+        <v>0.002521</v>
       </c>
     </row>
     <row r="704">
@@ -9569,7 +9569,7 @@
         <v>211</v>
       </c>
       <c r="C704" t="n">
-        <v>-0.002202</v>
+        <v>0.00258</v>
       </c>
     </row>
     <row r="705">
@@ -9582,7 +9582,7 @@
         <v>212</v>
       </c>
       <c r="C705" t="n">
-        <v>-0.002086</v>
+        <v>0.002867</v>
       </c>
     </row>
     <row r="706">
@@ -9595,7 +9595,7 @@
         <v>213</v>
       </c>
       <c r="C706" t="n">
-        <v>-0.001932</v>
+        <v>0.003785</v>
       </c>
     </row>
     <row r="707">
@@ -9608,7 +9608,7 @@
         <v>214</v>
       </c>
       <c r="C707" t="n">
-        <v>-0.001849</v>
+        <v>0.00387</v>
       </c>
     </row>
     <row r="708">
@@ -9621,7 +9621,7 @@
         <v>215</v>
       </c>
       <c r="C708" t="n">
-        <v>-0.001812</v>
+        <v>0.004113</v>
       </c>
     </row>
     <row r="709">
@@ -9634,7 +9634,7 @@
         <v>216</v>
       </c>
       <c r="C709" t="n">
-        <v>-0.001795</v>
+        <v>0.004158</v>
       </c>
     </row>
     <row r="710">
@@ -9647,7 +9647,7 @@
         <v>217</v>
       </c>
       <c r="C710" t="n">
-        <v>-0.001554</v>
+        <v>0.004324</v>
       </c>
     </row>
     <row r="711">
@@ -9660,7 +9660,7 @@
         <v>218</v>
       </c>
       <c r="C711" t="n">
-        <v>-0.001362</v>
+        <v>0.004384</v>
       </c>
     </row>
     <row r="712">
@@ -9673,7 +9673,7 @@
         <v>219</v>
       </c>
       <c r="C712" t="n">
-        <v>-0.001279</v>
+        <v>0.004719</v>
       </c>
     </row>
     <row r="713">
@@ -9686,7 +9686,7 @@
         <v>220</v>
       </c>
       <c r="C713" t="n">
-        <v>-0.001247</v>
+        <v>0.00494</v>
       </c>
     </row>
     <row r="714">
@@ -9699,7 +9699,7 @@
         <v>221</v>
       </c>
       <c r="C714" t="n">
-        <v>-0.001181</v>
+        <v>0.005039</v>
       </c>
     </row>
     <row r="715">
@@ -9712,7 +9712,7 @@
         <v>222</v>
       </c>
       <c r="C715" t="n">
-        <v>-0.001073</v>
+        <v>0.005251</v>
       </c>
     </row>
     <row r="716">
@@ -9725,7 +9725,7 @@
         <v>223</v>
       </c>
       <c r="C716" t="n">
-        <v>-0.000895</v>
+        <v>0.005333</v>
       </c>
     </row>
     <row r="717">
@@ -9738,7 +9738,7 @@
         <v>224</v>
       </c>
       <c r="C717" t="n">
-        <v>-0.000348</v>
+        <v>0.005371</v>
       </c>
     </row>
     <row r="718">
@@ -9751,7 +9751,7 @@
         <v>225</v>
       </c>
       <c r="C718" t="n">
-        <v>-0.000302</v>
+        <v>0.005447</v>
       </c>
     </row>
     <row r="719">
@@ -9764,7 +9764,7 @@
         <v>226</v>
       </c>
       <c r="C719" t="n">
-        <v>-0.000277</v>
+        <v>0.005777</v>
       </c>
     </row>
     <row r="720">
@@ -9777,7 +9777,7 @@
         <v>227</v>
       </c>
       <c r="C720" t="n">
-        <v>-0.000173</v>
+        <v>0.005837</v>
       </c>
     </row>
     <row r="721">
@@ -9790,7 +9790,7 @@
         <v>228</v>
       </c>
       <c r="C721" t="n">
-        <v>0</v>
+        <v>0.006082</v>
       </c>
     </row>
     <row r="722">
@@ -9803,7 +9803,7 @@
         <v>229</v>
       </c>
       <c r="C722" t="n">
-        <v>0</v>
+        <v>0.007774</v>
       </c>
     </row>
     <row r="723">
@@ -9816,7 +9816,7 @@
         <v>230</v>
       </c>
       <c r="C723" t="n">
-        <v>0</v>
+        <v>0.008286999999999999</v>
       </c>
     </row>
     <row r="724">
@@ -9829,7 +9829,7 @@
         <v>231</v>
       </c>
       <c r="C724" t="n">
-        <v>0</v>
+        <v>0.008463</v>
       </c>
     </row>
     <row r="725">
@@ -9842,7 +9842,7 @@
         <v>232</v>
       </c>
       <c r="C725" t="n">
-        <v>0</v>
+        <v>0.008534999999999999</v>
       </c>
     </row>
     <row r="726">
@@ -9855,7 +9855,7 @@
         <v>233</v>
       </c>
       <c r="C726" t="n">
-        <v>0</v>
+        <v>0.009383000000000001</v>
       </c>
     </row>
     <row r="727">
@@ -9868,7 +9868,7 @@
         <v>234</v>
       </c>
       <c r="C727" t="n">
-        <v>0</v>
+        <v>0.009622</v>
       </c>
     </row>
     <row r="728">
@@ -9881,7 +9881,7 @@
         <v>235</v>
       </c>
       <c r="C728" t="n">
-        <v>0</v>
+        <v>0.009691</v>
       </c>
     </row>
     <row r="729">
@@ -9894,7 +9894,7 @@
         <v>236</v>
       </c>
       <c r="C729" t="n">
-        <v>0</v>
+        <v>0.009783999999999999</v>
       </c>
     </row>
     <row r="730">
@@ -9907,7 +9907,7 @@
         <v>237</v>
       </c>
       <c r="C730" t="n">
-        <v>0</v>
+        <v>0.009868999999999999</v>
       </c>
     </row>
     <row r="731">
@@ -9920,7 +9920,7 @@
         <v>238</v>
       </c>
       <c r="C731" t="n">
-        <v>0</v>
+        <v>0.010202</v>
       </c>
     </row>
     <row r="732">
@@ -9933,7 +9933,7 @@
         <v>239</v>
       </c>
       <c r="C732" t="n">
-        <v>0</v>
+        <v>0.010573</v>
       </c>
     </row>
     <row r="733">
@@ -9946,7 +9946,7 @@
         <v>240</v>
       </c>
       <c r="C733" t="n">
-        <v>0</v>
+        <v>0.010685</v>
       </c>
     </row>
     <row r="734">
@@ -9959,7 +9959,7 @@
         <v>241</v>
       </c>
       <c r="C734" t="n">
-        <v>0</v>
+        <v>0.010857</v>
       </c>
     </row>
     <row r="735">
@@ -9972,7 +9972,7 @@
         <v>242</v>
       </c>
       <c r="C735" t="n">
-        <v>0</v>
+        <v>0.010952</v>
       </c>
     </row>
     <row r="736">
@@ -9985,7 +9985,7 @@
         <v>243</v>
       </c>
       <c r="C736" t="n">
-        <v>0</v>
+        <v>0.010964</v>
       </c>
     </row>
     <row r="737">
@@ -9998,7 +9998,7 @@
         <v>244</v>
       </c>
       <c r="C737" t="n">
-        <v>0</v>
+        <v>0.011149</v>
       </c>
     </row>
     <row r="738">
@@ -10011,7 +10011,7 @@
         <v>245</v>
       </c>
       <c r="C738" t="n">
-        <v>0</v>
+        <v>0.011332</v>
       </c>
     </row>
     <row r="739">
@@ -10024,7 +10024,7 @@
         <v>246</v>
       </c>
       <c r="C739" t="n">
-        <v>0</v>
+        <v>0.012351</v>
       </c>
     </row>
     <row r="740">
@@ -10037,7 +10037,7 @@
         <v>247</v>
       </c>
       <c r="C740" t="n">
-        <v>0.000563</v>
+        <v>0.012473</v>
       </c>
     </row>
     <row r="741">
@@ -10050,7 +10050,7 @@
         <v>248</v>
       </c>
       <c r="C741" t="n">
-        <v>0.00074</v>
+        <v>0.013219</v>
       </c>
     </row>
     <row r="742">
@@ -10063,7 +10063,7 @@
         <v>249</v>
       </c>
       <c r="C742" t="n">
-        <v>0.00132</v>
+        <v>0.013467</v>
       </c>
     </row>
     <row r="743">
@@ -10076,7 +10076,7 @@
         <v>250</v>
       </c>
       <c r="C743" t="n">
-        <v>0.001378</v>
+        <v>0.013541</v>
       </c>
     </row>
     <row r="744">
@@ -10089,7 +10089,7 @@
         <v>251</v>
       </c>
       <c r="C744" t="n">
-        <v>0.001387</v>
+        <v>0.013546</v>
       </c>
     </row>
     <row r="745">
@@ -10102,7 +10102,7 @@
         <v>252</v>
       </c>
       <c r="C745" t="n">
-        <v>0.001492</v>
+        <v>0.014397</v>
       </c>
     </row>
     <row r="746">
@@ -10115,7 +10115,7 @@
         <v>253</v>
       </c>
       <c r="C746" t="n">
-        <v>0.001503</v>
+        <v>0.014864</v>
       </c>
     </row>
     <row r="747">
@@ -10128,7 +10128,7 @@
         <v>254</v>
       </c>
       <c r="C747" t="n">
-        <v>0.001566</v>
+        <v>0.014868</v>
       </c>
     </row>
     <row r="748">
@@ -10141,7 +10141,7 @@
         <v>255</v>
       </c>
       <c r="C748" t="n">
-        <v>0.002038</v>
+        <v>0.015452</v>
       </c>
     </row>
     <row r="749">
@@ -10154,7 +10154,7 @@
         <v>256</v>
       </c>
       <c r="C749" t="n">
-        <v>0.002044</v>
+        <v>0.015572</v>
       </c>
     </row>
     <row r="750">
@@ -10167,7 +10167,7 @@
         <v>257</v>
       </c>
       <c r="C750" t="n">
-        <v>0.00206</v>
+        <v>0.016035</v>
       </c>
     </row>
     <row r="751">
@@ -10180,7 +10180,7 @@
         <v>258</v>
       </c>
       <c r="C751" t="n">
-        <v>0.002131</v>
+        <v>0.016162</v>
       </c>
     </row>
     <row r="752">
@@ -10193,7 +10193,7 @@
         <v>259</v>
       </c>
       <c r="C752" t="n">
-        <v>0.002193</v>
+        <v>0.016231</v>
       </c>
     </row>
     <row r="753">
@@ -10206,7 +10206,7 @@
         <v>260</v>
       </c>
       <c r="C753" t="n">
-        <v>0.002225</v>
+        <v>0.016517</v>
       </c>
     </row>
     <row r="754">
@@ -10219,7 +10219,7 @@
         <v>261</v>
       </c>
       <c r="C754" t="n">
-        <v>0.002351</v>
+        <v>0.017065</v>
       </c>
     </row>
     <row r="755">
@@ -10232,7 +10232,7 @@
         <v>262</v>
       </c>
       <c r="C755" t="n">
-        <v>0.002614</v>
+        <v>0.017254</v>
       </c>
     </row>
     <row r="756">
@@ -10245,7 +10245,7 @@
         <v>263</v>
       </c>
       <c r="C756" t="n">
-        <v>0.002915</v>
+        <v>0.017366</v>
       </c>
     </row>
     <row r="757">
@@ -10258,7 +10258,7 @@
         <v>264</v>
       </c>
       <c r="C757" t="n">
-        <v>0.003143</v>
+        <v>0.017998</v>
       </c>
     </row>
     <row r="758">
@@ -10271,7 +10271,7 @@
         <v>265</v>
       </c>
       <c r="C758" t="n">
-        <v>0.003726</v>
+        <v>0.018188</v>
       </c>
     </row>
     <row r="759">
@@ -10284,7 +10284,7 @@
         <v>266</v>
       </c>
       <c r="C759" t="n">
-        <v>0.003827</v>
+        <v>0.018379</v>
       </c>
     </row>
     <row r="760">
@@ -10297,7 +10297,7 @@
         <v>267</v>
       </c>
       <c r="C760" t="n">
-        <v>0.004072</v>
+        <v>0.018767</v>
       </c>
     </row>
     <row r="761">
@@ -10310,7 +10310,7 @@
         <v>268</v>
       </c>
       <c r="C761" t="n">
-        <v>0.004112</v>
+        <v>0.018834</v>
       </c>
     </row>
     <row r="762">
@@ -10323,7 +10323,7 @@
         <v>269</v>
       </c>
       <c r="C762" t="n">
-        <v>0.004443</v>
+        <v>0.019534</v>
       </c>
     </row>
     <row r="763">
@@ -10336,7 +10336,7 @@
         <v>270</v>
       </c>
       <c r="C763" t="n">
-        <v>0.004633</v>
+        <v>0.019751</v>
       </c>
     </row>
     <row r="764">
@@ -10349,7 +10349,7 @@
         <v>271</v>
       </c>
       <c r="C764" t="n">
-        <v>0.004855</v>
+        <v>0.01998</v>
       </c>
     </row>
     <row r="765">
@@ -10362,7 +10362,7 @@
         <v>272</v>
       </c>
       <c r="C765" t="n">
-        <v>0.004953</v>
+        <v>0.020583</v>
       </c>
     </row>
     <row r="766">
@@ -10375,7 +10375,7 @@
         <v>273</v>
       </c>
       <c r="C766" t="n">
-        <v>0.004955</v>
+        <v>0.021065</v>
       </c>
     </row>
     <row r="767">
@@ -10388,7 +10388,7 @@
         <v>274</v>
       </c>
       <c r="C767" t="n">
-        <v>0.005172</v>
+        <v>0.021329</v>
       </c>
     </row>
     <row r="768">
@@ -10401,7 +10401,7 @@
         <v>275</v>
       </c>
       <c r="C768" t="n">
-        <v>0.005365</v>
+        <v>0.02154</v>
       </c>
     </row>
     <row r="769">
@@ -10414,7 +10414,7 @@
         <v>276</v>
       </c>
       <c r="C769" t="n">
-        <v>0.005832</v>
+        <v>0.021805</v>
       </c>
     </row>
     <row r="770">
@@ -10427,7 +10427,7 @@
         <v>277</v>
       </c>
       <c r="C770" t="n">
-        <v>0.00596</v>
+        <v>0.02251</v>
       </c>
     </row>
     <row r="771">
@@ -10440,7 +10440,7 @@
         <v>278</v>
       </c>
       <c r="C771" t="n">
-        <v>0.006011</v>
+        <v>0.02277</v>
       </c>
     </row>
     <row r="772">
@@ -10453,7 +10453,7 @@
         <v>279</v>
       </c>
       <c r="C772" t="n">
-        <v>0.00611</v>
+        <v>0.023713</v>
       </c>
     </row>
     <row r="773">
@@ -10466,7 +10466,7 @@
         <v>280</v>
       </c>
       <c r="C773" t="n">
-        <v>0.006439</v>
+        <v>0.024241</v>
       </c>
     </row>
     <row r="774">
@@ -10479,7 +10479,7 @@
         <v>281</v>
       </c>
       <c r="C774" t="n">
-        <v>0.00653</v>
+        <v>0.02433</v>
       </c>
     </row>
     <row r="775">
@@ -10492,7 +10492,7 @@
         <v>282</v>
       </c>
       <c r="C775" t="n">
-        <v>0.006564</v>
+        <v>0.024547</v>
       </c>
     </row>
     <row r="776">
@@ -10505,7 +10505,7 @@
         <v>283</v>
       </c>
       <c r="C776" t="n">
-        <v>0.006747</v>
+        <v>0.024699</v>
       </c>
     </row>
     <row r="777">
@@ -10518,7 +10518,7 @@
         <v>284</v>
       </c>
       <c r="C777" t="n">
-        <v>0.006802</v>
+        <v>0.024807</v>
       </c>
     </row>
     <row r="778">
@@ -10531,7 +10531,7 @@
         <v>285</v>
       </c>
       <c r="C778" t="n">
-        <v>0.00685</v>
+        <v>0.024984</v>
       </c>
     </row>
     <row r="779">
@@ -10544,7 +10544,7 @@
         <v>286</v>
       </c>
       <c r="C779" t="n">
-        <v>0.007166</v>
+        <v>0.02537</v>
       </c>
     </row>
     <row r="780">
@@ -10557,7 +10557,7 @@
         <v>287</v>
       </c>
       <c r="C780" t="n">
-        <v>0.007171</v>
+        <v>0.027088</v>
       </c>
     </row>
     <row r="781">
@@ -10570,7 +10570,7 @@
         <v>288</v>
       </c>
       <c r="C781" t="n">
-        <v>0.007299</v>
+        <v>0.027482</v>
       </c>
     </row>
     <row r="782">
@@ -10583,7 +10583,7 @@
         <v>289</v>
       </c>
       <c r="C782" t="n">
-        <v>0.007556</v>
+        <v>0.027655</v>
       </c>
     </row>
     <row r="783">
@@ -10596,7 +10596,7 @@
         <v>290</v>
       </c>
       <c r="C783" t="n">
-        <v>0.007819</v>
+        <v>0.028192</v>
       </c>
     </row>
     <row r="784">
@@ -10609,7 +10609,7 @@
         <v>291</v>
       </c>
       <c r="C784" t="n">
-        <v>0.007959000000000001</v>
+        <v>0.028362</v>
       </c>
     </row>
     <row r="785">
@@ -10622,7 +10622,7 @@
         <v>292</v>
       </c>
       <c r="C785" t="n">
-        <v>0.007997000000000001</v>
+        <v>0.028467</v>
       </c>
     </row>
     <row r="786">
@@ -10635,7 +10635,7 @@
         <v>293</v>
       </c>
       <c r="C786" t="n">
-        <v>0.008192</v>
+        <v>0.028515</v>
       </c>
     </row>
     <row r="787">
@@ -10648,7 +10648,7 @@
         <v>294</v>
       </c>
       <c r="C787" t="n">
-        <v>0.008548999999999999</v>
+        <v>0.028936</v>
       </c>
     </row>
     <row r="788">
@@ -10661,7 +10661,7 @@
         <v>295</v>
       </c>
       <c r="C788" t="n">
-        <v>0.008874999999999999</v>
+        <v>0.029992</v>
       </c>
     </row>
     <row r="789">
@@ -10674,7 +10674,7 @@
         <v>296</v>
       </c>
       <c r="C789" t="n">
-        <v>0.008976</v>
+        <v>0.030083</v>
       </c>
     </row>
     <row r="790">
@@ -10687,7 +10687,7 @@
         <v>297</v>
       </c>
       <c r="C790" t="n">
-        <v>0.009086</v>
+        <v>0.030551</v>
       </c>
     </row>
     <row r="791">
@@ -10700,7 +10700,7 @@
         <v>298</v>
       </c>
       <c r="C791" t="n">
-        <v>0.009136999999999999</v>
+        <v>0.0308</v>
       </c>
     </row>
     <row r="792">
@@ -10713,7 +10713,7 @@
         <v>299</v>
       </c>
       <c r="C792" t="n">
-        <v>0.009211</v>
+        <v>0.03157</v>
       </c>
     </row>
     <row r="793">
@@ -10726,7 +10726,7 @@
         <v>300</v>
       </c>
       <c r="C793" t="n">
-        <v>0.009238</v>
+        <v>0.031584</v>
       </c>
     </row>
     <row r="794">
@@ -10739,7 +10739,7 @@
         <v>301</v>
       </c>
       <c r="C794" t="n">
-        <v>0.009424</v>
+        <v>0.031752</v>
       </c>
     </row>
     <row r="795">
@@ -10752,7 +10752,7 @@
         <v>302</v>
       </c>
       <c r="C795" t="n">
-        <v>0.009466</v>
+        <v>0.031813</v>
       </c>
     </row>
     <row r="796">
@@ -10765,7 +10765,7 @@
         <v>303</v>
       </c>
       <c r="C796" t="n">
-        <v>0.00966</v>
+        <v>0.031993</v>
       </c>
     </row>
     <row r="797">
@@ -10778,7 +10778,7 @@
         <v>304</v>
       </c>
       <c r="C797" t="n">
-        <v>0.009990000000000001</v>
+        <v>0.032673</v>
       </c>
     </row>
     <row r="798">
@@ -10791,7 +10791,7 @@
         <v>305</v>
       </c>
       <c r="C798" t="n">
-        <v>0.010309</v>
+        <v>0.032726</v>
       </c>
     </row>
     <row r="799">
@@ -10804,7 +10804,7 @@
         <v>306</v>
       </c>
       <c r="C799" t="n">
-        <v>0.010396</v>
+        <v>0.033323</v>
       </c>
     </row>
     <row r="800">
@@ -10817,7 +10817,7 @@
         <v>307</v>
       </c>
       <c r="C800" t="n">
-        <v>0.010451</v>
+        <v>0.033696</v>
       </c>
     </row>
     <row r="801">
@@ -10830,7 +10830,7 @@
         <v>308</v>
       </c>
       <c r="C801" t="n">
-        <v>0.010507</v>
+        <v>0.034174</v>
       </c>
     </row>
     <row r="802">
@@ -10843,7 +10843,7 @@
         <v>309</v>
       </c>
       <c r="C802" t="n">
-        <v>0.010536</v>
+        <v>0.034558</v>
       </c>
     </row>
     <row r="803">
@@ -10856,7 +10856,7 @@
         <v>310</v>
       </c>
       <c r="C803" t="n">
-        <v>0.010864</v>
+        <v>0.034629</v>
       </c>
     </row>
     <row r="804">
@@ -10869,7 +10869,7 @@
         <v>311</v>
       </c>
       <c r="C804" t="n">
-        <v>0.01101</v>
+        <v>0.035485</v>
       </c>
     </row>
     <row r="805">
@@ -10882,7 +10882,7 @@
         <v>312</v>
       </c>
       <c r="C805" t="n">
-        <v>0.011175</v>
+        <v>0.035517</v>
       </c>
     </row>
     <row r="806">
@@ -10895,7 +10895,7 @@
         <v>313</v>
       </c>
       <c r="C806" t="n">
-        <v>0.01137</v>
+        <v>0.035527</v>
       </c>
     </row>
     <row r="807">
@@ -10908,7 +10908,7 @@
         <v>314</v>
       </c>
       <c r="C807" t="n">
-        <v>0.011371</v>
+        <v>0.036056</v>
       </c>
     </row>
     <row r="808">
@@ -10921,7 +10921,7 @@
         <v>315</v>
       </c>
       <c r="C808" t="n">
-        <v>0.011389</v>
+        <v>0.036549</v>
       </c>
     </row>
     <row r="809">
@@ -10934,7 +10934,7 @@
         <v>316</v>
       </c>
       <c r="C809" t="n">
-        <v>0.01146</v>
+        <v>0.036625</v>
       </c>
     </row>
     <row r="810">
@@ -10947,7 +10947,7 @@
         <v>317</v>
       </c>
       <c r="C810" t="n">
-        <v>0.011806</v>
+        <v>0.037059</v>
       </c>
     </row>
     <row r="811">
@@ -10960,7 +10960,7 @@
         <v>318</v>
       </c>
       <c r="C811" t="n">
-        <v>0.011893</v>
+        <v>0.037395</v>
       </c>
     </row>
     <row r="812">
@@ -10973,7 +10973,7 @@
         <v>319</v>
       </c>
       <c r="C812" t="n">
-        <v>0.012101</v>
+        <v>0.037468</v>
       </c>
     </row>
     <row r="813">
@@ -10986,7 +10986,7 @@
         <v>320</v>
       </c>
       <c r="C813" t="n">
-        <v>0.012352</v>
+        <v>0.037835</v>
       </c>
     </row>
     <row r="814">
@@ -10999,7 +10999,7 @@
         <v>321</v>
       </c>
       <c r="C814" t="n">
-        <v>0.012418</v>
+        <v>0.038032</v>
       </c>
     </row>
     <row r="815">
@@ -11012,7 +11012,7 @@
         <v>322</v>
       </c>
       <c r="C815" t="n">
-        <v>0.012538</v>
+        <v>0.038672</v>
       </c>
     </row>
     <row r="816">
@@ -11025,7 +11025,7 @@
         <v>323</v>
       </c>
       <c r="C816" t="n">
-        <v>0.012704</v>
+        <v>0.03951</v>
       </c>
     </row>
     <row r="817">
@@ -11038,7 +11038,7 @@
         <v>324</v>
       </c>
       <c r="C817" t="n">
-        <v>0.012866</v>
+        <v>0.039767</v>
       </c>
     </row>
     <row r="818">
@@ -11051,7 +11051,7 @@
         <v>325</v>
       </c>
       <c r="C818" t="n">
-        <v>0.012973</v>
+        <v>0.039903</v>
       </c>
     </row>
     <row r="819">
@@ -11064,7 +11064,7 @@
         <v>326</v>
       </c>
       <c r="C819" t="n">
-        <v>0.013345</v>
+        <v>0.040072</v>
       </c>
     </row>
     <row r="820">
@@ -11077,7 +11077,7 @@
         <v>327</v>
       </c>
       <c r="C820" t="n">
-        <v>0.013428</v>
+        <v>0.040342</v>
       </c>
     </row>
     <row r="821">
@@ -11090,7 +11090,7 @@
         <v>328</v>
       </c>
       <c r="C821" t="n">
-        <v>0.014094</v>
+        <v>0.040805</v>
       </c>
     </row>
     <row r="822">
@@ -11103,7 +11103,7 @@
         <v>329</v>
       </c>
       <c r="C822" t="n">
-        <v>0.014264</v>
+        <v>0.041108</v>
       </c>
     </row>
     <row r="823">
@@ -11116,7 +11116,7 @@
         <v>330</v>
       </c>
       <c r="C823" t="n">
-        <v>0.014338</v>
+        <v>0.04122</v>
       </c>
     </row>
     <row r="824">
@@ -11129,7 +11129,7 @@
         <v>331</v>
       </c>
       <c r="C824" t="n">
-        <v>0.014424</v>
+        <v>0.041263</v>
       </c>
     </row>
     <row r="825">
@@ -11142,7 +11142,7 @@
         <v>332</v>
       </c>
       <c r="C825" t="n">
-        <v>0.014441</v>
+        <v>0.041829</v>
       </c>
     </row>
     <row r="826">
@@ -11155,7 +11155,7 @@
         <v>333</v>
       </c>
       <c r="C826" t="n">
-        <v>0.014536</v>
+        <v>0.041927</v>
       </c>
     </row>
     <row r="827">
@@ -11168,7 +11168,7 @@
         <v>334</v>
       </c>
       <c r="C827" t="n">
-        <v>0.014714</v>
+        <v>0.042393</v>
       </c>
     </row>
     <row r="828">
@@ -11181,7 +11181,7 @@
         <v>335</v>
       </c>
       <c r="C828" t="n">
-        <v>0.014849</v>
+        <v>0.042448</v>
       </c>
     </row>
     <row r="829">
@@ -11194,7 +11194,7 @@
         <v>336</v>
       </c>
       <c r="C829" t="n">
-        <v>0.014916</v>
+        <v>0.042549</v>
       </c>
     </row>
     <row r="830">
@@ -11207,7 +11207,7 @@
         <v>337</v>
       </c>
       <c r="C830" t="n">
-        <v>0.015887</v>
+        <v>0.042584</v>
       </c>
     </row>
     <row r="831">
@@ -11220,7 +11220,7 @@
         <v>338</v>
       </c>
       <c r="C831" t="n">
-        <v>0.016892</v>
+        <v>0.042598</v>
       </c>
     </row>
     <row r="832">
@@ -11233,7 +11233,7 @@
         <v>339</v>
       </c>
       <c r="C832" t="n">
-        <v>0.017236</v>
+        <v>0.042866</v>
       </c>
     </row>
     <row r="833">
@@ -11246,7 +11246,7 @@
         <v>340</v>
       </c>
       <c r="C833" t="n">
-        <v>0.017289</v>
+        <v>0.042883</v>
       </c>
     </row>
     <row r="834">
@@ -11259,7 +11259,7 @@
         <v>341</v>
       </c>
       <c r="C834" t="n">
-        <v>0.017313</v>
+        <v>0.044075</v>
       </c>
     </row>
     <row r="835">
@@ -11272,7 +11272,7 @@
         <v>342</v>
       </c>
       <c r="C835" t="n">
-        <v>0.017531</v>
+        <v>0.044079</v>
       </c>
     </row>
     <row r="836">
@@ -11285,7 +11285,7 @@
         <v>343</v>
       </c>
       <c r="C836" t="n">
-        <v>0.018129</v>
+        <v>0.044848</v>
       </c>
     </row>
     <row r="837">
@@ -11298,7 +11298,7 @@
         <v>344</v>
       </c>
       <c r="C837" t="n">
-        <v>0.018178</v>
+        <v>0.045071</v>
       </c>
     </row>
     <row r="838">
@@ -11311,7 +11311,7 @@
         <v>345</v>
       </c>
       <c r="C838" t="n">
-        <v>0.018229</v>
+        <v>0.045173</v>
       </c>
     </row>
     <row r="839">
@@ -11324,7 +11324,7 @@
         <v>346</v>
       </c>
       <c r="C839" t="n">
-        <v>0.018243</v>
+        <v>0.04552</v>
       </c>
     </row>
     <row r="840">
@@ -11337,7 +11337,7 @@
         <v>347</v>
       </c>
       <c r="C840" t="n">
-        <v>0.01825</v>
+        <v>0.046123</v>
       </c>
     </row>
     <row r="841">
@@ -11350,7 +11350,7 @@
         <v>348</v>
       </c>
       <c r="C841" t="n">
-        <v>0.018398</v>
+        <v>0.046465</v>
       </c>
     </row>
     <row r="842">
@@ -11363,7 +11363,7 @@
         <v>349</v>
       </c>
       <c r="C842" t="n">
-        <v>0.018542</v>
+        <v>0.047002</v>
       </c>
     </row>
     <row r="843">
@@ -11376,7 +11376,7 @@
         <v>350</v>
       </c>
       <c r="C843" t="n">
-        <v>0.019095</v>
+        <v>0.047089</v>
       </c>
     </row>
     <row r="844">
@@ -11389,7 +11389,7 @@
         <v>351</v>
       </c>
       <c r="C844" t="n">
-        <v>0.019584</v>
+        <v>0.047436</v>
       </c>
     </row>
     <row r="845">
@@ -11402,7 +11402,7 @@
         <v>352</v>
       </c>
       <c r="C845" t="n">
-        <v>0.020031</v>
+        <v>0.04761</v>
       </c>
     </row>
     <row r="846">
@@ -11415,7 +11415,7 @@
         <v>353</v>
       </c>
       <c r="C846" t="n">
-        <v>0.020092</v>
+        <v>0.048053</v>
       </c>
     </row>
     <row r="847">
@@ -11428,7 +11428,7 @@
         <v>354</v>
       </c>
       <c r="C847" t="n">
-        <v>0.020604</v>
+        <v>0.048983</v>
       </c>
     </row>
     <row r="848">
@@ -11441,7 +11441,7 @@
         <v>355</v>
       </c>
       <c r="C848" t="n">
-        <v>0.020888</v>
+        <v>0.049112</v>
       </c>
     </row>
     <row r="849">
@@ -11454,7 +11454,7 @@
         <v>356</v>
       </c>
       <c r="C849" t="n">
-        <v>0.021179</v>
+        <v>0.049273</v>
       </c>
     </row>
     <row r="850">
@@ -11467,7 +11467,7 @@
         <v>357</v>
       </c>
       <c r="C850" t="n">
-        <v>0.021466</v>
+        <v>0.049723</v>
       </c>
     </row>
     <row r="851">
@@ -11480,7 +11480,7 @@
         <v>358</v>
       </c>
       <c r="C851" t="n">
-        <v>0.021824</v>
+        <v>0.050154</v>
       </c>
     </row>
     <row r="852">
@@ -11493,7 +11493,7 @@
         <v>359</v>
       </c>
       <c r="C852" t="n">
-        <v>0.02201</v>
+        <v>0.050377</v>
       </c>
     </row>
     <row r="853">
@@ -11506,7 +11506,7 @@
         <v>360</v>
       </c>
       <c r="C853" t="n">
-        <v>0.02222</v>
+        <v>0.05078</v>
       </c>
     </row>
     <row r="854">
@@ -11519,7 +11519,7 @@
         <v>361</v>
       </c>
       <c r="C854" t="n">
-        <v>0.022221</v>
+        <v>0.0508</v>
       </c>
     </row>
     <row r="855">
@@ -11532,7 +11532,7 @@
         <v>362</v>
       </c>
       <c r="C855" t="n">
-        <v>0.022503</v>
+        <v>0.051353</v>
       </c>
     </row>
     <row r="856">
@@ -11545,7 +11545,7 @@
         <v>363</v>
       </c>
       <c r="C856" t="n">
-        <v>0.022981</v>
+        <v>0.051734</v>
       </c>
     </row>
     <row r="857">
@@ -11558,7 +11558,7 @@
         <v>364</v>
       </c>
       <c r="C857" t="n">
-        <v>0.023172</v>
+        <v>0.051824</v>
       </c>
     </row>
     <row r="858">
@@ -11571,7 +11571,7 @@
         <v>365</v>
       </c>
       <c r="C858" t="n">
-        <v>0.023193</v>
+        <v>0.051859</v>
       </c>
     </row>
     <row r="859">
@@ -11584,7 +11584,7 @@
         <v>366</v>
       </c>
       <c r="C859" t="n">
-        <v>0.023226</v>
+        <v>0.052258</v>
       </c>
     </row>
     <row r="860">
@@ -11597,7 +11597,7 @@
         <v>367</v>
       </c>
       <c r="C860" t="n">
-        <v>0.023258</v>
+        <v>0.052694</v>
       </c>
     </row>
     <row r="861">
@@ -11610,7 +11610,7 @@
         <v>368</v>
       </c>
       <c r="C861" t="n">
-        <v>0.023271</v>
+        <v>0.052855</v>
       </c>
     </row>
     <row r="862">
@@ -11623,7 +11623,7 @@
         <v>369</v>
       </c>
       <c r="C862" t="n">
-        <v>0.02376</v>
+        <v>0.053096</v>
       </c>
     </row>
     <row r="863">
@@ -11636,7 +11636,7 @@
         <v>370</v>
       </c>
       <c r="C863" t="n">
-        <v>0.023897</v>
+        <v>0.053417</v>
       </c>
     </row>
     <row r="864">
@@ -11649,7 +11649,7 @@
         <v>371</v>
       </c>
       <c r="C864" t="n">
-        <v>0.023961</v>
+        <v>0.054588</v>
       </c>
     </row>
     <row r="865">
@@ -11662,7 +11662,7 @@
         <v>372</v>
       </c>
       <c r="C865" t="n">
-        <v>0.02398</v>
+        <v>0.0576</v>
       </c>
     </row>
     <row r="866">
@@ -11675,7 +11675,7 @@
         <v>373</v>
       </c>
       <c r="C866" t="n">
-        <v>0.02399</v>
+        <v>0.057988</v>
       </c>
     </row>
     <row r="867">
@@ -11688,7 +11688,7 @@
         <v>374</v>
       </c>
       <c r="C867" t="n">
-        <v>0.024443</v>
+        <v>0.059035</v>
       </c>
     </row>
     <row r="868">
@@ -11701,7 +11701,7 @@
         <v>375</v>
       </c>
       <c r="C868" t="n">
-        <v>0.024993</v>
+        <v>0.059554</v>
       </c>
     </row>
     <row r="869">
@@ -11714,7 +11714,7 @@
         <v>376</v>
       </c>
       <c r="C869" t="n">
-        <v>0.02528</v>
+        <v>0.059931</v>
       </c>
     </row>
     <row r="870">
@@ -11727,7 +11727,7 @@
         <v>377</v>
       </c>
       <c r="C870" t="n">
-        <v>0.025346</v>
+        <v>0.060434</v>
       </c>
     </row>
     <row r="871">
@@ -11740,7 +11740,7 @@
         <v>378</v>
       </c>
       <c r="C871" t="n">
-        <v>0.025712</v>
+        <v>0.060581</v>
       </c>
     </row>
     <row r="872">
@@ -11753,7 +11753,7 @@
         <v>379</v>
       </c>
       <c r="C872" t="n">
-        <v>0.02577</v>
+        <v>0.061049</v>
       </c>
     </row>
     <row r="873">
@@ -11766,7 +11766,7 @@
         <v>380</v>
       </c>
       <c r="C873" t="n">
-        <v>0.02609</v>
+        <v>0.061278</v>
       </c>
     </row>
     <row r="874">
@@ -11779,7 +11779,7 @@
         <v>381</v>
       </c>
       <c r="C874" t="n">
-        <v>0.026798</v>
+        <v>0.06162</v>
       </c>
     </row>
     <row r="875">
@@ -11792,7 +11792,7 @@
         <v>382</v>
       </c>
       <c r="C875" t="n">
-        <v>0.027314</v>
+        <v>0.061908</v>
       </c>
     </row>
     <row r="876">
@@ -11805,7 +11805,7 @@
         <v>383</v>
       </c>
       <c r="C876" t="n">
-        <v>0.027723</v>
+        <v>0.062292</v>
       </c>
     </row>
     <row r="877">
@@ -11818,7 +11818,7 @@
         <v>384</v>
       </c>
       <c r="C877" t="n">
-        <v>0.027802</v>
+        <v>0.06237</v>
       </c>
     </row>
     <row r="878">
@@ -11831,7 +11831,7 @@
         <v>385</v>
       </c>
       <c r="C878" t="n">
-        <v>0.028129</v>
+        <v>0.062478</v>
       </c>
     </row>
     <row r="879">
@@ -11844,7 +11844,7 @@
         <v>386</v>
       </c>
       <c r="C879" t="n">
-        <v>0.028195</v>
+        <v>0.06293600000000001</v>
       </c>
     </row>
     <row r="880">
@@ -11857,7 +11857,7 @@
         <v>387</v>
       </c>
       <c r="C880" t="n">
-        <v>0.028412</v>
+        <v>0.06336</v>
       </c>
     </row>
     <row r="881">
@@ -11870,7 +11870,7 @@
         <v>388</v>
       </c>
       <c r="C881" t="n">
-        <v>0.028669</v>
+        <v>0.065238</v>
       </c>
     </row>
     <row r="882">
@@ -11883,7 +11883,7 @@
         <v>389</v>
       </c>
       <c r="C882" t="n">
-        <v>0.029301</v>
+        <v>0.065677</v>
       </c>
     </row>
     <row r="883">
@@ -11896,7 +11896,7 @@
         <v>390</v>
       </c>
       <c r="C883" t="n">
-        <v>0.029451</v>
+        <v>0.065734</v>
       </c>
     </row>
     <row r="884">
@@ -11909,7 +11909,7 @@
         <v>391</v>
       </c>
       <c r="C884" t="n">
-        <v>0.030135</v>
+        <v>0.06701699999999999</v>
       </c>
     </row>
     <row r="885">
@@ -11922,7 +11922,7 @@
         <v>392</v>
       </c>
       <c r="C885" t="n">
-        <v>0.030577</v>
+        <v>0.067551</v>
       </c>
     </row>
     <row r="886">
@@ -11935,7 +11935,7 @@
         <v>393</v>
       </c>
       <c r="C886" t="n">
-        <v>0.030811</v>
+        <v>0.06758400000000001</v>
       </c>
     </row>
     <row r="887">
@@ -11948,7 +11948,7 @@
         <v>394</v>
       </c>
       <c r="C887" t="n">
-        <v>0.031138</v>
+        <v>0.068353</v>
       </c>
     </row>
     <row r="888">
@@ -11961,7 +11961,7 @@
         <v>395</v>
       </c>
       <c r="C888" t="n">
-        <v>0.031735</v>
+        <v>0.06900000000000001</v>
       </c>
     </row>
     <row r="889">
@@ -11974,7 +11974,7 @@
         <v>396</v>
       </c>
       <c r="C889" t="n">
-        <v>0.031886</v>
+        <v>0.06900100000000001</v>
       </c>
     </row>
     <row r="890">
@@ -11987,7 +11987,7 @@
         <v>397</v>
       </c>
       <c r="C890" t="n">
-        <v>0.032194</v>
+        <v>0.07023600000000001</v>
       </c>
     </row>
     <row r="891">
@@ -12000,7 +12000,7 @@
         <v>398</v>
       </c>
       <c r="C891" t="n">
-        <v>0.03254</v>
+        <v>0.07054100000000001</v>
       </c>
     </row>
     <row r="892">
@@ -12013,7 +12013,7 @@
         <v>399</v>
       </c>
       <c r="C892" t="n">
-        <v>0.032643</v>
+        <v>0.070783</v>
       </c>
     </row>
     <row r="893">
@@ -12026,7 +12026,7 @@
         <v>400</v>
       </c>
       <c r="C893" t="n">
-        <v>0.03273</v>
+        <v>0.07180300000000001</v>
       </c>
     </row>
     <row r="894">
@@ -12039,7 +12039,7 @@
         <v>401</v>
       </c>
       <c r="C894" t="n">
-        <v>0.033701</v>
+        <v>0.07199700000000001</v>
       </c>
     </row>
     <row r="895">
@@ -12052,7 +12052,7 @@
         <v>402</v>
       </c>
       <c r="C895" t="n">
-        <v>0.034223</v>
+        <v>0.07201200000000001</v>
       </c>
     </row>
     <row r="896">
@@ -12065,7 +12065,7 @@
         <v>403</v>
       </c>
       <c r="C896" t="n">
-        <v>0.03423</v>
+        <v>0.07216599999999999</v>
       </c>
     </row>
     <row r="897">
@@ -12078,7 +12078,7 @@
         <v>404</v>
       </c>
       <c r="C897" t="n">
-        <v>0.034248</v>
+        <v>0.07248</v>
       </c>
     </row>
     <row r="898">
@@ -12091,7 +12091,7 @@
         <v>405</v>
       </c>
       <c r="C898" t="n">
-        <v>0.03438</v>
+        <v>0.072501</v>
       </c>
     </row>
     <row r="899">
@@ -12104,7 +12104,7 @@
         <v>406</v>
       </c>
       <c r="C899" t="n">
-        <v>0.034906</v>
+        <v>0.07272199999999999</v>
       </c>
     </row>
     <row r="900">
@@ -12117,7 +12117,7 @@
         <v>407</v>
       </c>
       <c r="C900" t="n">
-        <v>0.034937</v>
+        <v>0.072922</v>
       </c>
     </row>
     <row r="901">
@@ -12130,7 +12130,7 @@
         <v>408</v>
       </c>
       <c r="C901" t="n">
-        <v>0.035154</v>
+        <v>0.072994</v>
       </c>
     </row>
     <row r="902">
@@ -12143,7 +12143,7 @@
         <v>409</v>
       </c>
       <c r="C902" t="n">
-        <v>0.035182</v>
+        <v>0.073312</v>
       </c>
     </row>
     <row r="903">
@@ -12156,7 +12156,7 @@
         <v>410</v>
       </c>
       <c r="C903" t="n">
-        <v>0.035592</v>
+        <v>0.073904</v>
       </c>
     </row>
     <row r="904">
@@ -12169,7 +12169,7 @@
         <v>411</v>
       </c>
       <c r="C904" t="n">
-        <v>0.035959</v>
+        <v>0.074253</v>
       </c>
     </row>
     <row r="905">
@@ -12182,7 +12182,7 @@
         <v>412</v>
       </c>
       <c r="C905" t="n">
-        <v>0.036072</v>
+        <v>0.07434399999999999</v>
       </c>
     </row>
     <row r="906">
@@ -12195,7 +12195,7 @@
         <v>413</v>
       </c>
       <c r="C906" t="n">
-        <v>0.036163</v>
+        <v>0.074932</v>
       </c>
     </row>
     <row r="907">
@@ -12208,7 +12208,7 @@
         <v>414</v>
       </c>
       <c r="C907" t="n">
-        <v>0.036307</v>
+        <v>0.07549</v>
       </c>
     </row>
     <row r="908">
@@ -12221,7 +12221,7 @@
         <v>415</v>
       </c>
       <c r="C908" t="n">
-        <v>0.036858</v>
+        <v>0.079542</v>
       </c>
     </row>
     <row r="909">
@@ -12234,7 +12234,7 @@
         <v>416</v>
       </c>
       <c r="C909" t="n">
-        <v>0.037193</v>
+        <v>0.079663</v>
       </c>
     </row>
     <row r="910">
@@ -12247,7 +12247,7 @@
         <v>417</v>
       </c>
       <c r="C910" t="n">
-        <v>0.038055</v>
+        <v>0.080985</v>
       </c>
     </row>
     <row r="911">
@@ -12260,7 +12260,7 @@
         <v>418</v>
       </c>
       <c r="C911" t="n">
-        <v>0.038963</v>
+        <v>0.081458</v>
       </c>
     </row>
     <row r="912">
@@ -12273,7 +12273,7 @@
         <v>419</v>
       </c>
       <c r="C912" t="n">
-        <v>0.039012</v>
+        <v>0.083244</v>
       </c>
     </row>
     <row r="913">
@@ -12286,7 +12286,7 @@
         <v>420</v>
       </c>
       <c r="C913" t="n">
-        <v>0.039137</v>
+        <v>0.083772</v>
       </c>
     </row>
     <row r="914">
@@ -12299,7 +12299,7 @@
         <v>421</v>
       </c>
       <c r="C914" t="n">
-        <v>0.039154</v>
+        <v>0.08411</v>
       </c>
     </row>
     <row r="915">
@@ -12312,7 +12312,7 @@
         <v>422</v>
       </c>
       <c r="C915" t="n">
-        <v>0.039933</v>
+        <v>0.084355</v>
       </c>
     </row>
     <row r="916">
@@ -12325,7 +12325,7 @@
         <v>423</v>
       </c>
       <c r="C916" t="n">
-        <v>0.040119</v>
+        <v>0.08479100000000001</v>
       </c>
     </row>
     <row r="917">
@@ -12338,7 +12338,7 @@
         <v>424</v>
       </c>
       <c r="C917" t="n">
-        <v>0.040357</v>
+        <v>0.085094</v>
       </c>
     </row>
     <row r="918">
@@ -12351,7 +12351,7 @@
         <v>425</v>
       </c>
       <c r="C918" t="n">
-        <v>0.040711</v>
+        <v>0.08670799999999999</v>
       </c>
     </row>
     <row r="919">
@@ -12364,7 +12364,7 @@
         <v>426</v>
       </c>
       <c r="C919" t="n">
-        <v>0.04127</v>
+        <v>0.087604</v>
       </c>
     </row>
     <row r="920">
@@ -12377,7 +12377,7 @@
         <v>427</v>
       </c>
       <c r="C920" t="n">
-        <v>0.042031</v>
+        <v>0.08996999999999999</v>
       </c>
     </row>
     <row r="921">
@@ -12390,7 +12390,7 @@
         <v>428</v>
       </c>
       <c r="C921" t="n">
-        <v>0.042773</v>
+        <v>0.090321</v>
       </c>
     </row>
     <row r="922">
@@ -12403,7 +12403,7 @@
         <v>429</v>
       </c>
       <c r="C922" t="n">
-        <v>0.042968</v>
+        <v>0.090488</v>
       </c>
     </row>
     <row r="923">
@@ -12416,7 +12416,7 @@
         <v>430</v>
       </c>
       <c r="C923" t="n">
-        <v>0.043509</v>
+        <v>0.090684</v>
       </c>
     </row>
     <row r="924">
@@ -12429,7 +12429,7 @@
         <v>431</v>
       </c>
       <c r="C924" t="n">
-        <v>0.04454</v>
+        <v>0.09341000000000001</v>
       </c>
     </row>
     <row r="925">
@@ -12442,7 +12442,7 @@
         <v>432</v>
       </c>
       <c r="C925" t="n">
-        <v>0.045225</v>
+        <v>0.09364400000000001</v>
       </c>
     </row>
     <row r="926">
@@ -12455,7 +12455,7 @@
         <v>433</v>
       </c>
       <c r="C926" t="n">
-        <v>0.045447</v>
+        <v>0.094628</v>
       </c>
     </row>
     <row r="927">
@@ -12468,7 +12468,7 @@
         <v>434</v>
       </c>
       <c r="C927" t="n">
-        <v>0.04692</v>
+        <v>0.09479799999999999</v>
       </c>
     </row>
     <row r="928">
@@ -12481,7 +12481,7 @@
         <v>435</v>
       </c>
       <c r="C928" t="n">
-        <v>0.048464</v>
+        <v>0.09540800000000001</v>
       </c>
     </row>
     <row r="929">
@@ -12494,7 +12494,7 @@
         <v>436</v>
       </c>
       <c r="C929" t="n">
-        <v>0.049449</v>
+        <v>0.09744</v>
       </c>
     </row>
     <row r="930">
@@ -12507,7 +12507,7 @@
         <v>437</v>
       </c>
       <c r="C930" t="n">
-        <v>0.050122</v>
+        <v>0.098304</v>
       </c>
     </row>
     <row r="931">
@@ -12520,7 +12520,7 @@
         <v>438</v>
       </c>
       <c r="C931" t="n">
-        <v>0.050723</v>
+        <v>0.100853</v>
       </c>
     </row>
     <row r="932">
@@ -12533,7 +12533,7 @@
         <v>439</v>
       </c>
       <c r="C932" t="n">
-        <v>0.05193</v>
+        <v>0.101501</v>
       </c>
     </row>
     <row r="933">
@@ -12546,7 +12546,7 @@
         <v>440</v>
       </c>
       <c r="C933" t="n">
-        <v>0.053408</v>
+        <v>0.101815</v>
       </c>
     </row>
     <row r="934">
@@ -12559,7 +12559,7 @@
         <v>441</v>
       </c>
       <c r="C934" t="n">
-        <v>0.054243</v>
+        <v>0.104641</v>
       </c>
     </row>
     <row r="935">
@@ -12572,7 +12572,7 @@
         <v>442</v>
       </c>
       <c r="C935" t="n">
-        <v>0.054642</v>
+        <v>0.10635</v>
       </c>
     </row>
     <row r="936">
@@ -12585,7 +12585,7 @@
         <v>443</v>
       </c>
       <c r="C936" t="n">
-        <v>0.054677</v>
+        <v>0.107437</v>
       </c>
     </row>
     <row r="937">
@@ -12598,7 +12598,7 @@
         <v>444</v>
       </c>
       <c r="C937" t="n">
-        <v>0.054682</v>
+        <v>0.109914</v>
       </c>
     </row>
     <row r="938">
@@ -12611,7 +12611,7 @@
         <v>445</v>
       </c>
       <c r="C938" t="n">
-        <v>0.055605</v>
+        <v>0.113696</v>
       </c>
     </row>
     <row r="939">
@@ -12624,7 +12624,7 @@
         <v>446</v>
       </c>
       <c r="C939" t="n">
-        <v>0.055947</v>
+        <v>0.116878</v>
       </c>
     </row>
     <row r="940">
@@ -12637,7 +12637,7 @@
         <v>447</v>
       </c>
       <c r="C940" t="n">
-        <v>0.056187</v>
+        <v>0.118922</v>
       </c>
     </row>
     <row r="941">
@@ -12650,7 +12650,7 @@
         <v>448</v>
       </c>
       <c r="C941" t="n">
-        <v>0.057511</v>
+        <v>0.119417</v>
       </c>
     </row>
     <row r="942">
@@ -12663,7 +12663,7 @@
         <v>449</v>
       </c>
       <c r="C942" t="n">
-        <v>0.05775</v>
+        <v>0.122195</v>
       </c>
     </row>
     <row r="943">
@@ -12676,7 +12676,7 @@
         <v>450</v>
       </c>
       <c r="C943" t="n">
-        <v>0.059273</v>
+        <v>0.122416</v>
       </c>
     </row>
     <row r="944">
@@ -12689,7 +12689,7 @@
         <v>451</v>
       </c>
       <c r="C944" t="n">
-        <v>0.059938</v>
+        <v>0.122651</v>
       </c>
     </row>
     <row r="945">
@@ -12702,7 +12702,7 @@
         <v>452</v>
       </c>
       <c r="C945" t="n">
-        <v>0.064294</v>
+        <v>0.122933</v>
       </c>
     </row>
     <row r="946">
@@ -12715,7 +12715,7 @@
         <v>453</v>
       </c>
       <c r="C946" t="n">
-        <v>0.06469800000000001</v>
+        <v>0.123213</v>
       </c>
     </row>
     <row r="947">
@@ -12728,7 +12728,7 @@
         <v>454</v>
       </c>
       <c r="C947" t="n">
-        <v>0.06568599999999999</v>
+        <v>0.126332</v>
       </c>
     </row>
     <row r="948">
@@ -12741,7 +12741,7 @@
         <v>455</v>
       </c>
       <c r="C948" t="n">
-        <v>0.069674</v>
+        <v>0.1319</v>
       </c>
     </row>
     <row r="949">
@@ -12754,7 +12754,7 @@
         <v>456</v>
       </c>
       <c r="C949" t="n">
-        <v>0.069978</v>
+        <v>0.132711</v>
       </c>
     </row>
     <row r="950">
@@ -12767,7 +12767,7 @@
         <v>457</v>
       </c>
       <c r="C950" t="n">
-        <v>0.072381</v>
+        <v>0.133638</v>
       </c>
     </row>
     <row r="951">
@@ -12780,7 +12780,7 @@
         <v>458</v>
       </c>
       <c r="C951" t="n">
-        <v>0.073</v>
+        <v>0.133821</v>
       </c>
     </row>
     <row r="952">
@@ -12793,7 +12793,7 @@
         <v>459</v>
       </c>
       <c r="C952" t="n">
-        <v>0.07517</v>
+        <v>0.135713</v>
       </c>
     </row>
     <row r="953">
@@ -12806,7 +12806,7 @@
         <v>460</v>
       </c>
       <c r="C953" t="n">
-        <v>0.075423</v>
+        <v>0.136769</v>
       </c>
     </row>
     <row r="954">
@@ -12819,7 +12819,7 @@
         <v>461</v>
       </c>
       <c r="C954" t="n">
-        <v>0.075562</v>
+        <v>0.137899</v>
       </c>
     </row>
     <row r="955">
@@ -12832,7 +12832,7 @@
         <v>462</v>
       </c>
       <c r="C955" t="n">
-        <v>0.07824399999999999</v>
+        <v>0.138687</v>
       </c>
     </row>
     <row r="956">
@@ -12845,7 +12845,7 @@
         <v>463</v>
       </c>
       <c r="C956" t="n">
-        <v>0.078717</v>
+        <v>0.14186</v>
       </c>
     </row>
     <row r="957">
@@ -12858,7 +12858,7 @@
         <v>464</v>
       </c>
       <c r="C957" t="n">
-        <v>0.07914499999999999</v>
+        <v>0.148286</v>
       </c>
     </row>
     <row r="958">
@@ -12871,7 +12871,7 @@
         <v>465</v>
       </c>
       <c r="C958" t="n">
-        <v>0.081695</v>
+        <v>0.151501</v>
       </c>
     </row>
     <row r="959">
@@ -12884,7 +12884,7 @@
         <v>466</v>
       </c>
       <c r="C959" t="n">
-        <v>0.082123</v>
+        <v>0.152715</v>
       </c>
     </row>
     <row r="960">
@@ -12897,7 +12897,7 @@
         <v>467</v>
       </c>
       <c r="C960" t="n">
-        <v>0.084413</v>
+        <v>0.155988</v>
       </c>
     </row>
     <row r="961">
@@ -12910,7 +12910,7 @@
         <v>468</v>
       </c>
       <c r="C961" t="n">
-        <v>0.084914</v>
+        <v>0.157998</v>
       </c>
     </row>
     <row r="962">
@@ -12923,7 +12923,7 @@
         <v>469</v>
       </c>
       <c r="C962" t="n">
-        <v>0.09186999999999999</v>
+        <v>0.160496</v>
       </c>
     </row>
     <row r="963">
@@ -12936,7 +12936,7 @@
         <v>470</v>
       </c>
       <c r="C963" t="n">
-        <v>0.09209100000000001</v>
+        <v>0.176604</v>
       </c>
     </row>
     <row r="964">
@@ -12949,7 +12949,7 @@
         <v>471</v>
       </c>
       <c r="C964" t="n">
-        <v>0.095711</v>
+        <v>0.178572</v>
       </c>
     </row>
     <row r="965">
@@ -12962,7 +12962,7 @@
         <v>472</v>
       </c>
       <c r="C965" t="n">
-        <v>0.09672699999999999</v>
+        <v>0.180767</v>
       </c>
     </row>
     <row r="966">
@@ -12975,7 +12975,7 @@
         <v>473</v>
       </c>
       <c r="C966" t="n">
-        <v>0.100475</v>
+        <v>0.180831</v>
       </c>
     </row>
     <row r="967">
@@ -12988,7 +12988,7 @@
         <v>474</v>
       </c>
       <c r="C967" t="n">
-        <v>0.103932</v>
+        <v>0.181706</v>
       </c>
     </row>
     <row r="968">
@@ -13001,7 +13001,7 @@
         <v>475</v>
       </c>
       <c r="C968" t="n">
-        <v>0.105349</v>
+        <v>0.188004</v>
       </c>
     </row>
     <row r="969">
@@ -13014,7 +13014,7 @@
         <v>476</v>
       </c>
       <c r="C969" t="n">
-        <v>0.109188</v>
+        <v>0.203962</v>
       </c>
     </row>
     <row r="970">
@@ -13027,7 +13027,7 @@
         <v>477</v>
       </c>
       <c r="C970" t="n">
-        <v>0.110052</v>
+        <v>0.218074</v>
       </c>
     </row>
     <row r="971">
@@ -13040,7 +13040,7 @@
         <v>478</v>
       </c>
       <c r="C971" t="n">
-        <v>0.117282</v>
+        <v>0.243699</v>
       </c>
     </row>
     <row r="972">
@@ -13053,7 +13053,7 @@
         <v>479</v>
       </c>
       <c r="C972" t="n">
-        <v>0.122239</v>
+        <v>0.245528</v>
       </c>
     </row>
     <row r="973">
@@ -13066,7 +13066,7 @@
         <v>480</v>
       </c>
       <c r="C973" t="n">
-        <v>0.124275</v>
+        <v>0.265446</v>
       </c>
     </row>
     <row r="974">
@@ -13079,7 +13079,7 @@
         <v>481</v>
       </c>
       <c r="C974" t="n">
-        <v>0.125127</v>
+        <v>0.299569</v>
       </c>
     </row>
     <row r="975">
@@ -13092,7 +13092,7 @@
         <v>482</v>
       </c>
       <c r="C975" t="n">
-        <v>0.136168</v>
+        <v>0.317172</v>
       </c>
     </row>
     <row r="976">
@@ -13105,7 +13105,7 @@
         <v>483</v>
       </c>
       <c r="C976" t="n">
-        <v>0.157401</v>
+        <v>0.336181</v>
       </c>
     </row>
     <row r="977">
@@ -13118,7 +13118,7 @@
         <v>484</v>
       </c>
       <c r="C977" t="n">
-        <v>0.168227</v>
+        <v>0.363331</v>
       </c>
     </row>
     <row r="978">
@@ -13131,7 +13131,7 @@
         <v>485</v>
       </c>
       <c r="C978" t="n">
-        <v>0.246573</v>
+        <v>0.397879</v>
       </c>
     </row>
     <row r="979">
@@ -13144,7 +13144,7 @@
         <v>486</v>
       </c>
       <c r="C979" t="n">
-        <v>0.26908</v>
+        <v>0.410881</v>
       </c>
     </row>
     <row r="980">
@@ -13157,7 +13157,7 @@
         <v>487</v>
       </c>
       <c r="C980" t="n">
-        <v>0.282467</v>
+        <v>0.535842</v>
       </c>
     </row>
     <row r="981">
@@ -13170,7 +13170,7 @@
         <v>488</v>
       </c>
       <c r="C981" t="n">
-        <v>0.29084</v>
+        <v>0.682508</v>
       </c>
     </row>
     <row r="982">
@@ -13183,7 +13183,7 @@
         <v>489</v>
       </c>
       <c r="C982" t="n">
-        <v>0.310317</v>
+        <v>0.958378</v>
       </c>
     </row>
     <row r="983">
@@ -13196,7 +13196,7 @@
         <v>490</v>
       </c>
       <c r="C983" t="n">
-        <v>0.424287</v>
+        <v>0.968929</v>
       </c>
     </row>
   </sheetData>

--- a/vignettes/vignette-1/distribution_plot_data.xlsx
+++ b/vignettes/vignette-1/distribution_plot_data.xlsx
@@ -10700,7 +10700,7 @@
         <v>0</v>
       </c>
       <c r="C791" t="n">
-        <v>-0.554482</v>
+        <v>-0.513624</v>
       </c>
     </row>
     <row r="792">
@@ -10713,7 +10713,7 @@
         <v>1</v>
       </c>
       <c r="C792" t="n">
-        <v>-0.520149</v>
+        <v>-0.44755</v>
       </c>
     </row>
     <row r="793">
@@ -10726,7 +10726,7 @@
         <v>2</v>
       </c>
       <c r="C793" t="n">
-        <v>-0.444009</v>
+        <v>-0.443847</v>
       </c>
     </row>
     <row r="794">
@@ -10739,7 +10739,7 @@
         <v>3</v>
       </c>
       <c r="C794" t="n">
-        <v>-0.382724</v>
+        <v>-0.361805</v>
       </c>
     </row>
     <row r="795">
@@ -10752,7 +10752,7 @@
         <v>4</v>
       </c>
       <c r="C795" t="n">
-        <v>-0.366799</v>
+        <v>-0.340637</v>
       </c>
     </row>
     <row r="796">
@@ -10765,7 +10765,7 @@
         <v>5</v>
       </c>
       <c r="C796" t="n">
-        <v>-0.358385</v>
+        <v>-0.333913</v>
       </c>
     </row>
     <row r="797">
@@ -10778,7 +10778,7 @@
         <v>6</v>
       </c>
       <c r="C797" t="n">
-        <v>-0.318614</v>
+        <v>-0.320131</v>
       </c>
     </row>
     <row r="798">
@@ -10791,7 +10791,7 @@
         <v>7</v>
       </c>
       <c r="C798" t="n">
-        <v>-0.314779</v>
+        <v>-0.316197</v>
       </c>
     </row>
     <row r="799">
@@ -10804,7 +10804,7 @@
         <v>8</v>
       </c>
       <c r="C799" t="n">
-        <v>-0.26676</v>
+        <v>-0.263503</v>
       </c>
     </row>
     <row r="800">
@@ -10817,7 +10817,7 @@
         <v>9</v>
       </c>
       <c r="C800" t="n">
-        <v>-0.228984</v>
+        <v>-0.222762</v>
       </c>
     </row>
     <row r="801">
@@ -10830,7 +10830,7 @@
         <v>10</v>
       </c>
       <c r="C801" t="n">
-        <v>-0.223503</v>
+        <v>-0.21747</v>
       </c>
     </row>
     <row r="802">
@@ -10843,7 +10843,7 @@
         <v>11</v>
       </c>
       <c r="C802" t="n">
-        <v>-0.21519</v>
+        <v>-0.214694</v>
       </c>
     </row>
     <row r="803">
@@ -10856,7 +10856,7 @@
         <v>12</v>
       </c>
       <c r="C803" t="n">
-        <v>-0.211048</v>
+        <v>-0.210894</v>
       </c>
     </row>
     <row r="804">
@@ -10869,7 +10869,7 @@
         <v>13</v>
       </c>
       <c r="C804" t="n">
-        <v>-0.20904</v>
+        <v>-0.207484</v>
       </c>
     </row>
     <row r="805">
@@ -10882,7 +10882,7 @@
         <v>14</v>
       </c>
       <c r="C805" t="n">
-        <v>-0.20417</v>
+        <v>-0.203886</v>
       </c>
     </row>
     <row r="806">
@@ -10895,7 +10895,7 @@
         <v>15</v>
       </c>
       <c r="C806" t="n">
-        <v>-0.200103</v>
+        <v>-0.197424</v>
       </c>
     </row>
     <row r="807">
@@ -10908,7 +10908,7 @@
         <v>16</v>
       </c>
       <c r="C807" t="n">
-        <v>-0.187716</v>
+        <v>-0.190277</v>
       </c>
     </row>
     <row r="808">
@@ -10921,7 +10921,7 @@
         <v>17</v>
       </c>
       <c r="C808" t="n">
-        <v>-0.179867</v>
+        <v>-0.179568</v>
       </c>
     </row>
     <row r="809">
@@ -10934,7 +10934,7 @@
         <v>18</v>
       </c>
       <c r="C809" t="n">
-        <v>-0.171592</v>
+        <v>-0.166292</v>
       </c>
     </row>
     <row r="810">
@@ -10947,7 +10947,7 @@
         <v>19</v>
       </c>
       <c r="C810" t="n">
-        <v>-0.164787</v>
+        <v>-0.162812</v>
       </c>
     </row>
     <row r="811">
@@ -10960,7 +10960,7 @@
         <v>20</v>
       </c>
       <c r="C811" t="n">
-        <v>-0.158071</v>
+        <v>-0.157617</v>
       </c>
     </row>
     <row r="812">
@@ -10973,7 +10973,7 @@
         <v>21</v>
       </c>
       <c r="C812" t="n">
-        <v>-0.156037</v>
+        <v>-0.156066</v>
       </c>
     </row>
     <row r="813">
@@ -10986,7 +10986,7 @@
         <v>22</v>
       </c>
       <c r="C813" t="n">
-        <v>-0.144747</v>
+        <v>-0.145024</v>
       </c>
     </row>
     <row r="814">
@@ -10999,7 +10999,7 @@
         <v>23</v>
       </c>
       <c r="C814" t="n">
-        <v>-0.137877</v>
+        <v>-0.137297</v>
       </c>
     </row>
     <row r="815">
@@ -11012,7 +11012,7 @@
         <v>24</v>
       </c>
       <c r="C815" t="n">
-        <v>-0.133741</v>
+        <v>-0.13617</v>
       </c>
     </row>
     <row r="816">
@@ -11025,7 +11025,7 @@
         <v>25</v>
       </c>
       <c r="C816" t="n">
-        <v>-0.129266</v>
+        <v>-0.128377</v>
       </c>
     </row>
     <row r="817">
@@ -11038,7 +11038,7 @@
         <v>26</v>
       </c>
       <c r="C817" t="n">
-        <v>-0.128069</v>
+        <v>-0.128031</v>
       </c>
     </row>
     <row r="818">
@@ -11051,7 +11051,7 @@
         <v>27</v>
       </c>
       <c r="C818" t="n">
-        <v>-0.12474</v>
+        <v>-0.124162</v>
       </c>
     </row>
     <row r="819">
@@ -11064,7 +11064,7 @@
         <v>28</v>
       </c>
       <c r="C819" t="n">
-        <v>-0.123134</v>
+        <v>-0.121709</v>
       </c>
     </row>
     <row r="820">
@@ -11077,7 +11077,7 @@
         <v>29</v>
       </c>
       <c r="C820" t="n">
-        <v>-0.121327</v>
+        <v>-0.121092</v>
       </c>
     </row>
     <row r="821">
@@ -11090,7 +11090,7 @@
         <v>30</v>
       </c>
       <c r="C821" t="n">
-        <v>-0.120951</v>
+        <v>-0.120421</v>
       </c>
     </row>
     <row r="822">
@@ -11103,7 +11103,7 @@
         <v>31</v>
       </c>
       <c r="C822" t="n">
-        <v>-0.120561</v>
+        <v>-0.118742</v>
       </c>
     </row>
     <row r="823">
@@ -11116,7 +11116,7 @@
         <v>32</v>
       </c>
       <c r="C823" t="n">
-        <v>-0.120561</v>
+        <v>-0.118742</v>
       </c>
     </row>
     <row r="824">
@@ -11129,7 +11129,7 @@
         <v>33</v>
       </c>
       <c r="C824" t="n">
-        <v>-0.119056</v>
+        <v>-0.118433</v>
       </c>
     </row>
     <row r="825">
@@ -11142,7 +11142,7 @@
         <v>34</v>
       </c>
       <c r="C825" t="n">
-        <v>-0.11814</v>
+        <v>-0.11757</v>
       </c>
     </row>
     <row r="826">
@@ -11155,7 +11155,7 @@
         <v>35</v>
       </c>
       <c r="C826" t="n">
-        <v>-0.114284</v>
+        <v>-0.115379</v>
       </c>
     </row>
     <row r="827">
@@ -11168,7 +11168,7 @@
         <v>36</v>
       </c>
       <c r="C827" t="n">
-        <v>-0.110816</v>
+        <v>-0.110053</v>
       </c>
     </row>
     <row r="828">
@@ -11181,7 +11181,7 @@
         <v>37</v>
       </c>
       <c r="C828" t="n">
-        <v>-0.110259</v>
+        <v>-0.109207</v>
       </c>
     </row>
     <row r="829">
@@ -11194,7 +11194,7 @@
         <v>38</v>
       </c>
       <c r="C829" t="n">
-        <v>-0.109677</v>
+        <v>-0.107936</v>
       </c>
     </row>
     <row r="830">
@@ -11207,7 +11207,7 @@
         <v>39</v>
       </c>
       <c r="C830" t="n">
-        <v>-0.108616</v>
+        <v>-0.104428</v>
       </c>
     </row>
     <row r="831">
@@ -11220,7 +11220,7 @@
         <v>40</v>
       </c>
       <c r="C831" t="n">
-        <v>-0.107735</v>
+        <v>-0.102343</v>
       </c>
     </row>
     <row r="832">
@@ -11233,7 +11233,7 @@
         <v>41</v>
       </c>
       <c r="C832" t="n">
-        <v>-0.105621</v>
+        <v>-0.100468</v>
       </c>
     </row>
     <row r="833">
@@ -11246,7 +11246,7 @@
         <v>42</v>
       </c>
       <c r="C833" t="n">
-        <v>-0.102504</v>
+        <v>-0.09761499999999999</v>
       </c>
     </row>
     <row r="834">
@@ -11259,7 +11259,7 @@
         <v>43</v>
       </c>
       <c r="C834" t="n">
-        <v>-0.102365</v>
+        <v>-0.097568</v>
       </c>
     </row>
     <row r="835">
@@ -11272,7 +11272,7 @@
         <v>44</v>
       </c>
       <c r="C835" t="n">
-        <v>-0.100414</v>
+        <v>-0.09754400000000001</v>
       </c>
     </row>
     <row r="836">
@@ -11285,7 +11285,7 @@
         <v>45</v>
       </c>
       <c r="C836" t="n">
-        <v>-0.09987699999999999</v>
+        <v>-0.096687</v>
       </c>
     </row>
     <row r="837">
@@ -11298,7 +11298,7 @@
         <v>46</v>
       </c>
       <c r="C837" t="n">
-        <v>-0.099025</v>
+        <v>-0.095608</v>
       </c>
     </row>
     <row r="838">
@@ -11311,7 +11311,7 @@
         <v>47</v>
       </c>
       <c r="C838" t="n">
-        <v>-0.098814</v>
+        <v>-0.094983</v>
       </c>
     </row>
     <row r="839">
@@ -11324,7 +11324,7 @@
         <v>48</v>
       </c>
       <c r="C839" t="n">
-        <v>-0.098429</v>
+        <v>-0.09439699999999999</v>
       </c>
     </row>
     <row r="840">
@@ -11337,7 +11337,7 @@
         <v>49</v>
       </c>
       <c r="C840" t="n">
-        <v>-0.09638099999999999</v>
+        <v>-0.09395100000000001</v>
       </c>
     </row>
     <row r="841">
@@ -11350,7 +11350,7 @@
         <v>50</v>
       </c>
       <c r="C841" t="n">
-        <v>-0.096114</v>
+        <v>-0.093124</v>
       </c>
     </row>
     <row r="842">
@@ -11363,7 +11363,7 @@
         <v>51</v>
       </c>
       <c r="C842" t="n">
-        <v>-0.094572</v>
+        <v>-0.092517</v>
       </c>
     </row>
     <row r="843">
@@ -11376,7 +11376,7 @@
         <v>52</v>
       </c>
       <c r="C843" t="n">
-        <v>-0.094092</v>
+        <v>-0.09053</v>
       </c>
     </row>
     <row r="844">
@@ -11389,7 +11389,7 @@
         <v>53</v>
       </c>
       <c r="C844" t="n">
-        <v>-0.09386700000000001</v>
+        <v>-0.089846</v>
       </c>
     </row>
     <row r="845">
@@ -11402,7 +11402,7 @@
         <v>54</v>
       </c>
       <c r="C845" t="n">
-        <v>-0.09213</v>
+        <v>-0.08945400000000001</v>
       </c>
     </row>
     <row r="846">
@@ -11415,7 +11415,7 @@
         <v>55</v>
       </c>
       <c r="C846" t="n">
-        <v>-0.091419</v>
+        <v>-0.089334</v>
       </c>
     </row>
     <row r="847">
@@ -11428,7 +11428,7 @@
         <v>56</v>
       </c>
       <c r="C847" t="n">
-        <v>-0.089021</v>
+        <v>-0.086508</v>
       </c>
     </row>
     <row r="848">
@@ -11441,7 +11441,7 @@
         <v>57</v>
       </c>
       <c r="C848" t="n">
-        <v>-0.088965</v>
+        <v>-0.086352</v>
       </c>
     </row>
     <row r="849">
@@ -11454,7 +11454,7 @@
         <v>58</v>
       </c>
       <c r="C849" t="n">
-        <v>-0.088757</v>
+        <v>-0.085254</v>
       </c>
     </row>
     <row r="850">
@@ -11467,7 +11467,7 @@
         <v>59</v>
       </c>
       <c r="C850" t="n">
-        <v>-0.08604000000000001</v>
+        <v>-0.085123</v>
       </c>
     </row>
     <row r="851">
@@ -11480,7 +11480,7 @@
         <v>60</v>
       </c>
       <c r="C851" t="n">
-        <v>-0.08599900000000001</v>
+        <v>-0.081175</v>
       </c>
     </row>
     <row r="852">
@@ -11493,7 +11493,7 @@
         <v>61</v>
       </c>
       <c r="C852" t="n">
-        <v>-0.08505</v>
+        <v>-0.080056</v>
       </c>
     </row>
     <row r="853">
@@ -11506,7 +11506,7 @@
         <v>62</v>
       </c>
       <c r="C853" t="n">
-        <v>-0.081708</v>
+        <v>-0.079097</v>
       </c>
     </row>
     <row r="854">
@@ -11519,7 +11519,7 @@
         <v>63</v>
       </c>
       <c r="C854" t="n">
-        <v>-0.079759</v>
+        <v>-0.076193</v>
       </c>
     </row>
     <row r="855">
@@ -11532,7 +11532,7 @@
         <v>64</v>
       </c>
       <c r="C855" t="n">
-        <v>-0.076742</v>
+        <v>-0.07592699999999999</v>
       </c>
     </row>
     <row r="856">
@@ -11545,7 +11545,7 @@
         <v>65</v>
       </c>
       <c r="C856" t="n">
-        <v>-0.07671500000000001</v>
+        <v>-0.07553</v>
       </c>
     </row>
     <row r="857">
@@ -11558,7 +11558,7 @@
         <v>66</v>
       </c>
       <c r="C857" t="n">
-        <v>-0.07498199999999999</v>
+        <v>-0.074236</v>
       </c>
     </row>
     <row r="858">
@@ -11571,7 +11571,7 @@
         <v>67</v>
       </c>
       <c r="C858" t="n">
-        <v>-0.07470499999999999</v>
+        <v>-0.073519</v>
       </c>
     </row>
     <row r="859">
@@ -11584,7 +11584,7 @@
         <v>68</v>
       </c>
       <c r="C859" t="n">
-        <v>-0.07315199999999999</v>
+        <v>-0.072782</v>
       </c>
     </row>
     <row r="860">
@@ -11597,7 +11597,7 @@
         <v>69</v>
       </c>
       <c r="C860" t="n">
-        <v>-0.072657</v>
+        <v>-0.072322</v>
       </c>
     </row>
     <row r="861">
@@ -11610,7 +11610,7 @@
         <v>70</v>
       </c>
       <c r="C861" t="n">
-        <v>-0.072578</v>
+        <v>-0.07151299999999999</v>
       </c>
     </row>
     <row r="862">
@@ -11623,7 +11623,7 @@
         <v>71</v>
       </c>
       <c r="C862" t="n">
-        <v>-0.072149</v>
+        <v>-0.07117999999999999</v>
       </c>
     </row>
     <row r="863">
@@ -11636,7 +11636,7 @@
         <v>72</v>
       </c>
       <c r="C863" t="n">
-        <v>-0.07065</v>
+        <v>-0.06990399999999999</v>
       </c>
     </row>
     <row r="864">
@@ -11649,7 +11649,7 @@
         <v>73</v>
       </c>
       <c r="C864" t="n">
-        <v>-0.070261</v>
+        <v>-0.068289</v>
       </c>
     </row>
     <row r="865">
@@ -11662,7 +11662,7 @@
         <v>74</v>
       </c>
       <c r="C865" t="n">
-        <v>-0.069574</v>
+        <v>-0.067953</v>
       </c>
     </row>
     <row r="866">
@@ -11675,7 +11675,7 @@
         <v>75</v>
       </c>
       <c r="C866" t="n">
-        <v>-0.06897499999999999</v>
+        <v>-0.067736</v>
       </c>
     </row>
     <row r="867">
@@ -11688,7 +11688,7 @@
         <v>76</v>
       </c>
       <c r="C867" t="n">
-        <v>-0.06715</v>
+        <v>-0.066941</v>
       </c>
     </row>
     <row r="868">
@@ -11701,7 +11701,7 @@
         <v>77</v>
       </c>
       <c r="C868" t="n">
-        <v>-0.06639399999999999</v>
+        <v>-0.06668399999999999</v>
       </c>
     </row>
     <row r="869">
@@ -11714,7 +11714,7 @@
         <v>78</v>
       </c>
       <c r="C869" t="n">
-        <v>-0.06639399999999999</v>
+        <v>-0.066526</v>
       </c>
     </row>
     <row r="870">
@@ -11727,7 +11727,7 @@
         <v>79</v>
       </c>
       <c r="C870" t="n">
-        <v>-0.06612700000000001</v>
+        <v>-0.066223</v>
       </c>
     </row>
     <row r="871">
@@ -11740,7 +11740,7 @@
         <v>80</v>
       </c>
       <c r="C871" t="n">
-        <v>-0.065791</v>
+        <v>-0.066042</v>
       </c>
     </row>
     <row r="872">
@@ -11753,7 +11753,7 @@
         <v>81</v>
       </c>
       <c r="C872" t="n">
-        <v>-0.065401</v>
+        <v>-0.065751</v>
       </c>
     </row>
     <row r="873">
@@ -11766,7 +11766,7 @@
         <v>82</v>
       </c>
       <c r="C873" t="n">
-        <v>-0.06474100000000001</v>
+        <v>-0.064605</v>
       </c>
     </row>
     <row r="874">
@@ -11779,7 +11779,7 @@
         <v>83</v>
       </c>
       <c r="C874" t="n">
-        <v>-0.06394</v>
+        <v>-0.063996</v>
       </c>
     </row>
     <row r="875">
@@ -11792,7 +11792,7 @@
         <v>84</v>
       </c>
       <c r="C875" t="n">
-        <v>-0.062834</v>
+        <v>-0.06314</v>
       </c>
     </row>
     <row r="876">
@@ -11805,7 +11805,7 @@
         <v>85</v>
       </c>
       <c r="C876" t="n">
-        <v>-0.06257799999999999</v>
+        <v>-0.061625</v>
       </c>
     </row>
     <row r="877">
@@ -11818,7 +11818,7 @@
         <v>86</v>
       </c>
       <c r="C877" t="n">
-        <v>-0.061768</v>
+        <v>-0.061078</v>
       </c>
     </row>
     <row r="878">
@@ -11831,7 +11831,7 @@
         <v>87</v>
       </c>
       <c r="C878" t="n">
-        <v>-0.060868</v>
+        <v>-0.060533</v>
       </c>
     </row>
     <row r="879">
@@ -11844,7 +11844,7 @@
         <v>88</v>
       </c>
       <c r="C879" t="n">
-        <v>-0.060654</v>
+        <v>-0.059765</v>
       </c>
     </row>
     <row r="880">
@@ -11857,7 +11857,7 @@
         <v>89</v>
       </c>
       <c r="C880" t="n">
-        <v>-0.060071</v>
+        <v>-0.059478</v>
       </c>
     </row>
     <row r="881">
@@ -11870,7 +11870,7 @@
         <v>90</v>
       </c>
       <c r="C881" t="n">
-        <v>-0.059989</v>
+        <v>-0.059431</v>
       </c>
     </row>
     <row r="882">
@@ -11883,7 +11883,7 @@
         <v>91</v>
       </c>
       <c r="C882" t="n">
-        <v>-0.059752</v>
+        <v>-0.05874</v>
       </c>
     </row>
     <row r="883">
@@ -11896,7 +11896,7 @@
         <v>92</v>
       </c>
       <c r="C883" t="n">
-        <v>-0.059593</v>
+        <v>-0.057879</v>
       </c>
     </row>
     <row r="884">
@@ -11909,7 +11909,7 @@
         <v>93</v>
       </c>
       <c r="C884" t="n">
-        <v>-0.059114</v>
+        <v>-0.057083</v>
       </c>
     </row>
     <row r="885">
@@ -11922,7 +11922,7 @@
         <v>94</v>
       </c>
       <c r="C885" t="n">
-        <v>-0.058783</v>
+        <v>-0.057064</v>
       </c>
     </row>
     <row r="886">
@@ -11935,7 +11935,7 @@
         <v>95</v>
       </c>
       <c r="C886" t="n">
-        <v>-0.058758</v>
+        <v>-0.056901</v>
       </c>
     </row>
     <row r="887">
@@ -11948,7 +11948,7 @@
         <v>96</v>
       </c>
       <c r="C887" t="n">
-        <v>-0.058666</v>
+        <v>-0.056349</v>
       </c>
     </row>
     <row r="888">
@@ -11961,7 +11961,7 @@
         <v>97</v>
       </c>
       <c r="C888" t="n">
-        <v>-0.058563</v>
+        <v>-0.056296</v>
       </c>
     </row>
     <row r="889">
@@ -11974,7 +11974,7 @@
         <v>98</v>
       </c>
       <c r="C889" t="n">
-        <v>-0.058448</v>
+        <v>-0.05574</v>
       </c>
     </row>
     <row r="890">
@@ -11987,7 +11987,7 @@
         <v>99</v>
       </c>
       <c r="C890" t="n">
-        <v>-0.057863</v>
+        <v>-0.055737</v>
       </c>
     </row>
     <row r="891">
@@ -12000,7 +12000,7 @@
         <v>100</v>
       </c>
       <c r="C891" t="n">
-        <v>-0.057032</v>
+        <v>-0.055687</v>
       </c>
     </row>
     <row r="892">
@@ -12013,7 +12013,7 @@
         <v>101</v>
       </c>
       <c r="C892" t="n">
-        <v>-0.056492</v>
+        <v>-0.055634</v>
       </c>
     </row>
     <row r="893">
@@ -12026,7 +12026,7 @@
         <v>102</v>
       </c>
       <c r="C893" t="n">
-        <v>-0.056205</v>
+        <v>-0.055335</v>
       </c>
     </row>
     <row r="894">
@@ -12039,7 +12039,7 @@
         <v>103</v>
       </c>
       <c r="C894" t="n">
-        <v>-0.056099</v>
+        <v>-0.055317</v>
       </c>
     </row>
     <row r="895">
@@ -12052,7 +12052,7 @@
         <v>104</v>
       </c>
       <c r="C895" t="n">
-        <v>-0.055863</v>
+        <v>-0.05521</v>
       </c>
     </row>
     <row r="896">
@@ -12065,7 +12065,7 @@
         <v>105</v>
       </c>
       <c r="C896" t="n">
-        <v>-0.055302</v>
+        <v>-0.054589</v>
       </c>
     </row>
     <row r="897">
@@ -12078,7 +12078,7 @@
         <v>106</v>
       </c>
       <c r="C897" t="n">
-        <v>-0.055138</v>
+        <v>-0.054565</v>
       </c>
     </row>
     <row r="898">
@@ -12091,7 +12091,7 @@
         <v>107</v>
       </c>
       <c r="C898" t="n">
-        <v>-0.054354</v>
+        <v>-0.053891</v>
       </c>
     </row>
     <row r="899">
@@ -12104,7 +12104,7 @@
         <v>108</v>
       </c>
       <c r="C899" t="n">
-        <v>-0.054337</v>
+        <v>-0.053544</v>
       </c>
     </row>
     <row r="900">
@@ -12117,7 +12117,7 @@
         <v>109</v>
       </c>
       <c r="C900" t="n">
-        <v>-0.053898</v>
+        <v>-0.05317</v>
       </c>
     </row>
     <row r="901">
@@ -12130,7 +12130,7 @@
         <v>110</v>
       </c>
       <c r="C901" t="n">
-        <v>-0.053688</v>
+        <v>-0.052762</v>
       </c>
     </row>
     <row r="902">
@@ -12143,7 +12143,7 @@
         <v>111</v>
       </c>
       <c r="C902" t="n">
-        <v>-0.053091</v>
+        <v>-0.052545</v>
       </c>
     </row>
     <row r="903">
@@ -12156,7 +12156,7 @@
         <v>112</v>
       </c>
       <c r="C903" t="n">
-        <v>-0.053079</v>
+        <v>-0.052421</v>
       </c>
     </row>
     <row r="904">
@@ -12169,7 +12169,7 @@
         <v>113</v>
       </c>
       <c r="C904" t="n">
-        <v>-0.052737</v>
+        <v>-0.052171</v>
       </c>
     </row>
     <row r="905">
@@ -12182,7 +12182,7 @@
         <v>114</v>
       </c>
       <c r="C905" t="n">
-        <v>-0.051857</v>
+        <v>-0.052109</v>
       </c>
     </row>
     <row r="906">
@@ -12195,7 +12195,7 @@
         <v>115</v>
       </c>
       <c r="C906" t="n">
-        <v>-0.051768</v>
+        <v>-0.051655</v>
       </c>
     </row>
     <row r="907">
@@ -12208,7 +12208,7 @@
         <v>116</v>
       </c>
       <c r="C907" t="n">
-        <v>-0.051698</v>
+        <v>-0.05155</v>
       </c>
     </row>
     <row r="908">
@@ -12221,7 +12221,7 @@
         <v>117</v>
       </c>
       <c r="C908" t="n">
-        <v>-0.051629</v>
+        <v>-0.05144</v>
       </c>
     </row>
     <row r="909">
@@ -12234,7 +12234,7 @@
         <v>118</v>
       </c>
       <c r="C909" t="n">
-        <v>-0.051577</v>
+        <v>-0.051414</v>
       </c>
     </row>
     <row r="910">
@@ -12247,7 +12247,7 @@
         <v>119</v>
       </c>
       <c r="C910" t="n">
-        <v>-0.051493</v>
+        <v>-0.051338</v>
       </c>
     </row>
     <row r="911">
@@ -12260,7 +12260,7 @@
         <v>120</v>
       </c>
       <c r="C911" t="n">
-        <v>-0.051195</v>
+        <v>-0.051121</v>
       </c>
     </row>
     <row r="912">
@@ -12273,7 +12273,7 @@
         <v>121</v>
       </c>
       <c r="C912" t="n">
-        <v>-0.050775</v>
+        <v>-0.050246</v>
       </c>
     </row>
     <row r="913">
@@ -12286,7 +12286,7 @@
         <v>122</v>
       </c>
       <c r="C913" t="n">
-        <v>-0.050063</v>
+        <v>-0.049903</v>
       </c>
     </row>
     <row r="914">
@@ -12299,7 +12299,7 @@
         <v>123</v>
       </c>
       <c r="C914" t="n">
-        <v>-0.049896</v>
+        <v>-0.049576</v>
       </c>
     </row>
     <row r="915">
@@ -12312,7 +12312,7 @@
         <v>124</v>
       </c>
       <c r="C915" t="n">
-        <v>-0.049662</v>
+        <v>-0.049207</v>
       </c>
     </row>
     <row r="916">
@@ -12325,7 +12325,7 @@
         <v>125</v>
       </c>
       <c r="C916" t="n">
-        <v>-0.049578</v>
+        <v>-0.049176</v>
       </c>
     </row>
     <row r="917">
@@ -12338,7 +12338,7 @@
         <v>126</v>
       </c>
       <c r="C917" t="n">
-        <v>-0.049266</v>
+        <v>-0.048733</v>
       </c>
     </row>
     <row r="918">
@@ -12351,7 +12351,7 @@
         <v>127</v>
       </c>
       <c r="C918" t="n">
-        <v>-0.048906</v>
+        <v>-0.048722</v>
       </c>
     </row>
     <row r="919">
@@ -12364,7 +12364,7 @@
         <v>128</v>
       </c>
       <c r="C919" t="n">
-        <v>-0.048664</v>
+        <v>-0.048294</v>
       </c>
     </row>
     <row r="920">
@@ -12377,7 +12377,7 @@
         <v>129</v>
       </c>
       <c r="C920" t="n">
-        <v>-0.048425</v>
+        <v>-0.047353</v>
       </c>
     </row>
     <row r="921">
@@ -12390,7 +12390,7 @@
         <v>130</v>
       </c>
       <c r="C921" t="n">
-        <v>-0.048367</v>
+        <v>-0.047165</v>
       </c>
     </row>
     <row r="922">
@@ -12403,7 +12403,7 @@
         <v>131</v>
       </c>
       <c r="C922" t="n">
-        <v>-0.048254</v>
+        <v>-0.04696</v>
       </c>
     </row>
     <row r="923">
@@ -12416,7 +12416,7 @@
         <v>132</v>
       </c>
       <c r="C923" t="n">
-        <v>-0.047426</v>
+        <v>-0.046869</v>
       </c>
     </row>
     <row r="924">
@@ -12429,7 +12429,7 @@
         <v>133</v>
       </c>
       <c r="C924" t="n">
-        <v>-0.047139</v>
+        <v>-0.046393</v>
       </c>
     </row>
     <row r="925">
@@ -12442,7 +12442,7 @@
         <v>134</v>
       </c>
       <c r="C925" t="n">
-        <v>-0.046996</v>
+        <v>-0.044963</v>
       </c>
     </row>
     <row r="926">
@@ -12455,7 +12455,7 @@
         <v>135</v>
       </c>
       <c r="C926" t="n">
-        <v>-0.046684</v>
+        <v>-0.044774</v>
       </c>
     </row>
     <row r="927">
@@ -12468,7 +12468,7 @@
         <v>136</v>
       </c>
       <c r="C927" t="n">
-        <v>-0.046615</v>
+        <v>-0.044248</v>
       </c>
     </row>
     <row r="928">
@@ -12481,7 +12481,7 @@
         <v>137</v>
       </c>
       <c r="C928" t="n">
-        <v>-0.046248</v>
+        <v>-0.044228</v>
       </c>
     </row>
     <row r="929">
@@ -12494,7 +12494,7 @@
         <v>138</v>
       </c>
       <c r="C929" t="n">
-        <v>-0.045331</v>
+        <v>-0.044141</v>
       </c>
     </row>
     <row r="930">
@@ -12507,7 +12507,7 @@
         <v>139</v>
       </c>
       <c r="C930" t="n">
-        <v>-0.044995</v>
+        <v>-0.043431</v>
       </c>
     </row>
     <row r="931">
@@ -12520,7 +12520,7 @@
         <v>140</v>
       </c>
       <c r="C931" t="n">
-        <v>-0.044449</v>
+        <v>-0.043396</v>
       </c>
     </row>
     <row r="932">
@@ -12533,7 +12533,7 @@
         <v>141</v>
       </c>
       <c r="C932" t="n">
-        <v>-0.044128</v>
+        <v>-0.043107</v>
       </c>
     </row>
     <row r="933">
@@ -12546,7 +12546,7 @@
         <v>142</v>
       </c>
       <c r="C933" t="n">
-        <v>-0.044031</v>
+        <v>-0.043016</v>
       </c>
     </row>
     <row r="934">
@@ -12559,7 +12559,7 @@
         <v>143</v>
       </c>
       <c r="C934" t="n">
-        <v>-0.043706</v>
+        <v>-0.04297</v>
       </c>
     </row>
     <row r="935">
@@ -12572,7 +12572,7 @@
         <v>144</v>
       </c>
       <c r="C935" t="n">
-        <v>-0.043154</v>
+        <v>-0.042767</v>
       </c>
     </row>
     <row r="936">
@@ -12585,7 +12585,7 @@
         <v>145</v>
       </c>
       <c r="C936" t="n">
-        <v>-0.043108</v>
+        <v>-0.042669</v>
       </c>
     </row>
     <row r="937">
@@ -12598,7 +12598,7 @@
         <v>146</v>
       </c>
       <c r="C937" t="n">
-        <v>-0.043079</v>
+        <v>-0.042636</v>
       </c>
     </row>
     <row r="938">
@@ -12611,7 +12611,7 @@
         <v>147</v>
       </c>
       <c r="C938" t="n">
-        <v>-0.042826</v>
+        <v>-0.042493</v>
       </c>
     </row>
     <row r="939">
@@ -12624,7 +12624,7 @@
         <v>148</v>
       </c>
       <c r="C939" t="n">
-        <v>-0.042625</v>
+        <v>-0.04194</v>
       </c>
     </row>
     <row r="940">
@@ -12637,7 +12637,7 @@
         <v>149</v>
       </c>
       <c r="C940" t="n">
-        <v>-0.042607</v>
+        <v>-0.04177</v>
       </c>
     </row>
     <row r="941">
@@ -12650,7 +12650,7 @@
         <v>150</v>
       </c>
       <c r="C941" t="n">
-        <v>-0.042286</v>
+        <v>-0.04126</v>
       </c>
     </row>
     <row r="942">
@@ -12663,7 +12663,7 @@
         <v>151</v>
       </c>
       <c r="C942" t="n">
-        <v>-0.042286</v>
+        <v>-0.041118</v>
       </c>
     </row>
     <row r="943">
@@ -12676,7 +12676,7 @@
         <v>152</v>
       </c>
       <c r="C943" t="n">
-        <v>-0.041553</v>
+        <v>-0.040928</v>
       </c>
     </row>
     <row r="944">
@@ -12689,7 +12689,7 @@
         <v>153</v>
       </c>
       <c r="C944" t="n">
-        <v>-0.041304</v>
+        <v>-0.040821</v>
       </c>
     </row>
     <row r="945">
@@ -12702,7 +12702,7 @@
         <v>154</v>
       </c>
       <c r="C945" t="n">
-        <v>-0.040902</v>
+        <v>-0.040695</v>
       </c>
     </row>
     <row r="946">
@@ -12715,7 +12715,7 @@
         <v>155</v>
       </c>
       <c r="C946" t="n">
-        <v>-0.040646</v>
+        <v>-0.039552</v>
       </c>
     </row>
     <row r="947">
@@ -12728,7 +12728,7 @@
         <v>156</v>
       </c>
       <c r="C947" t="n">
-        <v>-0.040622</v>
+        <v>-0.038569</v>
       </c>
     </row>
     <row r="948">
@@ -12741,7 +12741,7 @@
         <v>157</v>
       </c>
       <c r="C948" t="n">
-        <v>-0.040374</v>
+        <v>-0.038507</v>
       </c>
     </row>
     <row r="949">
@@ -12754,7 +12754,7 @@
         <v>158</v>
       </c>
       <c r="C949" t="n">
-        <v>-0.038572</v>
+        <v>-0.038352</v>
       </c>
     </row>
     <row r="950">
@@ -12767,7 +12767,7 @@
         <v>159</v>
       </c>
       <c r="C950" t="n">
-        <v>-0.03853</v>
+        <v>-0.038193</v>
       </c>
     </row>
     <row r="951">
@@ -12780,7 +12780,7 @@
         <v>160</v>
       </c>
       <c r="C951" t="n">
-        <v>-0.038172</v>
+        <v>-0.037963</v>
       </c>
     </row>
     <row r="952">
@@ -12793,7 +12793,7 @@
         <v>161</v>
       </c>
       <c r="C952" t="n">
-        <v>-0.038085</v>
+        <v>-0.037954</v>
       </c>
     </row>
     <row r="953">
@@ -12806,7 +12806,7 @@
         <v>162</v>
       </c>
       <c r="C953" t="n">
-        <v>-0.037689</v>
+        <v>-0.037764</v>
       </c>
     </row>
     <row r="954">
@@ -12819,7 +12819,7 @@
         <v>163</v>
       </c>
       <c r="C954" t="n">
-        <v>-0.037641</v>
+        <v>-0.037446</v>
       </c>
     </row>
     <row r="955">
@@ -12832,7 +12832,7 @@
         <v>164</v>
       </c>
       <c r="C955" t="n">
-        <v>-0.03764</v>
+        <v>-0.036939</v>
       </c>
     </row>
     <row r="956">
@@ -12845,7 +12845,7 @@
         <v>165</v>
       </c>
       <c r="C956" t="n">
-        <v>-0.037434</v>
+        <v>-0.035463</v>
       </c>
     </row>
     <row r="957">
@@ -12858,7 +12858,7 @@
         <v>166</v>
       </c>
       <c r="C957" t="n">
-        <v>-0.037256</v>
+        <v>-0.035402</v>
       </c>
     </row>
     <row r="958">
@@ -12871,7 +12871,7 @@
         <v>167</v>
       </c>
       <c r="C958" t="n">
-        <v>-0.037243</v>
+        <v>-0.034189</v>
       </c>
     </row>
     <row r="959">
@@ -12884,7 +12884,7 @@
         <v>168</v>
       </c>
       <c r="C959" t="n">
-        <v>-0.036791</v>
+        <v>-0.033861</v>
       </c>
     </row>
     <row r="960">
@@ -12897,7 +12897,7 @@
         <v>169</v>
       </c>
       <c r="C960" t="n">
-        <v>-0.03556</v>
+        <v>-0.033585</v>
       </c>
     </row>
     <row r="961">
@@ -12910,7 +12910,7 @@
         <v>170</v>
       </c>
       <c r="C961" t="n">
-        <v>-0.034198</v>
+        <v>-0.033496</v>
       </c>
     </row>
     <row r="962">
@@ -12923,7 +12923,7 @@
         <v>171</v>
       </c>
       <c r="C962" t="n">
-        <v>-0.033193</v>
+        <v>-0.033477</v>
       </c>
     </row>
     <row r="963">
@@ -12936,7 +12936,7 @@
         <v>172</v>
       </c>
       <c r="C963" t="n">
-        <v>-0.033076</v>
+        <v>-0.032647</v>
       </c>
     </row>
     <row r="964">
@@ -12949,7 +12949,7 @@
         <v>173</v>
       </c>
       <c r="C964" t="n">
-        <v>-0.032963</v>
+        <v>-0.032481</v>
       </c>
     </row>
     <row r="965">
@@ -12962,7 +12962,7 @@
         <v>174</v>
       </c>
       <c r="C965" t="n">
-        <v>-0.032575</v>
+        <v>-0.032415</v>
       </c>
     </row>
     <row r="966">
@@ -12975,7 +12975,7 @@
         <v>175</v>
       </c>
       <c r="C966" t="n">
-        <v>-0.032325</v>
+        <v>-0.031784</v>
       </c>
     </row>
     <row r="967">
@@ -12988,7 +12988,7 @@
         <v>176</v>
       </c>
       <c r="C967" t="n">
-        <v>-0.032241</v>
+        <v>-0.031412</v>
       </c>
     </row>
     <row r="968">
@@ -13001,7 +13001,7 @@
         <v>177</v>
       </c>
       <c r="C968" t="n">
-        <v>-0.031108</v>
+        <v>-0.030962</v>
       </c>
     </row>
     <row r="969">
@@ -13014,7 +13014,7 @@
         <v>178</v>
       </c>
       <c r="C969" t="n">
-        <v>-0.031042</v>
+        <v>-0.030832</v>
       </c>
     </row>
     <row r="970">
@@ -13027,7 +13027,7 @@
         <v>179</v>
       </c>
       <c r="C970" t="n">
-        <v>-0.030931</v>
+        <v>-0.030221</v>
       </c>
     </row>
     <row r="971">
@@ -13040,7 +13040,7 @@
         <v>180</v>
       </c>
       <c r="C971" t="n">
-        <v>-0.030731</v>
+        <v>-0.030169</v>
       </c>
     </row>
     <row r="972">
@@ -13053,7 +13053,7 @@
         <v>181</v>
       </c>
       <c r="C972" t="n">
-        <v>-0.030285</v>
+        <v>-0.030162</v>
       </c>
     </row>
     <row r="973">
@@ -13066,7 +13066,7 @@
         <v>182</v>
       </c>
       <c r="C973" t="n">
-        <v>-0.030245</v>
+        <v>-0.029693</v>
       </c>
     </row>
     <row r="974">
@@ -13079,7 +13079,7 @@
         <v>183</v>
       </c>
       <c r="C974" t="n">
-        <v>-0.029823</v>
+        <v>-0.029537</v>
       </c>
     </row>
     <row r="975">
@@ -13092,7 +13092,7 @@
         <v>184</v>
       </c>
       <c r="C975" t="n">
-        <v>-0.029483</v>
+        <v>-0.029231</v>
       </c>
     </row>
     <row r="976">
@@ -13105,7 +13105,7 @@
         <v>185</v>
       </c>
       <c r="C976" t="n">
-        <v>-0.029452</v>
+        <v>-0.02908</v>
       </c>
     </row>
     <row r="977">
@@ -13118,7 +13118,7 @@
         <v>186</v>
       </c>
       <c r="C977" t="n">
-        <v>-0.029262</v>
+        <v>-0.028865</v>
       </c>
     </row>
     <row r="978">
@@ -13131,7 +13131,7 @@
         <v>187</v>
       </c>
       <c r="C978" t="n">
-        <v>-0.029093</v>
+        <v>-0.028754</v>
       </c>
     </row>
     <row r="979">
@@ -13144,7 +13144,7 @@
         <v>188</v>
       </c>
       <c r="C979" t="n">
-        <v>-0.028902</v>
+        <v>-0.028445</v>
       </c>
     </row>
     <row r="980">
@@ -13157,7 +13157,7 @@
         <v>189</v>
       </c>
       <c r="C980" t="n">
-        <v>-0.028854</v>
+        <v>-0.028137</v>
       </c>
     </row>
     <row r="981">
@@ -13170,7 +13170,7 @@
         <v>190</v>
       </c>
       <c r="C981" t="n">
-        <v>-0.028758</v>
+        <v>-0.027987</v>
       </c>
     </row>
     <row r="982">
@@ -13183,7 +13183,7 @@
         <v>191</v>
       </c>
       <c r="C982" t="n">
-        <v>-0.028571</v>
+        <v>-0.027976</v>
       </c>
     </row>
     <row r="983">
@@ -13196,7 +13196,7 @@
         <v>192</v>
       </c>
       <c r="C983" t="n">
-        <v>-0.028461</v>
+        <v>-0.027922</v>
       </c>
     </row>
     <row r="984">
@@ -13209,7 +13209,7 @@
         <v>193</v>
       </c>
       <c r="C984" t="n">
-        <v>-0.028109</v>
+        <v>-0.027883</v>
       </c>
     </row>
     <row r="985">
@@ -13222,7 +13222,7 @@
         <v>194</v>
       </c>
       <c r="C985" t="n">
-        <v>-0.027912</v>
+        <v>-0.027734</v>
       </c>
     </row>
     <row r="986">
@@ -13235,7 +13235,7 @@
         <v>195</v>
       </c>
       <c r="C986" t="n">
-        <v>-0.027833</v>
+        <v>-0.027722</v>
       </c>
     </row>
     <row r="987">
@@ -13248,7 +13248,7 @@
         <v>196</v>
       </c>
       <c r="C987" t="n">
-        <v>-0.027807</v>
+        <v>-0.027514</v>
       </c>
     </row>
     <row r="988">
@@ -13261,7 +13261,7 @@
         <v>197</v>
       </c>
       <c r="C988" t="n">
-        <v>-0.02777</v>
+        <v>-0.027433</v>
       </c>
     </row>
     <row r="989">
@@ -13274,7 +13274,7 @@
         <v>198</v>
       </c>
       <c r="C989" t="n">
-        <v>-0.027728</v>
+        <v>-0.027276</v>
       </c>
     </row>
     <row r="990">
@@ -13287,7 +13287,7 @@
         <v>199</v>
       </c>
       <c r="C990" t="n">
-        <v>-0.027437</v>
+        <v>-0.026691</v>
       </c>
     </row>
     <row r="991">
@@ -13300,7 +13300,7 @@
         <v>200</v>
       </c>
       <c r="C991" t="n">
-        <v>-0.027201</v>
+        <v>-0.026377</v>
       </c>
     </row>
     <row r="992">
@@ -13313,7 +13313,7 @@
         <v>201</v>
       </c>
       <c r="C992" t="n">
-        <v>-0.027135</v>
+        <v>-0.025985</v>
       </c>
     </row>
     <row r="993">
@@ -13326,7 +13326,7 @@
         <v>202</v>
       </c>
       <c r="C993" t="n">
-        <v>-0.026063</v>
+        <v>-0.025747</v>
       </c>
     </row>
     <row r="994">
@@ -13339,7 +13339,7 @@
         <v>203</v>
       </c>
       <c r="C994" t="n">
-        <v>-0.025999</v>
+        <v>-0.024949</v>
       </c>
     </row>
     <row r="995">
@@ -13352,7 +13352,7 @@
         <v>204</v>
       </c>
       <c r="C995" t="n">
-        <v>-0.025704</v>
+        <v>-0.024934</v>
       </c>
     </row>
     <row r="996">
@@ -13365,7 +13365,7 @@
         <v>205</v>
       </c>
       <c r="C996" t="n">
-        <v>-0.02542</v>
+        <v>-0.024851</v>
       </c>
     </row>
     <row r="997">
@@ -13378,7 +13378,7 @@
         <v>206</v>
       </c>
       <c r="C997" t="n">
-        <v>-0.025164</v>
+        <v>-0.02479</v>
       </c>
     </row>
     <row r="998">
@@ -13391,7 +13391,7 @@
         <v>207</v>
       </c>
       <c r="C998" t="n">
-        <v>-0.025061</v>
+        <v>-0.024535</v>
       </c>
     </row>
     <row r="999">
@@ -13404,7 +13404,7 @@
         <v>208</v>
       </c>
       <c r="C999" t="n">
-        <v>-0.02492</v>
+        <v>-0.024406</v>
       </c>
     </row>
     <row r="1000">
@@ -13417,7 +13417,7 @@
         <v>209</v>
       </c>
       <c r="C1000" t="n">
-        <v>-0.024905</v>
+        <v>-0.024397</v>
       </c>
     </row>
     <row r="1001">
@@ -13430,7 +13430,7 @@
         <v>210</v>
       </c>
       <c r="C1001" t="n">
-        <v>-0.024888</v>
+        <v>-0.024318</v>
       </c>
     </row>
     <row r="1002">
@@ -13443,7 +13443,7 @@
         <v>211</v>
       </c>
       <c r="C1002" t="n">
-        <v>-0.024744</v>
+        <v>-0.024318</v>
       </c>
     </row>
     <row r="1003">
@@ -13456,7 +13456,7 @@
         <v>212</v>
       </c>
       <c r="C1003" t="n">
-        <v>-0.024417</v>
+        <v>-0.023947</v>
       </c>
     </row>
     <row r="1004">
@@ -13469,7 +13469,7 @@
         <v>213</v>
       </c>
       <c r="C1004" t="n">
-        <v>-0.024104</v>
+        <v>-0.02389</v>
       </c>
     </row>
     <row r="1005">
@@ -13482,7 +13482,7 @@
         <v>214</v>
       </c>
       <c r="C1005" t="n">
-        <v>-0.024102</v>
+        <v>-0.023863</v>
       </c>
     </row>
     <row r="1006">
@@ -13495,7 +13495,7 @@
         <v>215</v>
       </c>
       <c r="C1006" t="n">
-        <v>-0.023926</v>
+        <v>-0.023696</v>
       </c>
     </row>
     <row r="1007">
@@ -13508,7 +13508,7 @@
         <v>216</v>
       </c>
       <c r="C1007" t="n">
-        <v>-0.023828</v>
+        <v>-0.023608</v>
       </c>
     </row>
     <row r="1008">
@@ -13521,7 +13521,7 @@
         <v>217</v>
       </c>
       <c r="C1008" t="n">
-        <v>-0.023784</v>
+        <v>-0.023569</v>
       </c>
     </row>
     <row r="1009">
@@ -13534,7 +13534,7 @@
         <v>218</v>
       </c>
       <c r="C1009" t="n">
-        <v>-0.023569</v>
+        <v>-0.022915</v>
       </c>
     </row>
     <row r="1010">
@@ -13547,7 +13547,7 @@
         <v>219</v>
       </c>
       <c r="C1010" t="n">
-        <v>-0.023105</v>
+        <v>-0.022701</v>
       </c>
     </row>
     <row r="1011">
@@ -13560,7 +13560,7 @@
         <v>220</v>
       </c>
       <c r="C1011" t="n">
-        <v>-0.0226</v>
+        <v>-0.022051</v>
       </c>
     </row>
     <row r="1012">
@@ -13573,7 +13573,7 @@
         <v>221</v>
       </c>
       <c r="C1012" t="n">
-        <v>-0.022535</v>
+        <v>-0.021836</v>
       </c>
     </row>
     <row r="1013">
@@ -13586,7 +13586,7 @@
         <v>222</v>
       </c>
       <c r="C1013" t="n">
-        <v>-0.021839</v>
+        <v>-0.021661</v>
       </c>
     </row>
     <row r="1014">
@@ -13599,7 +13599,7 @@
         <v>223</v>
       </c>
       <c r="C1014" t="n">
-        <v>-0.021103</v>
+        <v>-0.020927</v>
       </c>
     </row>
     <row r="1015">
@@ -13612,7 +13612,7 @@
         <v>224</v>
       </c>
       <c r="C1015" t="n">
-        <v>-0.020945</v>
+        <v>-0.020539</v>
       </c>
     </row>
     <row r="1016">
@@ -13625,7 +13625,7 @@
         <v>225</v>
       </c>
       <c r="C1016" t="n">
-        <v>-0.020396</v>
+        <v>-0.020463</v>
       </c>
     </row>
     <row r="1017">
@@ -13638,7 +13638,7 @@
         <v>226</v>
       </c>
       <c r="C1017" t="n">
-        <v>-0.020214</v>
+        <v>-0.019556</v>
       </c>
     </row>
     <row r="1018">
@@ -13651,7 +13651,7 @@
         <v>227</v>
       </c>
       <c r="C1018" t="n">
-        <v>-0.019858</v>
+        <v>-0.019543</v>
       </c>
     </row>
     <row r="1019">
@@ -13664,7 +13664,7 @@
         <v>228</v>
       </c>
       <c r="C1019" t="n">
-        <v>-0.019451</v>
+        <v>-0.019498</v>
       </c>
     </row>
     <row r="1020">
@@ -13677,7 +13677,7 @@
         <v>229</v>
       </c>
       <c r="C1020" t="n">
-        <v>-0.019438</v>
+        <v>-0.01937</v>
       </c>
     </row>
     <row r="1021">
@@ -13690,7 +13690,7 @@
         <v>230</v>
       </c>
       <c r="C1021" t="n">
-        <v>-0.019397</v>
+        <v>-0.019211</v>
       </c>
     </row>
     <row r="1022">
@@ -13703,7 +13703,7 @@
         <v>231</v>
       </c>
       <c r="C1022" t="n">
-        <v>-0.019149</v>
+        <v>-0.019146</v>
       </c>
     </row>
     <row r="1023">
@@ -13716,7 +13716,7 @@
         <v>232</v>
       </c>
       <c r="C1023" t="n">
-        <v>-0.018949</v>
+        <v>-0.019097</v>
       </c>
     </row>
     <row r="1024">
@@ -13729,7 +13729,7 @@
         <v>233</v>
       </c>
       <c r="C1024" t="n">
-        <v>-0.018895</v>
+        <v>-0.018988</v>
       </c>
     </row>
     <row r="1025">
@@ -13742,7 +13742,7 @@
         <v>234</v>
       </c>
       <c r="C1025" t="n">
-        <v>-0.018856</v>
+        <v>-0.018976</v>
       </c>
     </row>
     <row r="1026">
@@ -13755,7 +13755,7 @@
         <v>235</v>
       </c>
       <c r="C1026" t="n">
-        <v>-0.018829</v>
+        <v>-0.018386</v>
       </c>
     </row>
     <row r="1027">
@@ -13768,7 +13768,7 @@
         <v>236</v>
       </c>
       <c r="C1027" t="n">
-        <v>-0.018812</v>
+        <v>-0.018214</v>
       </c>
     </row>
     <row r="1028">
@@ -13781,7 +13781,7 @@
         <v>237</v>
       </c>
       <c r="C1028" t="n">
-        <v>-0.018277</v>
+        <v>-0.018148</v>
       </c>
     </row>
     <row r="1029">
@@ -13794,7 +13794,7 @@
         <v>238</v>
       </c>
       <c r="C1029" t="n">
-        <v>-0.018085</v>
+        <v>-0.018056</v>
       </c>
     </row>
     <row r="1030">
@@ -13807,7 +13807,7 @@
         <v>239</v>
       </c>
       <c r="C1030" t="n">
-        <v>-0.01803</v>
+        <v>-0.017997</v>
       </c>
     </row>
     <row r="1031">
@@ -13820,7 +13820,7 @@
         <v>240</v>
       </c>
       <c r="C1031" t="n">
-        <v>-0.017926</v>
+        <v>-0.017904</v>
       </c>
     </row>
     <row r="1032">
@@ -13833,7 +13833,7 @@
         <v>241</v>
       </c>
       <c r="C1032" t="n">
-        <v>-0.01792</v>
+        <v>-0.017881</v>
       </c>
     </row>
     <row r="1033">
@@ -13846,7 +13846,7 @@
         <v>242</v>
       </c>
       <c r="C1033" t="n">
-        <v>-0.017896</v>
+        <v>-0.01788</v>
       </c>
     </row>
     <row r="1034">
@@ -13859,7 +13859,7 @@
         <v>243</v>
       </c>
       <c r="C1034" t="n">
-        <v>-0.01786</v>
+        <v>-0.017665</v>
       </c>
     </row>
     <row r="1035">
@@ -13872,7 +13872,7 @@
         <v>244</v>
       </c>
       <c r="C1035" t="n">
-        <v>-0.017505</v>
+        <v>-0.017485</v>
       </c>
     </row>
     <row r="1036">
@@ -13885,7 +13885,7 @@
         <v>245</v>
       </c>
       <c r="C1036" t="n">
-        <v>-0.017411</v>
+        <v>-0.017465</v>
       </c>
     </row>
     <row r="1037">
@@ -13898,7 +13898,7 @@
         <v>246</v>
       </c>
       <c r="C1037" t="n">
-        <v>-0.017407</v>
+        <v>-0.017455</v>
       </c>
     </row>
     <row r="1038">
@@ -13911,7 +13911,7 @@
         <v>247</v>
       </c>
       <c r="C1038" t="n">
-        <v>-0.017156</v>
+        <v>-0.016945</v>
       </c>
     </row>
     <row r="1039">
@@ -13924,7 +13924,7 @@
         <v>248</v>
       </c>
       <c r="C1039" t="n">
-        <v>-0.016964</v>
+        <v>-0.016901</v>
       </c>
     </row>
     <row r="1040">
@@ -13937,7 +13937,7 @@
         <v>249</v>
       </c>
       <c r="C1040" t="n">
-        <v>-0.01694</v>
+        <v>-0.016363</v>
       </c>
     </row>
     <row r="1041">
@@ -13950,7 +13950,7 @@
         <v>250</v>
       </c>
       <c r="C1041" t="n">
-        <v>-0.016722</v>
+        <v>-0.016338</v>
       </c>
     </row>
     <row r="1042">
@@ -13963,7 +13963,7 @@
         <v>251</v>
       </c>
       <c r="C1042" t="n">
-        <v>-0.016602</v>
+        <v>-0.01612</v>
       </c>
     </row>
     <row r="1043">
@@ -13976,7 +13976,7 @@
         <v>252</v>
       </c>
       <c r="C1043" t="n">
-        <v>-0.016343</v>
+        <v>-0.015717</v>
       </c>
     </row>
     <row r="1044">
@@ -13989,7 +13989,7 @@
         <v>253</v>
       </c>
       <c r="C1044" t="n">
-        <v>-0.016148</v>
+        <v>-0.01544</v>
       </c>
     </row>
     <row r="1045">
@@ -14002,7 +14002,7 @@
         <v>254</v>
       </c>
       <c r="C1045" t="n">
-        <v>-0.015597</v>
+        <v>-0.015236</v>
       </c>
     </row>
     <row r="1046">
@@ -14015,7 +14015,7 @@
         <v>255</v>
       </c>
       <c r="C1046" t="n">
-        <v>-0.01516</v>
+        <v>-0.015047</v>
       </c>
     </row>
     <row r="1047">
@@ -14028,7 +14028,7 @@
         <v>256</v>
       </c>
       <c r="C1047" t="n">
-        <v>-0.014955</v>
+        <v>-0.014957</v>
       </c>
     </row>
     <row r="1048">
@@ -14041,7 +14041,7 @@
         <v>257</v>
       </c>
       <c r="C1048" t="n">
-        <v>-0.014869</v>
+        <v>-0.014851</v>
       </c>
     </row>
     <row r="1049">
@@ -14054,7 +14054,7 @@
         <v>258</v>
       </c>
       <c r="C1049" t="n">
-        <v>-0.014147</v>
+        <v>-0.01404</v>
       </c>
     </row>
     <row r="1050">
@@ -14067,7 +14067,7 @@
         <v>259</v>
       </c>
       <c r="C1050" t="n">
-        <v>-0.014129</v>
+        <v>-0.014011</v>
       </c>
     </row>
     <row r="1051">
@@ -14080,7 +14080,7 @@
         <v>260</v>
       </c>
       <c r="C1051" t="n">
-        <v>-0.013898</v>
+        <v>-0.013656</v>
       </c>
     </row>
     <row r="1052">
@@ -14093,7 +14093,7 @@
         <v>261</v>
       </c>
       <c r="C1052" t="n">
-        <v>-0.013576</v>
+        <v>-0.013526</v>
       </c>
     </row>
     <row r="1053">
@@ -14106,7 +14106,7 @@
         <v>262</v>
       </c>
       <c r="C1053" t="n">
-        <v>-0.013363</v>
+        <v>-0.012645</v>
       </c>
     </row>
     <row r="1054">
@@ -14119,7 +14119,7 @@
         <v>263</v>
       </c>
       <c r="C1054" t="n">
-        <v>-0.012653</v>
+        <v>-0.01259</v>
       </c>
     </row>
     <row r="1055">
@@ -14132,7 +14132,7 @@
         <v>264</v>
       </c>
       <c r="C1055" t="n">
-        <v>-0.012572</v>
+        <v>-0.012086</v>
       </c>
     </row>
     <row r="1056">
@@ -14145,7 +14145,7 @@
         <v>265</v>
       </c>
       <c r="C1056" t="n">
-        <v>-0.012553</v>
+        <v>-0.011903</v>
       </c>
     </row>
     <row r="1057">
@@ -14158,7 +14158,7 @@
         <v>266</v>
       </c>
       <c r="C1057" t="n">
-        <v>-0.012104</v>
+        <v>-0.011796</v>
       </c>
     </row>
     <row r="1058">
@@ -14171,7 +14171,7 @@
         <v>267</v>
       </c>
       <c r="C1058" t="n">
-        <v>-0.011849</v>
+        <v>-0.01142</v>
       </c>
     </row>
     <row r="1059">
@@ -14184,7 +14184,7 @@
         <v>268</v>
       </c>
       <c r="C1059" t="n">
-        <v>-0.011844</v>
+        <v>-0.011297</v>
       </c>
     </row>
     <row r="1060">
@@ -14197,7 +14197,7 @@
         <v>269</v>
       </c>
       <c r="C1060" t="n">
-        <v>-0.011814</v>
+        <v>-0.011207</v>
       </c>
     </row>
     <row r="1061">
@@ -14210,7 +14210,7 @@
         <v>270</v>
       </c>
       <c r="C1061" t="n">
-        <v>-0.011466</v>
+        <v>-0.011136</v>
       </c>
     </row>
     <row r="1062">
@@ -14223,7 +14223,7 @@
         <v>271</v>
       </c>
       <c r="C1062" t="n">
-        <v>-0.011149</v>
+        <v>-0.010986</v>
       </c>
     </row>
     <row r="1063">
@@ -14236,7 +14236,7 @@
         <v>272</v>
       </c>
       <c r="C1063" t="n">
-        <v>-0.011142</v>
+        <v>-0.010766</v>
       </c>
     </row>
     <row r="1064">
@@ -14249,7 +14249,7 @@
         <v>273</v>
       </c>
       <c r="C1064" t="n">
-        <v>-0.011069</v>
+        <v>-0.010662</v>
       </c>
     </row>
     <row r="1065">
@@ -14262,7 +14262,7 @@
         <v>274</v>
       </c>
       <c r="C1065" t="n">
-        <v>-0.010634</v>
+        <v>-0.010362</v>
       </c>
     </row>
     <row r="1066">
@@ -14275,7 +14275,7 @@
         <v>275</v>
       </c>
       <c r="C1066" t="n">
-        <v>-0.010165</v>
+        <v>-0.010006</v>
       </c>
     </row>
     <row r="1067">
@@ -14288,7 +14288,7 @@
         <v>276</v>
       </c>
       <c r="C1067" t="n">
-        <v>-0.009894</v>
+        <v>-0.01</v>
       </c>
     </row>
     <row r="1068">
@@ -14301,7 +14301,7 @@
         <v>277</v>
       </c>
       <c r="C1068" t="n">
-        <v>-0.009551</v>
+        <v>-0.009695</v>
       </c>
     </row>
     <row r="1069">
@@ -14314,7 +14314,7 @@
         <v>278</v>
       </c>
       <c r="C1069" t="n">
-        <v>-0.009479</v>
+        <v>-0.009471</v>
       </c>
     </row>
     <row r="1070">
@@ -14327,7 +14327,7 @@
         <v>279</v>
       </c>
       <c r="C1070" t="n">
-        <v>-0.00882</v>
+        <v>-0.008921</v>
       </c>
     </row>
     <row r="1071">
@@ -14340,7 +14340,7 @@
         <v>280</v>
       </c>
       <c r="C1071" t="n">
-        <v>-0.00872</v>
+        <v>-0.008813</v>
       </c>
     </row>
     <row r="1072">
@@ -14353,7 +14353,7 @@
         <v>281</v>
       </c>
       <c r="C1072" t="n">
-        <v>-0.008329</v>
+        <v>-0.008168</v>
       </c>
     </row>
     <row r="1073">
@@ -14366,7 +14366,7 @@
         <v>282</v>
       </c>
       <c r="C1073" t="n">
-        <v>-0.008187</v>
+        <v>-0.008125</v>
       </c>
     </row>
     <row r="1074">
@@ -14379,7 +14379,7 @@
         <v>283</v>
       </c>
       <c r="C1074" t="n">
-        <v>-0.007908999999999999</v>
+        <v>-0.007912000000000001</v>
       </c>
     </row>
     <row r="1075">
@@ -14392,7 +14392,7 @@
         <v>284</v>
       </c>
       <c r="C1075" t="n">
-        <v>-0.007892</v>
+        <v>-0.007875999999999999</v>
       </c>
     </row>
     <row r="1076">
@@ -14405,7 +14405,7 @@
         <v>285</v>
       </c>
       <c r="C1076" t="n">
-        <v>-0.007783</v>
+        <v>-0.007797</v>
       </c>
     </row>
     <row r="1077">
@@ -14418,7 +14418,7 @@
         <v>286</v>
       </c>
       <c r="C1077" t="n">
-        <v>-0.007647</v>
+        <v>-0.007603</v>
       </c>
     </row>
     <row r="1078">
@@ -14431,7 +14431,7 @@
         <v>287</v>
       </c>
       <c r="C1078" t="n">
-        <v>-0.007583</v>
+        <v>-0.007348</v>
       </c>
     </row>
     <row r="1079">
@@ -14444,7 +14444,7 @@
         <v>288</v>
       </c>
       <c r="C1079" t="n">
-        <v>-0.007501</v>
+        <v>-0.007258</v>
       </c>
     </row>
     <row r="1080">
@@ -14457,7 +14457,7 @@
         <v>289</v>
       </c>
       <c r="C1080" t="n">
-        <v>-0.007486</v>
+        <v>-0.007166</v>
       </c>
     </row>
     <row r="1081">
@@ -14470,7 +14470,7 @@
         <v>290</v>
       </c>
       <c r="C1081" t="n">
-        <v>-0.007348</v>
+        <v>-0.007054</v>
       </c>
     </row>
     <row r="1082">
@@ -14483,7 +14483,7 @@
         <v>291</v>
       </c>
       <c r="C1082" t="n">
-        <v>-0.007329</v>
+        <v>-0.007006</v>
       </c>
     </row>
     <row r="1083">
@@ -14496,7 +14496,7 @@
         <v>292</v>
       </c>
       <c r="C1083" t="n">
-        <v>-0.007319</v>
+        <v>-0.006972</v>
       </c>
     </row>
     <row r="1084">
@@ -14509,7 +14509,7 @@
         <v>293</v>
       </c>
       <c r="C1084" t="n">
-        <v>-0.007249</v>
+        <v>-0.006897</v>
       </c>
     </row>
     <row r="1085">
@@ -14522,7 +14522,7 @@
         <v>294</v>
       </c>
       <c r="C1085" t="n">
-        <v>-0.007213</v>
+        <v>-0.00677</v>
       </c>
     </row>
     <row r="1086">
@@ -14535,7 +14535,7 @@
         <v>295</v>
       </c>
       <c r="C1086" t="n">
-        <v>-0.007171</v>
+        <v>-0.006753</v>
       </c>
     </row>
     <row r="1087">
@@ -14548,7 +14548,7 @@
         <v>296</v>
       </c>
       <c r="C1087" t="n">
-        <v>-0.007155</v>
+        <v>-0.006745</v>
       </c>
     </row>
     <row r="1088">
@@ -14561,7 +14561,7 @@
         <v>297</v>
       </c>
       <c r="C1088" t="n">
-        <v>-0.007035</v>
+        <v>-0.00646</v>
       </c>
     </row>
     <row r="1089">
@@ -14574,7 +14574,7 @@
         <v>298</v>
       </c>
       <c r="C1089" t="n">
-        <v>-0.006761</v>
+        <v>-0.006393</v>
       </c>
     </row>
     <row r="1090">
@@ -14587,7 +14587,7 @@
         <v>299</v>
       </c>
       <c r="C1090" t="n">
-        <v>-0.006353</v>
+        <v>-0.00635</v>
       </c>
     </row>
     <row r="1091">
@@ -14600,7 +14600,7 @@
         <v>300</v>
       </c>
       <c r="C1091" t="n">
-        <v>-0.006015</v>
+        <v>-0.006005</v>
       </c>
     </row>
     <row r="1092">
@@ -14613,7 +14613,7 @@
         <v>301</v>
       </c>
       <c r="C1092" t="n">
-        <v>-0.005956</v>
+        <v>-0.005944</v>
       </c>
     </row>
     <row r="1093">
@@ -14626,7 +14626,7 @@
         <v>302</v>
       </c>
       <c r="C1093" t="n">
-        <v>-0.005795</v>
+        <v>-0.005824</v>
       </c>
     </row>
     <row r="1094">
@@ -14639,7 +14639,7 @@
         <v>303</v>
       </c>
       <c r="C1094" t="n">
-        <v>-0.005748</v>
+        <v>-0.005766</v>
       </c>
     </row>
     <row r="1095">
@@ -14652,7 +14652,7 @@
         <v>304</v>
       </c>
       <c r="C1095" t="n">
-        <v>-0.00561</v>
+        <v>-0.005715</v>
       </c>
     </row>
     <row r="1096">
@@ -14665,7 +14665,7 @@
         <v>305</v>
       </c>
       <c r="C1096" t="n">
-        <v>-0.005343</v>
+        <v>-0.005274</v>
       </c>
     </row>
     <row r="1097">
@@ -14678,7 +14678,7 @@
         <v>306</v>
       </c>
       <c r="C1097" t="n">
-        <v>-0.005083</v>
+        <v>-0.00514</v>
       </c>
     </row>
     <row r="1098">
@@ -14691,7 +14691,7 @@
         <v>307</v>
       </c>
       <c r="C1098" t="n">
-        <v>-0.005013</v>
+        <v>-0.005016</v>
       </c>
     </row>
     <row r="1099">
@@ -14704,7 +14704,7 @@
         <v>308</v>
       </c>
       <c r="C1099" t="n">
-        <v>-0.004434</v>
+        <v>-0.004395</v>
       </c>
     </row>
     <row r="1100">
@@ -14717,7 +14717,7 @@
         <v>309</v>
       </c>
       <c r="C1100" t="n">
-        <v>-0.004401</v>
+        <v>-0.004088</v>
       </c>
     </row>
     <row r="1101">
@@ -14730,7 +14730,7 @@
         <v>310</v>
       </c>
       <c r="C1101" t="n">
-        <v>-0.003994</v>
+        <v>-0.003983</v>
       </c>
     </row>
     <row r="1102">
@@ -14743,7 +14743,7 @@
         <v>311</v>
       </c>
       <c r="C1102" t="n">
-        <v>-0.003807</v>
+        <v>-0.003812</v>
       </c>
     </row>
     <row r="1103">
@@ -14756,7 +14756,7 @@
         <v>312</v>
       </c>
       <c r="C1103" t="n">
-        <v>-0.003644</v>
+        <v>-0.003672</v>
       </c>
     </row>
     <row r="1104">
@@ -14769,7 +14769,7 @@
         <v>313</v>
       </c>
       <c r="C1104" t="n">
-        <v>-0.003164</v>
+        <v>-0.003214</v>
       </c>
     </row>
     <row r="1105">
@@ -14782,7 +14782,7 @@
         <v>314</v>
       </c>
       <c r="C1105" t="n">
-        <v>-0.003154</v>
+        <v>-0.003175</v>
       </c>
     </row>
     <row r="1106">
@@ -14795,7 +14795,7 @@
         <v>315</v>
       </c>
       <c r="C1106" t="n">
-        <v>-0.003135</v>
+        <v>-0.003167</v>
       </c>
     </row>
     <row r="1107">
@@ -14808,7 +14808,7 @@
         <v>316</v>
       </c>
       <c r="C1107" t="n">
-        <v>-0.003024</v>
+        <v>-0.003017</v>
       </c>
     </row>
     <row r="1108">
@@ -14821,7 +14821,7 @@
         <v>317</v>
       </c>
       <c r="C1108" t="n">
-        <v>-0.002974</v>
+        <v>-0.003</v>
       </c>
     </row>
     <row r="1109">
@@ -14834,7 +14834,7 @@
         <v>318</v>
       </c>
       <c r="C1109" t="n">
-        <v>-0.002512</v>
+        <v>-0.002357</v>
       </c>
     </row>
     <row r="1110">
@@ -14847,7 +14847,7 @@
         <v>319</v>
       </c>
       <c r="C1110" t="n">
-        <v>-0.002191</v>
+        <v>-0.002192</v>
       </c>
     </row>
     <row r="1111">
@@ -14860,7 +14860,7 @@
         <v>320</v>
       </c>
       <c r="C1111" t="n">
-        <v>-0.00211</v>
+        <v>-0.002114</v>
       </c>
     </row>
     <row r="1112">
@@ -14873,7 +14873,7 @@
         <v>321</v>
       </c>
       <c r="C1112" t="n">
-        <v>-0.002091</v>
+        <v>-0.002014</v>
       </c>
     </row>
     <row r="1113">
@@ -14886,7 +14886,7 @@
         <v>322</v>
       </c>
       <c r="C1113" t="n">
-        <v>-0.001714</v>
+        <v>-0.001746</v>
       </c>
     </row>
     <row r="1114">
@@ -14899,7 +14899,7 @@
         <v>323</v>
       </c>
       <c r="C1114" t="n">
-        <v>-0.001689</v>
+        <v>-0.001652</v>
       </c>
     </row>
     <row r="1115">
@@ -14912,7 +14912,7 @@
         <v>324</v>
       </c>
       <c r="C1115" t="n">
-        <v>-0.00163</v>
+        <v>-0.001563</v>
       </c>
     </row>
     <row r="1116">
@@ -14925,7 +14925,7 @@
         <v>325</v>
       </c>
       <c r="C1116" t="n">
-        <v>-0.001495</v>
+        <v>-0.001358</v>
       </c>
     </row>
     <row r="1117">
@@ -14938,7 +14938,7 @@
         <v>326</v>
       </c>
       <c r="C1117" t="n">
-        <v>-0.001073</v>
+        <v>-0.001074</v>
       </c>
     </row>
     <row r="1118">
@@ -14951,7 +14951,7 @@
         <v>327</v>
       </c>
       <c r="C1118" t="n">
-        <v>-0.000953</v>
+        <v>-0.000951</v>
       </c>
     </row>
     <row r="1119">
@@ -14964,7 +14964,7 @@
         <v>328</v>
       </c>
       <c r="C1119" t="n">
-        <v>-0.000869</v>
+        <v>-0.000873</v>
       </c>
     </row>
     <row r="1120">
@@ -14977,7 +14977,7 @@
         <v>329</v>
       </c>
       <c r="C1120" t="n">
-        <v>-0.000731</v>
+        <v>-0.000745</v>
       </c>
     </row>
     <row r="1121">
@@ -14990,7 +14990,7 @@
         <v>330</v>
       </c>
       <c r="C1121" t="n">
-        <v>-0.00061</v>
+        <v>-0.00056</v>
       </c>
     </row>
     <row r="1122">
@@ -15016,7 +15016,7 @@
         <v>332</v>
       </c>
       <c r="C1123" t="n">
-        <v>-0.000386</v>
+        <v>-0.000387</v>
       </c>
     </row>
     <row r="1124">
@@ -15081,7 +15081,7 @@
         <v>337</v>
       </c>
       <c r="C1128" t="n">
-        <v>0.000111</v>
+        <v>0.000112</v>
       </c>
     </row>
     <row r="1129">
@@ -15094,7 +15094,7 @@
         <v>338</v>
       </c>
       <c r="C1129" t="n">
-        <v>0.000456</v>
+        <v>0.000432</v>
       </c>
     </row>
     <row r="1130">
@@ -15120,7 +15120,7 @@
         <v>340</v>
       </c>
       <c r="C1131" t="n">
-        <v>0.00052</v>
+        <v>0.000522</v>
       </c>
     </row>
     <row r="1132">
@@ -15133,7 +15133,7 @@
         <v>341</v>
       </c>
       <c r="C1132" t="n">
-        <v>0.0009890000000000001</v>
+        <v>0.000976</v>
       </c>
     </row>
     <row r="1133">
@@ -15146,7 +15146,7 @@
         <v>342</v>
       </c>
       <c r="C1133" t="n">
-        <v>0.001064</v>
+        <v>0.001075</v>
       </c>
     </row>
     <row r="1134">
@@ -15159,7 +15159,7 @@
         <v>343</v>
       </c>
       <c r="C1134" t="n">
-        <v>0.001642</v>
+        <v>0.00163</v>
       </c>
     </row>
     <row r="1135">
@@ -15172,7 +15172,7 @@
         <v>344</v>
       </c>
       <c r="C1135" t="n">
-        <v>0.001909</v>
+        <v>0.001907</v>
       </c>
     </row>
     <row r="1136">
@@ -15185,7 +15185,7 @@
         <v>345</v>
       </c>
       <c r="C1136" t="n">
-        <v>0.002006</v>
+        <v>0.002026</v>
       </c>
     </row>
     <row r="1137">
@@ -15198,7 +15198,7 @@
         <v>346</v>
       </c>
       <c r="C1137" t="n">
-        <v>0.002387</v>
+        <v>0.00237</v>
       </c>
     </row>
     <row r="1138">
@@ -15211,7 +15211,7 @@
         <v>347</v>
       </c>
       <c r="C1138" t="n">
-        <v>0.002521</v>
+        <v>0.002467</v>
       </c>
     </row>
     <row r="1139">
@@ -15224,7 +15224,7 @@
         <v>348</v>
       </c>
       <c r="C1139" t="n">
-        <v>0.002719</v>
+        <v>0.00273</v>
       </c>
     </row>
     <row r="1140">
@@ -15237,7 +15237,7 @@
         <v>349</v>
       </c>
       <c r="C1140" t="n">
-        <v>0.002825</v>
+        <v>0.002863</v>
       </c>
     </row>
     <row r="1141">
@@ -15250,7 +15250,7 @@
         <v>350</v>
       </c>
       <c r="C1141" t="n">
-        <v>0.003072</v>
+        <v>0.003041</v>
       </c>
     </row>
     <row r="1142">
@@ -15263,7 +15263,7 @@
         <v>351</v>
       </c>
       <c r="C1142" t="n">
-        <v>0.003244</v>
+        <v>0.003083</v>
       </c>
     </row>
     <row r="1143">
@@ -15276,7 +15276,7 @@
         <v>352</v>
       </c>
       <c r="C1143" t="n">
-        <v>0.00347</v>
+        <v>0.003427</v>
       </c>
     </row>
     <row r="1144">
@@ -15289,7 +15289,7 @@
         <v>353</v>
       </c>
       <c r="C1144" t="n">
-        <v>0.003797</v>
+        <v>0.003746</v>
       </c>
     </row>
     <row r="1145">
@@ -15302,7 +15302,7 @@
         <v>354</v>
       </c>
       <c r="C1145" t="n">
-        <v>0.003917</v>
+        <v>0.003904</v>
       </c>
     </row>
     <row r="1146">
@@ -15328,7 +15328,7 @@
         <v>356</v>
       </c>
       <c r="C1147" t="n">
-        <v>0.004209</v>
+        <v>0.00422</v>
       </c>
     </row>
     <row r="1148">
@@ -15341,7 +15341,7 @@
         <v>357</v>
       </c>
       <c r="C1148" t="n">
-        <v>0.004334</v>
+        <v>0.004338</v>
       </c>
     </row>
     <row r="1149">
@@ -15354,7 +15354,7 @@
         <v>358</v>
       </c>
       <c r="C1149" t="n">
-        <v>0.004483</v>
+        <v>0.004494</v>
       </c>
     </row>
     <row r="1150">
@@ -15367,7 +15367,7 @@
         <v>359</v>
       </c>
       <c r="C1150" t="n">
-        <v>0.004516</v>
+        <v>0.004502</v>
       </c>
     </row>
     <row r="1151">
@@ -15380,7 +15380,7 @@
         <v>360</v>
       </c>
       <c r="C1151" t="n">
-        <v>0.004699</v>
+        <v>0.004602</v>
       </c>
     </row>
     <row r="1152">
@@ -15393,7 +15393,7 @@
         <v>361</v>
       </c>
       <c r="C1152" t="n">
-        <v>0.004784</v>
+        <v>0.004624</v>
       </c>
     </row>
     <row r="1153">
@@ -15406,7 +15406,7 @@
         <v>362</v>
       </c>
       <c r="C1153" t="n">
-        <v>0.004812</v>
+        <v>0.00464</v>
       </c>
     </row>
     <row r="1154">
@@ -15419,7 +15419,7 @@
         <v>363</v>
       </c>
       <c r="C1154" t="n">
-        <v>0.004923</v>
+        <v>0.004714</v>
       </c>
     </row>
     <row r="1155">
@@ -15432,7 +15432,7 @@
         <v>364</v>
       </c>
       <c r="C1155" t="n">
-        <v>0.00493</v>
+        <v>0.00482</v>
       </c>
     </row>
     <row r="1156">
@@ -15445,7 +15445,7 @@
         <v>365</v>
       </c>
       <c r="C1156" t="n">
-        <v>0.004946</v>
+        <v>0.004869</v>
       </c>
     </row>
     <row r="1157">
@@ -15458,7 +15458,7 @@
         <v>366</v>
       </c>
       <c r="C1157" t="n">
-        <v>0.00509</v>
+        <v>0.004905</v>
       </c>
     </row>
     <row r="1158">
@@ -15471,7 +15471,7 @@
         <v>367</v>
       </c>
       <c r="C1158" t="n">
-        <v>0.005219</v>
+        <v>0.005207</v>
       </c>
     </row>
     <row r="1159">
@@ -15484,7 +15484,7 @@
         <v>368</v>
       </c>
       <c r="C1159" t="n">
-        <v>0.005569</v>
+        <v>0.005361</v>
       </c>
     </row>
     <row r="1160">
@@ -15497,7 +15497,7 @@
         <v>369</v>
       </c>
       <c r="C1160" t="n">
-        <v>0.005575</v>
+        <v>0.00568</v>
       </c>
     </row>
     <row r="1161">
@@ -15510,7 +15510,7 @@
         <v>370</v>
       </c>
       <c r="C1161" t="n">
-        <v>0.005686</v>
+        <v>0.005687</v>
       </c>
     </row>
     <row r="1162">
@@ -15523,7 +15523,7 @@
         <v>371</v>
       </c>
       <c r="C1162" t="n">
-        <v>0.005702</v>
+        <v>0.00572</v>
       </c>
     </row>
     <row r="1163">
@@ -15536,7 +15536,7 @@
         <v>372</v>
       </c>
       <c r="C1163" t="n">
-        <v>0.005814</v>
+        <v>0.005739</v>
       </c>
     </row>
     <row r="1164">
@@ -15549,7 +15549,7 @@
         <v>373</v>
       </c>
       <c r="C1164" t="n">
-        <v>0.006171</v>
+        <v>0.005825</v>
       </c>
     </row>
     <row r="1165">
@@ -15562,7 +15562,7 @@
         <v>374</v>
       </c>
       <c r="C1165" t="n">
-        <v>0.007702</v>
+        <v>0.007171</v>
       </c>
     </row>
     <row r="1166">
@@ -15575,7 +15575,7 @@
         <v>375</v>
       </c>
       <c r="C1166" t="n">
-        <v>0.008129000000000001</v>
+        <v>0.007697</v>
       </c>
     </row>
     <row r="1167">
@@ -15588,7 +15588,7 @@
         <v>376</v>
       </c>
       <c r="C1167" t="n">
-        <v>0.008227</v>
+        <v>0.008056000000000001</v>
       </c>
     </row>
     <row r="1168">
@@ -15601,7 +15601,7 @@
         <v>377</v>
       </c>
       <c r="C1168" t="n">
-        <v>0.008439</v>
+        <v>0.008225</v>
       </c>
     </row>
     <row r="1169">
@@ -15614,7 +15614,7 @@
         <v>378</v>
       </c>
       <c r="C1169" t="n">
-        <v>0.008742</v>
+        <v>0.00847</v>
       </c>
     </row>
     <row r="1170">
@@ -15627,7 +15627,7 @@
         <v>379</v>
       </c>
       <c r="C1170" t="n">
-        <v>0.008926</v>
+        <v>0.008989</v>
       </c>
     </row>
     <row r="1171">
@@ -15640,7 +15640,7 @@
         <v>380</v>
       </c>
       <c r="C1171" t="n">
-        <v>0.009280999999999999</v>
+        <v>0.009213000000000001</v>
       </c>
     </row>
     <row r="1172">
@@ -15653,7 +15653,7 @@
         <v>381</v>
       </c>
       <c r="C1172" t="n">
-        <v>0.009313</v>
+        <v>0.009220000000000001</v>
       </c>
     </row>
     <row r="1173">
@@ -15666,7 +15666,7 @@
         <v>382</v>
       </c>
       <c r="C1173" t="n">
-        <v>0.009443</v>
+        <v>0.009414</v>
       </c>
     </row>
     <row r="1174">
@@ -15679,7 +15679,7 @@
         <v>383</v>
       </c>
       <c r="C1174" t="n">
-        <v>0.009547</v>
+        <v>0.009436999999999999</v>
       </c>
     </row>
     <row r="1175">
@@ -15692,7 +15692,7 @@
         <v>384</v>
       </c>
       <c r="C1175" t="n">
-        <v>0.009763000000000001</v>
+        <v>0.009525</v>
       </c>
     </row>
     <row r="1176">
@@ -15705,7 +15705,7 @@
         <v>385</v>
       </c>
       <c r="C1176" t="n">
-        <v>0.009946999999999999</v>
+        <v>0.009572000000000001</v>
       </c>
     </row>
     <row r="1177">
@@ -15718,7 +15718,7 @@
         <v>386</v>
       </c>
       <c r="C1177" t="n">
-        <v>0.009962</v>
+        <v>0.009853000000000001</v>
       </c>
     </row>
     <row r="1178">
@@ -15731,7 +15731,7 @@
         <v>387</v>
       </c>
       <c r="C1178" t="n">
-        <v>0.010013</v>
+        <v>0.009953</v>
       </c>
     </row>
     <row r="1179">
@@ -15744,7 +15744,7 @@
         <v>388</v>
       </c>
       <c r="C1179" t="n">
-        <v>0.010026</v>
+        <v>0.010006</v>
       </c>
     </row>
     <row r="1180">
@@ -15757,7 +15757,7 @@
         <v>389</v>
       </c>
       <c r="C1180" t="n">
-        <v>0.010412</v>
+        <v>0.010053</v>
       </c>
     </row>
     <row r="1181">
@@ -15770,7 +15770,7 @@
         <v>390</v>
       </c>
       <c r="C1181" t="n">
-        <v>0.010732</v>
+        <v>0.010508</v>
       </c>
     </row>
     <row r="1182">
@@ -15783,7 +15783,7 @@
         <v>391</v>
       </c>
       <c r="C1182" t="n">
-        <v>0.010882</v>
+        <v>0.010817</v>
       </c>
     </row>
     <row r="1183">
@@ -15796,7 +15796,7 @@
         <v>392</v>
       </c>
       <c r="C1183" t="n">
-        <v>0.010928</v>
+        <v>0.010932</v>
       </c>
     </row>
     <row r="1184">
@@ -15809,7 +15809,7 @@
         <v>393</v>
       </c>
       <c r="C1184" t="n">
-        <v>0.010946</v>
+        <v>0.01095</v>
       </c>
     </row>
     <row r="1185">
@@ -15822,7 +15822,7 @@
         <v>394</v>
       </c>
       <c r="C1185" t="n">
-        <v>0.011175</v>
+        <v>0.01105</v>
       </c>
     </row>
     <row r="1186">
@@ -15835,7 +15835,7 @@
         <v>395</v>
       </c>
       <c r="C1186" t="n">
-        <v>0.011279</v>
+        <v>0.01123</v>
       </c>
     </row>
     <row r="1187">
@@ -15848,7 +15848,7 @@
         <v>396</v>
       </c>
       <c r="C1187" t="n">
-        <v>0.011319</v>
+        <v>0.011456</v>
       </c>
     </row>
     <row r="1188">
@@ -15861,7 +15861,7 @@
         <v>397</v>
       </c>
       <c r="C1188" t="n">
-        <v>0.011762</v>
+        <v>0.011609</v>
       </c>
     </row>
     <row r="1189">
@@ -15874,7 +15874,7 @@
         <v>398</v>
       </c>
       <c r="C1189" t="n">
-        <v>0.011794</v>
+        <v>0.01187</v>
       </c>
     </row>
     <row r="1190">
@@ -15887,7 +15887,7 @@
         <v>399</v>
       </c>
       <c r="C1190" t="n">
-        <v>0.012107</v>
+        <v>0.011886</v>
       </c>
     </row>
     <row r="1191">
@@ -15900,7 +15900,7 @@
         <v>400</v>
       </c>
       <c r="C1191" t="n">
-        <v>0.012257</v>
+        <v>0.012074</v>
       </c>
     </row>
     <row r="1192">
@@ -15913,7 +15913,7 @@
         <v>401</v>
       </c>
       <c r="C1192" t="n">
-        <v>0.012259</v>
+        <v>0.012208</v>
       </c>
     </row>
     <row r="1193">
@@ -15926,7 +15926,7 @@
         <v>402</v>
       </c>
       <c r="C1193" t="n">
-        <v>0.012797</v>
+        <v>0.012763</v>
       </c>
     </row>
     <row r="1194">
@@ -15939,7 +15939,7 @@
         <v>403</v>
       </c>
       <c r="C1194" t="n">
-        <v>0.012851</v>
+        <v>0.012807</v>
       </c>
     </row>
     <row r="1195">
@@ -15952,7 +15952,7 @@
         <v>404</v>
       </c>
       <c r="C1195" t="n">
-        <v>0.012987</v>
+        <v>0.012868</v>
       </c>
     </row>
     <row r="1196">
@@ -15965,7 +15965,7 @@
         <v>405</v>
       </c>
       <c r="C1196" t="n">
-        <v>0.01301</v>
+        <v>0.012915</v>
       </c>
     </row>
     <row r="1197">
@@ -15978,7 +15978,7 @@
         <v>406</v>
       </c>
       <c r="C1197" t="n">
-        <v>0.013045</v>
+        <v>0.013072</v>
       </c>
     </row>
     <row r="1198">
@@ -15991,7 +15991,7 @@
         <v>407</v>
       </c>
       <c r="C1198" t="n">
-        <v>0.013281</v>
+        <v>0.013419</v>
       </c>
     </row>
     <row r="1199">
@@ -16004,7 +16004,7 @@
         <v>408</v>
       </c>
       <c r="C1199" t="n">
-        <v>0.013694</v>
+        <v>0.013733</v>
       </c>
     </row>
     <row r="1200">
@@ -16017,7 +16017,7 @@
         <v>409</v>
       </c>
       <c r="C1200" t="n">
-        <v>0.0137</v>
+        <v>0.013833</v>
       </c>
     </row>
     <row r="1201">
@@ -16030,7 +16030,7 @@
         <v>410</v>
       </c>
       <c r="C1201" t="n">
-        <v>0.014059</v>
+        <v>0.013922</v>
       </c>
     </row>
     <row r="1202">
@@ -16043,7 +16043,7 @@
         <v>411</v>
       </c>
       <c r="C1202" t="n">
-        <v>0.014762</v>
+        <v>0.01469</v>
       </c>
     </row>
     <row r="1203">
@@ -16056,7 +16056,7 @@
         <v>412</v>
       </c>
       <c r="C1203" t="n">
-        <v>0.015268</v>
+        <v>0.01505</v>
       </c>
     </row>
     <row r="1204">
@@ -16069,7 +16069,7 @@
         <v>413</v>
       </c>
       <c r="C1204" t="n">
-        <v>0.015494</v>
+        <v>0.015152</v>
       </c>
     </row>
     <row r="1205">
@@ -16082,7 +16082,7 @@
         <v>414</v>
       </c>
       <c r="C1205" t="n">
-        <v>0.015618</v>
+        <v>0.015198</v>
       </c>
     </row>
     <row r="1206">
@@ -16095,7 +16095,7 @@
         <v>415</v>
       </c>
       <c r="C1206" t="n">
-        <v>0.015712</v>
+        <v>0.015592</v>
       </c>
     </row>
     <row r="1207">
@@ -16108,7 +16108,7 @@
         <v>416</v>
       </c>
       <c r="C1207" t="n">
-        <v>0.015714</v>
+        <v>0.015655</v>
       </c>
     </row>
     <row r="1208">
@@ -16121,7 +16121,7 @@
         <v>417</v>
       </c>
       <c r="C1208" t="n">
-        <v>0.015719</v>
+        <v>0.015667</v>
       </c>
     </row>
     <row r="1209">
@@ -16134,7 +16134,7 @@
         <v>418</v>
       </c>
       <c r="C1209" t="n">
-        <v>0.01583</v>
+        <v>0.015685</v>
       </c>
     </row>
     <row r="1210">
@@ -16147,7 +16147,7 @@
         <v>419</v>
       </c>
       <c r="C1210" t="n">
-        <v>0.01589</v>
+        <v>0.015783</v>
       </c>
     </row>
     <row r="1211">
@@ -16160,7 +16160,7 @@
         <v>420</v>
       </c>
       <c r="C1211" t="n">
-        <v>0.015995</v>
+        <v>0.015913</v>
       </c>
     </row>
     <row r="1212">
@@ -16173,7 +16173,7 @@
         <v>421</v>
       </c>
       <c r="C1212" t="n">
-        <v>0.016037</v>
+        <v>0.016039</v>
       </c>
     </row>
     <row r="1213">
@@ -16186,7 +16186,7 @@
         <v>422</v>
       </c>
       <c r="C1213" t="n">
-        <v>0.016066</v>
+        <v>0.016068</v>
       </c>
     </row>
     <row r="1214">
@@ -16199,7 +16199,7 @@
         <v>423</v>
       </c>
       <c r="C1214" t="n">
-        <v>0.016173</v>
+        <v>0.016093</v>
       </c>
     </row>
     <row r="1215">
@@ -16212,7 +16212,7 @@
         <v>424</v>
       </c>
       <c r="C1215" t="n">
-        <v>0.01674</v>
+        <v>0.016217</v>
       </c>
     </row>
     <row r="1216">
@@ -16225,7 +16225,7 @@
         <v>425</v>
       </c>
       <c r="C1216" t="n">
-        <v>0.016756</v>
+        <v>0.016262</v>
       </c>
     </row>
     <row r="1217">
@@ -16238,7 +16238,7 @@
         <v>426</v>
       </c>
       <c r="C1217" t="n">
-        <v>0.01685</v>
+        <v>0.016707</v>
       </c>
     </row>
     <row r="1218">
@@ -16251,7 +16251,7 @@
         <v>427</v>
       </c>
       <c r="C1218" t="n">
-        <v>0.016949</v>
+        <v>0.016786</v>
       </c>
     </row>
     <row r="1219">
@@ -16264,7 +16264,7 @@
         <v>428</v>
       </c>
       <c r="C1219" t="n">
-        <v>0.017346</v>
+        <v>0.017184</v>
       </c>
     </row>
     <row r="1220">
@@ -16277,7 +16277,7 @@
         <v>429</v>
       </c>
       <c r="C1220" t="n">
-        <v>0.017483</v>
+        <v>0.017421</v>
       </c>
     </row>
     <row r="1221">
@@ -16290,7 +16290,7 @@
         <v>430</v>
       </c>
       <c r="C1221" t="n">
-        <v>0.017684</v>
+        <v>0.017551</v>
       </c>
     </row>
     <row r="1222">
@@ -16303,7 +16303,7 @@
         <v>431</v>
       </c>
       <c r="C1222" t="n">
-        <v>0.018411</v>
+        <v>0.017851</v>
       </c>
     </row>
     <row r="1223">
@@ -16316,7 +16316,7 @@
         <v>432</v>
       </c>
       <c r="C1223" t="n">
-        <v>0.018473</v>
+        <v>0.018371</v>
       </c>
     </row>
     <row r="1224">
@@ -16329,7 +16329,7 @@
         <v>433</v>
       </c>
       <c r="C1224" t="n">
-        <v>0.018503</v>
+        <v>0.018431</v>
       </c>
     </row>
     <row r="1225">
@@ -16342,7 +16342,7 @@
         <v>434</v>
       </c>
       <c r="C1225" t="n">
-        <v>0.018611</v>
+        <v>0.01863</v>
       </c>
     </row>
     <row r="1226">
@@ -16355,7 +16355,7 @@
         <v>435</v>
       </c>
       <c r="C1226" t="n">
-        <v>0.018749</v>
+        <v>0.018824</v>
       </c>
     </row>
     <row r="1227">
@@ -16368,7 +16368,7 @@
         <v>436</v>
       </c>
       <c r="C1227" t="n">
-        <v>0.01901</v>
+        <v>0.018827</v>
       </c>
     </row>
     <row r="1228">
@@ -16381,7 +16381,7 @@
         <v>437</v>
       </c>
       <c r="C1228" t="n">
-        <v>0.019022</v>
+        <v>0.019025</v>
       </c>
     </row>
     <row r="1229">
@@ -16394,7 +16394,7 @@
         <v>438</v>
       </c>
       <c r="C1229" t="n">
-        <v>0.019322</v>
+        <v>0.019062</v>
       </c>
     </row>
     <row r="1230">
@@ -16407,7 +16407,7 @@
         <v>439</v>
       </c>
       <c r="C1230" t="n">
-        <v>0.019641</v>
+        <v>0.019306</v>
       </c>
     </row>
     <row r="1231">
@@ -16420,7 +16420,7 @@
         <v>440</v>
       </c>
       <c r="C1231" t="n">
-        <v>0.01968</v>
+        <v>0.019419</v>
       </c>
     </row>
     <row r="1232">
@@ -16433,7 +16433,7 @@
         <v>441</v>
       </c>
       <c r="C1232" t="n">
-        <v>0.019696</v>
+        <v>0.01958</v>
       </c>
     </row>
     <row r="1233">
@@ -16446,7 +16446,7 @@
         <v>442</v>
       </c>
       <c r="C1233" t="n">
-        <v>0.019838</v>
+        <v>0.019833</v>
       </c>
     </row>
     <row r="1234">
@@ -16459,7 +16459,7 @@
         <v>443</v>
       </c>
       <c r="C1234" t="n">
-        <v>0.01984</v>
+        <v>0.019865</v>
       </c>
     </row>
     <row r="1235">
@@ -16472,7 +16472,7 @@
         <v>444</v>
       </c>
       <c r="C1235" t="n">
-        <v>0.020056</v>
+        <v>0.01987</v>
       </c>
     </row>
     <row r="1236">
@@ -16485,7 +16485,7 @@
         <v>445</v>
       </c>
       <c r="C1236" t="n">
-        <v>0.020568</v>
+        <v>0.020072</v>
       </c>
     </row>
     <row r="1237">
@@ -16498,7 +16498,7 @@
         <v>446</v>
       </c>
       <c r="C1237" t="n">
-        <v>0.02065</v>
+        <v>0.02012</v>
       </c>
     </row>
     <row r="1238">
@@ -16511,7 +16511,7 @@
         <v>447</v>
       </c>
       <c r="C1238" t="n">
-        <v>0.020788</v>
+        <v>0.020754</v>
       </c>
     </row>
     <row r="1239">
@@ -16524,7 +16524,7 @@
         <v>448</v>
       </c>
       <c r="C1239" t="n">
-        <v>0.020836</v>
+        <v>0.020792</v>
       </c>
     </row>
     <row r="1240">
@@ -16537,7 +16537,7 @@
         <v>449</v>
       </c>
       <c r="C1240" t="n">
-        <v>0.021467</v>
+        <v>0.021145</v>
       </c>
     </row>
     <row r="1241">
@@ -16550,7 +16550,7 @@
         <v>450</v>
       </c>
       <c r="C1241" t="n">
-        <v>0.021726</v>
+        <v>0.021629</v>
       </c>
     </row>
     <row r="1242">
@@ -16563,7 +16563,7 @@
         <v>451</v>
       </c>
       <c r="C1242" t="n">
-        <v>0.021778</v>
+        <v>0.021773</v>
       </c>
     </row>
     <row r="1243">
@@ -16576,7 +16576,7 @@
         <v>452</v>
       </c>
       <c r="C1243" t="n">
-        <v>0.022623</v>
+        <v>0.022829</v>
       </c>
     </row>
     <row r="1244">
@@ -16589,7 +16589,7 @@
         <v>453</v>
       </c>
       <c r="C1244" t="n">
-        <v>0.022842</v>
+        <v>0.023012</v>
       </c>
     </row>
     <row r="1245">
@@ -16602,7 +16602,7 @@
         <v>454</v>
       </c>
       <c r="C1245" t="n">
-        <v>0.022956</v>
+        <v>0.023127</v>
       </c>
     </row>
     <row r="1246">
@@ -16615,7 +16615,7 @@
         <v>455</v>
       </c>
       <c r="C1246" t="n">
-        <v>0.024057</v>
+        <v>0.023137</v>
       </c>
     </row>
     <row r="1247">
@@ -16628,7 +16628,7 @@
         <v>456</v>
       </c>
       <c r="C1247" t="n">
-        <v>0.024188</v>
+        <v>0.02428</v>
       </c>
     </row>
     <row r="1248">
@@ -16641,7 +16641,7 @@
         <v>457</v>
       </c>
       <c r="C1248" t="n">
-        <v>0.024308</v>
+        <v>0.024661</v>
       </c>
     </row>
     <row r="1249">
@@ -16654,7 +16654,7 @@
         <v>458</v>
       </c>
       <c r="C1249" t="n">
-        <v>0.024592</v>
+        <v>0.024686</v>
       </c>
     </row>
     <row r="1250">
@@ -16667,7 +16667,7 @@
         <v>459</v>
       </c>
       <c r="C1250" t="n">
-        <v>0.024654</v>
+        <v>0.024733</v>
       </c>
     </row>
     <row r="1251">
@@ -16680,7 +16680,7 @@
         <v>460</v>
       </c>
       <c r="C1251" t="n">
-        <v>0.024926</v>
+        <v>0.025119</v>
       </c>
     </row>
     <row r="1252">
@@ -16693,7 +16693,7 @@
         <v>461</v>
       </c>
       <c r="C1252" t="n">
-        <v>0.025045</v>
+        <v>0.025139</v>
       </c>
     </row>
     <row r="1253">
@@ -16706,7 +16706,7 @@
         <v>462</v>
       </c>
       <c r="C1253" t="n">
-        <v>0.025211</v>
+        <v>0.025262</v>
       </c>
     </row>
     <row r="1254">
@@ -16719,7 +16719,7 @@
         <v>463</v>
       </c>
       <c r="C1254" t="n">
-        <v>0.02553</v>
+        <v>0.025648</v>
       </c>
     </row>
     <row r="1255">
@@ -16732,7 +16732,7 @@
         <v>464</v>
       </c>
       <c r="C1255" t="n">
-        <v>0.025842</v>
+        <v>0.025677</v>
       </c>
     </row>
     <row r="1256">
@@ -16745,7 +16745,7 @@
         <v>465</v>
       </c>
       <c r="C1256" t="n">
-        <v>0.025936</v>
+        <v>0.026139</v>
       </c>
     </row>
     <row r="1257">
@@ -16758,7 +16758,7 @@
         <v>466</v>
       </c>
       <c r="C1257" t="n">
-        <v>0.026144</v>
+        <v>0.026297</v>
       </c>
     </row>
     <row r="1258">
@@ -16771,7 +16771,7 @@
         <v>467</v>
       </c>
       <c r="C1258" t="n">
-        <v>0.027492</v>
+        <v>0.026431</v>
       </c>
     </row>
     <row r="1259">
@@ -16784,7 +16784,7 @@
         <v>468</v>
       </c>
       <c r="C1259" t="n">
-        <v>0.02779</v>
+        <v>0.026748</v>
       </c>
     </row>
     <row r="1260">
@@ -16797,7 +16797,7 @@
         <v>469</v>
       </c>
       <c r="C1260" t="n">
-        <v>0.027998</v>
+        <v>0.026931</v>
       </c>
     </row>
     <row r="1261">
@@ -16810,7 +16810,7 @@
         <v>470</v>
       </c>
       <c r="C1261" t="n">
-        <v>0.028042</v>
+        <v>0.02722</v>
       </c>
     </row>
     <row r="1262">
@@ -16823,7 +16823,7 @@
         <v>471</v>
       </c>
       <c r="C1262" t="n">
-        <v>0.028108</v>
+        <v>0.027517</v>
       </c>
     </row>
     <row r="1263">
@@ -16836,7 +16836,7 @@
         <v>472</v>
       </c>
       <c r="C1263" t="n">
-        <v>0.028532</v>
+        <v>0.027931</v>
       </c>
     </row>
     <row r="1264">
@@ -16849,7 +16849,7 @@
         <v>473</v>
       </c>
       <c r="C1264" t="n">
-        <v>0.029069</v>
+        <v>0.027959</v>
       </c>
     </row>
     <row r="1265">
@@ -16862,7 +16862,7 @@
         <v>474</v>
       </c>
       <c r="C1265" t="n">
-        <v>0.029198</v>
+        <v>0.028018</v>
       </c>
     </row>
     <row r="1266">
@@ -16875,7 +16875,7 @@
         <v>475</v>
       </c>
       <c r="C1266" t="n">
-        <v>0.029366</v>
+        <v>0.028237</v>
       </c>
     </row>
     <row r="1267">
@@ -16888,7 +16888,7 @@
         <v>476</v>
       </c>
       <c r="C1267" t="n">
-        <v>0.029384</v>
+        <v>0.028237</v>
       </c>
     </row>
     <row r="1268">
@@ -16901,7 +16901,7 @@
         <v>477</v>
       </c>
       <c r="C1268" t="n">
-        <v>0.029874</v>
+        <v>0.028384</v>
       </c>
     </row>
     <row r="1269">
@@ -16914,7 +16914,7 @@
         <v>478</v>
       </c>
       <c r="C1269" t="n">
-        <v>0.02999</v>
+        <v>0.028606</v>
       </c>
     </row>
     <row r="1270">
@@ -16927,7 +16927,7 @@
         <v>479</v>
       </c>
       <c r="C1270" t="n">
-        <v>0.030007</v>
+        <v>0.028889</v>
       </c>
     </row>
     <row r="1271">
@@ -16940,7 +16940,7 @@
         <v>480</v>
       </c>
       <c r="C1271" t="n">
-        <v>0.030052</v>
+        <v>0.029435</v>
       </c>
     </row>
     <row r="1272">
@@ -16953,7 +16953,7 @@
         <v>481</v>
       </c>
       <c r="C1272" t="n">
-        <v>0.030101</v>
+        <v>0.029533</v>
       </c>
     </row>
     <row r="1273">
@@ -16966,7 +16966,7 @@
         <v>482</v>
       </c>
       <c r="C1273" t="n">
-        <v>0.030264</v>
+        <v>0.02963</v>
       </c>
     </row>
     <row r="1274">
@@ -16979,7 +16979,7 @@
         <v>483</v>
       </c>
       <c r="C1274" t="n">
-        <v>0.030329</v>
+        <v>0.029938</v>
       </c>
     </row>
     <row r="1275">
@@ -16992,7 +16992,7 @@
         <v>484</v>
       </c>
       <c r="C1275" t="n">
-        <v>0.030334</v>
+        <v>0.030014</v>
       </c>
     </row>
     <row r="1276">
@@ -17005,7 +17005,7 @@
         <v>485</v>
       </c>
       <c r="C1276" t="n">
-        <v>0.030349</v>
+        <v>0.030014</v>
       </c>
     </row>
     <row r="1277">
@@ -17018,7 +17018,7 @@
         <v>486</v>
       </c>
       <c r="C1277" t="n">
-        <v>0.030866</v>
+        <v>0.030495</v>
       </c>
     </row>
     <row r="1278">
@@ -17031,7 +17031,7 @@
         <v>487</v>
       </c>
       <c r="C1278" t="n">
-        <v>0.031102</v>
+        <v>0.030752</v>
       </c>
     </row>
     <row r="1279">
@@ -17044,7 +17044,7 @@
         <v>488</v>
       </c>
       <c r="C1279" t="n">
-        <v>0.031178</v>
+        <v>0.030782</v>
       </c>
     </row>
     <row r="1280">
@@ -17057,7 +17057,7 @@
         <v>489</v>
       </c>
       <c r="C1280" t="n">
-        <v>0.031505</v>
+        <v>0.031291</v>
       </c>
     </row>
     <row r="1281">
@@ -17070,7 +17070,7 @@
         <v>490</v>
       </c>
       <c r="C1281" t="n">
-        <v>0.031576</v>
+        <v>0.031338</v>
       </c>
     </row>
     <row r="1282">
@@ -17083,7 +17083,7 @@
         <v>491</v>
       </c>
       <c r="C1282" t="n">
-        <v>0.031911</v>
+        <v>0.031621</v>
       </c>
     </row>
     <row r="1283">
@@ -17096,7 +17096,7 @@
         <v>492</v>
       </c>
       <c r="C1283" t="n">
-        <v>0.032521</v>
+        <v>0.032062</v>
       </c>
     </row>
     <row r="1284">
@@ -17109,7 +17109,7 @@
         <v>493</v>
       </c>
       <c r="C1284" t="n">
-        <v>0.032631</v>
+        <v>0.032133</v>
       </c>
     </row>
     <row r="1285">
@@ -17122,7 +17122,7 @@
         <v>494</v>
       </c>
       <c r="C1285" t="n">
-        <v>0.03296</v>
+        <v>0.03214</v>
       </c>
     </row>
     <row r="1286">
@@ -17135,7 +17135,7 @@
         <v>495</v>
       </c>
       <c r="C1286" t="n">
-        <v>0.033306</v>
+        <v>0.032614</v>
       </c>
     </row>
     <row r="1287">
@@ -17148,7 +17148,7 @@
         <v>496</v>
       </c>
       <c r="C1287" t="n">
-        <v>0.033461</v>
+        <v>0.032681</v>
       </c>
     </row>
     <row r="1288">
@@ -17161,7 +17161,7 @@
         <v>497</v>
       </c>
       <c r="C1288" t="n">
-        <v>0.033506</v>
+        <v>0.032742</v>
       </c>
     </row>
     <row r="1289">
@@ -17174,7 +17174,7 @@
         <v>498</v>
       </c>
       <c r="C1289" t="n">
-        <v>0.033977</v>
+        <v>0.033512</v>
       </c>
     </row>
     <row r="1290">
@@ -17187,7 +17187,7 @@
         <v>499</v>
       </c>
       <c r="C1290" t="n">
-        <v>0.034058</v>
+        <v>0.033553</v>
       </c>
     </row>
     <row r="1291">
@@ -17200,7 +17200,7 @@
         <v>500</v>
       </c>
       <c r="C1291" t="n">
-        <v>0.034761</v>
+        <v>0.033879</v>
       </c>
     </row>
     <row r="1292">
@@ -17213,7 +17213,7 @@
         <v>501</v>
       </c>
       <c r="C1292" t="n">
-        <v>0.034826</v>
+        <v>0.033996</v>
       </c>
     </row>
     <row r="1293">
@@ -17226,7 +17226,7 @@
         <v>502</v>
       </c>
       <c r="C1293" t="n">
-        <v>0.035429</v>
+        <v>0.034831</v>
       </c>
     </row>
     <row r="1294">
@@ -17239,7 +17239,7 @@
         <v>503</v>
       </c>
       <c r="C1294" t="n">
-        <v>0.035769</v>
+        <v>0.034843</v>
       </c>
     </row>
     <row r="1295">
@@ -17252,7 +17252,7 @@
         <v>504</v>
       </c>
       <c r="C1295" t="n">
-        <v>0.035945</v>
+        <v>0.035081</v>
       </c>
     </row>
     <row r="1296">
@@ -17265,7 +17265,7 @@
         <v>505</v>
       </c>
       <c r="C1296" t="n">
-        <v>0.035949</v>
+        <v>0.035159</v>
       </c>
     </row>
     <row r="1297">
@@ -17278,7 +17278,7 @@
         <v>506</v>
       </c>
       <c r="C1297" t="n">
-        <v>0.036172</v>
+        <v>0.035301</v>
       </c>
     </row>
     <row r="1298">
@@ -17291,7 +17291,7 @@
         <v>507</v>
       </c>
       <c r="C1298" t="n">
-        <v>0.036471</v>
+        <v>0.035618</v>
       </c>
     </row>
     <row r="1299">
@@ -17304,7 +17304,7 @@
         <v>508</v>
       </c>
       <c r="C1299" t="n">
-        <v>0.036569</v>
+        <v>0.035935</v>
       </c>
     </row>
     <row r="1300">
@@ -17317,7 +17317,7 @@
         <v>509</v>
       </c>
       <c r="C1300" t="n">
-        <v>0.036575</v>
+        <v>0.036126</v>
       </c>
     </row>
     <row r="1301">
@@ -17330,7 +17330,7 @@
         <v>510</v>
       </c>
       <c r="C1301" t="n">
-        <v>0.036834</v>
+        <v>0.036553</v>
       </c>
     </row>
     <row r="1302">
@@ -17343,7 +17343,7 @@
         <v>511</v>
       </c>
       <c r="C1302" t="n">
-        <v>0.03721</v>
+        <v>0.036565</v>
       </c>
     </row>
     <row r="1303">
@@ -17356,7 +17356,7 @@
         <v>512</v>
       </c>
       <c r="C1303" t="n">
-        <v>0.037261</v>
+        <v>0.036771</v>
       </c>
     </row>
     <row r="1304">
@@ -17369,7 +17369,7 @@
         <v>513</v>
       </c>
       <c r="C1304" t="n">
-        <v>0.037564</v>
+        <v>0.037006</v>
       </c>
     </row>
     <row r="1305">
@@ -17382,7 +17382,7 @@
         <v>514</v>
       </c>
       <c r="C1305" t="n">
-        <v>0.037868</v>
+        <v>0.037062</v>
       </c>
     </row>
     <row r="1306">
@@ -17395,7 +17395,7 @@
         <v>515</v>
       </c>
       <c r="C1306" t="n">
-        <v>0.03797</v>
+        <v>0.037485</v>
       </c>
     </row>
     <row r="1307">
@@ -17408,7 +17408,7 @@
         <v>516</v>
       </c>
       <c r="C1307" t="n">
-        <v>0.038091</v>
+        <v>0.037533</v>
       </c>
     </row>
     <row r="1308">
@@ -17421,7 +17421,7 @@
         <v>517</v>
       </c>
       <c r="C1308" t="n">
-        <v>0.038122</v>
+        <v>0.037652</v>
       </c>
     </row>
     <row r="1309">
@@ -17434,7 +17434,7 @@
         <v>518</v>
       </c>
       <c r="C1309" t="n">
-        <v>0.038558</v>
+        <v>0.037693</v>
       </c>
     </row>
     <row r="1310">
@@ -17447,7 +17447,7 @@
         <v>519</v>
       </c>
       <c r="C1310" t="n">
-        <v>0.038837</v>
+        <v>0.037746</v>
       </c>
     </row>
     <row r="1311">
@@ -17460,7 +17460,7 @@
         <v>520</v>
       </c>
       <c r="C1311" t="n">
-        <v>0.039063</v>
+        <v>0.038031</v>
       </c>
     </row>
     <row r="1312">
@@ -17473,7 +17473,7 @@
         <v>521</v>
       </c>
       <c r="C1312" t="n">
-        <v>0.03927</v>
+        <v>0.038073</v>
       </c>
     </row>
     <row r="1313">
@@ -17486,7 +17486,7 @@
         <v>522</v>
       </c>
       <c r="C1313" t="n">
-        <v>0.039336</v>
+        <v>0.038217</v>
       </c>
     </row>
     <row r="1314">
@@ -17499,7 +17499,7 @@
         <v>523</v>
       </c>
       <c r="C1314" t="n">
-        <v>0.039622</v>
+        <v>0.0383</v>
       </c>
     </row>
     <row r="1315">
@@ -17512,7 +17512,7 @@
         <v>524</v>
       </c>
       <c r="C1315" t="n">
-        <v>0.039664</v>
+        <v>0.038477</v>
       </c>
     </row>
     <row r="1316">
@@ -17525,7 +17525,7 @@
         <v>525</v>
       </c>
       <c r="C1316" t="n">
-        <v>0.040071</v>
+        <v>0.039129</v>
       </c>
     </row>
     <row r="1317">
@@ -17538,7 +17538,7 @@
         <v>526</v>
       </c>
       <c r="C1317" t="n">
-        <v>0.040533</v>
+        <v>0.039294</v>
       </c>
     </row>
     <row r="1318">
@@ -17551,7 +17551,7 @@
         <v>527</v>
       </c>
       <c r="C1318" t="n">
-        <v>0.040602</v>
+        <v>0.039305</v>
       </c>
     </row>
     <row r="1319">
@@ -17564,7 +17564,7 @@
         <v>528</v>
       </c>
       <c r="C1319" t="n">
-        <v>0.040836</v>
+        <v>0.039587</v>
       </c>
     </row>
     <row r="1320">
@@ -17577,7 +17577,7 @@
         <v>529</v>
       </c>
       <c r="C1320" t="n">
-        <v>0.041045</v>
+        <v>0.039739</v>
       </c>
     </row>
     <row r="1321">
@@ -17590,7 +17590,7 @@
         <v>530</v>
       </c>
       <c r="C1321" t="n">
-        <v>0.041087</v>
+        <v>0.039831</v>
       </c>
     </row>
     <row r="1322">
@@ -17603,7 +17603,7 @@
         <v>531</v>
       </c>
       <c r="C1322" t="n">
-        <v>0.041097</v>
+        <v>0.040232</v>
       </c>
     </row>
     <row r="1323">
@@ -17616,7 +17616,7 @@
         <v>532</v>
       </c>
       <c r="C1323" t="n">
-        <v>0.041174</v>
+        <v>0.040352</v>
       </c>
     </row>
     <row r="1324">
@@ -17629,7 +17629,7 @@
         <v>533</v>
       </c>
       <c r="C1324" t="n">
-        <v>0.042121</v>
+        <v>0.040387</v>
       </c>
     </row>
     <row r="1325">
@@ -17642,7 +17642,7 @@
         <v>534</v>
       </c>
       <c r="C1325" t="n">
-        <v>0.042124</v>
+        <v>0.040715</v>
       </c>
     </row>
     <row r="1326">
@@ -17655,7 +17655,7 @@
         <v>535</v>
       </c>
       <c r="C1326" t="n">
-        <v>0.042135</v>
+        <v>0.040998</v>
       </c>
     </row>
     <row r="1327">
@@ -17668,7 +17668,7 @@
         <v>536</v>
       </c>
       <c r="C1327" t="n">
-        <v>0.042335</v>
+        <v>0.041161</v>
       </c>
     </row>
     <row r="1328">
@@ -17681,7 +17681,7 @@
         <v>537</v>
       </c>
       <c r="C1328" t="n">
-        <v>0.042834</v>
+        <v>0.041806</v>
       </c>
     </row>
     <row r="1329">
@@ -17694,7 +17694,7 @@
         <v>538</v>
       </c>
       <c r="C1329" t="n">
-        <v>0.043603</v>
+        <v>0.042036</v>
       </c>
     </row>
     <row r="1330">
@@ -17707,7 +17707,7 @@
         <v>539</v>
       </c>
       <c r="C1330" t="n">
-        <v>0.043892</v>
+        <v>0.042238</v>
       </c>
     </row>
     <row r="1331">
@@ -17720,7 +17720,7 @@
         <v>540</v>
       </c>
       <c r="C1331" t="n">
-        <v>0.043913</v>
+        <v>0.042335</v>
       </c>
     </row>
     <row r="1332">
@@ -17733,7 +17733,7 @@
         <v>541</v>
       </c>
       <c r="C1332" t="n">
-        <v>0.044188</v>
+        <v>0.042679</v>
       </c>
     </row>
     <row r="1333">
@@ -17746,7 +17746,7 @@
         <v>542</v>
       </c>
       <c r="C1333" t="n">
-        <v>0.044236</v>
+        <v>0.042684</v>
       </c>
     </row>
     <row r="1334">
@@ -17759,7 +17759,7 @@
         <v>543</v>
       </c>
       <c r="C1334" t="n">
-        <v>0.044332</v>
+        <v>0.04271</v>
       </c>
     </row>
     <row r="1335">
@@ -17772,7 +17772,7 @@
         <v>544</v>
       </c>
       <c r="C1335" t="n">
-        <v>0.044334</v>
+        <v>0.042816</v>
       </c>
     </row>
     <row r="1336">
@@ -17785,7 +17785,7 @@
         <v>545</v>
       </c>
       <c r="C1336" t="n">
-        <v>0.045101</v>
+        <v>0.043264</v>
       </c>
     </row>
     <row r="1337">
@@ -17798,7 +17798,7 @@
         <v>546</v>
       </c>
       <c r="C1337" t="n">
-        <v>0.045121</v>
+        <v>0.043568</v>
       </c>
     </row>
     <row r="1338">
@@ -17811,7 +17811,7 @@
         <v>547</v>
       </c>
       <c r="C1338" t="n">
-        <v>0.04519</v>
+        <v>0.043751</v>
       </c>
     </row>
     <row r="1339">
@@ -17824,7 +17824,7 @@
         <v>548</v>
       </c>
       <c r="C1339" t="n">
-        <v>0.045236</v>
+        <v>0.044079</v>
       </c>
     </row>
     <row r="1340">
@@ -17837,7 +17837,7 @@
         <v>549</v>
       </c>
       <c r="C1340" t="n">
-        <v>0.045424</v>
+        <v>0.044107</v>
       </c>
     </row>
     <row r="1341">
@@ -17850,7 +17850,7 @@
         <v>550</v>
       </c>
       <c r="C1341" t="n">
-        <v>0.045669</v>
+        <v>0.044746</v>
       </c>
     </row>
     <row r="1342">
@@ -17863,7 +17863,7 @@
         <v>551</v>
       </c>
       <c r="C1342" t="n">
-        <v>0.045739</v>
+        <v>0.044881</v>
       </c>
     </row>
     <row r="1343">
@@ -17876,7 +17876,7 @@
         <v>552</v>
       </c>
       <c r="C1343" t="n">
-        <v>0.045946</v>
+        <v>0.045163</v>
       </c>
     </row>
     <row r="1344">
@@ -17889,7 +17889,7 @@
         <v>553</v>
       </c>
       <c r="C1344" t="n">
-        <v>0.046613</v>
+        <v>0.045305</v>
       </c>
     </row>
     <row r="1345">
@@ -17902,7 +17902,7 @@
         <v>554</v>
       </c>
       <c r="C1345" t="n">
-        <v>0.046744</v>
+        <v>0.046818</v>
       </c>
     </row>
     <row r="1346">
@@ -17915,7 +17915,7 @@
         <v>555</v>
       </c>
       <c r="C1346" t="n">
-        <v>0.047391</v>
+        <v>0.047266</v>
       </c>
     </row>
     <row r="1347">
@@ -17928,7 +17928,7 @@
         <v>556</v>
       </c>
       <c r="C1347" t="n">
-        <v>0.047476</v>
+        <v>0.047561</v>
       </c>
     </row>
     <row r="1348">
@@ -17941,7 +17941,7 @@
         <v>557</v>
       </c>
       <c r="C1348" t="n">
-        <v>0.048257</v>
+        <v>0.048013</v>
       </c>
     </row>
     <row r="1349">
@@ -17954,7 +17954,7 @@
         <v>558</v>
       </c>
       <c r="C1349" t="n">
-        <v>0.048968</v>
+        <v>0.0486</v>
       </c>
     </row>
     <row r="1350">
@@ -17967,7 +17967,7 @@
         <v>559</v>
       </c>
       <c r="C1350" t="n">
-        <v>0.049272</v>
+        <v>0.048833</v>
       </c>
     </row>
     <row r="1351">
@@ -17980,7 +17980,7 @@
         <v>560</v>
       </c>
       <c r="C1351" t="n">
-        <v>0.049435</v>
+        <v>0.04886</v>
       </c>
     </row>
     <row r="1352">
@@ -17993,7 +17993,7 @@
         <v>561</v>
       </c>
       <c r="C1352" t="n">
-        <v>0.049466</v>
+        <v>0.049067</v>
       </c>
     </row>
     <row r="1353">
@@ -18006,7 +18006,7 @@
         <v>562</v>
       </c>
       <c r="C1353" t="n">
-        <v>0.049708</v>
+        <v>0.049204</v>
       </c>
     </row>
     <row r="1354">
@@ -18019,7 +18019,7 @@
         <v>563</v>
       </c>
       <c r="C1354" t="n">
-        <v>0.04972</v>
+        <v>0.049505</v>
       </c>
     </row>
     <row r="1355">
@@ -18032,7 +18032,7 @@
         <v>564</v>
       </c>
       <c r="C1355" t="n">
-        <v>0.05032</v>
+        <v>0.049639</v>
       </c>
     </row>
     <row r="1356">
@@ -18045,7 +18045,7 @@
         <v>565</v>
       </c>
       <c r="C1356" t="n">
-        <v>0.050505</v>
+        <v>0.050096</v>
       </c>
     </row>
     <row r="1357">
@@ -18058,7 +18058,7 @@
         <v>566</v>
       </c>
       <c r="C1357" t="n">
-        <v>0.051549</v>
+        <v>0.050492</v>
       </c>
     </row>
     <row r="1358">
@@ -18071,7 +18071,7 @@
         <v>567</v>
       </c>
       <c r="C1358" t="n">
-        <v>0.05176</v>
+        <v>0.050526</v>
       </c>
     </row>
     <row r="1359">
@@ -18084,7 +18084,7 @@
         <v>568</v>
       </c>
       <c r="C1359" t="n">
-        <v>0.052841</v>
+        <v>0.051557</v>
       </c>
     </row>
     <row r="1360">
@@ -18097,7 +18097,7 @@
         <v>569</v>
       </c>
       <c r="C1360" t="n">
-        <v>0.05288</v>
+        <v>0.051627</v>
       </c>
     </row>
     <row r="1361">
@@ -18110,7 +18110,7 @@
         <v>570</v>
       </c>
       <c r="C1361" t="n">
-        <v>0.052886</v>
+        <v>0.052538</v>
       </c>
     </row>
     <row r="1362">
@@ -18123,7 +18123,7 @@
         <v>571</v>
       </c>
       <c r="C1362" t="n">
-        <v>0.052938</v>
+        <v>0.05308</v>
       </c>
     </row>
     <row r="1363">
@@ -18136,7 +18136,7 @@
         <v>572</v>
       </c>
       <c r="C1363" t="n">
-        <v>0.05331</v>
+        <v>0.053217</v>
       </c>
     </row>
     <row r="1364">
@@ -18149,7 +18149,7 @@
         <v>573</v>
       </c>
       <c r="C1364" t="n">
-        <v>0.053734</v>
+        <v>0.053375</v>
       </c>
     </row>
     <row r="1365">
@@ -18162,7 +18162,7 @@
         <v>574</v>
       </c>
       <c r="C1365" t="n">
-        <v>0.054402</v>
+        <v>0.053593</v>
       </c>
     </row>
     <row r="1366">
@@ -18175,7 +18175,7 @@
         <v>575</v>
       </c>
       <c r="C1366" t="n">
-        <v>0.054569</v>
+        <v>0.05362</v>
       </c>
     </row>
     <row r="1367">
@@ -18188,7 +18188,7 @@
         <v>576</v>
       </c>
       <c r="C1367" t="n">
-        <v>0.054769</v>
+        <v>0.054666</v>
       </c>
     </row>
     <row r="1368">
@@ -18201,7 +18201,7 @@
         <v>577</v>
       </c>
       <c r="C1368" t="n">
-        <v>0.055034</v>
+        <v>0.054871</v>
       </c>
     </row>
     <row r="1369">
@@ -18214,7 +18214,7 @@
         <v>578</v>
       </c>
       <c r="C1369" t="n">
-        <v>0.056156</v>
+        <v>0.055241</v>
       </c>
     </row>
     <row r="1370">
@@ -18227,7 +18227,7 @@
         <v>579</v>
       </c>
       <c r="C1370" t="n">
-        <v>0.05621</v>
+        <v>0.055289</v>
       </c>
     </row>
     <row r="1371">
@@ -18240,7 +18240,7 @@
         <v>580</v>
       </c>
       <c r="C1371" t="n">
-        <v>0.056869</v>
+        <v>0.055782</v>
       </c>
     </row>
     <row r="1372">
@@ -18253,7 +18253,7 @@
         <v>581</v>
       </c>
       <c r="C1372" t="n">
-        <v>0.05697</v>
+        <v>0.056428</v>
       </c>
     </row>
     <row r="1373">
@@ -18266,7 +18266,7 @@
         <v>582</v>
       </c>
       <c r="C1373" t="n">
-        <v>0.057173</v>
+        <v>0.056868</v>
       </c>
     </row>
     <row r="1374">
@@ -18279,7 +18279,7 @@
         <v>583</v>
       </c>
       <c r="C1374" t="n">
-        <v>0.059445</v>
+        <v>0.057239</v>
       </c>
     </row>
     <row r="1375">
@@ -18292,7 +18292,7 @@
         <v>584</v>
       </c>
       <c r="C1375" t="n">
-        <v>0.059701</v>
+        <v>0.057427</v>
       </c>
     </row>
     <row r="1376">
@@ -18305,7 +18305,7 @@
         <v>585</v>
       </c>
       <c r="C1376" t="n">
-        <v>0.060067</v>
+        <v>0.057667</v>
       </c>
     </row>
     <row r="1377">
@@ -18318,7 +18318,7 @@
         <v>586</v>
       </c>
       <c r="C1377" t="n">
-        <v>0.060115</v>
+        <v>0.059213</v>
       </c>
     </row>
     <row r="1378">
@@ -18331,7 +18331,7 @@
         <v>587</v>
       </c>
       <c r="C1378" t="n">
-        <v>0.060406</v>
+        <v>0.059446</v>
       </c>
     </row>
     <row r="1379">
@@ -18344,7 +18344,7 @@
         <v>588</v>
       </c>
       <c r="C1379" t="n">
-        <v>0.060776</v>
+        <v>0.059935</v>
       </c>
     </row>
     <row r="1380">
@@ -18357,7 +18357,7 @@
         <v>589</v>
       </c>
       <c r="C1380" t="n">
-        <v>0.060955</v>
+        <v>0.060226</v>
       </c>
     </row>
     <row r="1381">
@@ -18370,7 +18370,7 @@
         <v>590</v>
       </c>
       <c r="C1381" t="n">
-        <v>0.061256</v>
+        <v>0.060659</v>
       </c>
     </row>
     <row r="1382">
@@ -18383,7 +18383,7 @@
         <v>591</v>
       </c>
       <c r="C1382" t="n">
-        <v>0.062174</v>
+        <v>0.060668</v>
       </c>
     </row>
     <row r="1383">
@@ -18396,7 +18396,7 @@
         <v>592</v>
       </c>
       <c r="C1383" t="n">
-        <v>0.062277</v>
+        <v>0.060909</v>
       </c>
     </row>
     <row r="1384">
@@ -18409,7 +18409,7 @@
         <v>593</v>
       </c>
       <c r="C1384" t="n">
-        <v>0.062447</v>
+        <v>0.060942</v>
       </c>
     </row>
     <row r="1385">
@@ -18422,7 +18422,7 @@
         <v>594</v>
       </c>
       <c r="C1385" t="n">
-        <v>0.062663</v>
+        <v>0.061118</v>
       </c>
     </row>
     <row r="1386">
@@ -18435,7 +18435,7 @@
         <v>595</v>
       </c>
       <c r="C1386" t="n">
-        <v>0.063208</v>
+        <v>0.061564</v>
       </c>
     </row>
     <row r="1387">
@@ -18448,7 +18448,7 @@
         <v>596</v>
       </c>
       <c r="C1387" t="n">
-        <v>0.063245</v>
+        <v>0.062491</v>
       </c>
     </row>
     <row r="1388">
@@ -18461,7 +18461,7 @@
         <v>597</v>
       </c>
       <c r="C1388" t="n">
-        <v>0.063481</v>
+        <v>0.062502</v>
       </c>
     </row>
     <row r="1389">
@@ -18474,7 +18474,7 @@
         <v>598</v>
       </c>
       <c r="C1389" t="n">
-        <v>0.063656</v>
+        <v>0.06349200000000001</v>
       </c>
     </row>
     <row r="1390">
@@ -18487,7 +18487,7 @@
         <v>599</v>
       </c>
       <c r="C1390" t="n">
-        <v>0.063939</v>
+        <v>0.063793</v>
       </c>
     </row>
     <row r="1391">
@@ -18500,7 +18500,7 @@
         <v>600</v>
       </c>
       <c r="C1391" t="n">
-        <v>0.06410299999999999</v>
+        <v>0.06407400000000001</v>
       </c>
     </row>
     <row r="1392">
@@ -18513,7 +18513,7 @@
         <v>601</v>
       </c>
       <c r="C1392" t="n">
-        <v>0.064327</v>
+        <v>0.064083</v>
       </c>
     </row>
     <row r="1393">
@@ -18526,7 +18526,7 @@
         <v>602</v>
       </c>
       <c r="C1393" t="n">
-        <v>0.064913</v>
+        <v>0.064193</v>
       </c>
     </row>
     <row r="1394">
@@ -18539,7 +18539,7 @@
         <v>603</v>
       </c>
       <c r="C1394" t="n">
-        <v>0.06506000000000001</v>
+        <v>0.064263</v>
       </c>
     </row>
     <row r="1395">
@@ -18552,7 +18552,7 @@
         <v>604</v>
       </c>
       <c r="C1395" t="n">
-        <v>0.06518500000000001</v>
+        <v>0.064683</v>
       </c>
     </row>
     <row r="1396">
@@ -18565,7 +18565,7 @@
         <v>605</v>
       </c>
       <c r="C1396" t="n">
-        <v>0.06619700000000001</v>
+        <v>0.064708</v>
       </c>
     </row>
     <row r="1397">
@@ -18578,7 +18578,7 @@
         <v>606</v>
       </c>
       <c r="C1397" t="n">
-        <v>0.06743300000000001</v>
+        <v>0.065014</v>
       </c>
     </row>
     <row r="1398">
@@ -18591,7 +18591,7 @@
         <v>607</v>
       </c>
       <c r="C1398" t="n">
-        <v>0.067647</v>
+        <v>0.06503100000000001</v>
       </c>
     </row>
     <row r="1399">
@@ -18604,7 +18604,7 @@
         <v>608</v>
       </c>
       <c r="C1399" t="n">
-        <v>0.067735</v>
+        <v>0.065346</v>
       </c>
     </row>
     <row r="1400">
@@ -18617,7 +18617,7 @@
         <v>609</v>
       </c>
       <c r="C1400" t="n">
-        <v>0.067963</v>
+        <v>0.06557499999999999</v>
       </c>
     </row>
     <row r="1401">
@@ -18630,7 +18630,7 @@
         <v>610</v>
       </c>
       <c r="C1401" t="n">
-        <v>0.068125</v>
+        <v>0.06566</v>
       </c>
     </row>
     <row r="1402">
@@ -18643,7 +18643,7 @@
         <v>611</v>
       </c>
       <c r="C1402" t="n">
-        <v>0.068352</v>
+        <v>0.06707299999999999</v>
       </c>
     </row>
     <row r="1403">
@@ -18656,7 +18656,7 @@
         <v>612</v>
       </c>
       <c r="C1403" t="n">
-        <v>0.068423</v>
+        <v>0.067288</v>
       </c>
     </row>
     <row r="1404">
@@ -18669,7 +18669,7 @@
         <v>613</v>
       </c>
       <c r="C1404" t="n">
-        <v>0.06929200000000001</v>
+        <v>0.067457</v>
       </c>
     </row>
     <row r="1405">
@@ -18682,7 +18682,7 @@
         <v>614</v>
       </c>
       <c r="C1405" t="n">
-        <v>0.069494</v>
+        <v>0.06748800000000001</v>
       </c>
     </row>
     <row r="1406">
@@ -18695,7 +18695,7 @@
         <v>615</v>
       </c>
       <c r="C1406" t="n">
-        <v>0.069505</v>
+        <v>0.06770900000000001</v>
       </c>
     </row>
     <row r="1407">
@@ -18708,7 +18708,7 @@
         <v>616</v>
       </c>
       <c r="C1407" t="n">
-        <v>0.06967</v>
+        <v>0.06825100000000001</v>
       </c>
     </row>
     <row r="1408">
@@ -18721,7 +18721,7 @@
         <v>617</v>
       </c>
       <c r="C1408" t="n">
-        <v>0.069697</v>
+        <v>0.068319</v>
       </c>
     </row>
     <row r="1409">
@@ -18734,7 +18734,7 @@
         <v>618</v>
       </c>
       <c r="C1409" t="n">
-        <v>0.069857</v>
+        <v>0.068482</v>
       </c>
     </row>
     <row r="1410">
@@ -18747,7 +18747,7 @@
         <v>619</v>
       </c>
       <c r="C1410" t="n">
-        <v>0.070039</v>
+        <v>0.068897</v>
       </c>
     </row>
     <row r="1411">
@@ -18760,7 +18760,7 @@
         <v>620</v>
       </c>
       <c r="C1411" t="n">
-        <v>0.070299</v>
+        <v>0.06959700000000001</v>
       </c>
     </row>
     <row r="1412">
@@ -18773,7 +18773,7 @@
         <v>621</v>
       </c>
       <c r="C1412" t="n">
-        <v>0.070324</v>
+        <v>0.06983200000000001</v>
       </c>
     </row>
     <row r="1413">
@@ -18786,7 +18786,7 @@
         <v>622</v>
       </c>
       <c r="C1413" t="n">
-        <v>0.071003</v>
+        <v>0.06997200000000001</v>
       </c>
     </row>
     <row r="1414">
@@ -18799,7 +18799,7 @@
         <v>623</v>
       </c>
       <c r="C1414" t="n">
-        <v>0.07116599999999999</v>
+        <v>0.070104</v>
       </c>
     </row>
     <row r="1415">
@@ -18812,7 +18812,7 @@
         <v>624</v>
       </c>
       <c r="C1415" t="n">
-        <v>0.071436</v>
+        <v>0.07015299999999999</v>
       </c>
     </row>
     <row r="1416">
@@ -18825,7 +18825,7 @@
         <v>625</v>
       </c>
       <c r="C1416" t="n">
-        <v>0.071475</v>
+        <v>0.07027</v>
       </c>
     </row>
     <row r="1417">
@@ -18838,7 +18838,7 @@
         <v>626</v>
       </c>
       <c r="C1417" t="n">
-        <v>0.071592</v>
+        <v>0.07121</v>
       </c>
     </row>
     <row r="1418">
@@ -18851,7 +18851,7 @@
         <v>627</v>
       </c>
       <c r="C1418" t="n">
-        <v>0.071677</v>
+        <v>0.07148</v>
       </c>
     </row>
     <row r="1419">
@@ -18864,7 +18864,7 @@
         <v>628</v>
       </c>
       <c r="C1419" t="n">
-        <v>0.072135</v>
+        <v>0.07192900000000001</v>
       </c>
     </row>
     <row r="1420">
@@ -18877,7 +18877,7 @@
         <v>629</v>
       </c>
       <c r="C1420" t="n">
-        <v>0.072495</v>
+        <v>0.072209</v>
       </c>
     </row>
     <row r="1421">
@@ -18890,7 +18890,7 @@
         <v>630</v>
       </c>
       <c r="C1421" t="n">
-        <v>0.072976</v>
+        <v>0.07222000000000001</v>
       </c>
     </row>
     <row r="1422">
@@ -18903,7 +18903,7 @@
         <v>631</v>
       </c>
       <c r="C1422" t="n">
-        <v>0.073297</v>
+        <v>0.072326</v>
       </c>
     </row>
     <row r="1423">
@@ -18916,7 +18916,7 @@
         <v>632</v>
       </c>
       <c r="C1423" t="n">
-        <v>0.07363500000000001</v>
+        <v>0.072334</v>
       </c>
     </row>
     <row r="1424">
@@ -18929,7 +18929,7 @@
         <v>633</v>
       </c>
       <c r="C1424" t="n">
-        <v>0.074832</v>
+        <v>0.072629</v>
       </c>
     </row>
     <row r="1425">
@@ -18942,7 +18942,7 @@
         <v>634</v>
       </c>
       <c r="C1425" t="n">
-        <v>0.074849</v>
+        <v>0.073333</v>
       </c>
     </row>
     <row r="1426">
@@ -18955,7 +18955,7 @@
         <v>635</v>
       </c>
       <c r="C1426" t="n">
-        <v>0.075041</v>
+        <v>0.073546</v>
       </c>
     </row>
     <row r="1427">
@@ -18968,7 +18968,7 @@
         <v>636</v>
       </c>
       <c r="C1427" t="n">
-        <v>0.075097</v>
+        <v>0.073657</v>
       </c>
     </row>
     <row r="1428">
@@ -18981,7 +18981,7 @@
         <v>637</v>
       </c>
       <c r="C1428" t="n">
-        <v>0.07513400000000001</v>
+        <v>0.073808</v>
       </c>
     </row>
     <row r="1429">
@@ -18994,7 +18994,7 @@
         <v>638</v>
       </c>
       <c r="C1429" t="n">
-        <v>0.076284</v>
+        <v>0.074457</v>
       </c>
     </row>
     <row r="1430">
@@ -19007,7 +19007,7 @@
         <v>639</v>
       </c>
       <c r="C1430" t="n">
-        <v>0.07717499999999999</v>
+        <v>0.074841</v>
       </c>
     </row>
     <row r="1431">
@@ -19020,7 +19020,7 @@
         <v>640</v>
       </c>
       <c r="C1431" t="n">
-        <v>0.077227</v>
+        <v>0.074986</v>
       </c>
     </row>
     <row r="1432">
@@ -19033,7 +19033,7 @@
         <v>641</v>
       </c>
       <c r="C1432" t="n">
-        <v>0.077417</v>
+        <v>0.075199</v>
       </c>
     </row>
     <row r="1433">
@@ -19046,7 +19046,7 @@
         <v>642</v>
       </c>
       <c r="C1433" t="n">
-        <v>0.07825500000000001</v>
+        <v>0.07555099999999999</v>
       </c>
     </row>
     <row r="1434">
@@ -19059,7 +19059,7 @@
         <v>643</v>
       </c>
       <c r="C1434" t="n">
-        <v>0.07835499999999999</v>
+        <v>0.075748</v>
       </c>
     </row>
     <row r="1435">
@@ -19072,7 +19072,7 @@
         <v>644</v>
       </c>
       <c r="C1435" t="n">
-        <v>0.07872800000000001</v>
+        <v>0.07605000000000001</v>
       </c>
     </row>
     <row r="1436">
@@ -19085,7 +19085,7 @@
         <v>645</v>
       </c>
       <c r="C1436" t="n">
-        <v>0.078846</v>
+        <v>0.076889</v>
       </c>
     </row>
     <row r="1437">
@@ -19098,7 +19098,7 @@
         <v>646</v>
       </c>
       <c r="C1437" t="n">
-        <v>0.078985</v>
+        <v>0.078237</v>
       </c>
     </row>
     <row r="1438">
@@ -19111,7 +19111,7 @@
         <v>647</v>
       </c>
       <c r="C1438" t="n">
-        <v>0.079128</v>
+        <v>0.078781</v>
       </c>
     </row>
     <row r="1439">
@@ -19124,7 +19124,7 @@
         <v>648</v>
       </c>
       <c r="C1439" t="n">
-        <v>0.079625</v>
+        <v>0.079085</v>
       </c>
     </row>
     <row r="1440">
@@ -19137,7 +19137,7 @@
         <v>649</v>
       </c>
       <c r="C1440" t="n">
-        <v>0.080016</v>
+        <v>0.079746</v>
       </c>
     </row>
     <row r="1441">
@@ -19150,7 +19150,7 @@
         <v>650</v>
       </c>
       <c r="C1441" t="n">
-        <v>0.080982</v>
+        <v>0.079816</v>
       </c>
     </row>
     <row r="1442">
@@ -19163,7 +19163,7 @@
         <v>651</v>
       </c>
       <c r="C1442" t="n">
-        <v>0.08172599999999999</v>
+        <v>0.079848</v>
       </c>
     </row>
     <row r="1443">
@@ -19176,7 +19176,7 @@
         <v>652</v>
       </c>
       <c r="C1443" t="n">
-        <v>0.082027</v>
+        <v>0.08075599999999999</v>
       </c>
     </row>
     <row r="1444">
@@ -19189,7 +19189,7 @@
         <v>653</v>
       </c>
       <c r="C1444" t="n">
-        <v>0.082056</v>
+        <v>0.081105</v>
       </c>
     </row>
     <row r="1445">
@@ -19202,7 +19202,7 @@
         <v>654</v>
       </c>
       <c r="C1445" t="n">
-        <v>0.08275399999999999</v>
+        <v>0.081569</v>
       </c>
     </row>
     <row r="1446">
@@ -19215,7 +19215,7 @@
         <v>655</v>
       </c>
       <c r="C1446" t="n">
-        <v>0.08276799999999999</v>
+        <v>0.081606</v>
       </c>
     </row>
     <row r="1447">
@@ -19228,7 +19228,7 @@
         <v>656</v>
       </c>
       <c r="C1447" t="n">
-        <v>0.084367</v>
+        <v>0.08219</v>
       </c>
     </row>
     <row r="1448">
@@ -19241,7 +19241,7 @@
         <v>657</v>
       </c>
       <c r="C1448" t="n">
-        <v>0.08450299999999999</v>
+        <v>0.082258</v>
       </c>
     </row>
     <row r="1449">
@@ -19254,7 +19254,7 @@
         <v>658</v>
       </c>
       <c r="C1449" t="n">
-        <v>0.084575</v>
+        <v>0.083331</v>
       </c>
     </row>
     <row r="1450">
@@ -19267,7 +19267,7 @@
         <v>659</v>
       </c>
       <c r="C1450" t="n">
-        <v>0.084855</v>
+        <v>0.083847</v>
       </c>
     </row>
     <row r="1451">
@@ -19280,7 +19280,7 @@
         <v>660</v>
       </c>
       <c r="C1451" t="n">
-        <v>0.08545899999999999</v>
+        <v>0.084328</v>
       </c>
     </row>
     <row r="1452">
@@ -19293,7 +19293,7 @@
         <v>661</v>
       </c>
       <c r="C1452" t="n">
-        <v>0.086294</v>
+        <v>0.08505500000000001</v>
       </c>
     </row>
     <row r="1453">
@@ -19306,7 +19306,7 @@
         <v>662</v>
       </c>
       <c r="C1453" t="n">
-        <v>0.08637400000000001</v>
+        <v>0.085384</v>
       </c>
     </row>
     <row r="1454">
@@ -19319,7 +19319,7 @@
         <v>663</v>
       </c>
       <c r="C1454" t="n">
-        <v>0.086394</v>
+        <v>0.085646</v>
       </c>
     </row>
     <row r="1455">
@@ -19332,7 +19332,7 @@
         <v>664</v>
       </c>
       <c r="C1455" t="n">
-        <v>0.086994</v>
+        <v>0.085956</v>
       </c>
     </row>
     <row r="1456">
@@ -19345,7 +19345,7 @@
         <v>665</v>
       </c>
       <c r="C1456" t="n">
-        <v>0.08901299999999999</v>
+        <v>0.086109</v>
       </c>
     </row>
     <row r="1457">
@@ -19358,7 +19358,7 @@
         <v>666</v>
       </c>
       <c r="C1457" t="n">
-        <v>0.08958099999999999</v>
+        <v>0.086157</v>
       </c>
     </row>
     <row r="1458">
@@ -19371,7 +19371,7 @@
         <v>667</v>
       </c>
       <c r="C1458" t="n">
-        <v>0.089666</v>
+        <v>0.086741</v>
       </c>
     </row>
     <row r="1459">
@@ -19384,7 +19384,7 @@
         <v>668</v>
       </c>
       <c r="C1459" t="n">
-        <v>0.090169</v>
+        <v>0.08683100000000001</v>
       </c>
     </row>
     <row r="1460">
@@ -19397,7 +19397,7 @@
         <v>669</v>
       </c>
       <c r="C1460" t="n">
-        <v>0.09128799999999999</v>
+        <v>0.088212</v>
       </c>
     </row>
     <row r="1461">
@@ -19410,7 +19410,7 @@
         <v>670</v>
       </c>
       <c r="C1461" t="n">
-        <v>0.09148299999999999</v>
+        <v>0.08834699999999999</v>
       </c>
     </row>
     <row r="1462">
@@ -19423,7 +19423,7 @@
         <v>671</v>
       </c>
       <c r="C1462" t="n">
-        <v>0.092144</v>
+        <v>0.08877599999999999</v>
       </c>
     </row>
     <row r="1463">
@@ -19436,7 +19436,7 @@
         <v>672</v>
       </c>
       <c r="C1463" t="n">
-        <v>0.092414</v>
+        <v>0.088826</v>
       </c>
     </row>
     <row r="1464">
@@ -19449,7 +19449,7 @@
         <v>673</v>
       </c>
       <c r="C1464" t="n">
-        <v>0.092475</v>
+        <v>0.090172</v>
       </c>
     </row>
     <row r="1465">
@@ -19462,7 +19462,7 @@
         <v>674</v>
       </c>
       <c r="C1465" t="n">
-        <v>0.093226</v>
+        <v>0.090271</v>
       </c>
     </row>
     <row r="1466">
@@ -19475,7 +19475,7 @@
         <v>675</v>
       </c>
       <c r="C1466" t="n">
-        <v>0.093319</v>
+        <v>0.090702</v>
       </c>
     </row>
     <row r="1467">
@@ -19488,7 +19488,7 @@
         <v>676</v>
       </c>
       <c r="C1467" t="n">
-        <v>0.093444</v>
+        <v>0.0919</v>
       </c>
     </row>
     <row r="1468">
@@ -19501,7 +19501,7 @@
         <v>677</v>
       </c>
       <c r="C1468" t="n">
-        <v>0.094275</v>
+        <v>0.092486</v>
       </c>
     </row>
     <row r="1469">
@@ -19514,7 +19514,7 @@
         <v>678</v>
       </c>
       <c r="C1469" t="n">
-        <v>0.094308</v>
+        <v>0.092556</v>
       </c>
     </row>
     <row r="1470">
@@ -19527,7 +19527,7 @@
         <v>679</v>
       </c>
       <c r="C1470" t="n">
-        <v>0.094374</v>
+        <v>0.093601</v>
       </c>
     </row>
     <row r="1471">
@@ -19540,7 +19540,7 @@
         <v>680</v>
       </c>
       <c r="C1471" t="n">
-        <v>0.09514599999999999</v>
+        <v>0.094264</v>
       </c>
     </row>
     <row r="1472">
@@ -19553,7 +19553,7 @@
         <v>681</v>
       </c>
       <c r="C1472" t="n">
-        <v>0.095454</v>
+        <v>0.09496400000000001</v>
       </c>
     </row>
     <row r="1473">
@@ -19566,7 +19566,7 @@
         <v>682</v>
       </c>
       <c r="C1473" t="n">
-        <v>0.09629</v>
+        <v>0.095235</v>
       </c>
     </row>
     <row r="1474">
@@ -19579,7 +19579,7 @@
         <v>683</v>
       </c>
       <c r="C1474" t="n">
-        <v>0.096786</v>
+        <v>0.09618699999999999</v>
       </c>
     </row>
     <row r="1475">
@@ -19592,7 +19592,7 @@
         <v>684</v>
       </c>
       <c r="C1475" t="n">
-        <v>0.097355</v>
+        <v>0.097113</v>
       </c>
     </row>
     <row r="1476">
@@ -19605,7 +19605,7 @@
         <v>685</v>
       </c>
       <c r="C1476" t="n">
-        <v>0.09861300000000001</v>
+        <v>0.097233</v>
       </c>
     </row>
     <row r="1477">
@@ -19618,7 +19618,7 @@
         <v>686</v>
       </c>
       <c r="C1477" t="n">
-        <v>0.09864000000000001</v>
+        <v>0.097951</v>
       </c>
     </row>
     <row r="1478">
@@ -19631,7 +19631,7 @@
         <v>687</v>
       </c>
       <c r="C1478" t="n">
-        <v>0.098653</v>
+        <v>0.099319</v>
       </c>
     </row>
     <row r="1479">
@@ -19644,7 +19644,7 @@
         <v>688</v>
       </c>
       <c r="C1479" t="n">
-        <v>0.100076</v>
+        <v>0.099511</v>
       </c>
     </row>
     <row r="1480">
@@ -19657,7 +19657,7 @@
         <v>689</v>
       </c>
       <c r="C1480" t="n">
-        <v>0.1011</v>
+        <v>0.099927</v>
       </c>
     </row>
     <row r="1481">
@@ -19670,7 +19670,7 @@
         <v>690</v>
       </c>
       <c r="C1481" t="n">
-        <v>0.103473</v>
+        <v>0.100026</v>
       </c>
     </row>
     <row r="1482">
@@ -19683,7 +19683,7 @@
         <v>691</v>
       </c>
       <c r="C1482" t="n">
-        <v>0.105587</v>
+        <v>0.100592</v>
       </c>
     </row>
     <row r="1483">
@@ -19696,7 +19696,7 @@
         <v>692</v>
       </c>
       <c r="C1483" t="n">
-        <v>0.105689</v>
+        <v>0.101767</v>
       </c>
     </row>
     <row r="1484">
@@ -19709,7 +19709,7 @@
         <v>693</v>
       </c>
       <c r="C1484" t="n">
-        <v>0.106297</v>
+        <v>0.1019</v>
       </c>
     </row>
     <row r="1485">
@@ -19722,7 +19722,7 @@
         <v>694</v>
       </c>
       <c r="C1485" t="n">
-        <v>0.107254</v>
+        <v>0.102788</v>
       </c>
     </row>
     <row r="1486">
@@ -19735,7 +19735,7 @@
         <v>695</v>
       </c>
       <c r="C1486" t="n">
-        <v>0.107466</v>
+        <v>0.106009</v>
       </c>
     </row>
     <row r="1487">
@@ -19748,7 +19748,7 @@
         <v>696</v>
       </c>
       <c r="C1487" t="n">
-        <v>0.108627</v>
+        <v>0.107031</v>
       </c>
     </row>
     <row r="1488">
@@ -19761,7 +19761,7 @@
         <v>697</v>
       </c>
       <c r="C1488" t="n">
-        <v>0.108998</v>
+        <v>0.108222</v>
       </c>
     </row>
     <row r="1489">
@@ -19774,7 +19774,7 @@
         <v>698</v>
       </c>
       <c r="C1489" t="n">
-        <v>0.111546</v>
+        <v>0.109455</v>
       </c>
     </row>
     <row r="1490">
@@ -19787,7 +19787,7 @@
         <v>699</v>
       </c>
       <c r="C1490" t="n">
-        <v>0.111612</v>
+        <v>0.110851</v>
       </c>
     </row>
     <row r="1491">
@@ -19800,7 +19800,7 @@
         <v>700</v>
       </c>
       <c r="C1491" t="n">
-        <v>0.113035</v>
+        <v>0.111345</v>
       </c>
     </row>
     <row r="1492">
@@ -19813,7 +19813,7 @@
         <v>701</v>
       </c>
       <c r="C1492" t="n">
-        <v>0.114834</v>
+        <v>0.112739</v>
       </c>
     </row>
     <row r="1493">
@@ -19826,7 +19826,7 @@
         <v>702</v>
       </c>
       <c r="C1493" t="n">
-        <v>0.115102</v>
+        <v>0.113011</v>
       </c>
     </row>
     <row r="1494">
@@ -19839,7 +19839,7 @@
         <v>703</v>
       </c>
       <c r="C1494" t="n">
-        <v>0.115907</v>
+        <v>0.113265</v>
       </c>
     </row>
     <row r="1495">
@@ -19852,7 +19852,7 @@
         <v>704</v>
       </c>
       <c r="C1495" t="n">
-        <v>0.117953</v>
+        <v>0.115701</v>
       </c>
     </row>
     <row r="1496">
@@ -19865,7 +19865,7 @@
         <v>705</v>
       </c>
       <c r="C1496" t="n">
-        <v>0.11807</v>
+        <v>0.116624</v>
       </c>
     </row>
     <row r="1497">
@@ -19878,7 +19878,7 @@
         <v>706</v>
       </c>
       <c r="C1497" t="n">
-        <v>0.118658</v>
+        <v>0.117001</v>
       </c>
     </row>
     <row r="1498">
@@ -19891,7 +19891,7 @@
         <v>707</v>
       </c>
       <c r="C1498" t="n">
-        <v>0.120241</v>
+        <v>0.11729</v>
       </c>
     </row>
     <row r="1499">
@@ -19904,7 +19904,7 @@
         <v>708</v>
       </c>
       <c r="C1499" t="n">
-        <v>0.121614</v>
+        <v>0.119936</v>
       </c>
     </row>
     <row r="1500">
@@ -19917,7 +19917,7 @@
         <v>709</v>
       </c>
       <c r="C1500" t="n">
-        <v>0.121629</v>
+        <v>0.120496</v>
       </c>
     </row>
     <row r="1501">
@@ -19930,7 +19930,7 @@
         <v>710</v>
       </c>
       <c r="C1501" t="n">
-        <v>0.122872</v>
+        <v>0.122149</v>
       </c>
     </row>
     <row r="1502">
@@ -19943,7 +19943,7 @@
         <v>711</v>
       </c>
       <c r="C1502" t="n">
-        <v>0.123726</v>
+        <v>0.122371</v>
       </c>
     </row>
     <row r="1503">
@@ -19956,7 +19956,7 @@
         <v>712</v>
       </c>
       <c r="C1503" t="n">
-        <v>0.123912</v>
+        <v>0.12245</v>
       </c>
     </row>
     <row r="1504">
@@ -19969,7 +19969,7 @@
         <v>713</v>
       </c>
       <c r="C1504" t="n">
-        <v>0.1252</v>
+        <v>0.123873</v>
       </c>
     </row>
     <row r="1505">
@@ -19982,7 +19982,7 @@
         <v>714</v>
       </c>
       <c r="C1505" t="n">
-        <v>0.125834</v>
+        <v>0.124617</v>
       </c>
     </row>
     <row r="1506">
@@ -19995,7 +19995,7 @@
         <v>715</v>
       </c>
       <c r="C1506" t="n">
-        <v>0.126517</v>
+        <v>0.12475</v>
       </c>
     </row>
     <row r="1507">
@@ -20008,7 +20008,7 @@
         <v>716</v>
       </c>
       <c r="C1507" t="n">
-        <v>0.127526</v>
+        <v>0.125711</v>
       </c>
     </row>
     <row r="1508">
@@ -20021,7 +20021,7 @@
         <v>717</v>
       </c>
       <c r="C1508" t="n">
-        <v>0.127876</v>
+        <v>0.126436</v>
       </c>
     </row>
     <row r="1509">
@@ -20034,7 +20034,7 @@
         <v>718</v>
       </c>
       <c r="C1509" t="n">
-        <v>0.128244</v>
+        <v>0.127613</v>
       </c>
     </row>
     <row r="1510">
@@ -20047,7 +20047,7 @@
         <v>719</v>
       </c>
       <c r="C1510" t="n">
-        <v>0.132756</v>
+        <v>0.127752</v>
       </c>
     </row>
     <row r="1511">
@@ -20060,7 +20060,7 @@
         <v>720</v>
       </c>
       <c r="C1511" t="n">
-        <v>0.132948</v>
+        <v>0.128601</v>
       </c>
     </row>
     <row r="1512">
@@ -20073,7 +20073,7 @@
         <v>721</v>
       </c>
       <c r="C1512" t="n">
-        <v>0.133145</v>
+        <v>0.128754</v>
       </c>
     </row>
     <row r="1513">
@@ -20086,7 +20086,7 @@
         <v>722</v>
       </c>
       <c r="C1513" t="n">
-        <v>0.133656</v>
+        <v>0.129246</v>
       </c>
     </row>
     <row r="1514">
@@ -20099,7 +20099,7 @@
         <v>723</v>
       </c>
       <c r="C1514" t="n">
-        <v>0.1343</v>
+        <v>0.132716</v>
       </c>
     </row>
     <row r="1515">
@@ -20112,7 +20112,7 @@
         <v>724</v>
       </c>
       <c r="C1515" t="n">
-        <v>0.136586</v>
+        <v>0.133321</v>
       </c>
     </row>
     <row r="1516">
@@ -20125,7 +20125,7 @@
         <v>725</v>
       </c>
       <c r="C1516" t="n">
-        <v>0.137129</v>
+        <v>0.133331</v>
       </c>
     </row>
     <row r="1517">
@@ -20138,7 +20138,7 @@
         <v>726</v>
       </c>
       <c r="C1517" t="n">
-        <v>0.138508</v>
+        <v>0.134727</v>
       </c>
     </row>
     <row r="1518">
@@ -20151,7 +20151,7 @@
         <v>727</v>
       </c>
       <c r="C1518" t="n">
-        <v>0.141194</v>
+        <v>0.134783</v>
       </c>
     </row>
     <row r="1519">
@@ -20164,7 +20164,7 @@
         <v>728</v>
       </c>
       <c r="C1519" t="n">
-        <v>0.144415</v>
+        <v>0.135526</v>
       </c>
     </row>
     <row r="1520">
@@ -20177,7 +20177,7 @@
         <v>729</v>
       </c>
       <c r="C1520" t="n">
-        <v>0.144932</v>
+        <v>0.136342</v>
       </c>
     </row>
     <row r="1521">
@@ -20190,7 +20190,7 @@
         <v>730</v>
       </c>
       <c r="C1521" t="n">
-        <v>0.145252</v>
+        <v>0.138644</v>
       </c>
     </row>
     <row r="1522">
@@ -20203,7 +20203,7 @@
         <v>731</v>
       </c>
       <c r="C1522" t="n">
-        <v>0.147664</v>
+        <v>0.139208</v>
       </c>
     </row>
     <row r="1523">
@@ -20216,7 +20216,7 @@
         <v>732</v>
       </c>
       <c r="C1523" t="n">
-        <v>0.148255</v>
+        <v>0.143301</v>
       </c>
     </row>
     <row r="1524">
@@ -20229,7 +20229,7 @@
         <v>733</v>
       </c>
       <c r="C1524" t="n">
-        <v>0.149594</v>
+        <v>0.14364</v>
       </c>
     </row>
     <row r="1525">
@@ -20242,7 +20242,7 @@
         <v>734</v>
       </c>
       <c r="C1525" t="n">
-        <v>0.150896</v>
+        <v>0.144938</v>
       </c>
     </row>
     <row r="1526">
@@ -20255,7 +20255,7 @@
         <v>735</v>
       </c>
       <c r="C1526" t="n">
-        <v>0.150969</v>
+        <v>0.148018</v>
       </c>
     </row>
     <row r="1527">
@@ -20268,7 +20268,7 @@
         <v>736</v>
       </c>
       <c r="C1527" t="n">
-        <v>0.152865</v>
+        <v>0.149791</v>
       </c>
     </row>
     <row r="1528">
@@ -20281,7 +20281,7 @@
         <v>737</v>
       </c>
       <c r="C1528" t="n">
-        <v>0.153746</v>
+        <v>0.150906</v>
       </c>
     </row>
     <row r="1529">
@@ -20294,7 +20294,7 @@
         <v>738</v>
       </c>
       <c r="C1529" t="n">
-        <v>0.154138</v>
+        <v>0.153213</v>
       </c>
     </row>
     <row r="1530">
@@ -20307,7 +20307,7 @@
         <v>739</v>
       </c>
       <c r="C1530" t="n">
-        <v>0.156635</v>
+        <v>0.155049</v>
       </c>
     </row>
     <row r="1531">
@@ -20320,7 +20320,7 @@
         <v>740</v>
       </c>
       <c r="C1531" t="n">
-        <v>0.157229</v>
+        <v>0.157527</v>
       </c>
     </row>
     <row r="1532">
@@ -20333,7 +20333,7 @@
         <v>741</v>
       </c>
       <c r="C1532" t="n">
-        <v>0.162685</v>
+        <v>0.158509</v>
       </c>
     </row>
     <row r="1533">
@@ -20346,7 +20346,7 @@
         <v>742</v>
       </c>
       <c r="C1533" t="n">
-        <v>0.163087</v>
+        <v>0.163156</v>
       </c>
     </row>
     <row r="1534">
@@ -20359,7 +20359,7 @@
         <v>743</v>
       </c>
       <c r="C1534" t="n">
-        <v>0.168563</v>
+        <v>0.163622</v>
       </c>
     </row>
     <row r="1535">
@@ -20372,7 +20372,7 @@
         <v>744</v>
       </c>
       <c r="C1535" t="n">
-        <v>0.169944</v>
+        <v>0.164656</v>
       </c>
     </row>
     <row r="1536">
@@ -20385,7 +20385,7 @@
         <v>745</v>
       </c>
       <c r="C1536" t="n">
-        <v>0.171642</v>
+        <v>0.167691</v>
       </c>
     </row>
     <row r="1537">
@@ -20398,7 +20398,7 @@
         <v>746</v>
       </c>
       <c r="C1537" t="n">
-        <v>0.171642</v>
+        <v>0.168478</v>
       </c>
     </row>
     <row r="1538">
@@ -20411,7 +20411,7 @@
         <v>747</v>
       </c>
       <c r="C1538" t="n">
-        <v>0.171642</v>
+        <v>0.169374</v>
       </c>
     </row>
     <row r="1539">
@@ -20424,7 +20424,7 @@
         <v>748</v>
       </c>
       <c r="C1539" t="n">
-        <v>0.172747</v>
+        <v>0.169374</v>
       </c>
     </row>
     <row r="1540">
@@ -20437,7 +20437,7 @@
         <v>749</v>
       </c>
       <c r="C1540" t="n">
-        <v>0.177674</v>
+        <v>0.169374</v>
       </c>
     </row>
     <row r="1541">
@@ -20450,7 +20450,7 @@
         <v>750</v>
       </c>
       <c r="C1541" t="n">
-        <v>0.181466</v>
+        <v>0.169918</v>
       </c>
     </row>
     <row r="1542">
@@ -20463,7 +20463,7 @@
         <v>751</v>
       </c>
       <c r="C1542" t="n">
-        <v>0.181841</v>
+        <v>0.171184</v>
       </c>
     </row>
     <row r="1543">
@@ -20476,7 +20476,7 @@
         <v>752</v>
       </c>
       <c r="C1543" t="n">
-        <v>0.183769</v>
+        <v>0.174478</v>
       </c>
     </row>
     <row r="1544">
@@ -20489,7 +20489,7 @@
         <v>753</v>
       </c>
       <c r="C1544" t="n">
-        <v>0.184006</v>
+        <v>0.176903</v>
       </c>
     </row>
     <row r="1545">
@@ -20502,7 +20502,7 @@
         <v>754</v>
       </c>
       <c r="C1545" t="n">
-        <v>0.185126</v>
+        <v>0.180769</v>
       </c>
     </row>
     <row r="1546">
@@ -20515,7 +20515,7 @@
         <v>755</v>
       </c>
       <c r="C1546" t="n">
-        <v>0.185238</v>
+        <v>0.183293</v>
       </c>
     </row>
     <row r="1547">
@@ -20528,7 +20528,7 @@
         <v>756</v>
       </c>
       <c r="C1547" t="n">
-        <v>0.189366</v>
+        <v>0.184943</v>
       </c>
     </row>
     <row r="1548">
@@ -20541,7 +20541,7 @@
         <v>757</v>
       </c>
       <c r="C1548" t="n">
-        <v>0.19419</v>
+        <v>0.18934</v>
       </c>
     </row>
     <row r="1549">
@@ -20554,7 +20554,7 @@
         <v>758</v>
       </c>
       <c r="C1549" t="n">
-        <v>0.194228</v>
+        <v>0.196198</v>
       </c>
     </row>
     <row r="1550">
@@ -20567,7 +20567,7 @@
         <v>759</v>
       </c>
       <c r="C1550" t="n">
-        <v>0.196957</v>
+        <v>0.198464</v>
       </c>
     </row>
     <row r="1551">
@@ -20580,7 +20580,7 @@
         <v>760</v>
       </c>
       <c r="C1551" t="n">
-        <v>0.203954</v>
+        <v>0.199678</v>
       </c>
     </row>
     <row r="1552">
@@ -20593,7 +20593,7 @@
         <v>761</v>
       </c>
       <c r="C1552" t="n">
-        <v>0.211249</v>
+        <v>0.211655</v>
       </c>
     </row>
     <row r="1553">
@@ -20606,7 +20606,7 @@
         <v>762</v>
       </c>
       <c r="C1553" t="n">
-        <v>0.21856</v>
+        <v>0.212513</v>
       </c>
     </row>
     <row r="1554">
@@ -20619,7 +20619,7 @@
         <v>763</v>
       </c>
       <c r="C1554" t="n">
-        <v>0.220686</v>
+        <v>0.218092</v>
       </c>
     </row>
     <row r="1555">
@@ -20632,7 +20632,7 @@
         <v>764</v>
       </c>
       <c r="C1555" t="n">
-        <v>0.220853</v>
+        <v>0.218454</v>
       </c>
     </row>
     <row r="1556">
@@ -20645,7 +20645,7 @@
         <v>765</v>
       </c>
       <c r="C1556" t="n">
-        <v>0.221921</v>
+        <v>0.220225</v>
       </c>
     </row>
     <row r="1557">
@@ -20658,7 +20658,7 @@
         <v>766</v>
       </c>
       <c r="C1557" t="n">
-        <v>0.224118</v>
+        <v>0.22026</v>
       </c>
     </row>
     <row r="1558">
@@ -20671,7 +20671,7 @@
         <v>767</v>
       </c>
       <c r="C1558" t="n">
-        <v>0.227008</v>
+        <v>0.222214</v>
       </c>
     </row>
     <row r="1559">
@@ -20684,7 +20684,7 @@
         <v>768</v>
       </c>
       <c r="C1559" t="n">
-        <v>0.245408</v>
+        <v>0.224456</v>
       </c>
     </row>
     <row r="1560">
@@ -20697,7 +20697,7 @@
         <v>769</v>
       </c>
       <c r="C1560" t="n">
-        <v>0.261297</v>
+        <v>0.25728</v>
       </c>
     </row>
     <row r="1561">
@@ -20710,7 +20710,7 @@
         <v>770</v>
       </c>
       <c r="C1561" t="n">
-        <v>0.269983</v>
+        <v>0.262101</v>
       </c>
     </row>
     <row r="1562">
@@ -20723,7 +20723,7 @@
         <v>771</v>
       </c>
       <c r="C1562" t="n">
-        <v>0.272346</v>
+        <v>0.273501</v>
       </c>
     </row>
     <row r="1563">
@@ -20736,7 +20736,7 @@
         <v>772</v>
       </c>
       <c r="C1563" t="n">
-        <v>0.279901</v>
+        <v>0.277274</v>
       </c>
     </row>
     <row r="1564">
@@ -20749,7 +20749,7 @@
         <v>773</v>
       </c>
       <c r="C1564" t="n">
-        <v>0.309101</v>
+        <v>0.308065</v>
       </c>
     </row>
     <row r="1565">
@@ -20762,7 +20762,7 @@
         <v>774</v>
       </c>
       <c r="C1565" t="n">
-        <v>0.309286</v>
+        <v>0.308375</v>
       </c>
     </row>
     <row r="1566">
@@ -20775,7 +20775,7 @@
         <v>775</v>
       </c>
       <c r="C1566" t="n">
-        <v>0.333689</v>
+        <v>0.314041</v>
       </c>
     </row>
     <row r="1567">
@@ -20788,7 +20788,7 @@
         <v>776</v>
       </c>
       <c r="C1567" t="n">
-        <v>0.343426</v>
+        <v>0.340947</v>
       </c>
     </row>
     <row r="1568">
@@ -20801,7 +20801,7 @@
         <v>777</v>
       </c>
       <c r="C1568" t="n">
-        <v>0.374591</v>
+        <v>0.362405</v>
       </c>
     </row>
     <row r="1569">
@@ -20814,7 +20814,7 @@
         <v>778</v>
       </c>
       <c r="C1569" t="n">
-        <v>0.388884</v>
+        <v>0.364905</v>
       </c>
     </row>
     <row r="1570">
@@ -20827,7 +20827,7 @@
         <v>779</v>
       </c>
       <c r="C1570" t="n">
-        <v>0.395558</v>
+        <v>0.371448</v>
       </c>
     </row>
     <row r="1571">
@@ -20840,7 +20840,7 @@
         <v>780</v>
       </c>
       <c r="C1571" t="n">
-        <v>0.420689</v>
+        <v>0.384788</v>
       </c>
     </row>
     <row r="1572">
@@ -20853,7 +20853,7 @@
         <v>781</v>
       </c>
       <c r="C1572" t="n">
-        <v>0.430412</v>
+        <v>0.399614</v>
       </c>
     </row>
     <row r="1573">
@@ -20866,7 +20866,7 @@
         <v>782</v>
       </c>
       <c r="C1573" t="n">
-        <v>0.535328</v>
+        <v>0.530528</v>
       </c>
     </row>
     <row r="1574">
@@ -20879,7 +20879,7 @@
         <v>783</v>
       </c>
       <c r="C1574" t="n">
-        <v>0.548977</v>
+        <v>0.551198</v>
       </c>
     </row>
     <row r="1575">
@@ -20892,7 +20892,7 @@
         <v>784</v>
       </c>
       <c r="C1575" t="n">
-        <v>0.674305</v>
+        <v>0.678392</v>
       </c>
     </row>
     <row r="1576">
@@ -20905,7 +20905,7 @@
         <v>785</v>
       </c>
       <c r="C1576" t="n">
-        <v>0.697815</v>
+        <v>0.700649</v>
       </c>
     </row>
     <row r="1577">
@@ -20918,7 +20918,7 @@
         <v>786</v>
       </c>
       <c r="C1577" t="n">
-        <v>1.055045</v>
+        <v>1.002024</v>
       </c>
     </row>
     <row r="1578">
@@ -20931,7 +20931,7 @@
         <v>787</v>
       </c>
       <c r="C1578" t="n">
-        <v>1.109808</v>
+        <v>1.058084</v>
       </c>
     </row>
     <row r="1579">
@@ -20944,7 +20944,7 @@
         <v>788</v>
       </c>
       <c r="C1579" t="n">
-        <v>1.330462</v>
+        <v>1.351286</v>
       </c>
     </row>
   </sheetData>

--- a/vignettes/vignette-1/distribution_plot_data.xlsx
+++ b/vignettes/vignette-1/distribution_plot_data.xlsx
@@ -9881,7 +9881,7 @@
         <v>0</v>
       </c>
       <c r="C728" t="n">
-        <v>-0.516242</v>
+        <v>-0.516564</v>
       </c>
     </row>
     <row r="729">
@@ -9894,7 +9894,7 @@
         <v>1</v>
       </c>
       <c r="C729" t="n">
-        <v>-0.455765</v>
+        <v>-0.455594</v>
       </c>
     </row>
     <row r="730">
@@ -9907,7 +9907,7 @@
         <v>2</v>
       </c>
       <c r="C730" t="n">
-        <v>-0.445532</v>
+        <v>-0.445643</v>
       </c>
     </row>
     <row r="731">
@@ -9920,7 +9920,7 @@
         <v>3</v>
       </c>
       <c r="C731" t="n">
-        <v>-0.371526</v>
+        <v>-0.370773</v>
       </c>
     </row>
     <row r="732">
@@ -9933,7 +9933,7 @@
         <v>4</v>
       </c>
       <c r="C732" t="n">
-        <v>-0.344036</v>
+        <v>-0.343896</v>
       </c>
     </row>
     <row r="733">
@@ -9946,7 +9946,7 @@
         <v>5</v>
       </c>
       <c r="C733" t="n">
-        <v>-0.332405</v>
+        <v>-0.333061</v>
       </c>
     </row>
     <row r="734">
@@ -9959,7 +9959,7 @@
         <v>6</v>
       </c>
       <c r="C734" t="n">
-        <v>-0.321955</v>
+        <v>-0.322419</v>
       </c>
     </row>
     <row r="735">
@@ -9972,7 +9972,7 @@
         <v>7</v>
       </c>
       <c r="C735" t="n">
-        <v>-0.316793</v>
+        <v>-0.317152</v>
       </c>
     </row>
     <row r="736">
@@ -9985,7 +9985,7 @@
         <v>8</v>
       </c>
       <c r="C736" t="n">
-        <v>-0.269488</v>
+        <v>-0.269021</v>
       </c>
     </row>
     <row r="737">
@@ -9998,7 +9998,7 @@
         <v>9</v>
       </c>
       <c r="C737" t="n">
-        <v>-0.224997</v>
+        <v>-0.224983</v>
       </c>
     </row>
     <row r="738">
@@ -10011,7 +10011,7 @@
         <v>10</v>
       </c>
       <c r="C738" t="n">
-        <v>-0.218939</v>
+        <v>-0.219008</v>
       </c>
     </row>
     <row r="739">
@@ -10024,7 +10024,7 @@
         <v>11</v>
       </c>
       <c r="C739" t="n">
-        <v>-0.216005</v>
+        <v>-0.216443</v>
       </c>
     </row>
     <row r="740">
@@ -10037,7 +10037,7 @@
         <v>12</v>
       </c>
       <c r="C740" t="n">
-        <v>-0.212798</v>
+        <v>-0.212892</v>
       </c>
     </row>
     <row r="741">
@@ -10050,7 +10050,7 @@
         <v>13</v>
       </c>
       <c r="C741" t="n">
-        <v>-0.210798</v>
+        <v>-0.210632</v>
       </c>
     </row>
     <row r="742">
@@ -10063,7 +10063,7 @@
         <v>14</v>
       </c>
       <c r="C742" t="n">
-        <v>-0.205651</v>
+        <v>-0.20571</v>
       </c>
     </row>
     <row r="743">
@@ -10076,7 +10076,7 @@
         <v>15</v>
       </c>
       <c r="C743" t="n">
-        <v>-0.188811</v>
+        <v>-0.189111</v>
       </c>
     </row>
     <row r="744">
@@ -10089,7 +10089,7 @@
         <v>16</v>
       </c>
       <c r="C744" t="n">
-        <v>-0.181744</v>
+        <v>-0.181806</v>
       </c>
     </row>
     <row r="745">
@@ -10102,7 +10102,7 @@
         <v>17</v>
       </c>
       <c r="C745" t="n">
-        <v>-0.166557</v>
+        <v>-0.166276</v>
       </c>
     </row>
     <row r="746">
@@ -10115,7 +10115,7 @@
         <v>18</v>
       </c>
       <c r="C746" t="n">
-        <v>-0.164853</v>
+        <v>-0.165117</v>
       </c>
     </row>
     <row r="747">
@@ -10128,7 +10128,7 @@
         <v>19</v>
       </c>
       <c r="C747" t="n">
-        <v>-0.159639</v>
+        <v>-0.159656</v>
       </c>
     </row>
     <row r="748">
@@ -10141,7 +10141,7 @@
         <v>20</v>
       </c>
       <c r="C748" t="n">
-        <v>-0.145165</v>
+        <v>-0.145238</v>
       </c>
     </row>
     <row r="749">
@@ -10154,7 +10154,7 @@
         <v>21</v>
       </c>
       <c r="C749" t="n">
-        <v>-0.139349</v>
+        <v>-0.139331</v>
       </c>
     </row>
     <row r="750">
@@ -10167,7 +10167,7 @@
         <v>22</v>
       </c>
       <c r="C750" t="n">
-        <v>-0.134819</v>
+        <v>-0.135048</v>
       </c>
     </row>
     <row r="751">
@@ -10180,7 +10180,7 @@
         <v>23</v>
       </c>
       <c r="C751" t="n">
-        <v>-0.130399</v>
+        <v>-0.130242</v>
       </c>
     </row>
     <row r="752">
@@ -10193,7 +10193,7 @@
         <v>24</v>
       </c>
       <c r="C752" t="n">
-        <v>-0.129002</v>
+        <v>-0.129118</v>
       </c>
     </row>
     <row r="753">
@@ -10206,7 +10206,7 @@
         <v>25</v>
       </c>
       <c r="C753" t="n">
-        <v>-0.126117</v>
+        <v>-0.126091</v>
       </c>
     </row>
     <row r="754">
@@ -10219,7 +10219,7 @@
         <v>26</v>
       </c>
       <c r="C754" t="n">
-        <v>-0.12205</v>
+        <v>-0.122024</v>
       </c>
     </row>
     <row r="755">
@@ -10232,7 +10232,7 @@
         <v>27</v>
       </c>
       <c r="C755" t="n">
-        <v>-0.12205</v>
+        <v>-0.121764</v>
       </c>
     </row>
     <row r="756">
@@ -10245,7 +10245,7 @@
         <v>28</v>
       </c>
       <c r="C756" t="n">
-        <v>-0.121922</v>
+        <v>-0.121764</v>
       </c>
     </row>
     <row r="757">
@@ -10258,7 +10258,7 @@
         <v>29</v>
       </c>
       <c r="C757" t="n">
-        <v>-0.121519</v>
+        <v>-0.121586</v>
       </c>
     </row>
     <row r="758">
@@ -10271,7 +10271,7 @@
         <v>30</v>
       </c>
       <c r="C758" t="n">
-        <v>-0.120352</v>
+        <v>-0.120638</v>
       </c>
     </row>
     <row r="759">
@@ -10284,7 +10284,7 @@
         <v>31</v>
       </c>
       <c r="C759" t="n">
-        <v>-0.117689</v>
+        <v>-0.117922</v>
       </c>
     </row>
     <row r="760">
@@ -10297,7 +10297,7 @@
         <v>32</v>
       </c>
       <c r="C760" t="n">
-        <v>-0.11482</v>
+        <v>-0.114979</v>
       </c>
     </row>
     <row r="761">
@@ -10310,7 +10310,7 @@
         <v>33</v>
       </c>
       <c r="C761" t="n">
-        <v>-0.110491</v>
+        <v>-0.110608</v>
       </c>
     </row>
     <row r="762">
@@ -10323,7 +10323,7 @@
         <v>34</v>
       </c>
       <c r="C762" t="n">
-        <v>-0.10905</v>
+        <v>-0.109159</v>
       </c>
     </row>
     <row r="763">
@@ -10336,7 +10336,7 @@
         <v>35</v>
       </c>
       <c r="C763" t="n">
-        <v>-0.10839</v>
+        <v>-0.108471</v>
       </c>
     </row>
     <row r="764">
@@ -10349,7 +10349,7 @@
         <v>36</v>
       </c>
       <c r="C764" t="n">
-        <v>-0.103576</v>
+        <v>-0.103789</v>
       </c>
     </row>
     <row r="765">
@@ -10362,7 +10362,7 @@
         <v>37</v>
       </c>
       <c r="C765" t="n">
-        <v>-0.102759</v>
+        <v>-0.102844</v>
       </c>
     </row>
     <row r="766">
@@ -10375,7 +10375,7 @@
         <v>38</v>
       </c>
       <c r="C766" t="n">
-        <v>-0.101991</v>
+        <v>-0.102079</v>
       </c>
     </row>
     <row r="767">
@@ -10388,7 +10388,7 @@
         <v>39</v>
       </c>
       <c r="C767" t="n">
-        <v>-0.100782</v>
+        <v>-0.100561</v>
       </c>
     </row>
     <row r="768">
@@ -10401,7 +10401,7 @@
         <v>40</v>
       </c>
       <c r="C768" t="n">
-        <v>-0.097067</v>
+        <v>-0.09725200000000001</v>
       </c>
     </row>
     <row r="769">
@@ -10414,7 +10414,7 @@
         <v>41</v>
       </c>
       <c r="C769" t="n">
-        <v>-0.096789</v>
+        <v>-0.096967</v>
       </c>
     </row>
     <row r="770">
@@ -10427,7 +10427,7 @@
         <v>42</v>
       </c>
       <c r="C770" t="n">
-        <v>-0.09578399999999999</v>
+        <v>-0.095905</v>
       </c>
     </row>
     <row r="771">
@@ -10440,7 +10440,7 @@
         <v>43</v>
       </c>
       <c r="C771" t="n">
-        <v>-0.094565</v>
+        <v>-0.094627</v>
       </c>
     </row>
     <row r="772">
@@ -10453,7 +10453,7 @@
         <v>44</v>
       </c>
       <c r="C772" t="n">
-        <v>-0.09454700000000001</v>
+        <v>-0.094537</v>
       </c>
     </row>
     <row r="773">
@@ -10466,7 +10466,7 @@
         <v>45</v>
       </c>
       <c r="C773" t="n">
-        <v>-0.094265</v>
+        <v>-0.09431</v>
       </c>
     </row>
     <row r="774">
@@ -10479,7 +10479,7 @@
         <v>46</v>
       </c>
       <c r="C774" t="n">
-        <v>-0.09407</v>
+        <v>-0.094225</v>
       </c>
     </row>
     <row r="775">
@@ -10492,7 +10492,7 @@
         <v>47</v>
       </c>
       <c r="C775" t="n">
-        <v>-0.09217599999999999</v>
+        <v>-0.092346</v>
       </c>
     </row>
     <row r="776">
@@ -10505,7 +10505,7 @@
         <v>48</v>
       </c>
       <c r="C776" t="n">
-        <v>-0.090021</v>
+        <v>-0.090043</v>
       </c>
     </row>
     <row r="777">
@@ -10518,7 +10518,7 @@
         <v>49</v>
       </c>
       <c r="C777" t="n">
-        <v>-0.089299</v>
+        <v>-0.089392</v>
       </c>
     </row>
     <row r="778">
@@ -10531,7 +10531,7 @@
         <v>50</v>
       </c>
       <c r="C778" t="n">
-        <v>-0.08925</v>
+        <v>-0.08932</v>
       </c>
     </row>
     <row r="779">
@@ -10544,7 +10544,7 @@
         <v>51</v>
       </c>
       <c r="C779" t="n">
-        <v>-0.08727799999999999</v>
+        <v>-0.08716400000000001</v>
       </c>
     </row>
     <row r="780">
@@ -10557,7 +10557,7 @@
         <v>52</v>
       </c>
       <c r="C780" t="n">
-        <v>-0.08713</v>
+        <v>-0.086995</v>
       </c>
     </row>
     <row r="781">
@@ -10570,7 +10570,7 @@
         <v>53</v>
       </c>
       <c r="C781" t="n">
-        <v>-0.086923</v>
+        <v>-0.086978</v>
       </c>
     </row>
     <row r="782">
@@ -10583,7 +10583,7 @@
         <v>54</v>
       </c>
       <c r="C782" t="n">
-        <v>-0.086378</v>
+        <v>-0.086448</v>
       </c>
     </row>
     <row r="783">
@@ -10596,7 +10596,7 @@
         <v>55</v>
       </c>
       <c r="C783" t="n">
-        <v>-0.082068</v>
+        <v>-0.082092</v>
       </c>
     </row>
     <row r="784">
@@ -10609,7 +10609,7 @@
         <v>56</v>
       </c>
       <c r="C784" t="n">
-        <v>-0.080121</v>
+        <v>-0.080191</v>
       </c>
     </row>
     <row r="785">
@@ -10622,7 +10622,7 @@
         <v>57</v>
       </c>
       <c r="C785" t="n">
-        <v>-0.07968</v>
+        <v>-0.079747</v>
       </c>
     </row>
     <row r="786">
@@ -10635,7 +10635,7 @@
         <v>58</v>
       </c>
       <c r="C786" t="n">
-        <v>-0.077836</v>
+        <v>-0.077727</v>
       </c>
     </row>
     <row r="787">
@@ -10648,7 +10648,7 @@
         <v>59</v>
       </c>
       <c r="C787" t="n">
-        <v>-0.077622</v>
+        <v>-0.077574</v>
       </c>
     </row>
     <row r="788">
@@ -10661,7 +10661,7 @@
         <v>60</v>
       </c>
       <c r="C788" t="n">
-        <v>-0.07616199999999999</v>
+        <v>-0.07606499999999999</v>
       </c>
     </row>
     <row r="789">
@@ -10674,7 +10674,7 @@
         <v>61</v>
       </c>
       <c r="C789" t="n">
-        <v>-0.075069</v>
+        <v>-0.07517699999999999</v>
       </c>
     </row>
     <row r="790">
@@ -10687,7 +10687,7 @@
         <v>62</v>
       </c>
       <c r="C790" t="n">
-        <v>-0.07420499999999999</v>
+        <v>-0.07409</v>
       </c>
     </row>
     <row r="791">
@@ -10700,7 +10700,7 @@
         <v>63</v>
       </c>
       <c r="C791" t="n">
-        <v>-0.07370599999999999</v>
+        <v>-0.073657</v>
       </c>
     </row>
     <row r="792">
@@ -10713,7 +10713,7 @@
         <v>64</v>
       </c>
       <c r="C792" t="n">
-        <v>-0.073145</v>
+        <v>-0.073279</v>
       </c>
     </row>
     <row r="793">
@@ -10726,7 +10726,7 @@
         <v>65</v>
       </c>
       <c r="C793" t="n">
-        <v>-0.072306</v>
+        <v>-0.07222099999999999</v>
       </c>
     </row>
     <row r="794">
@@ -10739,7 +10739,7 @@
         <v>66</v>
       </c>
       <c r="C794" t="n">
-        <v>-0.071688</v>
+        <v>-0.071589</v>
       </c>
     </row>
     <row r="795">
@@ -10752,7 +10752,7 @@
         <v>67</v>
       </c>
       <c r="C795" t="n">
-        <v>-0.070747</v>
+        <v>-0.07088</v>
       </c>
     </row>
     <row r="796">
@@ -10765,7 +10765,7 @@
         <v>68</v>
       </c>
       <c r="C796" t="n">
-        <v>-0.070039</v>
+        <v>-0.069951</v>
       </c>
     </row>
     <row r="797">
@@ -10778,7 +10778,7 @@
         <v>69</v>
       </c>
       <c r="C797" t="n">
-        <v>-0.06744799999999999</v>
+        <v>-0.067536</v>
       </c>
     </row>
     <row r="798">
@@ -10791,7 +10791,7 @@
         <v>70</v>
       </c>
       <c r="C798" t="n">
-        <v>-0.06693399999999999</v>
+        <v>-0.067051</v>
       </c>
     </row>
     <row r="799">
@@ -10804,7 +10804,7 @@
         <v>71</v>
       </c>
       <c r="C799" t="n">
-        <v>-0.06683</v>
+        <v>-0.066834</v>
       </c>
     </row>
     <row r="800">
@@ -10817,7 +10817,7 @@
         <v>72</v>
       </c>
       <c r="C800" t="n">
-        <v>-0.066382</v>
+        <v>-0.066451</v>
       </c>
     </row>
     <row r="801">
@@ -10830,7 +10830,7 @@
         <v>73</v>
       </c>
       <c r="C801" t="n">
-        <v>-0.06617199999999999</v>
+        <v>-0.06628100000000001</v>
       </c>
     </row>
     <row r="802">
@@ -10843,7 +10843,7 @@
         <v>74</v>
       </c>
       <c r="C802" t="n">
-        <v>-0.066135</v>
+        <v>-0.066277</v>
       </c>
     </row>
     <row r="803">
@@ -10856,7 +10856,7 @@
         <v>75</v>
       </c>
       <c r="C803" t="n">
-        <v>-0.066092</v>
+        <v>-0.06618499999999999</v>
       </c>
     </row>
     <row r="804">
@@ -10869,7 +10869,7 @@
         <v>76</v>
       </c>
       <c r="C804" t="n">
-        <v>-0.06561400000000001</v>
+        <v>-0.065635</v>
       </c>
     </row>
     <row r="805">
@@ -10882,7 +10882,7 @@
         <v>77</v>
       </c>
       <c r="C805" t="n">
-        <v>-0.06489499999999999</v>
+        <v>-0.064954</v>
       </c>
     </row>
     <row r="806">
@@ -10895,7 +10895,7 @@
         <v>78</v>
       </c>
       <c r="C806" t="n">
-        <v>-0.063165</v>
+        <v>-0.063234</v>
       </c>
     </row>
     <row r="807">
@@ -10908,7 +10908,7 @@
         <v>79</v>
       </c>
       <c r="C807" t="n">
-        <v>-0.062355</v>
+        <v>-0.062261</v>
       </c>
     </row>
     <row r="808">
@@ -10921,7 +10921,7 @@
         <v>80</v>
       </c>
       <c r="C808" t="n">
-        <v>-0.061313</v>
+        <v>-0.061432</v>
       </c>
     </row>
     <row r="809">
@@ -10934,7 +10934,7 @@
         <v>81</v>
       </c>
       <c r="C809" t="n">
-        <v>-0.06086</v>
+        <v>-0.060791</v>
       </c>
     </row>
     <row r="810">
@@ -10947,7 +10947,7 @@
         <v>82</v>
       </c>
       <c r="C810" t="n">
-        <v>-0.060747</v>
+        <v>-0.06074</v>
       </c>
     </row>
     <row r="811">
@@ -10960,7 +10960,7 @@
         <v>83</v>
       </c>
       <c r="C811" t="n">
-        <v>-0.060632</v>
+        <v>-0.060336</v>
       </c>
     </row>
     <row r="812">
@@ -10973,7 +10973,7 @@
         <v>84</v>
       </c>
       <c r="C812" t="n">
-        <v>-0.059448</v>
+        <v>-0.059485</v>
       </c>
     </row>
     <row r="813">
@@ -10986,7 +10986,7 @@
         <v>85</v>
       </c>
       <c r="C813" t="n">
-        <v>-0.059101</v>
+        <v>-0.059219</v>
       </c>
     </row>
     <row r="814">
@@ -10999,7 +10999,7 @@
         <v>86</v>
       </c>
       <c r="C814" t="n">
-        <v>-0.058279</v>
+        <v>-0.058312</v>
       </c>
     </row>
     <row r="815">
@@ -11012,7 +11012,7 @@
         <v>87</v>
       </c>
       <c r="C815" t="n">
-        <v>-0.057716</v>
+        <v>-0.057619</v>
       </c>
     </row>
     <row r="816">
@@ -11025,7 +11025,7 @@
         <v>88</v>
       </c>
       <c r="C816" t="n">
-        <v>-0.05737</v>
+        <v>-0.057256</v>
       </c>
     </row>
     <row r="817">
@@ -11038,7 +11038,7 @@
         <v>89</v>
       </c>
       <c r="C817" t="n">
-        <v>-0.056783</v>
+        <v>-0.056835</v>
       </c>
     </row>
     <row r="818">
@@ -11051,7 +11051,7 @@
         <v>90</v>
       </c>
       <c r="C818" t="n">
-        <v>-0.056724</v>
+        <v>-0.056812</v>
       </c>
     </row>
     <row r="819">
@@ -11064,7 +11064,7 @@
         <v>91</v>
       </c>
       <c r="C819" t="n">
-        <v>-0.056624</v>
+        <v>-0.056736</v>
       </c>
     </row>
     <row r="820">
@@ -11077,7 +11077,7 @@
         <v>92</v>
       </c>
       <c r="C820" t="n">
-        <v>-0.056174</v>
+        <v>-0.056179</v>
       </c>
     </row>
     <row r="821">
@@ -11090,7 +11090,7 @@
         <v>93</v>
       </c>
       <c r="C821" t="n">
-        <v>-0.055823</v>
+        <v>-0.055878</v>
       </c>
     </row>
     <row r="822">
@@ -11103,7 +11103,7 @@
         <v>94</v>
       </c>
       <c r="C822" t="n">
-        <v>-0.055494</v>
+        <v>-0.055601</v>
       </c>
     </row>
     <row r="823">
@@ -11116,7 +11116,7 @@
         <v>95</v>
       </c>
       <c r="C823" t="n">
-        <v>-0.055364</v>
+        <v>-0.055359</v>
       </c>
     </row>
     <row r="824">
@@ -11129,7 +11129,7 @@
         <v>96</v>
       </c>
       <c r="C824" t="n">
-        <v>-0.055113</v>
+        <v>-0.055202</v>
       </c>
     </row>
     <row r="825">
@@ -11142,7 +11142,7 @@
         <v>97</v>
       </c>
       <c r="C825" t="n">
-        <v>-0.054356</v>
+        <v>-0.054272</v>
       </c>
     </row>
     <row r="826">
@@ -11155,7 +11155,7 @@
         <v>98</v>
       </c>
       <c r="C826" t="n">
-        <v>-0.054205</v>
+        <v>-0.054176</v>
       </c>
     </row>
     <row r="827">
@@ -11168,7 +11168,7 @@
         <v>99</v>
       </c>
       <c r="C827" t="n">
-        <v>-0.053459</v>
+        <v>-0.053534</v>
       </c>
     </row>
     <row r="828">
@@ -11181,7 +11181,7 @@
         <v>100</v>
       </c>
       <c r="C828" t="n">
-        <v>-0.053446</v>
+        <v>-0.053429</v>
       </c>
     </row>
     <row r="829">
@@ -11194,7 +11194,7 @@
         <v>101</v>
       </c>
       <c r="C829" t="n">
-        <v>-0.053171</v>
+        <v>-0.053167</v>
       </c>
     </row>
     <row r="830">
@@ -11207,7 +11207,7 @@
         <v>102</v>
       </c>
       <c r="C830" t="n">
-        <v>-0.052666</v>
+        <v>-0.05271</v>
       </c>
     </row>
     <row r="831">
@@ -11220,7 +11220,7 @@
         <v>103</v>
       </c>
       <c r="C831" t="n">
-        <v>-0.052593</v>
+        <v>-0.052684</v>
       </c>
     </row>
     <row r="832">
@@ -11233,7 +11233,7 @@
         <v>104</v>
       </c>
       <c r="C832" t="n">
-        <v>-0.052139</v>
+        <v>-0.05222</v>
       </c>
     </row>
     <row r="833">
@@ -11246,7 +11246,7 @@
         <v>105</v>
       </c>
       <c r="C833" t="n">
-        <v>-0.052025</v>
+        <v>-0.05203</v>
       </c>
     </row>
     <row r="834">
@@ -11259,7 +11259,7 @@
         <v>106</v>
       </c>
       <c r="C834" t="n">
-        <v>-0.051886</v>
+        <v>-0.051944</v>
       </c>
     </row>
     <row r="835">
@@ -11272,7 +11272,7 @@
         <v>107</v>
       </c>
       <c r="C835" t="n">
-        <v>-0.051702</v>
+        <v>-0.051695</v>
       </c>
     </row>
     <row r="836">
@@ -11285,7 +11285,7 @@
         <v>108</v>
       </c>
       <c r="C836" t="n">
-        <v>-0.051414</v>
+        <v>-0.051511</v>
       </c>
     </row>
     <row r="837">
@@ -11298,7 +11298,7 @@
         <v>109</v>
       </c>
       <c r="C837" t="n">
-        <v>-0.051354</v>
+        <v>-0.051404</v>
       </c>
     </row>
     <row r="838">
@@ -11311,7 +11311,7 @@
         <v>110</v>
       </c>
       <c r="C838" t="n">
-        <v>-0.051006</v>
+        <v>-0.051103</v>
       </c>
     </row>
     <row r="839">
@@ -11324,7 +11324,7 @@
         <v>111</v>
       </c>
       <c r="C839" t="n">
-        <v>-0.050289</v>
+        <v>-0.050318</v>
       </c>
     </row>
     <row r="840">
@@ -11337,7 +11337,7 @@
         <v>112</v>
       </c>
       <c r="C840" t="n">
-        <v>-0.050259</v>
+        <v>-0.0503</v>
       </c>
     </row>
     <row r="841">
@@ -11350,7 +11350,7 @@
         <v>113</v>
       </c>
       <c r="C841" t="n">
-        <v>-0.049842</v>
+        <v>-0.049863</v>
       </c>
     </row>
     <row r="842">
@@ -11363,7 +11363,7 @@
         <v>114</v>
       </c>
       <c r="C842" t="n">
-        <v>-0.049569</v>
+        <v>-0.049583</v>
       </c>
     </row>
     <row r="843">
@@ -11376,7 +11376,7 @@
         <v>115</v>
       </c>
       <c r="C843" t="n">
-        <v>-0.048667</v>
+        <v>-0.048738</v>
       </c>
     </row>
     <row r="844">
@@ -11389,7 +11389,7 @@
         <v>116</v>
       </c>
       <c r="C844" t="n">
-        <v>-0.048667</v>
+        <v>-0.048702</v>
       </c>
     </row>
     <row r="845">
@@ -11402,7 +11402,7 @@
         <v>117</v>
       </c>
       <c r="C845" t="n">
-        <v>-0.048345</v>
+        <v>-0.048435</v>
       </c>
     </row>
     <row r="846">
@@ -11415,7 +11415,7 @@
         <v>118</v>
       </c>
       <c r="C846" t="n">
-        <v>-0.047727</v>
+        <v>-0.047765</v>
       </c>
     </row>
     <row r="847">
@@ -11428,7 +11428,7 @@
         <v>119</v>
       </c>
       <c r="C847" t="n">
-        <v>-0.047715</v>
+        <v>-0.047725</v>
       </c>
     </row>
     <row r="848">
@@ -11441,7 +11441,7 @@
         <v>120</v>
       </c>
       <c r="C848" t="n">
-        <v>-0.047191</v>
+        <v>-0.047268</v>
       </c>
     </row>
     <row r="849">
@@ -11454,7 +11454,7 @@
         <v>121</v>
       </c>
       <c r="C849" t="n">
-        <v>-0.046865</v>
+        <v>-0.046919</v>
       </c>
     </row>
     <row r="850">
@@ -11467,7 +11467,7 @@
         <v>122</v>
       </c>
       <c r="C850" t="n">
-        <v>-0.046529</v>
+        <v>-0.04662</v>
       </c>
     </row>
     <row r="851">
@@ -11480,7 +11480,7 @@
         <v>123</v>
       </c>
       <c r="C851" t="n">
-        <v>-0.045241</v>
+        <v>-0.045254</v>
       </c>
     </row>
     <row r="852">
@@ -11493,7 +11493,7 @@
         <v>124</v>
       </c>
       <c r="C852" t="n">
-        <v>-0.044627</v>
+        <v>-0.044699</v>
       </c>
     </row>
     <row r="853">
@@ -11506,7 +11506,7 @@
         <v>125</v>
       </c>
       <c r="C853" t="n">
-        <v>-0.044606</v>
+        <v>-0.044654</v>
       </c>
     </row>
     <row r="854">
@@ -11519,7 +11519,7 @@
         <v>126</v>
       </c>
       <c r="C854" t="n">
-        <v>-0.044311</v>
+        <v>-0.044328</v>
       </c>
     </row>
     <row r="855">
@@ -11532,7 +11532,7 @@
         <v>127</v>
       </c>
       <c r="C855" t="n">
-        <v>-0.044137</v>
+        <v>-0.044089</v>
       </c>
     </row>
     <row r="856">
@@ -11545,7 +11545,7 @@
         <v>128</v>
       </c>
       <c r="C856" t="n">
-        <v>-0.044005</v>
+        <v>-0.044086</v>
       </c>
     </row>
     <row r="857">
@@ -11558,7 +11558,7 @@
         <v>129</v>
       </c>
       <c r="C857" t="n">
-        <v>-0.043432</v>
+        <v>-0.043445</v>
       </c>
     </row>
     <row r="858">
@@ -11571,7 +11571,7 @@
         <v>130</v>
       </c>
       <c r="C858" t="n">
-        <v>-0.043402</v>
+        <v>-0.0434</v>
       </c>
     </row>
     <row r="859">
@@ -11584,7 +11584,7 @@
         <v>131</v>
       </c>
       <c r="C859" t="n">
-        <v>-0.043366</v>
+        <v>-0.04336</v>
       </c>
     </row>
     <row r="860">
@@ -11597,7 +11597,7 @@
         <v>132</v>
       </c>
       <c r="C860" t="n">
-        <v>-0.043314</v>
+        <v>-0.043322</v>
       </c>
     </row>
     <row r="861">
@@ -11610,7 +11610,7 @@
         <v>133</v>
       </c>
       <c r="C861" t="n">
-        <v>-0.043182</v>
+        <v>-0.043243</v>
       </c>
     </row>
     <row r="862">
@@ -11623,7 +11623,7 @@
         <v>134</v>
       </c>
       <c r="C862" t="n">
-        <v>-0.043135</v>
+        <v>-0.043068</v>
       </c>
     </row>
     <row r="863">
@@ -11636,7 +11636,7 @@
         <v>135</v>
       </c>
       <c r="C863" t="n">
-        <v>-0.042995</v>
+        <v>-0.043025</v>
       </c>
     </row>
     <row r="864">
@@ -11649,7 +11649,7 @@
         <v>136</v>
       </c>
       <c r="C864" t="n">
-        <v>-0.042618</v>
+        <v>-0.042695</v>
       </c>
     </row>
     <row r="865">
@@ -11662,7 +11662,7 @@
         <v>137</v>
       </c>
       <c r="C865" t="n">
-        <v>-0.042568</v>
+        <v>-0.042619</v>
       </c>
     </row>
     <row r="866">
@@ -11675,7 +11675,7 @@
         <v>138</v>
       </c>
       <c r="C866" t="n">
-        <v>-0.041899</v>
+        <v>-0.041854</v>
       </c>
     </row>
     <row r="867">
@@ -11688,7 +11688,7 @@
         <v>139</v>
       </c>
       <c r="C867" t="n">
-        <v>-0.041269</v>
+        <v>-0.04131</v>
       </c>
     </row>
     <row r="868">
@@ -11701,7 +11701,7 @@
         <v>140</v>
       </c>
       <c r="C868" t="n">
-        <v>-0.041052</v>
+        <v>-0.04109</v>
       </c>
     </row>
     <row r="869">
@@ -11714,7 +11714,7 @@
         <v>141</v>
       </c>
       <c r="C869" t="n">
-        <v>-0.040815</v>
+        <v>-0.04091</v>
       </c>
     </row>
     <row r="870">
@@ -11727,7 +11727,7 @@
         <v>142</v>
       </c>
       <c r="C870" t="n">
-        <v>-0.039842</v>
+        <v>-0.039859</v>
       </c>
     </row>
     <row r="871">
@@ -11740,7 +11740,7 @@
         <v>143</v>
       </c>
       <c r="C871" t="n">
-        <v>-0.03888</v>
+        <v>-0.038871</v>
       </c>
     </row>
     <row r="872">
@@ -11753,7 +11753,7 @@
         <v>144</v>
       </c>
       <c r="C872" t="n">
-        <v>-0.03836</v>
+        <v>-0.038413</v>
       </c>
     </row>
     <row r="873">
@@ -11766,7 +11766,7 @@
         <v>145</v>
       </c>
       <c r="C873" t="n">
-        <v>-0.037848</v>
+        <v>-0.037888</v>
       </c>
     </row>
     <row r="874">
@@ -11779,7 +11779,7 @@
         <v>146</v>
       </c>
       <c r="C874" t="n">
-        <v>-0.037835</v>
+        <v>-0.037882</v>
       </c>
     </row>
     <row r="875">
@@ -11792,7 +11792,7 @@
         <v>147</v>
       </c>
       <c r="C875" t="n">
-        <v>-0.037613</v>
+        <v>-0.037665</v>
       </c>
     </row>
     <row r="876">
@@ -11805,7 +11805,7 @@
         <v>148</v>
       </c>
       <c r="C876" t="n">
-        <v>-0.037551</v>
+        <v>-0.037513</v>
       </c>
     </row>
     <row r="877">
@@ -11818,7 +11818,7 @@
         <v>149</v>
       </c>
       <c r="C877" t="n">
-        <v>-0.03744</v>
+        <v>-0.037483</v>
       </c>
     </row>
     <row r="878">
@@ -11831,7 +11831,7 @@
         <v>150</v>
       </c>
       <c r="C878" t="n">
-        <v>-0.036177</v>
+        <v>-0.036185</v>
       </c>
     </row>
     <row r="879">
@@ -11844,7 +11844,7 @@
         <v>151</v>
       </c>
       <c r="C879" t="n">
-        <v>-0.035475</v>
+        <v>-0.035542</v>
       </c>
     </row>
     <row r="880">
@@ -11857,7 +11857,7 @@
         <v>152</v>
       </c>
       <c r="C880" t="n">
-        <v>-0.034404</v>
+        <v>-0.03442</v>
       </c>
     </row>
     <row r="881">
@@ -11870,7 +11870,7 @@
         <v>153</v>
       </c>
       <c r="C881" t="n">
-        <v>-0.03381</v>
+        <v>-0.033825</v>
       </c>
     </row>
     <row r="882">
@@ -11883,7 +11883,7 @@
         <v>154</v>
       </c>
       <c r="C882" t="n">
-        <v>-0.033763</v>
+        <v>-0.033791</v>
       </c>
     </row>
     <row r="883">
@@ -11896,7 +11896,7 @@
         <v>155</v>
       </c>
       <c r="C883" t="n">
-        <v>-0.033362</v>
+        <v>-0.033408</v>
       </c>
     </row>
     <row r="884">
@@ -11909,7 +11909,7 @@
         <v>156</v>
       </c>
       <c r="C884" t="n">
-        <v>-0.033242</v>
+        <v>-0.033298</v>
       </c>
     </row>
     <row r="885">
@@ -11922,7 +11922,7 @@
         <v>157</v>
       </c>
       <c r="C885" t="n">
-        <v>-0.032837</v>
+        <v>-0.032839</v>
       </c>
     </row>
     <row r="886">
@@ -11935,7 +11935,7 @@
         <v>158</v>
       </c>
       <c r="C886" t="n">
-        <v>-0.032666</v>
+        <v>-0.032703</v>
       </c>
     </row>
     <row r="887">
@@ -11948,7 +11948,7 @@
         <v>159</v>
       </c>
       <c r="C887" t="n">
-        <v>-0.032463</v>
+        <v>-0.032524</v>
       </c>
     </row>
     <row r="888">
@@ -11974,7 +11974,7 @@
         <v>161</v>
       </c>
       <c r="C889" t="n">
-        <v>-0.031463</v>
+        <v>-0.031533</v>
       </c>
     </row>
     <row r="890">
@@ -11987,7 +11987,7 @@
         <v>162</v>
       </c>
       <c r="C890" t="n">
-        <v>-0.031341</v>
+        <v>-0.031346</v>
       </c>
     </row>
     <row r="891">
@@ -12000,7 +12000,7 @@
         <v>163</v>
       </c>
       <c r="C891" t="n">
-        <v>-0.031088</v>
+        <v>-0.031085</v>
       </c>
     </row>
     <row r="892">
@@ -12013,7 +12013,7 @@
         <v>164</v>
       </c>
       <c r="C892" t="n">
-        <v>-0.030398</v>
+        <v>-0.030389</v>
       </c>
     </row>
     <row r="893">
@@ -12026,7 +12026,7 @@
         <v>165</v>
       </c>
       <c r="C893" t="n">
-        <v>-0.030379</v>
+        <v>-0.030387</v>
       </c>
     </row>
     <row r="894">
@@ -12039,7 +12039,7 @@
         <v>166</v>
       </c>
       <c r="C894" t="n">
-        <v>-0.03033</v>
+        <v>-0.030381</v>
       </c>
     </row>
     <row r="895">
@@ -12052,7 +12052,7 @@
         <v>167</v>
       </c>
       <c r="C895" t="n">
-        <v>-0.029956</v>
+        <v>-0.029927</v>
       </c>
     </row>
     <row r="896">
@@ -12065,7 +12065,7 @@
         <v>168</v>
       </c>
       <c r="C896" t="n">
-        <v>-0.029928</v>
+        <v>-0.029685</v>
       </c>
     </row>
     <row r="897">
@@ -12078,7 +12078,7 @@
         <v>169</v>
       </c>
       <c r="C897" t="n">
-        <v>-0.029619</v>
+        <v>-0.029644</v>
       </c>
     </row>
     <row r="898">
@@ -12091,7 +12091,7 @@
         <v>170</v>
       </c>
       <c r="C898" t="n">
-        <v>-0.029468</v>
+        <v>-0.029523</v>
       </c>
     </row>
     <row r="899">
@@ -12104,7 +12104,7 @@
         <v>171</v>
       </c>
       <c r="C899" t="n">
-        <v>-0.028636</v>
+        <v>-0.028647</v>
       </c>
     </row>
     <row r="900">
@@ -12117,7 +12117,7 @@
         <v>172</v>
       </c>
       <c r="C900" t="n">
-        <v>-0.028412</v>
+        <v>-0.028376</v>
       </c>
     </row>
     <row r="901">
@@ -12130,7 +12130,7 @@
         <v>173</v>
       </c>
       <c r="C901" t="n">
-        <v>-0.028248</v>
+        <v>-0.028209</v>
       </c>
     </row>
     <row r="902">
@@ -12143,7 +12143,7 @@
         <v>174</v>
       </c>
       <c r="C902" t="n">
-        <v>-0.028047</v>
+        <v>-0.028069</v>
       </c>
     </row>
     <row r="903">
@@ -12156,7 +12156,7 @@
         <v>175</v>
       </c>
       <c r="C903" t="n">
-        <v>-0.027997</v>
+        <v>-0.028043</v>
       </c>
     </row>
     <row r="904">
@@ -12169,7 +12169,7 @@
         <v>176</v>
       </c>
       <c r="C904" t="n">
-        <v>-0.027861</v>
+        <v>-0.027887</v>
       </c>
     </row>
     <row r="905">
@@ -12182,7 +12182,7 @@
         <v>177</v>
       </c>
       <c r="C905" t="n">
-        <v>-0.027821</v>
+        <v>-0.027847</v>
       </c>
     </row>
     <row r="906">
@@ -12195,7 +12195,7 @@
         <v>178</v>
       </c>
       <c r="C906" t="n">
-        <v>-0.027539</v>
+        <v>-0.027547</v>
       </c>
     </row>
     <row r="907">
@@ -12208,7 +12208,7 @@
         <v>179</v>
       </c>
       <c r="C907" t="n">
-        <v>-0.027248</v>
+        <v>-0.027275</v>
       </c>
     </row>
     <row r="908">
@@ -12221,7 +12221,7 @@
         <v>180</v>
       </c>
       <c r="C908" t="n">
-        <v>-0.026803</v>
+        <v>-0.026835</v>
       </c>
     </row>
     <row r="909">
@@ -12234,7 +12234,7 @@
         <v>181</v>
       </c>
       <c r="C909" t="n">
-        <v>-0.026186</v>
+        <v>-0.026096</v>
       </c>
     </row>
     <row r="910">
@@ -12247,7 +12247,7 @@
         <v>182</v>
       </c>
       <c r="C910" t="n">
-        <v>-0.025816</v>
+        <v>-0.025832</v>
       </c>
     </row>
     <row r="911">
@@ -12260,7 +12260,7 @@
         <v>183</v>
       </c>
       <c r="C911" t="n">
-        <v>-0.0254</v>
+        <v>-0.025396</v>
       </c>
     </row>
     <row r="912">
@@ -12273,7 +12273,7 @@
         <v>184</v>
       </c>
       <c r="C912" t="n">
-        <v>-0.025382</v>
+        <v>-0.025307</v>
       </c>
     </row>
     <row r="913">
@@ -12286,7 +12286,7 @@
         <v>185</v>
       </c>
       <c r="C913" t="n">
-        <v>-0.025066</v>
+        <v>-0.025062</v>
       </c>
     </row>
     <row r="914">
@@ -12299,7 +12299,7 @@
         <v>186</v>
       </c>
       <c r="C914" t="n">
-        <v>-0.024863</v>
+        <v>-0.024888</v>
       </c>
     </row>
     <row r="915">
@@ -12312,7 +12312,7 @@
         <v>187</v>
       </c>
       <c r="C915" t="n">
-        <v>-0.02468</v>
+        <v>-0.024719</v>
       </c>
     </row>
     <row r="916">
@@ -12325,7 +12325,7 @@
         <v>188</v>
       </c>
       <c r="C916" t="n">
-        <v>-0.02452</v>
+        <v>-0.024527</v>
       </c>
     </row>
     <row r="917">
@@ -12338,7 +12338,7 @@
         <v>189</v>
       </c>
       <c r="C917" t="n">
-        <v>-0.02429</v>
+        <v>-0.024303</v>
       </c>
     </row>
     <row r="918">
@@ -12351,7 +12351,7 @@
         <v>190</v>
       </c>
       <c r="C918" t="n">
-        <v>-0.024259</v>
+        <v>-0.024276</v>
       </c>
     </row>
     <row r="919">
@@ -12364,7 +12364,7 @@
         <v>191</v>
       </c>
       <c r="C919" t="n">
-        <v>-0.02423</v>
+        <v>-0.02424</v>
       </c>
     </row>
     <row r="920">
@@ -12377,7 +12377,7 @@
         <v>192</v>
       </c>
       <c r="C920" t="n">
-        <v>-0.02409</v>
+        <v>-0.02414</v>
       </c>
     </row>
     <row r="921">
@@ -12390,7 +12390,7 @@
         <v>193</v>
       </c>
       <c r="C921" t="n">
-        <v>-0.023928</v>
+        <v>-0.023908</v>
       </c>
     </row>
     <row r="922">
@@ -12403,7 +12403,7 @@
         <v>194</v>
       </c>
       <c r="C922" t="n">
-        <v>-0.023661</v>
+        <v>-0.023703</v>
       </c>
     </row>
     <row r="923">
@@ -12416,7 +12416,7 @@
         <v>195</v>
       </c>
       <c r="C923" t="n">
-        <v>-0.023656</v>
+        <v>-0.023669</v>
       </c>
     </row>
     <row r="924">
@@ -12429,7 +12429,7 @@
         <v>196</v>
       </c>
       <c r="C924" t="n">
-        <v>-0.022888</v>
+        <v>-0.02294</v>
       </c>
     </row>
     <row r="925">
@@ -12442,7 +12442,7 @@
         <v>197</v>
       </c>
       <c r="C925" t="n">
-        <v>-0.022719</v>
+        <v>-0.022742</v>
       </c>
     </row>
     <row r="926">
@@ -12455,7 +12455,7 @@
         <v>198</v>
       </c>
       <c r="C926" t="n">
-        <v>-0.02219</v>
+        <v>-0.022206</v>
       </c>
     </row>
     <row r="927">
@@ -12468,7 +12468,7 @@
         <v>199</v>
       </c>
       <c r="C927" t="n">
-        <v>-0.021895</v>
+        <v>-0.021934</v>
       </c>
     </row>
     <row r="928">
@@ -12481,7 +12481,7 @@
         <v>200</v>
       </c>
       <c r="C928" t="n">
-        <v>-0.021462</v>
+        <v>-0.021507</v>
       </c>
     </row>
     <row r="929">
@@ -12494,7 +12494,7 @@
         <v>201</v>
       </c>
       <c r="C929" t="n">
-        <v>-0.021086</v>
+        <v>-0.021093</v>
       </c>
     </row>
     <row r="930">
@@ -12507,7 +12507,7 @@
         <v>202</v>
       </c>
       <c r="C930" t="n">
-        <v>-0.020535</v>
+        <v>-0.020565</v>
       </c>
     </row>
     <row r="931">
@@ -12520,7 +12520,7 @@
         <v>203</v>
       </c>
       <c r="C931" t="n">
-        <v>-0.020338</v>
+        <v>-0.020372</v>
       </c>
     </row>
     <row r="932">
@@ -12533,7 +12533,7 @@
         <v>204</v>
       </c>
       <c r="C932" t="n">
-        <v>-0.019681</v>
+        <v>-0.019713</v>
       </c>
     </row>
     <row r="933">
@@ -12546,7 +12546,7 @@
         <v>205</v>
       </c>
       <c r="C933" t="n">
-        <v>-0.019543</v>
+        <v>-0.019569</v>
       </c>
     </row>
     <row r="934">
@@ -12559,7 +12559,7 @@
         <v>206</v>
       </c>
       <c r="C934" t="n">
-        <v>-0.019423</v>
+        <v>-0.019449</v>
       </c>
     </row>
     <row r="935">
@@ -12572,7 +12572,7 @@
         <v>207</v>
       </c>
       <c r="C935" t="n">
-        <v>-0.019348</v>
+        <v>-0.019237</v>
       </c>
     </row>
     <row r="936">
@@ -12585,7 +12585,7 @@
         <v>208</v>
       </c>
       <c r="C936" t="n">
-        <v>-0.019038</v>
+        <v>-0.019051</v>
       </c>
     </row>
     <row r="937">
@@ -12598,7 +12598,7 @@
         <v>209</v>
       </c>
       <c r="C937" t="n">
-        <v>-0.018956</v>
+        <v>-0.018984</v>
       </c>
     </row>
     <row r="938">
@@ -12611,7 +12611,7 @@
         <v>210</v>
       </c>
       <c r="C938" t="n">
-        <v>-0.018942</v>
+        <v>-0.018973</v>
       </c>
     </row>
     <row r="939">
@@ -12624,7 +12624,7 @@
         <v>211</v>
       </c>
       <c r="C939" t="n">
-        <v>-0.018311</v>
+        <v>-0.018324</v>
       </c>
     </row>
     <row r="940">
@@ -12637,7 +12637,7 @@
         <v>212</v>
       </c>
       <c r="C940" t="n">
-        <v>-0.018169</v>
+        <v>-0.018179</v>
       </c>
     </row>
     <row r="941">
@@ -12650,7 +12650,7 @@
         <v>213</v>
       </c>
       <c r="C941" t="n">
-        <v>-0.018149</v>
+        <v>-0.018175</v>
       </c>
     </row>
     <row r="942">
@@ -12663,7 +12663,7 @@
         <v>214</v>
       </c>
       <c r="C942" t="n">
-        <v>-0.018091</v>
+        <v>-0.018108</v>
       </c>
     </row>
     <row r="943">
@@ -12676,7 +12676,7 @@
         <v>215</v>
       </c>
       <c r="C943" t="n">
-        <v>-0.018027</v>
+        <v>-0.018053</v>
       </c>
     </row>
     <row r="944">
@@ -12689,7 +12689,7 @@
         <v>216</v>
       </c>
       <c r="C944" t="n">
-        <v>-0.017984</v>
+        <v>-0.017986</v>
       </c>
     </row>
     <row r="945">
@@ -12702,7 +12702,7 @@
         <v>217</v>
       </c>
       <c r="C945" t="n">
-        <v>-0.017669</v>
+        <v>-0.01769</v>
       </c>
     </row>
     <row r="946">
@@ -12715,7 +12715,7 @@
         <v>218</v>
       </c>
       <c r="C946" t="n">
-        <v>-0.017598</v>
+        <v>-0.017599</v>
       </c>
     </row>
     <row r="947">
@@ -12728,7 +12728,7 @@
         <v>219</v>
       </c>
       <c r="C947" t="n">
-        <v>-0.017529</v>
+        <v>-0.017549</v>
       </c>
     </row>
     <row r="948">
@@ -12741,7 +12741,7 @@
         <v>220</v>
       </c>
       <c r="C948" t="n">
-        <v>-0.017505</v>
+        <v>-0.017519</v>
       </c>
     </row>
     <row r="949">
@@ -12754,7 +12754,7 @@
         <v>221</v>
       </c>
       <c r="C949" t="n">
-        <v>-0.017063</v>
+        <v>-0.017065</v>
       </c>
     </row>
     <row r="950">
@@ -12767,7 +12767,7 @@
         <v>222</v>
       </c>
       <c r="C950" t="n">
-        <v>-0.017009</v>
+        <v>-0.017011</v>
       </c>
     </row>
     <row r="951">
@@ -12780,7 +12780,7 @@
         <v>223</v>
       </c>
       <c r="C951" t="n">
-        <v>-0.016945</v>
+        <v>-0.016906</v>
       </c>
     </row>
     <row r="952">
@@ -12793,7 +12793,7 @@
         <v>224</v>
       </c>
       <c r="C952" t="n">
-        <v>-0.016451</v>
+        <v>-0.016458</v>
       </c>
     </row>
     <row r="953">
@@ -12806,7 +12806,7 @@
         <v>225</v>
       </c>
       <c r="C953" t="n">
-        <v>-0.015729</v>
+        <v>-0.015755</v>
       </c>
     </row>
     <row r="954">
@@ -12819,7 +12819,7 @@
         <v>226</v>
       </c>
       <c r="C954" t="n">
-        <v>-0.015373</v>
+        <v>-0.015403</v>
       </c>
     </row>
     <row r="955">
@@ -12832,7 +12832,7 @@
         <v>227</v>
       </c>
       <c r="C955" t="n">
-        <v>-0.01509</v>
+        <v>-0.015099</v>
       </c>
     </row>
     <row r="956">
@@ -12845,7 +12845,7 @@
         <v>228</v>
       </c>
       <c r="C956" t="n">
-        <v>-0.014945</v>
+        <v>-0.014955</v>
       </c>
     </row>
     <row r="957">
@@ -12858,7 +12858,7 @@
         <v>229</v>
       </c>
       <c r="C957" t="n">
-        <v>-0.014319</v>
+        <v>-0.014311</v>
       </c>
     </row>
     <row r="958">
@@ -12871,7 +12871,7 @@
         <v>230</v>
       </c>
       <c r="C958" t="n">
-        <v>-0.014028</v>
+        <v>-0.014053</v>
       </c>
     </row>
     <row r="959">
@@ -12884,7 +12884,7 @@
         <v>231</v>
       </c>
       <c r="C959" t="n">
-        <v>-0.013555</v>
+        <v>-0.013581</v>
       </c>
     </row>
     <row r="960">
@@ -12897,7 +12897,7 @@
         <v>232</v>
       </c>
       <c r="C960" t="n">
-        <v>-0.013514</v>
+        <v>-0.013548</v>
       </c>
     </row>
     <row r="961">
@@ -12910,7 +12910,7 @@
         <v>233</v>
       </c>
       <c r="C961" t="n">
-        <v>-0.012639</v>
+        <v>-0.012653</v>
       </c>
     </row>
     <row r="962">
@@ -12923,7 +12923,7 @@
         <v>234</v>
       </c>
       <c r="C962" t="n">
-        <v>-0.012601</v>
+        <v>-0.012609</v>
       </c>
     </row>
     <row r="963">
@@ -12936,7 +12936,7 @@
         <v>235</v>
       </c>
       <c r="C963" t="n">
-        <v>-0.012382</v>
+        <v>-0.012369</v>
       </c>
     </row>
     <row r="964">
@@ -12949,7 +12949,7 @@
         <v>236</v>
       </c>
       <c r="C964" t="n">
-        <v>-0.011901</v>
+        <v>-0.011912</v>
       </c>
     </row>
     <row r="965">
@@ -12962,7 +12962,7 @@
         <v>237</v>
       </c>
       <c r="C965" t="n">
-        <v>-0.011828</v>
+        <v>-0.011827</v>
       </c>
     </row>
     <row r="966">
@@ -12988,7 +12988,7 @@
         <v>239</v>
       </c>
       <c r="C967" t="n">
-        <v>-0.011447</v>
+        <v>-0.011456</v>
       </c>
     </row>
     <row r="968">
@@ -13001,7 +13001,7 @@
         <v>240</v>
       </c>
       <c r="C968" t="n">
-        <v>-0.01122</v>
+        <v>-0.011224</v>
       </c>
     </row>
     <row r="969">
@@ -13014,7 +13014,7 @@
         <v>241</v>
       </c>
       <c r="C969" t="n">
-        <v>-0.011147</v>
+        <v>-0.011142</v>
       </c>
     </row>
     <row r="970">
@@ -13027,7 +13027,7 @@
         <v>242</v>
       </c>
       <c r="C970" t="n">
-        <v>-0.010888</v>
+        <v>-0.010891</v>
       </c>
     </row>
     <row r="971">
@@ -13040,7 +13040,7 @@
         <v>243</v>
       </c>
       <c r="C971" t="n">
-        <v>-0.010687</v>
+        <v>-0.010696</v>
       </c>
     </row>
     <row r="972">
@@ -13053,7 +13053,7 @@
         <v>244</v>
       </c>
       <c r="C972" t="n">
-        <v>-0.010286</v>
+        <v>-0.010284</v>
       </c>
     </row>
     <row r="973">
@@ -13066,7 +13066,7 @@
         <v>245</v>
       </c>
       <c r="C973" t="n">
-        <v>-0.010267</v>
+        <v>-0.01026</v>
       </c>
     </row>
     <row r="974">
@@ -13079,7 +13079,7 @@
         <v>246</v>
       </c>
       <c r="C974" t="n">
-        <v>-0.009948</v>
+        <v>-0.009963</v>
       </c>
     </row>
     <row r="975">
@@ -13092,7 +13092,7 @@
         <v>247</v>
       </c>
       <c r="C975" t="n">
-        <v>-0.009535999999999999</v>
+        <v>-0.00954</v>
       </c>
     </row>
     <row r="976">
@@ -13105,7 +13105,7 @@
         <v>248</v>
       </c>
       <c r="C976" t="n">
-        <v>-0.008872</v>
+        <v>-0.008886</v>
       </c>
     </row>
     <row r="977">
@@ -13118,7 +13118,7 @@
         <v>249</v>
       </c>
       <c r="C977" t="n">
-        <v>-0.007922</v>
+        <v>-0.007927999999999999</v>
       </c>
     </row>
     <row r="978">
@@ -13131,7 +13131,7 @@
         <v>250</v>
       </c>
       <c r="C978" t="n">
-        <v>-0.007847</v>
+        <v>-0.007854</v>
       </c>
     </row>
     <row r="979">
@@ -13144,7 +13144,7 @@
         <v>251</v>
       </c>
       <c r="C979" t="n">
-        <v>-0.007676</v>
+        <v>-0.007685</v>
       </c>
     </row>
     <row r="980">
@@ -13157,7 +13157,7 @@
         <v>252</v>
       </c>
       <c r="C980" t="n">
-        <v>-0.007436</v>
+        <v>-0.007445</v>
       </c>
     </row>
     <row r="981">
@@ -13170,7 +13170,7 @@
         <v>253</v>
       </c>
       <c r="C981" t="n">
-        <v>-0.007042</v>
+        <v>-0.007053</v>
       </c>
     </row>
     <row r="982">
@@ -13183,7 +13183,7 @@
         <v>254</v>
       </c>
       <c r="C982" t="n">
-        <v>-0.00694</v>
+        <v>-0.006954</v>
       </c>
     </row>
     <row r="983">
@@ -13196,7 +13196,7 @@
         <v>255</v>
       </c>
       <c r="C983" t="n">
-        <v>-0.006936</v>
+        <v>-0.00695</v>
       </c>
     </row>
     <row r="984">
@@ -13209,7 +13209,7 @@
         <v>256</v>
       </c>
       <c r="C984" t="n">
-        <v>-0.006924</v>
+        <v>-0.006927</v>
       </c>
     </row>
     <row r="985">
@@ -13222,7 +13222,7 @@
         <v>257</v>
       </c>
       <c r="C985" t="n">
-        <v>-0.006922</v>
+        <v>-0.00688</v>
       </c>
     </row>
     <row r="986">
@@ -13235,7 +13235,7 @@
         <v>258</v>
       </c>
       <c r="C986" t="n">
-        <v>-0.006799</v>
+        <v>-0.006804</v>
       </c>
     </row>
     <row r="987">
@@ -13248,7 +13248,7 @@
         <v>259</v>
       </c>
       <c r="C987" t="n">
-        <v>-0.00678</v>
+        <v>-0.006793</v>
       </c>
     </row>
     <row r="988">
@@ -13261,7 +13261,7 @@
         <v>260</v>
       </c>
       <c r="C988" t="n">
-        <v>-0.006677</v>
+        <v>-0.006689</v>
       </c>
     </row>
     <row r="989">
@@ -13274,7 +13274,7 @@
         <v>261</v>
       </c>
       <c r="C989" t="n">
-        <v>-0.006383</v>
+        <v>-0.006385</v>
       </c>
     </row>
     <row r="990">
@@ -13287,7 +13287,7 @@
         <v>262</v>
       </c>
       <c r="C990" t="n">
-        <v>-0.006081</v>
+        <v>-0.006083</v>
       </c>
     </row>
     <row r="991">
@@ -13313,7 +13313,7 @@
         <v>264</v>
       </c>
       <c r="C992" t="n">
-        <v>-0.005835</v>
+        <v>-0.005842</v>
       </c>
     </row>
     <row r="993">
@@ -13326,7 +13326,7 @@
         <v>265</v>
       </c>
       <c r="C993" t="n">
-        <v>-0.005656</v>
+        <v>-0.005666</v>
       </c>
     </row>
     <row r="994">
@@ -13339,7 +13339,7 @@
         <v>266</v>
       </c>
       <c r="C994" t="n">
-        <v>-0.005426</v>
+        <v>-0.005415</v>
       </c>
     </row>
     <row r="995">
@@ -13352,7 +13352,7 @@
         <v>267</v>
       </c>
       <c r="C995" t="n">
-        <v>-0.005122</v>
+        <v>-0.005132</v>
       </c>
     </row>
     <row r="996">
@@ -13365,7 +13365,7 @@
         <v>268</v>
       </c>
       <c r="C996" t="n">
-        <v>-0.00505</v>
+        <v>-0.005053</v>
       </c>
     </row>
     <row r="997">
@@ -13378,7 +13378,7 @@
         <v>269</v>
       </c>
       <c r="C997" t="n">
-        <v>-0.004414</v>
+        <v>-0.004415</v>
       </c>
     </row>
     <row r="998">
@@ -13417,7 +13417,7 @@
         <v>272</v>
       </c>
       <c r="C1000" t="n">
-        <v>-0.003831</v>
+        <v>-0.003834</v>
       </c>
     </row>
     <row r="1001">
@@ -13430,7 +13430,7 @@
         <v>273</v>
       </c>
       <c r="C1001" t="n">
-        <v>-0.003657</v>
+        <v>-0.003661</v>
       </c>
     </row>
     <row r="1002">
@@ -13443,7 +13443,7 @@
         <v>274</v>
       </c>
       <c r="C1002" t="n">
-        <v>-0.003184</v>
+        <v>-0.003187</v>
       </c>
     </row>
     <row r="1003">
@@ -13456,7 +13456,7 @@
         <v>275</v>
       </c>
       <c r="C1003" t="n">
-        <v>-0.00318</v>
+        <v>-0.003185</v>
       </c>
     </row>
     <row r="1004">
@@ -13469,7 +13469,7 @@
         <v>276</v>
       </c>
       <c r="C1004" t="n">
-        <v>-0.003149</v>
+        <v>-0.003153</v>
       </c>
     </row>
     <row r="1005">
@@ -13495,7 +13495,7 @@
         <v>278</v>
       </c>
       <c r="C1006" t="n">
-        <v>-0.00299</v>
+        <v>-0.002994</v>
       </c>
     </row>
     <row r="1007">
@@ -13508,7 +13508,7 @@
         <v>279</v>
       </c>
       <c r="C1007" t="n">
-        <v>-0.002354</v>
+        <v>-0.002358</v>
       </c>
     </row>
     <row r="1008">
@@ -13521,7 +13521,7 @@
         <v>280</v>
       </c>
       <c r="C1008" t="n">
-        <v>-0.002201</v>
+        <v>-0.002202</v>
       </c>
     </row>
     <row r="1009">
@@ -13534,7 +13534,7 @@
         <v>281</v>
       </c>
       <c r="C1009" t="n">
-        <v>-0.002103</v>
+        <v>-0.002107</v>
       </c>
     </row>
     <row r="1010">
@@ -13547,7 +13547,7 @@
         <v>282</v>
       </c>
       <c r="C1010" t="n">
-        <v>-0.001997</v>
+        <v>-0.002</v>
       </c>
     </row>
     <row r="1011">
@@ -13560,7 +13560,7 @@
         <v>283</v>
       </c>
       <c r="C1011" t="n">
-        <v>-0.001729</v>
+        <v>-0.001732</v>
       </c>
     </row>
     <row r="1012">
@@ -13573,7 +13573,7 @@
         <v>284</v>
       </c>
       <c r="C1012" t="n">
-        <v>-0.001643</v>
+        <v>-0.001647</v>
       </c>
     </row>
     <row r="1013">
@@ -13586,7 +13586,7 @@
         <v>285</v>
       </c>
       <c r="C1013" t="n">
-        <v>-0.001566</v>
+        <v>-0.001567</v>
       </c>
     </row>
     <row r="1014">
@@ -13599,7 +13599,7 @@
         <v>286</v>
       </c>
       <c r="C1014" t="n">
-        <v>-0.001412</v>
+        <v>-0.001408</v>
       </c>
     </row>
     <row r="1015">
@@ -13612,7 +13612,7 @@
         <v>287</v>
       </c>
       <c r="C1015" t="n">
-        <v>-0.00108</v>
+        <v>-0.001081</v>
       </c>
     </row>
     <row r="1016">
@@ -13638,7 +13638,7 @@
         <v>289</v>
       </c>
       <c r="C1017" t="n">
-        <v>-0.000737</v>
+        <v>-0.000739</v>
       </c>
     </row>
     <row r="1018">
@@ -13742,7 +13742,7 @@
         <v>297</v>
       </c>
       <c r="C1025" t="n">
-        <v>0.000111</v>
+        <v>0.000112</v>
       </c>
     </row>
     <row r="1026">
@@ -13755,7 +13755,7 @@
         <v>298</v>
       </c>
       <c r="C1026" t="n">
-        <v>0.000428</v>
+        <v>0.000429</v>
       </c>
     </row>
     <row r="1027">
@@ -13794,7 +13794,7 @@
         <v>301</v>
       </c>
       <c r="C1029" t="n">
-        <v>0.001</v>
+        <v>0.000998</v>
       </c>
     </row>
     <row r="1030">
@@ -13807,7 +13807,7 @@
         <v>302</v>
       </c>
       <c r="C1030" t="n">
-        <v>0.001069</v>
+        <v>0.00107</v>
       </c>
     </row>
     <row r="1031">
@@ -13820,7 +13820,7 @@
         <v>303</v>
       </c>
       <c r="C1031" t="n">
-        <v>0.001653</v>
+        <v>0.001652</v>
       </c>
     </row>
     <row r="1032">
@@ -13846,7 +13846,7 @@
         <v>305</v>
       </c>
       <c r="C1033" t="n">
-        <v>0.002016</v>
+        <v>0.002019</v>
       </c>
     </row>
     <row r="1034">
@@ -13859,7 +13859,7 @@
         <v>306</v>
       </c>
       <c r="C1034" t="n">
-        <v>0.002407</v>
+        <v>0.002405</v>
       </c>
     </row>
     <row r="1035">
@@ -13872,7 +13872,7 @@
         <v>307</v>
       </c>
       <c r="C1035" t="n">
-        <v>0.002565</v>
+        <v>0.002555</v>
       </c>
     </row>
     <row r="1036">
@@ -13885,7 +13885,7 @@
         <v>308</v>
       </c>
       <c r="C1036" t="n">
-        <v>0.00275</v>
+        <v>0.002753</v>
       </c>
     </row>
     <row r="1037">
@@ -13898,7 +13898,7 @@
         <v>309</v>
       </c>
       <c r="C1037" t="n">
-        <v>0.002843</v>
+        <v>0.002848</v>
       </c>
     </row>
     <row r="1038">
@@ -13911,7 +13911,7 @@
         <v>310</v>
       </c>
       <c r="C1038" t="n">
-        <v>0.003017</v>
+        <v>0.003023</v>
       </c>
     </row>
     <row r="1039">
@@ -13924,7 +13924,7 @@
         <v>311</v>
       </c>
       <c r="C1039" t="n">
-        <v>0.003097</v>
+        <v>0.0031</v>
       </c>
     </row>
     <row r="1040">
@@ -13937,7 +13937,7 @@
         <v>312</v>
       </c>
       <c r="C1040" t="n">
-        <v>0.003499</v>
+        <v>0.003492</v>
       </c>
     </row>
     <row r="1041">
@@ -13950,7 +13950,7 @@
         <v>313</v>
       </c>
       <c r="C1041" t="n">
-        <v>0.003887</v>
+        <v>0.003879</v>
       </c>
     </row>
     <row r="1042">
@@ -13963,7 +13963,7 @@
         <v>314</v>
       </c>
       <c r="C1042" t="n">
-        <v>0.00396</v>
+        <v>0.003958</v>
       </c>
     </row>
     <row r="1043">
@@ -13976,7 +13976,7 @@
         <v>315</v>
       </c>
       <c r="C1043" t="n">
-        <v>0.004235</v>
+        <v>0.004238</v>
       </c>
     </row>
     <row r="1044">
@@ -13989,7 +13989,7 @@
         <v>316</v>
       </c>
       <c r="C1044" t="n">
-        <v>0.004346</v>
+        <v>0.004348</v>
       </c>
     </row>
     <row r="1045">
@@ -14002,7 +14002,7 @@
         <v>317</v>
       </c>
       <c r="C1045" t="n">
-        <v>0.00453</v>
+        <v>0.004536</v>
       </c>
     </row>
     <row r="1046">
@@ -14015,7 +14015,7 @@
         <v>318</v>
       </c>
       <c r="C1046" t="n">
-        <v>0.004564</v>
+        <v>0.004563</v>
       </c>
     </row>
     <row r="1047">
@@ -14028,7 +14028,7 @@
         <v>319</v>
       </c>
       <c r="C1047" t="n">
-        <v>0.004601</v>
+        <v>0.004606</v>
       </c>
     </row>
     <row r="1048">
@@ -14041,7 +14041,7 @@
         <v>320</v>
       </c>
       <c r="C1048" t="n">
-        <v>0.004656</v>
+        <v>0.004661</v>
       </c>
     </row>
     <row r="1049">
@@ -14054,7 +14054,7 @@
         <v>321</v>
       </c>
       <c r="C1049" t="n">
-        <v>0.004783</v>
+        <v>0.004771</v>
       </c>
     </row>
     <row r="1050">
@@ -14067,7 +14067,7 @@
         <v>322</v>
       </c>
       <c r="C1050" t="n">
-        <v>0.004827</v>
+        <v>0.004816</v>
       </c>
     </row>
     <row r="1051">
@@ -14080,7 +14080,7 @@
         <v>323</v>
       </c>
       <c r="C1051" t="n">
-        <v>0.004885</v>
+        <v>0.00489</v>
       </c>
     </row>
     <row r="1052">
@@ -14093,7 +14093,7 @@
         <v>324</v>
       </c>
       <c r="C1052" t="n">
-        <v>0.004983</v>
+        <v>0.004974</v>
       </c>
     </row>
     <row r="1053">
@@ -14106,7 +14106,7 @@
         <v>325</v>
       </c>
       <c r="C1053" t="n">
-        <v>0.004988</v>
+        <v>0.004983</v>
       </c>
     </row>
     <row r="1054">
@@ -14132,7 +14132,7 @@
         <v>327</v>
       </c>
       <c r="C1055" t="n">
-        <v>0.005324</v>
+        <v>0.005332</v>
       </c>
     </row>
     <row r="1056">
@@ -14145,7 +14145,7 @@
         <v>328</v>
       </c>
       <c r="C1056" t="n">
-        <v>0.005623</v>
+        <v>0.005633</v>
       </c>
     </row>
     <row r="1057">
@@ -14158,7 +14158,7 @@
         <v>329</v>
       </c>
       <c r="C1057" t="n">
-        <v>0.005696</v>
+        <v>0.0057</v>
       </c>
     </row>
     <row r="1058">
@@ -14171,7 +14171,7 @@
         <v>330</v>
       </c>
       <c r="C1058" t="n">
-        <v>0.005752</v>
+        <v>0.005753</v>
       </c>
     </row>
     <row r="1059">
@@ -14184,7 +14184,7 @@
         <v>331</v>
       </c>
       <c r="C1059" t="n">
-        <v>0.005878</v>
+        <v>0.005884</v>
       </c>
     </row>
     <row r="1060">
@@ -14197,7 +14197,7 @@
         <v>332</v>
       </c>
       <c r="C1060" t="n">
-        <v>0.007399</v>
+        <v>0.00739</v>
       </c>
     </row>
     <row r="1061">
@@ -14210,7 +14210,7 @@
         <v>333</v>
       </c>
       <c r="C1061" t="n">
-        <v>0.007736</v>
+        <v>0.007738</v>
       </c>
     </row>
     <row r="1062">
@@ -14223,7 +14223,7 @@
         <v>334</v>
       </c>
       <c r="C1062" t="n">
-        <v>0.008163</v>
+        <v>0.008160000000000001</v>
       </c>
     </row>
     <row r="1063">
@@ -14236,7 +14236,7 @@
         <v>335</v>
       </c>
       <c r="C1063" t="n">
-        <v>0.008279999999999999</v>
+        <v>0.008284</v>
       </c>
     </row>
     <row r="1064">
@@ -14249,7 +14249,7 @@
         <v>336</v>
       </c>
       <c r="C1064" t="n">
-        <v>0.008505</v>
+        <v>0.008515</v>
       </c>
     </row>
     <row r="1065">
@@ -14262,7 +14262,7 @@
         <v>337</v>
       </c>
       <c r="C1065" t="n">
-        <v>0.008964</v>
+        <v>0.008973999999999999</v>
       </c>
     </row>
     <row r="1066">
@@ -14275,7 +14275,7 @@
         <v>338</v>
       </c>
       <c r="C1066" t="n">
-        <v>0.009357000000000001</v>
+        <v>0.009369000000000001</v>
       </c>
     </row>
     <row r="1067">
@@ -14288,7 +14288,7 @@
         <v>339</v>
       </c>
       <c r="C1067" t="n">
-        <v>0.009382</v>
+        <v>0.009375</v>
       </c>
     </row>
     <row r="1068">
@@ -14301,7 +14301,7 @@
         <v>340</v>
       </c>
       <c r="C1068" t="n">
-        <v>0.009527000000000001</v>
+        <v>0.009528</v>
       </c>
     </row>
     <row r="1069">
@@ -14314,7 +14314,7 @@
         <v>341</v>
       </c>
       <c r="C1069" t="n">
-        <v>0.009651</v>
+        <v>0.009662</v>
       </c>
     </row>
     <row r="1070">
@@ -14327,7 +14327,7 @@
         <v>342</v>
       </c>
       <c r="C1070" t="n">
-        <v>0.009955</v>
+        <v>0.009911</v>
       </c>
     </row>
     <row r="1071">
@@ -14340,7 +14340,7 @@
         <v>343</v>
       </c>
       <c r="C1071" t="n">
-        <v>0.010016</v>
+        <v>0.010031</v>
       </c>
     </row>
     <row r="1072">
@@ -14353,7 +14353,7 @@
         <v>344</v>
       </c>
       <c r="C1072" t="n">
-        <v>0.010045</v>
+        <v>0.010061</v>
       </c>
     </row>
     <row r="1073">
@@ -14366,7 +14366,7 @@
         <v>345</v>
       </c>
       <c r="C1073" t="n">
-        <v>0.010105</v>
+        <v>0.010097</v>
       </c>
     </row>
     <row r="1074">
@@ -14379,7 +14379,7 @@
         <v>346</v>
       </c>
       <c r="C1074" t="n">
-        <v>0.010128</v>
+        <v>0.010103</v>
       </c>
     </row>
     <row r="1075">
@@ -14392,7 +14392,7 @@
         <v>347</v>
       </c>
       <c r="C1075" t="n">
-        <v>0.010524</v>
+        <v>0.010534</v>
       </c>
     </row>
     <row r="1076">
@@ -14405,7 +14405,7 @@
         <v>348</v>
       </c>
       <c r="C1076" t="n">
-        <v>0.010789</v>
+        <v>0.010804</v>
       </c>
     </row>
     <row r="1077">
@@ -14418,7 +14418,7 @@
         <v>349</v>
       </c>
       <c r="C1077" t="n">
-        <v>0.010979</v>
+        <v>0.010983</v>
       </c>
     </row>
     <row r="1078">
@@ -14431,7 +14431,7 @@
         <v>350</v>
       </c>
       <c r="C1078" t="n">
-        <v>0.011003</v>
+        <v>0.011033</v>
       </c>
     </row>
     <row r="1079">
@@ -14444,7 +14444,7 @@
         <v>351</v>
       </c>
       <c r="C1079" t="n">
-        <v>0.011094</v>
+        <v>0.011103</v>
       </c>
     </row>
     <row r="1080">
@@ -14457,7 +14457,7 @@
         <v>352</v>
       </c>
       <c r="C1080" t="n">
-        <v>0.011241</v>
+        <v>0.011253</v>
       </c>
     </row>
     <row r="1081">
@@ -14470,7 +14470,7 @@
         <v>353</v>
       </c>
       <c r="C1081" t="n">
-        <v>0.011375</v>
+        <v>0.011391</v>
       </c>
     </row>
     <row r="1082">
@@ -14483,7 +14483,7 @@
         <v>354</v>
       </c>
       <c r="C1082" t="n">
-        <v>0.011773</v>
+        <v>0.011795</v>
       </c>
     </row>
     <row r="1083">
@@ -14496,7 +14496,7 @@
         <v>355</v>
       </c>
       <c r="C1083" t="n">
-        <v>0.011857</v>
+        <v>0.011872</v>
       </c>
     </row>
     <row r="1084">
@@ -14509,7 +14509,7 @@
         <v>356</v>
       </c>
       <c r="C1084" t="n">
-        <v>0.012058</v>
+        <v>0.012034</v>
       </c>
     </row>
     <row r="1085">
@@ -14522,7 +14522,7 @@
         <v>357</v>
       </c>
       <c r="C1085" t="n">
-        <v>0.012197</v>
+        <v>0.012198</v>
       </c>
     </row>
     <row r="1086">
@@ -14535,7 +14535,7 @@
         <v>358</v>
       </c>
       <c r="C1086" t="n">
-        <v>0.012403</v>
+        <v>0.012401</v>
       </c>
     </row>
     <row r="1087">
@@ -14548,7 +14548,7 @@
         <v>359</v>
       </c>
       <c r="C1087" t="n">
-        <v>0.012845</v>
+        <v>0.012858</v>
       </c>
     </row>
     <row r="1088">
@@ -14561,7 +14561,7 @@
         <v>360</v>
       </c>
       <c r="C1088" t="n">
-        <v>0.012929</v>
+        <v>0.012927</v>
       </c>
     </row>
     <row r="1089">
@@ -14574,7 +14574,7 @@
         <v>361</v>
       </c>
       <c r="C1089" t="n">
-        <v>0.013059</v>
+        <v>0.013053</v>
       </c>
     </row>
     <row r="1090">
@@ -14587,7 +14587,7 @@
         <v>362</v>
       </c>
       <c r="C1090" t="n">
-        <v>0.013114</v>
+        <v>0.013124</v>
       </c>
     </row>
     <row r="1091">
@@ -14600,7 +14600,7 @@
         <v>363</v>
       </c>
       <c r="C1091" t="n">
-        <v>0.013212</v>
+        <v>0.013169</v>
       </c>
     </row>
     <row r="1092">
@@ -14613,7 +14613,7 @@
         <v>364</v>
       </c>
       <c r="C1092" t="n">
-        <v>0.013429</v>
+        <v>0.013459</v>
       </c>
     </row>
     <row r="1093">
@@ -14626,7 +14626,7 @@
         <v>365</v>
       </c>
       <c r="C1093" t="n">
-        <v>0.013766</v>
+        <v>0.013776</v>
       </c>
     </row>
     <row r="1094">
@@ -14639,7 +14639,7 @@
         <v>366</v>
       </c>
       <c r="C1094" t="n">
-        <v>0.013807</v>
+        <v>0.013834</v>
       </c>
     </row>
     <row r="1095">
@@ -14652,7 +14652,7 @@
         <v>367</v>
       </c>
       <c r="C1095" t="n">
-        <v>0.014288</v>
+        <v>0.01427</v>
       </c>
     </row>
     <row r="1096">
@@ -14665,7 +14665,7 @@
         <v>368</v>
       </c>
       <c r="C1096" t="n">
-        <v>0.014866</v>
+        <v>0.014861</v>
       </c>
     </row>
     <row r="1097">
@@ -14678,7 +14678,7 @@
         <v>369</v>
       </c>
       <c r="C1097" t="n">
-        <v>0.014894</v>
+        <v>0.01492</v>
       </c>
     </row>
     <row r="1098">
@@ -14691,7 +14691,7 @@
         <v>370</v>
       </c>
       <c r="C1098" t="n">
-        <v>0.015286</v>
+        <v>0.015298</v>
       </c>
     </row>
     <row r="1099">
@@ -14704,7 +14704,7 @@
         <v>371</v>
       </c>
       <c r="C1099" t="n">
-        <v>0.015436</v>
+        <v>0.015433</v>
       </c>
     </row>
     <row r="1100">
@@ -14717,7 +14717,7 @@
         <v>372</v>
       </c>
       <c r="C1100" t="n">
-        <v>0.015549</v>
+        <v>0.015566</v>
       </c>
     </row>
     <row r="1101">
@@ -14730,7 +14730,7 @@
         <v>373</v>
       </c>
       <c r="C1101" t="n">
-        <v>0.01555</v>
+        <v>0.015574</v>
       </c>
     </row>
     <row r="1102">
@@ -14743,7 +14743,7 @@
         <v>374</v>
       </c>
       <c r="C1102" t="n">
-        <v>0.015709</v>
+        <v>0.015721</v>
       </c>
     </row>
     <row r="1103">
@@ -14756,7 +14756,7 @@
         <v>375</v>
       </c>
       <c r="C1103" t="n">
-        <v>0.015802</v>
+        <v>0.015827</v>
       </c>
     </row>
     <row r="1104">
@@ -14769,7 +14769,7 @@
         <v>376</v>
       </c>
       <c r="C1104" t="n">
-        <v>0.015836</v>
+        <v>0.015835</v>
       </c>
     </row>
     <row r="1105">
@@ -14782,7 +14782,7 @@
         <v>377</v>
       </c>
       <c r="C1105" t="n">
-        <v>0.016002</v>
+        <v>0.016029</v>
       </c>
     </row>
     <row r="1106">
@@ -14795,7 +14795,7 @@
         <v>378</v>
       </c>
       <c r="C1106" t="n">
-        <v>0.016075</v>
+        <v>0.016091</v>
       </c>
     </row>
     <row r="1107">
@@ -14808,7 +14808,7 @@
         <v>379</v>
       </c>
       <c r="C1107" t="n">
-        <v>0.016097</v>
+        <v>0.016103</v>
       </c>
     </row>
     <row r="1108">
@@ -14821,7 +14821,7 @@
         <v>380</v>
       </c>
       <c r="C1108" t="n">
-        <v>0.016269</v>
+        <v>0.016283</v>
       </c>
     </row>
     <row r="1109">
@@ -14847,7 +14847,7 @@
         <v>382</v>
       </c>
       <c r="C1110" t="n">
-        <v>0.017281</v>
+        <v>0.017297</v>
       </c>
     </row>
     <row r="1111">
@@ -14860,7 +14860,7 @@
         <v>383</v>
       </c>
       <c r="C1111" t="n">
-        <v>0.017454</v>
+        <v>0.017484</v>
       </c>
     </row>
     <row r="1112">
@@ -14873,7 +14873,7 @@
         <v>384</v>
       </c>
       <c r="C1112" t="n">
-        <v>0.017643</v>
+        <v>0.017642</v>
       </c>
     </row>
     <row r="1113">
@@ -14886,7 +14886,7 @@
         <v>385</v>
       </c>
       <c r="C1113" t="n">
-        <v>0.017878</v>
+        <v>0.017916</v>
       </c>
     </row>
     <row r="1114">
@@ -14899,7 +14899,7 @@
         <v>386</v>
       </c>
       <c r="C1114" t="n">
-        <v>0.018526</v>
+        <v>0.018525</v>
       </c>
     </row>
     <row r="1115">
@@ -14912,7 +14912,7 @@
         <v>387</v>
       </c>
       <c r="C1115" t="n">
-        <v>0.018685</v>
+        <v>0.018672</v>
       </c>
     </row>
     <row r="1116">
@@ -14925,7 +14925,7 @@
         <v>388</v>
       </c>
       <c r="C1116" t="n">
-        <v>0.018725</v>
+        <v>0.018756</v>
       </c>
     </row>
     <row r="1117">
@@ -14938,7 +14938,7 @@
         <v>389</v>
       </c>
       <c r="C1117" t="n">
-        <v>0.018856</v>
+        <v>0.018862</v>
       </c>
     </row>
     <row r="1118">
@@ -14951,7 +14951,7 @@
         <v>390</v>
       </c>
       <c r="C1118" t="n">
-        <v>0.018881</v>
+        <v>0.018917</v>
       </c>
     </row>
     <row r="1119">
@@ -14964,7 +14964,7 @@
         <v>391</v>
       </c>
       <c r="C1119" t="n">
-        <v>0.019133</v>
+        <v>0.01915</v>
       </c>
     </row>
     <row r="1120">
@@ -14977,7 +14977,7 @@
         <v>392</v>
       </c>
       <c r="C1120" t="n">
-        <v>0.019438</v>
+        <v>0.019444</v>
       </c>
     </row>
     <row r="1121">
@@ -15003,7 +15003,7 @@
         <v>394</v>
       </c>
       <c r="C1122" t="n">
-        <v>0.019806</v>
+        <v>0.019802</v>
       </c>
     </row>
     <row r="1123">
@@ -15016,7 +15016,7 @@
         <v>395</v>
       </c>
       <c r="C1123" t="n">
-        <v>0.019892</v>
+        <v>0.019883</v>
       </c>
     </row>
     <row r="1124">
@@ -15029,7 +15029,7 @@
         <v>396</v>
       </c>
       <c r="C1124" t="n">
-        <v>0.019927</v>
+        <v>0.019933</v>
       </c>
     </row>
     <row r="1125">
@@ -15042,7 +15042,7 @@
         <v>397</v>
       </c>
       <c r="C1125" t="n">
-        <v>0.02028</v>
+        <v>0.020305</v>
       </c>
     </row>
     <row r="1126">
@@ -15055,7 +15055,7 @@
         <v>398</v>
       </c>
       <c r="C1126" t="n">
-        <v>0.020738</v>
+        <v>0.020762</v>
       </c>
     </row>
     <row r="1127">
@@ -15068,7 +15068,7 @@
         <v>399</v>
       </c>
       <c r="C1127" t="n">
-        <v>0.020887</v>
+        <v>0.02089</v>
       </c>
     </row>
     <row r="1128">
@@ -15081,7 +15081,7 @@
         <v>400</v>
       </c>
       <c r="C1128" t="n">
-        <v>0.021384</v>
+        <v>0.021235</v>
       </c>
     </row>
     <row r="1129">
@@ -15094,7 +15094,7 @@
         <v>401</v>
       </c>
       <c r="C1129" t="n">
-        <v>0.02174</v>
+        <v>0.02169</v>
       </c>
     </row>
     <row r="1130">
@@ -15107,7 +15107,7 @@
         <v>402</v>
       </c>
       <c r="C1130" t="n">
-        <v>0.021865</v>
+        <v>0.021859</v>
       </c>
     </row>
     <row r="1131">
@@ -15120,7 +15120,7 @@
         <v>403</v>
       </c>
       <c r="C1131" t="n">
-        <v>0.022018</v>
+        <v>0.022032</v>
       </c>
     </row>
     <row r="1132">
@@ -15133,7 +15133,7 @@
         <v>404</v>
       </c>
       <c r="C1132" t="n">
-        <v>0.022751</v>
+        <v>0.022786</v>
       </c>
     </row>
     <row r="1133">
@@ -15146,7 +15146,7 @@
         <v>405</v>
       </c>
       <c r="C1133" t="n">
-        <v>0.022835</v>
+        <v>0.022874</v>
       </c>
     </row>
     <row r="1134">
@@ -15159,7 +15159,7 @@
         <v>406</v>
       </c>
       <c r="C1134" t="n">
-        <v>0.023087</v>
+        <v>0.02312</v>
       </c>
     </row>
     <row r="1135">
@@ -15172,7 +15172,7 @@
         <v>407</v>
       </c>
       <c r="C1135" t="n">
-        <v>0.024357</v>
+        <v>0.024383</v>
       </c>
     </row>
     <row r="1136">
@@ -15185,7 +15185,7 @@
         <v>408</v>
       </c>
       <c r="C1136" t="n">
-        <v>0.02447</v>
+        <v>0.02451</v>
       </c>
     </row>
     <row r="1137">
@@ -15198,7 +15198,7 @@
         <v>409</v>
       </c>
       <c r="C1137" t="n">
-        <v>0.0247</v>
+        <v>0.024714</v>
       </c>
     </row>
     <row r="1138">
@@ -15211,7 +15211,7 @@
         <v>410</v>
       </c>
       <c r="C1138" t="n">
-        <v>0.024718</v>
+        <v>0.024737</v>
       </c>
     </row>
     <row r="1139">
@@ -15224,7 +15224,7 @@
         <v>411</v>
       </c>
       <c r="C1139" t="n">
-        <v>0.025093</v>
+        <v>0.025139</v>
       </c>
     </row>
     <row r="1140">
@@ -15237,7 +15237,7 @@
         <v>412</v>
       </c>
       <c r="C1140" t="n">
-        <v>0.025205</v>
+        <v>0.025232</v>
       </c>
     </row>
     <row r="1141">
@@ -15250,7 +15250,7 @@
         <v>413</v>
       </c>
       <c r="C1141" t="n">
-        <v>0.025624</v>
+        <v>0.025639</v>
       </c>
     </row>
     <row r="1142">
@@ -15263,7 +15263,7 @@
         <v>414</v>
       </c>
       <c r="C1142" t="n">
-        <v>0.025638</v>
+        <v>0.025646</v>
       </c>
     </row>
     <row r="1143">
@@ -15276,7 +15276,7 @@
         <v>415</v>
       </c>
       <c r="C1143" t="n">
-        <v>0.026096</v>
+        <v>0.026092</v>
       </c>
     </row>
     <row r="1144">
@@ -15289,7 +15289,7 @@
         <v>416</v>
       </c>
       <c r="C1144" t="n">
-        <v>0.026106</v>
+        <v>0.026135</v>
       </c>
     </row>
     <row r="1145">
@@ -15302,7 +15302,7 @@
         <v>417</v>
       </c>
       <c r="C1145" t="n">
-        <v>0.026309</v>
+        <v>0.026354</v>
       </c>
     </row>
     <row r="1146">
@@ -15315,7 +15315,7 @@
         <v>418</v>
       </c>
       <c r="C1146" t="n">
-        <v>0.026397</v>
+        <v>0.026414</v>
       </c>
     </row>
     <row r="1147">
@@ -15328,7 +15328,7 @@
         <v>419</v>
       </c>
       <c r="C1147" t="n">
-        <v>0.026675</v>
+        <v>0.02672</v>
       </c>
     </row>
     <row r="1148">
@@ -15341,7 +15341,7 @@
         <v>420</v>
       </c>
       <c r="C1148" t="n">
-        <v>0.027298</v>
+        <v>0.027313</v>
       </c>
     </row>
     <row r="1149">
@@ -15354,7 +15354,7 @@
         <v>421</v>
       </c>
       <c r="C1149" t="n">
-        <v>0.027654</v>
+        <v>0.027576</v>
       </c>
     </row>
     <row r="1150">
@@ -15367,7 +15367,7 @@
         <v>422</v>
       </c>
       <c r="C1150" t="n">
-        <v>0.027773</v>
+        <v>0.027795</v>
       </c>
     </row>
     <row r="1151">
@@ -15380,7 +15380,7 @@
         <v>423</v>
       </c>
       <c r="C1151" t="n">
-        <v>0.028097</v>
+        <v>0.028145</v>
       </c>
     </row>
     <row r="1152">
@@ -15393,7 +15393,7 @@
         <v>424</v>
       </c>
       <c r="C1152" t="n">
-        <v>0.028171</v>
+        <v>0.028178</v>
       </c>
     </row>
     <row r="1153">
@@ -15406,7 +15406,7 @@
         <v>425</v>
       </c>
       <c r="C1153" t="n">
-        <v>0.028223</v>
+        <v>0.028209</v>
       </c>
     </row>
     <row r="1154">
@@ -15419,7 +15419,7 @@
         <v>426</v>
       </c>
       <c r="C1154" t="n">
-        <v>0.028226</v>
+        <v>0.028258</v>
       </c>
     </row>
     <row r="1155">
@@ -15432,7 +15432,7 @@
         <v>427</v>
       </c>
       <c r="C1155" t="n">
-        <v>0.028255</v>
+        <v>0.028306</v>
       </c>
     </row>
     <row r="1156">
@@ -15445,7 +15445,7 @@
         <v>428</v>
       </c>
       <c r="C1156" t="n">
-        <v>0.028339</v>
+        <v>0.028346</v>
       </c>
     </row>
     <row r="1157">
@@ -15458,7 +15458,7 @@
         <v>429</v>
       </c>
       <c r="C1157" t="n">
-        <v>0.028723</v>
+        <v>0.028748</v>
       </c>
     </row>
     <row r="1158">
@@ -15471,7 +15471,7 @@
         <v>430</v>
       </c>
       <c r="C1158" t="n">
-        <v>0.028793</v>
+        <v>0.028833</v>
       </c>
     </row>
     <row r="1159">
@@ -15484,7 +15484,7 @@
         <v>431</v>
       </c>
       <c r="C1159" t="n">
-        <v>0.029315</v>
+        <v>0.029351</v>
       </c>
     </row>
     <row r="1160">
@@ -15497,7 +15497,7 @@
         <v>432</v>
       </c>
       <c r="C1160" t="n">
-        <v>0.029596</v>
+        <v>0.029634</v>
       </c>
     </row>
     <row r="1161">
@@ -15510,7 +15510,7 @@
         <v>433</v>
       </c>
       <c r="C1161" t="n">
-        <v>0.029879</v>
+        <v>0.029922</v>
       </c>
     </row>
     <row r="1162">
@@ -15523,7 +15523,7 @@
         <v>434</v>
       </c>
       <c r="C1162" t="n">
-        <v>0.030113</v>
+        <v>0.030123</v>
       </c>
     </row>
     <row r="1163">
@@ -15536,7 +15536,7 @@
         <v>435</v>
       </c>
       <c r="C1163" t="n">
-        <v>0.030226</v>
+        <v>0.030253</v>
       </c>
     </row>
     <row r="1164">
@@ -15549,7 +15549,7 @@
         <v>436</v>
       </c>
       <c r="C1164" t="n">
-        <v>0.030255</v>
+        <v>0.030284</v>
       </c>
     </row>
     <row r="1165">
@@ -15562,7 +15562,7 @@
         <v>437</v>
       </c>
       <c r="C1165" t="n">
-        <v>0.03094</v>
+        <v>0.030894</v>
       </c>
     </row>
     <row r="1166">
@@ -15575,7 +15575,7 @@
         <v>438</v>
       </c>
       <c r="C1166" t="n">
-        <v>0.03108</v>
+        <v>0.031076</v>
       </c>
     </row>
     <row r="1167">
@@ -15588,7 +15588,7 @@
         <v>439</v>
       </c>
       <c r="C1167" t="n">
-        <v>0.031383</v>
+        <v>0.031416</v>
       </c>
     </row>
     <row r="1168">
@@ -15601,7 +15601,7 @@
         <v>440</v>
       </c>
       <c r="C1168" t="n">
-        <v>0.031458</v>
+        <v>0.031421</v>
       </c>
     </row>
     <row r="1169">
@@ -15614,7 +15614,7 @@
         <v>441</v>
       </c>
       <c r="C1169" t="n">
-        <v>0.031604</v>
+        <v>0.031627</v>
       </c>
     </row>
     <row r="1170">
@@ -15627,7 +15627,7 @@
         <v>442</v>
       </c>
       <c r="C1170" t="n">
-        <v>0.031812</v>
+        <v>0.031777</v>
       </c>
     </row>
     <row r="1171">
@@ -15640,7 +15640,7 @@
         <v>443</v>
       </c>
       <c r="C1171" t="n">
-        <v>0.031878</v>
+        <v>0.03194</v>
       </c>
     </row>
     <row r="1172">
@@ -15653,7 +15653,7 @@
         <v>444</v>
       </c>
       <c r="C1172" t="n">
-        <v>0.032079</v>
+        <v>0.03212</v>
       </c>
     </row>
     <row r="1173">
@@ -15666,7 +15666,7 @@
         <v>445</v>
       </c>
       <c r="C1173" t="n">
-        <v>0.032241</v>
+        <v>0.032268</v>
       </c>
     </row>
     <row r="1174">
@@ -15679,7 +15679,7 @@
         <v>446</v>
       </c>
       <c r="C1174" t="n">
-        <v>0.032628</v>
+        <v>0.03265</v>
       </c>
     </row>
     <row r="1175">
@@ -15692,7 +15692,7 @@
         <v>447</v>
       </c>
       <c r="C1175" t="n">
-        <v>0.033162</v>
+        <v>0.03314</v>
       </c>
     </row>
     <row r="1176">
@@ -15705,7 +15705,7 @@
         <v>448</v>
       </c>
       <c r="C1176" t="n">
-        <v>0.03324</v>
+        <v>0.033195</v>
       </c>
     </row>
     <row r="1177">
@@ -15718,7 +15718,7 @@
         <v>449</v>
       </c>
       <c r="C1177" t="n">
-        <v>0.033461</v>
+        <v>0.033503</v>
       </c>
     </row>
     <row r="1178">
@@ -15731,7 +15731,7 @@
         <v>450</v>
       </c>
       <c r="C1178" t="n">
-        <v>0.033709</v>
+        <v>0.033766</v>
       </c>
     </row>
     <row r="1179">
@@ -15744,7 +15744,7 @@
         <v>451</v>
       </c>
       <c r="C1179" t="n">
-        <v>0.033767</v>
+        <v>0.033795</v>
       </c>
     </row>
     <row r="1180">
@@ -15757,7 +15757,7 @@
         <v>452</v>
       </c>
       <c r="C1180" t="n">
-        <v>0.034093</v>
+        <v>0.034088</v>
       </c>
     </row>
     <row r="1181">
@@ -15770,7 +15770,7 @@
         <v>453</v>
       </c>
       <c r="C1181" t="n">
-        <v>0.034564</v>
+        <v>0.034624</v>
       </c>
     </row>
     <row r="1182">
@@ -15783,7 +15783,7 @@
         <v>454</v>
       </c>
       <c r="C1182" t="n">
-        <v>0.034941</v>
+        <v>0.034992</v>
       </c>
     </row>
     <row r="1183">
@@ -15796,7 +15796,7 @@
         <v>455</v>
       </c>
       <c r="C1183" t="n">
-        <v>0.034953</v>
+        <v>0.035022</v>
       </c>
     </row>
     <row r="1184">
@@ -15809,7 +15809,7 @@
         <v>456</v>
       </c>
       <c r="C1184" t="n">
-        <v>0.035248</v>
+        <v>0.035262</v>
       </c>
     </row>
     <row r="1185">
@@ -15822,7 +15822,7 @@
         <v>457</v>
       </c>
       <c r="C1185" t="n">
-        <v>0.03567</v>
+        <v>0.035639</v>
       </c>
     </row>
     <row r="1186">
@@ -15835,7 +15835,7 @@
         <v>458</v>
       </c>
       <c r="C1186" t="n">
-        <v>0.036001</v>
+        <v>0.035992</v>
       </c>
     </row>
     <row r="1187">
@@ -15848,7 +15848,7 @@
         <v>459</v>
       </c>
       <c r="C1187" t="n">
-        <v>0.036228</v>
+        <v>0.036275</v>
       </c>
     </row>
     <row r="1188">
@@ -15861,7 +15861,7 @@
         <v>460</v>
       </c>
       <c r="C1188" t="n">
-        <v>0.036421</v>
+        <v>0.036487</v>
       </c>
     </row>
     <row r="1189">
@@ -15874,7 +15874,7 @@
         <v>461</v>
       </c>
       <c r="C1189" t="n">
-        <v>0.036526</v>
+        <v>0.036552</v>
       </c>
     </row>
     <row r="1190">
@@ -15887,7 +15887,7 @@
         <v>462</v>
       </c>
       <c r="C1190" t="n">
-        <v>0.036616</v>
+        <v>0.03664</v>
       </c>
     </row>
     <row r="1191">
@@ -15900,7 +15900,7 @@
         <v>463</v>
       </c>
       <c r="C1191" t="n">
-        <v>0.037088</v>
+        <v>0.037139</v>
       </c>
     </row>
     <row r="1192">
@@ -15913,7 +15913,7 @@
         <v>464</v>
       </c>
       <c r="C1192" t="n">
-        <v>0.037348</v>
+        <v>0.03734</v>
       </c>
     </row>
     <row r="1193">
@@ -15926,7 +15926,7 @@
         <v>465</v>
       </c>
       <c r="C1193" t="n">
-        <v>0.037387</v>
+        <v>0.037435</v>
       </c>
     </row>
     <row r="1194">
@@ -15939,7 +15939,7 @@
         <v>466</v>
       </c>
       <c r="C1194" t="n">
-        <v>0.037422</v>
+        <v>0.037467</v>
       </c>
     </row>
     <row r="1195">
@@ -15952,7 +15952,7 @@
         <v>467</v>
       </c>
       <c r="C1195" t="n">
-        <v>0.037717</v>
+        <v>0.037693</v>
       </c>
     </row>
     <row r="1196">
@@ -15965,7 +15965,7 @@
         <v>468</v>
       </c>
       <c r="C1196" t="n">
-        <v>0.037807</v>
+        <v>0.037852</v>
       </c>
     </row>
     <row r="1197">
@@ -15978,7 +15978,7 @@
         <v>469</v>
       </c>
       <c r="C1197" t="n">
-        <v>0.03804</v>
+        <v>0.038081</v>
       </c>
     </row>
     <row r="1198">
@@ -15991,7 +15991,7 @@
         <v>470</v>
       </c>
       <c r="C1198" t="n">
-        <v>0.03823</v>
+        <v>0.0382</v>
       </c>
     </row>
     <row r="1199">
@@ -16004,7 +16004,7 @@
         <v>471</v>
       </c>
       <c r="C1199" t="n">
-        <v>0.038259</v>
+        <v>0.03829</v>
       </c>
     </row>
     <row r="1200">
@@ -16017,7 +16017,7 @@
         <v>472</v>
       </c>
       <c r="C1200" t="n">
-        <v>0.038329</v>
+        <v>0.03835</v>
       </c>
     </row>
     <row r="1201">
@@ -16030,7 +16030,7 @@
         <v>473</v>
       </c>
       <c r="C1201" t="n">
-        <v>0.038759</v>
+        <v>0.03868</v>
       </c>
     </row>
     <row r="1202">
@@ -16043,7 +16043,7 @@
         <v>474</v>
       </c>
       <c r="C1202" t="n">
-        <v>0.039066</v>
+        <v>0.039121</v>
       </c>
     </row>
     <row r="1203">
@@ -16056,7 +16056,7 @@
         <v>475</v>
       </c>
       <c r="C1203" t="n">
-        <v>0.039642</v>
+        <v>0.039658</v>
       </c>
     </row>
     <row r="1204">
@@ -16069,7 +16069,7 @@
         <v>476</v>
       </c>
       <c r="C1204" t="n">
-        <v>0.039886</v>
+        <v>0.03978</v>
       </c>
     </row>
     <row r="1205">
@@ -16082,7 +16082,7 @@
         <v>477</v>
       </c>
       <c r="C1205" t="n">
-        <v>0.039919</v>
+        <v>0.039924</v>
       </c>
     </row>
     <row r="1206">
@@ -16095,7 +16095,7 @@
         <v>478</v>
       </c>
       <c r="C1206" t="n">
-        <v>0.040012</v>
+        <v>0.039969</v>
       </c>
     </row>
     <row r="1207">
@@ -16108,7 +16108,7 @@
         <v>479</v>
       </c>
       <c r="C1207" t="n">
-        <v>0.040016</v>
+        <v>0.040031</v>
       </c>
     </row>
     <row r="1208">
@@ -16121,7 +16121,7 @@
         <v>480</v>
       </c>
       <c r="C1208" t="n">
-        <v>0.040477</v>
+        <v>0.04051</v>
       </c>
     </row>
     <row r="1209">
@@ -16134,7 +16134,7 @@
         <v>481</v>
       </c>
       <c r="C1209" t="n">
-        <v>0.040767</v>
+        <v>0.040811</v>
       </c>
     </row>
     <row r="1210">
@@ -16147,7 +16147,7 @@
         <v>482</v>
       </c>
       <c r="C1210" t="n">
-        <v>0.040883</v>
+        <v>0.040841</v>
       </c>
     </row>
     <row r="1211">
@@ -16160,7 +16160,7 @@
         <v>483</v>
       </c>
       <c r="C1211" t="n">
-        <v>0.041258</v>
+        <v>0.041197</v>
       </c>
     </row>
     <row r="1212">
@@ -16173,7 +16173,7 @@
         <v>484</v>
       </c>
       <c r="C1212" t="n">
-        <v>0.041452</v>
+        <v>0.041442</v>
       </c>
     </row>
     <row r="1213">
@@ -16186,7 +16186,7 @@
         <v>485</v>
       </c>
       <c r="C1213" t="n">
-        <v>0.041777</v>
+        <v>0.041807</v>
       </c>
     </row>
     <row r="1214">
@@ -16199,7 +16199,7 @@
         <v>486</v>
       </c>
       <c r="C1214" t="n">
-        <v>0.041792</v>
+        <v>0.041856</v>
       </c>
     </row>
     <row r="1215">
@@ -16212,7 +16212,7 @@
         <v>487</v>
       </c>
       <c r="C1215" t="n">
-        <v>0.042122</v>
+        <v>0.042196</v>
       </c>
     </row>
     <row r="1216">
@@ -16225,7 +16225,7 @@
         <v>488</v>
       </c>
       <c r="C1216" t="n">
-        <v>0.042471</v>
+        <v>0.042563</v>
       </c>
     </row>
     <row r="1217">
@@ -16238,7 +16238,7 @@
         <v>489</v>
       </c>
       <c r="C1217" t="n">
-        <v>0.04255</v>
+        <v>0.042567</v>
       </c>
     </row>
     <row r="1218">
@@ -16251,7 +16251,7 @@
         <v>490</v>
       </c>
       <c r="C1218" t="n">
-        <v>0.042612</v>
+        <v>0.042731</v>
       </c>
     </row>
     <row r="1219">
@@ -16264,7 +16264,7 @@
         <v>491</v>
       </c>
       <c r="C1219" t="n">
-        <v>0.042868</v>
+        <v>0.042943</v>
       </c>
     </row>
     <row r="1220">
@@ -16277,7 +16277,7 @@
         <v>492</v>
       </c>
       <c r="C1220" t="n">
-        <v>0.043047</v>
+        <v>0.04304</v>
       </c>
     </row>
     <row r="1221">
@@ -16290,7 +16290,7 @@
         <v>493</v>
       </c>
       <c r="C1221" t="n">
-        <v>0.043047</v>
+        <v>0.043055</v>
       </c>
     </row>
     <row r="1222">
@@ -16303,7 +16303,7 @@
         <v>494</v>
       </c>
       <c r="C1222" t="n">
-        <v>0.043926</v>
+        <v>0.043972</v>
       </c>
     </row>
     <row r="1223">
@@ -16316,7 +16316,7 @@
         <v>495</v>
       </c>
       <c r="C1223" t="n">
-        <v>0.044264</v>
+        <v>0.044319</v>
       </c>
     </row>
     <row r="1224">
@@ -16329,7 +16329,7 @@
         <v>496</v>
       </c>
       <c r="C1224" t="n">
-        <v>0.044576</v>
+        <v>0.044583</v>
       </c>
     </row>
     <row r="1225">
@@ -16342,7 +16342,7 @@
         <v>497</v>
       </c>
       <c r="C1225" t="n">
-        <v>0.045421</v>
+        <v>0.045402</v>
       </c>
     </row>
     <row r="1226">
@@ -16355,7 +16355,7 @@
         <v>498</v>
       </c>
       <c r="C1226" t="n">
-        <v>0.045649</v>
+        <v>0.045583</v>
       </c>
     </row>
     <row r="1227">
@@ -16368,7 +16368,7 @@
         <v>499</v>
       </c>
       <c r="C1227" t="n">
-        <v>0.045669</v>
+        <v>0.045713</v>
       </c>
     </row>
     <row r="1228">
@@ -16381,7 +16381,7 @@
         <v>500</v>
       </c>
       <c r="C1228" t="n">
-        <v>0.045973</v>
+        <v>0.045916</v>
       </c>
     </row>
     <row r="1229">
@@ -16394,7 +16394,7 @@
         <v>501</v>
       </c>
       <c r="C1229" t="n">
-        <v>0.046822</v>
+        <v>0.046838</v>
       </c>
     </row>
     <row r="1230">
@@ -16407,7 +16407,7 @@
         <v>502</v>
       </c>
       <c r="C1230" t="n">
-        <v>0.047573</v>
+        <v>0.047552</v>
       </c>
     </row>
     <row r="1231">
@@ -16420,7 +16420,7 @@
         <v>503</v>
       </c>
       <c r="C1231" t="n">
-        <v>0.047638</v>
+        <v>0.047682</v>
       </c>
     </row>
     <row r="1232">
@@ -16433,7 +16433,7 @@
         <v>504</v>
       </c>
       <c r="C1232" t="n">
-        <v>0.047992</v>
+        <v>0.048023</v>
       </c>
     </row>
     <row r="1233">
@@ -16446,7 +16446,7 @@
         <v>505</v>
       </c>
       <c r="C1233" t="n">
-        <v>0.048408</v>
+        <v>0.048487</v>
       </c>
     </row>
     <row r="1234">
@@ -16459,7 +16459,7 @@
         <v>506</v>
       </c>
       <c r="C1234" t="n">
-        <v>0.048494</v>
+        <v>0.048555</v>
       </c>
     </row>
     <row r="1235">
@@ -16472,7 +16472,7 @@
         <v>507</v>
       </c>
       <c r="C1235" t="n">
-        <v>0.049307</v>
+        <v>0.049309</v>
       </c>
     </row>
     <row r="1236">
@@ -16485,7 +16485,7 @@
         <v>508</v>
       </c>
       <c r="C1236" t="n">
-        <v>0.049614</v>
+        <v>0.049691</v>
       </c>
     </row>
     <row r="1237">
@@ -16498,7 +16498,7 @@
         <v>509</v>
       </c>
       <c r="C1237" t="n">
-        <v>0.050085</v>
+        <v>0.050069</v>
       </c>
     </row>
     <row r="1238">
@@ -16511,7 +16511,7 @@
         <v>510</v>
       </c>
       <c r="C1238" t="n">
-        <v>0.050116</v>
+        <v>0.05011</v>
       </c>
     </row>
     <row r="1239">
@@ -16524,7 +16524,7 @@
         <v>511</v>
       </c>
       <c r="C1239" t="n">
-        <v>0.050121</v>
+        <v>0.050201</v>
       </c>
     </row>
     <row r="1240">
@@ -16537,7 +16537,7 @@
         <v>512</v>
       </c>
       <c r="C1240" t="n">
-        <v>0.050471</v>
+        <v>0.050433</v>
       </c>
     </row>
     <row r="1241">
@@ -16550,7 +16550,7 @@
         <v>513</v>
       </c>
       <c r="C1241" t="n">
-        <v>0.05068</v>
+        <v>0.050693</v>
       </c>
     </row>
     <row r="1242">
@@ -16563,7 +16563,7 @@
         <v>514</v>
       </c>
       <c r="C1242" t="n">
-        <v>0.051971</v>
+        <v>0.052025</v>
       </c>
     </row>
     <row r="1243">
@@ -16576,7 +16576,7 @@
         <v>515</v>
       </c>
       <c r="C1243" t="n">
-        <v>0.052036</v>
+        <v>0.052073</v>
       </c>
     </row>
     <row r="1244">
@@ -16589,7 +16589,7 @@
         <v>516</v>
       </c>
       <c r="C1244" t="n">
-        <v>0.052892</v>
+        <v>0.05279</v>
       </c>
     </row>
     <row r="1245">
@@ -16602,7 +16602,7 @@
         <v>517</v>
       </c>
       <c r="C1245" t="n">
-        <v>0.053114</v>
+        <v>0.053174</v>
       </c>
     </row>
     <row r="1246">
@@ -16615,7 +16615,7 @@
         <v>518</v>
       </c>
       <c r="C1246" t="n">
-        <v>0.053134</v>
+        <v>0.053207</v>
       </c>
     </row>
     <row r="1247">
@@ -16628,7 +16628,7 @@
         <v>519</v>
       </c>
       <c r="C1247" t="n">
-        <v>0.05341</v>
+        <v>0.053483</v>
       </c>
     </row>
     <row r="1248">
@@ -16641,7 +16641,7 @@
         <v>520</v>
       </c>
       <c r="C1248" t="n">
-        <v>0.053509</v>
+        <v>0.053563</v>
       </c>
     </row>
     <row r="1249">
@@ -16654,7 +16654,7 @@
         <v>521</v>
       </c>
       <c r="C1249" t="n">
-        <v>0.054621</v>
+        <v>0.054673</v>
       </c>
     </row>
     <row r="1250">
@@ -16667,7 +16667,7 @@
         <v>522</v>
       </c>
       <c r="C1250" t="n">
-        <v>0.05465</v>
+        <v>0.054745</v>
       </c>
     </row>
     <row r="1251">
@@ -16680,7 +16680,7 @@
         <v>523</v>
       </c>
       <c r="C1251" t="n">
-        <v>0.054955</v>
+        <v>0.055027</v>
       </c>
     </row>
     <row r="1252">
@@ -16693,7 +16693,7 @@
         <v>524</v>
       </c>
       <c r="C1252" t="n">
-        <v>0.055341</v>
+        <v>0.055458</v>
       </c>
     </row>
     <row r="1253">
@@ -16706,7 +16706,7 @@
         <v>525</v>
       </c>
       <c r="C1253" t="n">
-        <v>0.055476</v>
+        <v>0.055594</v>
       </c>
     </row>
     <row r="1254">
@@ -16719,7 +16719,7 @@
         <v>526</v>
       </c>
       <c r="C1254" t="n">
-        <v>0.056461</v>
+        <v>0.056523</v>
       </c>
     </row>
     <row r="1255">
@@ -16732,7 +16732,7 @@
         <v>527</v>
       </c>
       <c r="C1255" t="n">
-        <v>0.056667</v>
+        <v>0.056765</v>
       </c>
     </row>
     <row r="1256">
@@ -16745,7 +16745,7 @@
         <v>528</v>
       </c>
       <c r="C1256" t="n">
-        <v>0.056884</v>
+        <v>0.05699</v>
       </c>
     </row>
     <row r="1257">
@@ -16758,7 +16758,7 @@
         <v>529</v>
       </c>
       <c r="C1257" t="n">
-        <v>0.057703</v>
+        <v>0.057736</v>
       </c>
     </row>
     <row r="1258">
@@ -16771,7 +16771,7 @@
         <v>530</v>
       </c>
       <c r="C1258" t="n">
-        <v>0.059305</v>
+        <v>0.059408</v>
       </c>
     </row>
     <row r="1259">
@@ -16784,7 +16784,7 @@
         <v>531</v>
       </c>
       <c r="C1259" t="n">
-        <v>0.059569</v>
+        <v>0.059658</v>
       </c>
     </row>
     <row r="1260">
@@ -16797,7 +16797,7 @@
         <v>532</v>
       </c>
       <c r="C1260" t="n">
-        <v>0.060159</v>
+        <v>0.060102</v>
       </c>
     </row>
     <row r="1261">
@@ -16810,7 +16810,7 @@
         <v>533</v>
       </c>
       <c r="C1261" t="n">
-        <v>0.060251</v>
+        <v>0.060346</v>
       </c>
     </row>
     <row r="1262">
@@ -16823,7 +16823,7 @@
         <v>534</v>
       </c>
       <c r="C1262" t="n">
-        <v>0.060688</v>
+        <v>0.060702</v>
       </c>
     </row>
     <row r="1263">
@@ -16836,7 +16836,7 @@
         <v>535</v>
       </c>
       <c r="C1263" t="n">
-        <v>0.060947</v>
+        <v>0.061062</v>
       </c>
     </row>
     <row r="1264">
@@ -16849,7 +16849,7 @@
         <v>536</v>
       </c>
       <c r="C1264" t="n">
-        <v>0.061281</v>
+        <v>0.061295</v>
       </c>
     </row>
     <row r="1265">
@@ -16862,7 +16862,7 @@
         <v>537</v>
       </c>
       <c r="C1265" t="n">
-        <v>0.06138</v>
+        <v>0.061404</v>
       </c>
     </row>
     <row r="1266">
@@ -16875,7 +16875,7 @@
         <v>538</v>
       </c>
       <c r="C1266" t="n">
-        <v>0.061679</v>
+        <v>0.061687</v>
       </c>
     </row>
     <row r="1267">
@@ -16888,7 +16888,7 @@
         <v>539</v>
       </c>
       <c r="C1267" t="n">
-        <v>0.062088</v>
+        <v>0.062001</v>
       </c>
     </row>
     <row r="1268">
@@ -16901,7 +16901,7 @@
         <v>540</v>
       </c>
       <c r="C1268" t="n">
-        <v>0.062809</v>
+        <v>0.062843</v>
       </c>
     </row>
     <row r="1269">
@@ -16914,7 +16914,7 @@
         <v>541</v>
       </c>
       <c r="C1269" t="n">
-        <v>0.063051</v>
+        <v>0.063054</v>
       </c>
     </row>
     <row r="1270">
@@ -16927,7 +16927,7 @@
         <v>542</v>
       </c>
       <c r="C1270" t="n">
-        <v>0.06358900000000001</v>
+        <v>0.06365899999999999</v>
       </c>
     </row>
     <row r="1271">
@@ -16940,7 +16940,7 @@
         <v>543</v>
       </c>
       <c r="C1271" t="n">
-        <v>0.06368799999999999</v>
+        <v>0.06381000000000001</v>
       </c>
     </row>
     <row r="1272">
@@ -16953,7 +16953,7 @@
         <v>544</v>
       </c>
       <c r="C1272" t="n">
-        <v>0.064133</v>
+        <v>0.064181</v>
       </c>
     </row>
     <row r="1273">
@@ -16966,7 +16966,7 @@
         <v>545</v>
       </c>
       <c r="C1273" t="n">
-        <v>0.06421399999999999</v>
+        <v>0.06424100000000001</v>
       </c>
     </row>
     <row r="1274">
@@ -16979,7 +16979,7 @@
         <v>546</v>
       </c>
       <c r="C1274" t="n">
-        <v>0.064572</v>
+        <v>0.064583</v>
       </c>
     </row>
     <row r="1275">
@@ -16992,7 +16992,7 @@
         <v>547</v>
       </c>
       <c r="C1275" t="n">
-        <v>0.064583</v>
+        <v>0.06465899999999999</v>
       </c>
     </row>
     <row r="1276">
@@ -17005,7 +17005,7 @@
         <v>548</v>
       </c>
       <c r="C1276" t="n">
-        <v>0.064606</v>
+        <v>0.06468699999999999</v>
       </c>
     </row>
     <row r="1277">
@@ -17018,7 +17018,7 @@
         <v>549</v>
       </c>
       <c r="C1277" t="n">
-        <v>0.064692</v>
+        <v>0.06479500000000001</v>
       </c>
     </row>
     <row r="1278">
@@ -17031,7 +17031,7 @@
         <v>550</v>
       </c>
       <c r="C1278" t="n">
-        <v>0.065197</v>
+        <v>0.065237</v>
       </c>
     </row>
     <row r="1279">
@@ -17044,7 +17044,7 @@
         <v>551</v>
       </c>
       <c r="C1279" t="n">
-        <v>0.065798</v>
+        <v>0.065909</v>
       </c>
     </row>
     <row r="1280">
@@ -17057,7 +17057,7 @@
         <v>552</v>
       </c>
       <c r="C1280" t="n">
-        <v>0.066097</v>
+        <v>0.065981</v>
       </c>
     </row>
     <row r="1281">
@@ -17070,7 +17070,7 @@
         <v>553</v>
       </c>
       <c r="C1281" t="n">
-        <v>0.066898</v>
+        <v>0.066972</v>
       </c>
     </row>
     <row r="1282">
@@ -17083,7 +17083,7 @@
         <v>554</v>
       </c>
       <c r="C1282" t="n">
-        <v>0.067097</v>
+        <v>0.067037</v>
       </c>
     </row>
     <row r="1283">
@@ -17096,7 +17096,7 @@
         <v>555</v>
       </c>
       <c r="C1283" t="n">
-        <v>0.06794500000000001</v>
+        <v>0.067979</v>
       </c>
     </row>
     <row r="1284">
@@ -17109,7 +17109,7 @@
         <v>556</v>
       </c>
       <c r="C1284" t="n">
-        <v>0.068067</v>
+        <v>0.06811200000000001</v>
       </c>
     </row>
     <row r="1285">
@@ -17122,7 +17122,7 @@
         <v>557</v>
       </c>
       <c r="C1285" t="n">
-        <v>0.068117</v>
+        <v>0.06822499999999999</v>
       </c>
     </row>
     <row r="1286">
@@ -17135,7 +17135,7 @@
         <v>558</v>
       </c>
       <c r="C1286" t="n">
-        <v>0.06820900000000001</v>
+        <v>0.068272</v>
       </c>
     </row>
     <row r="1287">
@@ -17148,7 +17148,7 @@
         <v>559</v>
       </c>
       <c r="C1287" t="n">
-        <v>0.068635</v>
+        <v>0.06851400000000001</v>
       </c>
     </row>
     <row r="1288">
@@ -17161,7 +17161,7 @@
         <v>560</v>
       </c>
       <c r="C1288" t="n">
-        <v>0.069091</v>
+        <v>0.06922499999999999</v>
       </c>
     </row>
     <row r="1289">
@@ -17174,7 +17174,7 @@
         <v>561</v>
       </c>
       <c r="C1289" t="n">
-        <v>0.06965</v>
+        <v>0.06972100000000001</v>
       </c>
     </row>
     <row r="1290">
@@ -17187,7 +17187,7 @@
         <v>562</v>
       </c>
       <c r="C1290" t="n">
-        <v>0.069913</v>
+        <v>0.06995</v>
       </c>
     </row>
     <row r="1291">
@@ -17200,7 +17200,7 @@
         <v>563</v>
       </c>
       <c r="C1291" t="n">
-        <v>0.07006800000000001</v>
+        <v>0.070117</v>
       </c>
     </row>
     <row r="1292">
@@ -17213,7 +17213,7 @@
         <v>564</v>
       </c>
       <c r="C1292" t="n">
-        <v>0.07027600000000001</v>
+        <v>0.070287</v>
       </c>
     </row>
     <row r="1293">
@@ -17226,7 +17226,7 @@
         <v>565</v>
       </c>
       <c r="C1293" t="n">
-        <v>0.070341</v>
+        <v>0.070423</v>
       </c>
     </row>
     <row r="1294">
@@ -17239,7 +17239,7 @@
         <v>566</v>
       </c>
       <c r="C1294" t="n">
-        <v>0.07053</v>
+        <v>0.070567</v>
       </c>
     </row>
     <row r="1295">
@@ -17252,7 +17252,7 @@
         <v>567</v>
       </c>
       <c r="C1295" t="n">
-        <v>0.071239</v>
+        <v>0.070983</v>
       </c>
     </row>
     <row r="1296">
@@ -17265,7 +17265,7 @@
         <v>568</v>
       </c>
       <c r="C1296" t="n">
-        <v>0.071612</v>
+        <v>0.071742</v>
       </c>
     </row>
     <row r="1297">
@@ -17278,7 +17278,7 @@
         <v>569</v>
       </c>
       <c r="C1297" t="n">
-        <v>0.071657</v>
+        <v>0.071773</v>
       </c>
     </row>
     <row r="1298">
@@ -17291,7 +17291,7 @@
         <v>570</v>
       </c>
       <c r="C1298" t="n">
-        <v>0.07179099999999999</v>
+        <v>0.07191400000000001</v>
       </c>
     </row>
     <row r="1299">
@@ -17304,7 +17304,7 @@
         <v>571</v>
       </c>
       <c r="C1299" t="n">
-        <v>0.07194200000000001</v>
+        <v>0.07204099999999999</v>
       </c>
     </row>
     <row r="1300">
@@ -17317,7 +17317,7 @@
         <v>572</v>
       </c>
       <c r="C1300" t="n">
-        <v>0.072072</v>
+        <v>0.07206600000000001</v>
       </c>
     </row>
     <row r="1301">
@@ -17330,7 +17330,7 @@
         <v>573</v>
       </c>
       <c r="C1301" t="n">
-        <v>0.07215000000000001</v>
+        <v>0.07215199999999999</v>
       </c>
     </row>
     <row r="1302">
@@ -17343,7 +17343,7 @@
         <v>574</v>
       </c>
       <c r="C1302" t="n">
-        <v>0.072521</v>
+        <v>0.072562</v>
       </c>
     </row>
     <row r="1303">
@@ -17356,7 +17356,7 @@
         <v>575</v>
       </c>
       <c r="C1303" t="n">
-        <v>0.073001</v>
+        <v>0.073126</v>
       </c>
     </row>
     <row r="1304">
@@ -17369,7 +17369,7 @@
         <v>576</v>
       </c>
       <c r="C1304" t="n">
-        <v>0.07352599999999999</v>
+        <v>0.07355100000000001</v>
       </c>
     </row>
     <row r="1305">
@@ -17382,7 +17382,7 @@
         <v>577</v>
       </c>
       <c r="C1305" t="n">
-        <v>0.073935</v>
+        <v>0.074075</v>
       </c>
     </row>
     <row r="1306">
@@ -17395,7 +17395,7 @@
         <v>578</v>
       </c>
       <c r="C1306" t="n">
-        <v>0.074293</v>
+        <v>0.074295</v>
       </c>
     </row>
     <row r="1307">
@@ -17408,7 +17408,7 @@
         <v>579</v>
       </c>
       <c r="C1307" t="n">
-        <v>0.074308</v>
+        <v>0.074366</v>
       </c>
     </row>
     <row r="1308">
@@ -17421,7 +17421,7 @@
         <v>580</v>
       </c>
       <c r="C1308" t="n">
-        <v>0.07439</v>
+        <v>0.074518</v>
       </c>
     </row>
     <row r="1309">
@@ -17434,7 +17434,7 @@
         <v>581</v>
       </c>
       <c r="C1309" t="n">
-        <v>0.075057</v>
+        <v>0.075074</v>
       </c>
     </row>
     <row r="1310">
@@ -17447,7 +17447,7 @@
         <v>582</v>
       </c>
       <c r="C1310" t="n">
-        <v>0.07510699999999999</v>
+        <v>0.075159</v>
       </c>
     </row>
     <row r="1311">
@@ -17460,7 +17460,7 @@
         <v>583</v>
       </c>
       <c r="C1311" t="n">
-        <v>0.075347</v>
+        <v>0.075418</v>
       </c>
     </row>
     <row r="1312">
@@ -17473,7 +17473,7 @@
         <v>584</v>
       </c>
       <c r="C1312" t="n">
-        <v>0.075352</v>
+        <v>0.075437</v>
       </c>
     </row>
     <row r="1313">
@@ -17486,7 +17486,7 @@
         <v>585</v>
       </c>
       <c r="C1313" t="n">
-        <v>0.07538</v>
+        <v>0.075487</v>
       </c>
     </row>
     <row r="1314">
@@ -17499,7 +17499,7 @@
         <v>586</v>
       </c>
       <c r="C1314" t="n">
-        <v>0.07549699999999999</v>
+        <v>0.075603</v>
       </c>
     </row>
     <row r="1315">
@@ -17512,7 +17512,7 @@
         <v>587</v>
       </c>
       <c r="C1315" t="n">
-        <v>0.077775</v>
+        <v>0.077767</v>
       </c>
     </row>
     <row r="1316">
@@ -17525,7 +17525,7 @@
         <v>588</v>
       </c>
       <c r="C1316" t="n">
-        <v>0.07926</v>
+        <v>0.079346</v>
       </c>
     </row>
     <row r="1317">
@@ -17538,7 +17538,7 @@
         <v>589</v>
       </c>
       <c r="C1317" t="n">
-        <v>0.079387</v>
+        <v>0.079559</v>
       </c>
     </row>
     <row r="1318">
@@ -17551,7 +17551,7 @@
         <v>590</v>
       </c>
       <c r="C1318" t="n">
-        <v>0.079656</v>
+        <v>0.079747</v>
       </c>
     </row>
     <row r="1319">
@@ -17564,7 +17564,7 @@
         <v>591</v>
       </c>
       <c r="C1319" t="n">
-        <v>0.07981100000000001</v>
+        <v>0.07978499999999999</v>
       </c>
     </row>
     <row r="1320">
@@ -17577,7 +17577,7 @@
         <v>592</v>
       </c>
       <c r="C1320" t="n">
-        <v>0.080396</v>
+        <v>0.080494</v>
       </c>
     </row>
     <row r="1321">
@@ -17590,7 +17590,7 @@
         <v>593</v>
       </c>
       <c r="C1321" t="n">
-        <v>0.080737</v>
+        <v>0.080925</v>
       </c>
     </row>
     <row r="1322">
@@ -17603,7 +17603,7 @@
         <v>594</v>
       </c>
       <c r="C1322" t="n">
-        <v>0.08110100000000001</v>
+        <v>0.080987</v>
       </c>
     </row>
     <row r="1323">
@@ -17616,7 +17616,7 @@
         <v>595</v>
       </c>
       <c r="C1323" t="n">
-        <v>0.082189</v>
+        <v>0.082218</v>
       </c>
     </row>
     <row r="1324">
@@ -17629,7 +17629,7 @@
         <v>596</v>
       </c>
       <c r="C1324" t="n">
-        <v>0.082325</v>
+        <v>0.082342</v>
       </c>
     </row>
     <row r="1325">
@@ -17642,7 +17642,7 @@
         <v>597</v>
       </c>
       <c r="C1325" t="n">
-        <v>0.083159</v>
+        <v>0.082728</v>
       </c>
     </row>
     <row r="1326">
@@ -17655,7 +17655,7 @@
         <v>598</v>
       </c>
       <c r="C1326" t="n">
-        <v>0.083179</v>
+        <v>0.08312799999999999</v>
       </c>
     </row>
     <row r="1327">
@@ -17668,7 +17668,7 @@
         <v>599</v>
       </c>
       <c r="C1327" t="n">
-        <v>0.08422</v>
+        <v>0.08404200000000001</v>
       </c>
     </row>
     <row r="1328">
@@ -17681,7 +17681,7 @@
         <v>600</v>
       </c>
       <c r="C1328" t="n">
-        <v>0.084332</v>
+        <v>0.084325</v>
       </c>
     </row>
     <row r="1329">
@@ -17694,7 +17694,7 @@
         <v>601</v>
       </c>
       <c r="C1329" t="n">
-        <v>0.084463</v>
+        <v>0.084468</v>
       </c>
     </row>
     <row r="1330">
@@ -17707,7 +17707,7 @@
         <v>602</v>
       </c>
       <c r="C1330" t="n">
-        <v>0.085137</v>
+        <v>0.085188</v>
       </c>
     </row>
     <row r="1331">
@@ -17720,7 +17720,7 @@
         <v>603</v>
       </c>
       <c r="C1331" t="n">
-        <v>0.085201</v>
+        <v>0.085354</v>
       </c>
     </row>
     <row r="1332">
@@ -17733,7 +17733,7 @@
         <v>604</v>
       </c>
       <c r="C1332" t="n">
-        <v>0.085684</v>
+        <v>0.085615</v>
       </c>
     </row>
     <row r="1333">
@@ -17746,7 +17746,7 @@
         <v>605</v>
       </c>
       <c r="C1333" t="n">
-        <v>0.085842</v>
+        <v>0.085952</v>
       </c>
     </row>
     <row r="1334">
@@ -17759,7 +17759,7 @@
         <v>606</v>
       </c>
       <c r="C1334" t="n">
-        <v>0.086657</v>
+        <v>0.086726</v>
       </c>
     </row>
     <row r="1335">
@@ -17772,7 +17772,7 @@
         <v>607</v>
       </c>
       <c r="C1335" t="n">
-        <v>0.086856</v>
+        <v>0.086868</v>
       </c>
     </row>
     <row r="1336">
@@ -17785,7 +17785,7 @@
         <v>608</v>
       </c>
       <c r="C1336" t="n">
-        <v>0.087024</v>
+        <v>0.087022</v>
       </c>
     </row>
     <row r="1337">
@@ -17798,7 +17798,7 @@
         <v>609</v>
       </c>
       <c r="C1337" t="n">
-        <v>0.087626</v>
+        <v>0.08759500000000001</v>
       </c>
     </row>
     <row r="1338">
@@ -17811,7 +17811,7 @@
         <v>610</v>
       </c>
       <c r="C1338" t="n">
-        <v>0.08798599999999999</v>
+        <v>0.087839</v>
       </c>
     </row>
     <row r="1339">
@@ -17824,7 +17824,7 @@
         <v>611</v>
       </c>
       <c r="C1339" t="n">
-        <v>0.088687</v>
+        <v>0.088897</v>
       </c>
     </row>
     <row r="1340">
@@ -17837,7 +17837,7 @@
         <v>612</v>
       </c>
       <c r="C1340" t="n">
-        <v>0.089295</v>
+        <v>0.089339</v>
       </c>
     </row>
     <row r="1341">
@@ -17850,7 +17850,7 @@
         <v>613</v>
       </c>
       <c r="C1341" t="n">
-        <v>0.089339</v>
+        <v>0.08946999999999999</v>
       </c>
     </row>
     <row r="1342">
@@ -17863,7 +17863,7 @@
         <v>614</v>
       </c>
       <c r="C1342" t="n">
-        <v>0.089613</v>
+        <v>0.08951199999999999</v>
       </c>
     </row>
     <row r="1343">
@@ -17876,7 +17876,7 @@
         <v>615</v>
       </c>
       <c r="C1343" t="n">
-        <v>0.090735</v>
+        <v>0.09064999999999999</v>
       </c>
     </row>
     <row r="1344">
@@ -17889,7 +17889,7 @@
         <v>616</v>
       </c>
       <c r="C1344" t="n">
-        <v>0.09078799999999999</v>
+        <v>0.090794</v>
       </c>
     </row>
     <row r="1345">
@@ -17902,7 +17902,7 @@
         <v>617</v>
       </c>
       <c r="C1345" t="n">
-        <v>0.091819</v>
+        <v>0.09194099999999999</v>
       </c>
     </row>
     <row r="1346">
@@ -17915,7 +17915,7 @@
         <v>618</v>
       </c>
       <c r="C1346" t="n">
-        <v>0.092167</v>
+        <v>0.092073</v>
       </c>
     </row>
     <row r="1347">
@@ -17928,7 +17928,7 @@
         <v>619</v>
       </c>
       <c r="C1347" t="n">
-        <v>0.092707</v>
+        <v>0.09280099999999999</v>
       </c>
     </row>
     <row r="1348">
@@ -17941,7 +17941,7 @@
         <v>620</v>
       </c>
       <c r="C1348" t="n">
-        <v>0.093142</v>
+        <v>0.093204</v>
       </c>
     </row>
     <row r="1349">
@@ -17954,7 +17954,7 @@
         <v>621</v>
       </c>
       <c r="C1349" t="n">
-        <v>0.09317300000000001</v>
+        <v>0.093371</v>
       </c>
     </row>
     <row r="1350">
@@ -17967,7 +17967,7 @@
         <v>622</v>
       </c>
       <c r="C1350" t="n">
-        <v>0.094234</v>
+        <v>0.09440999999999999</v>
       </c>
     </row>
     <row r="1351">
@@ -17980,7 +17980,7 @@
         <v>623</v>
       </c>
       <c r="C1351" t="n">
-        <v>0.094719</v>
+        <v>0.094754</v>
       </c>
     </row>
     <row r="1352">
@@ -17993,7 +17993,7 @@
         <v>624</v>
       </c>
       <c r="C1352" t="n">
-        <v>0.095026</v>
+        <v>0.09515899999999999</v>
       </c>
     </row>
     <row r="1353">
@@ -18006,7 +18006,7 @@
         <v>625</v>
       </c>
       <c r="C1353" t="n">
-        <v>0.09615600000000001</v>
+        <v>0.096305</v>
       </c>
     </row>
     <row r="1354">
@@ -18019,7 +18019,7 @@
         <v>626</v>
       </c>
       <c r="C1354" t="n">
-        <v>0.097334</v>
+        <v>0.09754500000000001</v>
       </c>
     </row>
     <row r="1355">
@@ -18032,7 +18032,7 @@
         <v>627</v>
       </c>
       <c r="C1355" t="n">
-        <v>0.09777</v>
+        <v>0.09787700000000001</v>
       </c>
     </row>
     <row r="1356">
@@ -18045,7 +18045,7 @@
         <v>628</v>
       </c>
       <c r="C1356" t="n">
-        <v>0.09872599999999999</v>
+        <v>0.098678</v>
       </c>
     </row>
     <row r="1357">
@@ -18058,7 +18058,7 @@
         <v>629</v>
       </c>
       <c r="C1357" t="n">
-        <v>0.099217</v>
+        <v>0.09934900000000001</v>
       </c>
     </row>
     <row r="1358">
@@ -18071,7 +18071,7 @@
         <v>630</v>
       </c>
       <c r="C1358" t="n">
-        <v>0.099383</v>
+        <v>0.09955600000000001</v>
       </c>
     </row>
     <row r="1359">
@@ -18084,7 +18084,7 @@
         <v>631</v>
       </c>
       <c r="C1359" t="n">
-        <v>0.099428</v>
+        <v>0.099643</v>
       </c>
     </row>
     <row r="1360">
@@ -18097,7 +18097,7 @@
         <v>632</v>
       </c>
       <c r="C1360" t="n">
-        <v>0.10077</v>
+        <v>0.100897</v>
       </c>
     </row>
     <row r="1361">
@@ -18110,7 +18110,7 @@
         <v>633</v>
       </c>
       <c r="C1361" t="n">
-        <v>0.101665</v>
+        <v>0.101748</v>
       </c>
     </row>
     <row r="1362">
@@ -18123,7 +18123,7 @@
         <v>634</v>
       </c>
       <c r="C1362" t="n">
-        <v>0.101851</v>
+        <v>0.102031</v>
       </c>
     </row>
     <row r="1363">
@@ -18136,7 +18136,7 @@
         <v>635</v>
       </c>
       <c r="C1363" t="n">
-        <v>0.102147</v>
+        <v>0.102242</v>
       </c>
     </row>
     <row r="1364">
@@ -18149,7 +18149,7 @@
         <v>636</v>
       </c>
       <c r="C1364" t="n">
-        <v>0.105948</v>
+        <v>0.106032</v>
       </c>
     </row>
     <row r="1365">
@@ -18162,7 +18162,7 @@
         <v>637</v>
       </c>
       <c r="C1365" t="n">
-        <v>0.106661</v>
+        <v>0.106771</v>
       </c>
     </row>
     <row r="1366">
@@ -18175,7 +18175,7 @@
         <v>638</v>
       </c>
       <c r="C1366" t="n">
-        <v>0.107941</v>
+        <v>0.108079</v>
       </c>
     </row>
     <row r="1367">
@@ -18188,7 +18188,7 @@
         <v>639</v>
       </c>
       <c r="C1367" t="n">
-        <v>0.108305</v>
+        <v>0.108507</v>
       </c>
     </row>
     <row r="1368">
@@ -18201,7 +18201,7 @@
         <v>640</v>
       </c>
       <c r="C1368" t="n">
-        <v>0.112361</v>
+        <v>0.112556</v>
       </c>
     </row>
     <row r="1369">
@@ -18214,7 +18214,7 @@
         <v>641</v>
       </c>
       <c r="C1369" t="n">
-        <v>0.112851</v>
+        <v>0.112903</v>
       </c>
     </row>
     <row r="1370">
@@ -18227,7 +18227,7 @@
         <v>642</v>
       </c>
       <c r="C1370" t="n">
-        <v>0.113494</v>
+        <v>0.11353</v>
       </c>
     </row>
     <row r="1371">
@@ -18240,7 +18240,7 @@
         <v>643</v>
       </c>
       <c r="C1371" t="n">
-        <v>0.115626</v>
+        <v>0.115827</v>
       </c>
     </row>
     <row r="1372">
@@ -18253,7 +18253,7 @@
         <v>644</v>
       </c>
       <c r="C1372" t="n">
-        <v>0.116928</v>
+        <v>0.117003</v>
       </c>
     </row>
     <row r="1373">
@@ -18266,7 +18266,7 @@
         <v>645</v>
       </c>
       <c r="C1373" t="n">
-        <v>0.117034</v>
+        <v>0.117069</v>
       </c>
     </row>
     <row r="1374">
@@ -18279,7 +18279,7 @@
         <v>646</v>
       </c>
       <c r="C1374" t="n">
-        <v>0.119355</v>
+        <v>0.119343</v>
       </c>
     </row>
     <row r="1375">
@@ -18292,7 +18292,7 @@
         <v>647</v>
       </c>
       <c r="C1375" t="n">
-        <v>0.119389</v>
+        <v>0.11955</v>
       </c>
     </row>
     <row r="1376">
@@ -18305,7 +18305,7 @@
         <v>648</v>
       </c>
       <c r="C1376" t="n">
-        <v>0.120886</v>
+        <v>0.120975</v>
       </c>
     </row>
     <row r="1377">
@@ -18318,7 +18318,7 @@
         <v>649</v>
       </c>
       <c r="C1377" t="n">
-        <v>0.122062</v>
+        <v>0.122184</v>
       </c>
     </row>
     <row r="1378">
@@ -18331,7 +18331,7 @@
         <v>650</v>
       </c>
       <c r="C1378" t="n">
-        <v>0.124185</v>
+        <v>0.124232</v>
       </c>
     </row>
     <row r="1379">
@@ -18344,7 +18344,7 @@
         <v>651</v>
       </c>
       <c r="C1379" t="n">
-        <v>0.124229</v>
+        <v>0.124245</v>
       </c>
     </row>
     <row r="1380">
@@ -18357,7 +18357,7 @@
         <v>652</v>
       </c>
       <c r="C1380" t="n">
-        <v>0.12434</v>
+        <v>0.124458</v>
       </c>
     </row>
     <row r="1381">
@@ -18370,7 +18370,7 @@
         <v>653</v>
       </c>
       <c r="C1381" t="n">
-        <v>0.125393</v>
+        <v>0.125234</v>
       </c>
     </row>
     <row r="1382">
@@ -18383,7 +18383,7 @@
         <v>654</v>
       </c>
       <c r="C1382" t="n">
-        <v>0.12597</v>
+        <v>0.126103</v>
       </c>
     </row>
     <row r="1383">
@@ -18396,7 +18396,7 @@
         <v>655</v>
       </c>
       <c r="C1383" t="n">
-        <v>0.126858</v>
+        <v>0.126929</v>
       </c>
     </row>
     <row r="1384">
@@ -18409,7 +18409,7 @@
         <v>656</v>
       </c>
       <c r="C1384" t="n">
-        <v>0.127056</v>
+        <v>0.126979</v>
       </c>
     </row>
     <row r="1385">
@@ -18422,7 +18422,7 @@
         <v>657</v>
       </c>
       <c r="C1385" t="n">
-        <v>0.127871</v>
+        <v>0.127728</v>
       </c>
     </row>
     <row r="1386">
@@ -18435,7 +18435,7 @@
         <v>658</v>
       </c>
       <c r="C1386" t="n">
-        <v>0.128353</v>
+        <v>0.128481</v>
       </c>
     </row>
     <row r="1387">
@@ -18448,7 +18448,7 @@
         <v>659</v>
       </c>
       <c r="C1387" t="n">
-        <v>0.128693</v>
+        <v>0.128875</v>
       </c>
     </row>
     <row r="1388">
@@ -18461,7 +18461,7 @@
         <v>660</v>
       </c>
       <c r="C1388" t="n">
-        <v>0.129268</v>
+        <v>0.12934</v>
       </c>
     </row>
     <row r="1389">
@@ -18474,7 +18474,7 @@
         <v>661</v>
       </c>
       <c r="C1389" t="n">
-        <v>0.130568</v>
+        <v>0.130382</v>
       </c>
     </row>
     <row r="1390">
@@ -18487,7 +18487,7 @@
         <v>662</v>
       </c>
       <c r="C1390" t="n">
-        <v>0.133341</v>
+        <v>0.133384</v>
       </c>
     </row>
     <row r="1391">
@@ -18500,7 +18500,7 @@
         <v>663</v>
       </c>
       <c r="C1391" t="n">
-        <v>0.133416</v>
+        <v>0.133507</v>
       </c>
     </row>
     <row r="1392">
@@ -18513,7 +18513,7 @@
         <v>664</v>
       </c>
       <c r="C1392" t="n">
-        <v>0.134803</v>
+        <v>0.134924</v>
       </c>
     </row>
     <row r="1393">
@@ -18526,7 +18526,7 @@
         <v>665</v>
       </c>
       <c r="C1393" t="n">
-        <v>0.134823</v>
+        <v>0.134929</v>
       </c>
     </row>
     <row r="1394">
@@ -18539,7 +18539,7 @@
         <v>666</v>
       </c>
       <c r="C1394" t="n">
-        <v>0.134889</v>
+        <v>0.135091</v>
       </c>
     </row>
     <row r="1395">
@@ -18552,7 +18552,7 @@
         <v>667</v>
       </c>
       <c r="C1395" t="n">
-        <v>0.135322</v>
+        <v>0.135527</v>
       </c>
     </row>
     <row r="1396">
@@ -18565,7 +18565,7 @@
         <v>668</v>
       </c>
       <c r="C1396" t="n">
-        <v>0.136479</v>
+        <v>0.136775</v>
       </c>
     </row>
     <row r="1397">
@@ -18578,7 +18578,7 @@
         <v>669</v>
       </c>
       <c r="C1397" t="n">
-        <v>0.138144</v>
+        <v>0.138536</v>
       </c>
     </row>
     <row r="1398">
@@ -18591,7 +18591,7 @@
         <v>670</v>
       </c>
       <c r="C1398" t="n">
-        <v>0.138785</v>
+        <v>0.138828</v>
       </c>
     </row>
     <row r="1399">
@@ -18604,7 +18604,7 @@
         <v>671</v>
       </c>
       <c r="C1399" t="n">
-        <v>0.142216</v>
+        <v>0.142469</v>
       </c>
     </row>
     <row r="1400">
@@ -18617,7 +18617,7 @@
         <v>672</v>
       </c>
       <c r="C1400" t="n">
-        <v>0.145372</v>
+        <v>0.145245</v>
       </c>
     </row>
     <row r="1401">
@@ -18630,7 +18630,7 @@
         <v>673</v>
       </c>
       <c r="C1401" t="n">
-        <v>0.146421</v>
+        <v>0.146683</v>
       </c>
     </row>
     <row r="1402">
@@ -18643,7 +18643,7 @@
         <v>674</v>
       </c>
       <c r="C1402" t="n">
-        <v>0.147224</v>
+        <v>0.147097</v>
       </c>
     </row>
     <row r="1403">
@@ -18656,7 +18656,7 @@
         <v>675</v>
       </c>
       <c r="C1403" t="n">
-        <v>0.153113</v>
+        <v>0.153228</v>
       </c>
     </row>
     <row r="1404">
@@ -18669,7 +18669,7 @@
         <v>676</v>
       </c>
       <c r="C1404" t="n">
-        <v>0.154657</v>
+        <v>0.154805</v>
       </c>
     </row>
     <row r="1405">
@@ -18682,7 +18682,7 @@
         <v>677</v>
       </c>
       <c r="C1405" t="n">
-        <v>0.155726</v>
+        <v>0.155551</v>
       </c>
     </row>
     <row r="1406">
@@ -18695,7 +18695,7 @@
         <v>678</v>
       </c>
       <c r="C1406" t="n">
-        <v>0.156101</v>
+        <v>0.155733</v>
       </c>
     </row>
     <row r="1407">
@@ -18708,7 +18708,7 @@
         <v>679</v>
       </c>
       <c r="C1407" t="n">
-        <v>0.158058</v>
+        <v>0.158168</v>
       </c>
     </row>
     <row r="1408">
@@ -18721,7 +18721,7 @@
         <v>680</v>
       </c>
       <c r="C1408" t="n">
-        <v>0.159915</v>
+        <v>0.159895</v>
       </c>
     </row>
     <row r="1409">
@@ -18734,7 +18734,7 @@
         <v>681</v>
       </c>
       <c r="C1409" t="n">
-        <v>0.163767</v>
+        <v>0.163976</v>
       </c>
     </row>
     <row r="1410">
@@ -18747,7 +18747,7 @@
         <v>682</v>
       </c>
       <c r="C1410" t="n">
-        <v>0.163984</v>
+        <v>0.164151</v>
       </c>
     </row>
     <row r="1411">
@@ -18760,7 +18760,7 @@
         <v>683</v>
       </c>
       <c r="C1411" t="n">
-        <v>0.166755</v>
+        <v>0.166474</v>
       </c>
     </row>
     <row r="1412">
@@ -18773,7 +18773,7 @@
         <v>684</v>
       </c>
       <c r="C1412" t="n">
-        <v>0.168603</v>
+        <v>0.168632</v>
       </c>
     </row>
     <row r="1413">
@@ -18786,7 +18786,7 @@
         <v>685</v>
       </c>
       <c r="C1413" t="n">
-        <v>0.170408</v>
+        <v>0.170824</v>
       </c>
     </row>
     <row r="1414">
@@ -18799,7 +18799,7 @@
         <v>686</v>
       </c>
       <c r="C1414" t="n">
-        <v>0.170813</v>
+        <v>0.170871</v>
       </c>
     </row>
     <row r="1415">
@@ -18812,7 +18812,7 @@
         <v>687</v>
       </c>
       <c r="C1415" t="n">
-        <v>0.173669</v>
+        <v>0.173332</v>
       </c>
     </row>
     <row r="1416">
@@ -18825,7 +18825,7 @@
         <v>688</v>
       </c>
       <c r="C1416" t="n">
-        <v>0.173669</v>
+        <v>0.173332</v>
       </c>
     </row>
     <row r="1417">
@@ -18838,7 +18838,7 @@
         <v>689</v>
       </c>
       <c r="C1417" t="n">
-        <v>0.173669</v>
+        <v>0.173332</v>
       </c>
     </row>
     <row r="1418">
@@ -18851,7 +18851,7 @@
         <v>690</v>
       </c>
       <c r="C1418" t="n">
-        <v>0.173949</v>
+        <v>0.174256</v>
       </c>
     </row>
     <row r="1419">
@@ -18864,7 +18864,7 @@
         <v>691</v>
       </c>
       <c r="C1419" t="n">
-        <v>0.180248</v>
+        <v>0.180291</v>
       </c>
     </row>
     <row r="1420">
@@ -18877,7 +18877,7 @@
         <v>692</v>
       </c>
       <c r="C1420" t="n">
-        <v>0.183297</v>
+        <v>0.183205</v>
       </c>
     </row>
     <row r="1421">
@@ -18890,7 +18890,7 @@
         <v>693</v>
       </c>
       <c r="C1421" t="n">
-        <v>0.184944</v>
+        <v>0.184954</v>
       </c>
     </row>
     <row r="1422">
@@ -18903,7 +18903,7 @@
         <v>694</v>
       </c>
       <c r="C1422" t="n">
-        <v>0.185032</v>
+        <v>0.185242</v>
       </c>
     </row>
     <row r="1423">
@@ -18916,7 +18916,7 @@
         <v>695</v>
       </c>
       <c r="C1423" t="n">
-        <v>0.190994</v>
+        <v>0.1911</v>
       </c>
     </row>
     <row r="1424">
@@ -18929,7 +18929,7 @@
         <v>696</v>
       </c>
       <c r="C1424" t="n">
-        <v>0.195022</v>
+        <v>0.195277</v>
       </c>
     </row>
     <row r="1425">
@@ -18942,7 +18942,7 @@
         <v>697</v>
       </c>
       <c r="C1425" t="n">
-        <v>0.196468</v>
+        <v>0.196811</v>
       </c>
     </row>
     <row r="1426">
@@ -18955,7 +18955,7 @@
         <v>698</v>
       </c>
       <c r="C1426" t="n">
-        <v>0.198213</v>
+        <v>0.198557</v>
       </c>
     </row>
     <row r="1427">
@@ -18968,7 +18968,7 @@
         <v>699</v>
       </c>
       <c r="C1427" t="n">
-        <v>0.212103</v>
+        <v>0.212371</v>
       </c>
     </row>
     <row r="1428">
@@ -18981,7 +18981,7 @@
         <v>700</v>
       </c>
       <c r="C1428" t="n">
-        <v>0.212711</v>
+        <v>0.213001</v>
       </c>
     </row>
     <row r="1429">
@@ -18994,7 +18994,7 @@
         <v>701</v>
       </c>
       <c r="C1429" t="n">
-        <v>0.2207</v>
+        <v>0.220753</v>
       </c>
     </row>
     <row r="1430">
@@ -19007,7 +19007,7 @@
         <v>702</v>
       </c>
       <c r="C1430" t="n">
-        <v>0.222038</v>
+        <v>0.222097</v>
       </c>
     </row>
     <row r="1431">
@@ -19020,7 +19020,7 @@
         <v>703</v>
       </c>
       <c r="C1431" t="n">
-        <v>0.222369</v>
+        <v>0.222764</v>
       </c>
     </row>
     <row r="1432">
@@ -19033,7 +19033,7 @@
         <v>704</v>
       </c>
       <c r="C1432" t="n">
-        <v>0.224057</v>
+        <v>0.223806</v>
       </c>
     </row>
     <row r="1433">
@@ -19046,7 +19046,7 @@
         <v>705</v>
       </c>
       <c r="C1433" t="n">
-        <v>0.224132</v>
+        <v>0.224246</v>
       </c>
     </row>
     <row r="1434">
@@ -19059,7 +19059,7 @@
         <v>706</v>
       </c>
       <c r="C1434" t="n">
-        <v>0.22845</v>
+        <v>0.22779</v>
       </c>
     </row>
     <row r="1435">
@@ -19072,7 +19072,7 @@
         <v>707</v>
       </c>
       <c r="C1435" t="n">
-        <v>0.25557</v>
+        <v>0.256024</v>
       </c>
     </row>
     <row r="1436">
@@ -19085,7 +19085,7 @@
         <v>708</v>
       </c>
       <c r="C1436" t="n">
-        <v>0.264792</v>
+        <v>0.26513</v>
       </c>
     </row>
     <row r="1437">
@@ -19098,7 +19098,7 @@
         <v>709</v>
       </c>
       <c r="C1437" t="n">
-        <v>0.273416</v>
+        <v>0.273655</v>
       </c>
     </row>
     <row r="1438">
@@ -19111,7 +19111,7 @@
         <v>710</v>
       </c>
       <c r="C1438" t="n">
-        <v>0.280968</v>
+        <v>0.280619</v>
       </c>
     </row>
     <row r="1439">
@@ -19124,7 +19124,7 @@
         <v>711</v>
       </c>
       <c r="C1439" t="n">
-        <v>0.310594</v>
+        <v>0.310768</v>
       </c>
     </row>
     <row r="1440">
@@ -19137,7 +19137,7 @@
         <v>712</v>
       </c>
       <c r="C1440" t="n">
-        <v>0.311532</v>
+        <v>0.31212</v>
       </c>
     </row>
     <row r="1441">
@@ -19150,7 +19150,7 @@
         <v>713</v>
       </c>
       <c r="C1441" t="n">
-        <v>0.313572</v>
+        <v>0.313599</v>
       </c>
     </row>
     <row r="1442">
@@ -19163,7 +19163,7 @@
         <v>714</v>
       </c>
       <c r="C1442" t="n">
-        <v>0.347652</v>
+        <v>0.347408</v>
       </c>
     </row>
     <row r="1443">
@@ -19176,7 +19176,7 @@
         <v>715</v>
       </c>
       <c r="C1443" t="n">
-        <v>0.358997</v>
+        <v>0.359666</v>
       </c>
     </row>
     <row r="1444">
@@ -19189,7 +19189,7 @@
         <v>716</v>
       </c>
       <c r="C1444" t="n">
-        <v>0.363725</v>
+        <v>0.364409</v>
       </c>
     </row>
     <row r="1445">
@@ -19202,7 +19202,7 @@
         <v>717</v>
       </c>
       <c r="C1445" t="n">
-        <v>0.378047</v>
+        <v>0.377683</v>
       </c>
     </row>
     <row r="1446">
@@ -19215,7 +19215,7 @@
         <v>718</v>
       </c>
       <c r="C1446" t="n">
-        <v>0.388232</v>
+        <v>0.388225</v>
       </c>
     </row>
     <row r="1447">
@@ -19228,7 +19228,7 @@
         <v>719</v>
       </c>
       <c r="C1447" t="n">
-        <v>0.39996</v>
+        <v>0.400477</v>
       </c>
     </row>
     <row r="1448">
@@ -19241,7 +19241,7 @@
         <v>720</v>
       </c>
       <c r="C1448" t="n">
-        <v>0.540816</v>
+        <v>0.540237</v>
       </c>
     </row>
     <row r="1449">
@@ -19254,7 +19254,7 @@
         <v>721</v>
       </c>
       <c r="C1449" t="n">
-        <v>0.551154</v>
+        <v>0.551625</v>
       </c>
     </row>
     <row r="1450">
@@ -19267,7 +19267,7 @@
         <v>722</v>
       </c>
       <c r="C1450" t="n">
-        <v>0.682852</v>
+        <v>0.684051</v>
       </c>
     </row>
     <row r="1451">
@@ -19280,7 +19280,7 @@
         <v>723</v>
       </c>
       <c r="C1451" t="n">
-        <v>0.70228</v>
+        <v>0.703035</v>
       </c>
     </row>
     <row r="1452">
@@ -19293,7 +19293,7 @@
         <v>724</v>
       </c>
       <c r="C1452" t="n">
-        <v>1.047587</v>
+        <v>1.049405</v>
       </c>
     </row>
     <row r="1453">
@@ -19306,7 +19306,7 @@
         <v>725</v>
       </c>
       <c r="C1453" t="n">
-        <v>1.344885</v>
+        <v>1.348523</v>
       </c>
     </row>
   </sheetData>
